--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -504,7 +504,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sabine Pass: Partial - missing Trunkline/Creole Trail (Energy Transfer) and Transco (Williams).</t>
+          <t>Sabine Pass: Mostly complete - KMLP, NGPL, and Creole Trail deliveries from Trunkline and Texas Eastern; Transco (Williams) not yet covered.</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cameron: Partial - Cameron Interstate's other supply interconnects not yet covered.</t>
+          <t>Cameron: Complete - Cameron Interstate's delivery meter into the terminal.</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Golden Pass: Not yet covered - fed by Gulf Run (Energy Transfer) and Trident (intrastate).</t>
+          <t>Golden Pass: Partial - Gulf Run's delivery into Golden Pass Pipeline; Permian gas via Kinder Morgan's Trident (intrastate) is not seen.</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column.</t>
+          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate) and Energy Transfer Messenger+ equivalents.</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -654,6 +654,11 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Golden Pass</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
@@ -663,13 +668,13 @@
         <v>46292</v>
       </c>
       <c r="B2" t="n">
-        <v>1.878</v>
+        <v>2.128</v>
       </c>
       <c r="C2" t="n">
         <v>3.344</v>
       </c>
       <c r="D2" t="n">
-        <v>1.085</v>
+        <v>1.377</v>
       </c>
       <c r="E2" t="n">
         <v>0.3</v>
@@ -684,7 +689,10 @@
         <v>0.362</v>
       </c>
       <c r="I2" t="n">
-        <v>8.029</v>
+        <v>0.746</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9.317</v>
       </c>
     </row>
   </sheetData>
@@ -727,52 +735,52 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Sabine Pass | Trunkline -&gt; Cheniere Creole Trail, Beauregard Par. (TGC 82742)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Plaquemines | Tennessee Gas -&gt; VG Gator Express, Evangeline Pass (TGP 55833)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Plaquemines | Texas Eastern -&gt; Gator Express (TE 74530)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Cameron | Tennessee Gas -&gt; Cameron Interstate, Banken Rd (TGP 49446)</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Cameron | Texas Eastern -&gt; Sempra/Cameron (TE 73882)</t>
+          <t>Cameron | Cameron Interstate -&gt; Cameron LNG (CAMERON 772300)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Cameron | Texas Eastern -&gt; Cameron Interstate, Beauregard Par. (TE 75533)</t>
+          <t>Calcasieu Pass | Texas Eastern -&gt; TransCameron, Oak Grove (TE 74529)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Calcasieu Pass | Texas Eastern -&gt; TransCameron, Oak Grove (TE 74529)</t>
+          <t>Corpus Christi | NGPL -&gt; Cheniere Corpus Christi Pipeline, Sinton (NGPL 48934)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Corpus Christi | NGPL -&gt; Cheniere Corpus Christi Pipeline, Sinton (NGPL 48934)</t>
+          <t>Corpus Christi | Tennessee Gas -&gt; Cheniere Corpus Christi Pipeline, Sinton (TGP 49861)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Corpus Christi | Tennessee Gas -&gt; Cheniere Corpus Christi Pipeline, Sinton (TGP 49861)</t>
+          <t>Freeport | Texas Eastern -&gt; Stratton Ridge (TE 79999)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Freeport | Texas Eastern -&gt; Stratton Ridge (TE 79999)</t>
+          <t>Elba Island | Elba Express -&gt; Elba Liquefaction, Chatham (EEC 660700)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Elba Island | Elba Express -&gt; Elba Liquefaction, Chatham (EEC 660700)</t>
+          <t>Golden Pass | Gulf Run -&gt; Golden Pass Pipeline (GR 808311)</t>
         </is>
       </c>
     </row>
@@ -790,34 +798,34 @@
         <v>25000</v>
       </c>
       <c r="E2" t="n">
+        <v>259977</v>
+      </c>
+      <c r="F2" t="n">
         <v>1999274</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1468619</v>
       </c>
-      <c r="G2" t="n">
-        <v>889241</v>
-      </c>
       <c r="H2" t="n">
-        <v>225405</v>
+        <v>1428275</v>
       </c>
       <c r="I2" t="n">
-        <v>10998</v>
+        <v>310625</v>
       </c>
       <c r="J2" t="n">
-        <v>310625</v>
+        <v>562512</v>
       </c>
       <c r="K2" t="n">
-        <v>562512</v>
+        <v>346883</v>
       </c>
       <c r="L2" t="n">
-        <v>346883</v>
+        <v>189475</v>
       </c>
       <c r="M2" t="n">
-        <v>189475</v>
+        <v>375660</v>
       </c>
       <c r="N2" t="n">
-        <v>375660</v>
+        <v>773586</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -504,7 +504,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sabine Pass: Mostly complete - KMLP, NGPL, and Creole Trail deliveries from Trunkline and Texas Eastern; Transco (Williams) not yet covered.</t>
+          <t>Sabine Pass: Near complete - the plant's three feed pipes' delivery meters: Creole Trail, Kinder Morgan Louisiana and NGPL.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Corpus Christi: Partial - Permian supply arrives on intrastate pipes (GCX, Whistler, ADCC) with no public data; only NGPL/TGP deliveries into Cheniere's Corpus Christi Pipeline are seen.</t>
+          <t>Corpus Christi: Mostly complete - Cheniere Corpus Christi Pipeline's delivery into the plant, which includes intrastate Permian gas it receives; gas delivered straight to the plant by the intrastate ADCC pipeline is not seen.</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate) and Energy Transfer Messenger+ equivalents.</t>
+          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate), Energy Transfer Messenger+ and Cheniere LNG Connection equivalents - all operator-hosted.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
         <v>46292</v>
       </c>
       <c r="B2" t="n">
-        <v>2.128</v>
+        <v>3.307</v>
       </c>
       <c r="C2" t="n">
         <v>3.344</v>
@@ -680,7 +680,7 @@
         <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>0.877</v>
+        <v>2.432</v>
       </c>
       <c r="G2" t="n">
         <v>0.183</v>
@@ -692,7 +692,7 @@
         <v>0.746</v>
       </c>
       <c r="J2" t="n">
-        <v>9.317</v>
+        <v>12.052</v>
       </c>
     </row>
   </sheetData>
@@ -706,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Sabine Pass | Texas Eastern -&gt; Cheniere (Creole Trail), Beauregard Par. (TE 75866)</t>
+          <t>Sabine Pass | Creole Trail -&gt; Sabine Pass Liquefaction (200 CT200111)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Sabine Pass | Trunkline -&gt; Cheniere Creole Trail, Beauregard Par. (TGC 82742)</t>
+          <t>Sabine Pass | Creole Trail -&gt; Sabine Pass LNG (200 SPLNGD)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -760,25 +760,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Corpus Christi | NGPL -&gt; Cheniere Corpus Christi Pipeline, Sinton (NGPL 48934)</t>
+          <t>Corpus Christi | Corpus Christi Pipeline -&gt; Corpus Christi Liquefaction (400 CC200221)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Corpus Christi | Tennessee Gas -&gt; Cheniere Corpus Christi Pipeline, Sinton (TGP 49861)</t>
+          <t>Freeport | Texas Eastern -&gt; Stratton Ridge (TE 79999)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Freeport | Texas Eastern -&gt; Stratton Ridge (TE 79999)</t>
+          <t>Elba Island | Elba Express -&gt; Elba Liquefaction, Chatham (EEC 660700)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>Elba Island | Elba Express -&gt; Elba Liquefaction, Chatham (EEC 660700)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
         <is>
           <t>Golden Pass | Gulf Run -&gt; Golden Pass Pipeline (GR 808311)</t>
         </is>
@@ -795,10 +790,10 @@
         <v>646110</v>
       </c>
       <c r="D2" t="n">
-        <v>25000</v>
+        <v>1498302</v>
       </c>
       <c r="E2" t="n">
-        <v>259977</v>
+        <v>9100</v>
       </c>
       <c r="F2" t="n">
         <v>1999274</v>
@@ -813,18 +808,15 @@
         <v>310625</v>
       </c>
       <c r="J2" t="n">
-        <v>562512</v>
+        <v>2522392</v>
       </c>
       <c r="K2" t="n">
-        <v>346883</v>
+        <v>189475</v>
       </c>
       <c r="L2" t="n">
-        <v>189475</v>
+        <v>375660</v>
       </c>
       <c r="M2" t="n">
-        <v>375660</v>
-      </c>
-      <c r="N2" t="n">
         <v>773586</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -8059,47 +8059,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Calcasieu Pass</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Golden Pass</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Cameron</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Calcasieu Pass</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cove Point</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Golden Pass</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Cove Point</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Plaquemines</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Freeport</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="F2" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="F3" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="F4" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="F5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="F6" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="F7" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>0.373</v>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>0.364</v>
       </c>
     </row>
@@ -8199,7 +8199,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>0.346</v>
       </c>
     </row>
@@ -8209,7 +8209,7 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>0.597</v>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>0.552</v>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>0.966</v>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>0.607</v>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>1.196</v>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1.468</v>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1.801</v>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>2.024</v>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>1.528</v>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>1.838</v>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>2.136</v>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>1.905</v>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>1.883</v>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>1.597</v>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>1.986</v>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>2.832</v>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>2.906</v>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>2.543</v>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>2.864</v>
       </c>
     </row>
@@ -8419,10 +8419,10 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>3.11</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -8432,10 +8432,10 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>2.788</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.325</v>
       </c>
     </row>
@@ -8445,10 +8445,10 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>2.562</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>0.77</v>
       </c>
     </row>
@@ -8458,10 +8458,10 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>2.213</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>0.457</v>
       </c>
     </row>
@@ -8471,10 +8471,10 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>2.778</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>0.675</v>
       </c>
     </row>
@@ -8484,10 +8484,10 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>2.54</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>0.676</v>
       </c>
     </row>
@@ -8497,10 +8497,10 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>2.507</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>0.449</v>
       </c>
     </row>
@@ -8510,10 +8510,10 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>2.932</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -8523,10 +8523,10 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>3.202</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>0.701</v>
       </c>
     </row>
@@ -8536,14 +8536,14 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>3.36</v>
       </c>
-      <c r="E42" t="n">
+      <c r="I42" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J42" t="n">
         <v>0.241</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0.711</v>
       </c>
     </row>
     <row r="43">
@@ -8552,14 +8552,14 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>3.367</v>
       </c>
-      <c r="E43" t="n">
+      <c r="I43" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="J43" t="n">
         <v>0.378</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.714</v>
       </c>
     </row>
     <row r="44">
@@ -8568,14 +8568,14 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>2.942</v>
       </c>
-      <c r="E44" t="n">
+      <c r="I44" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.145</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.915</v>
       </c>
     </row>
     <row r="45">
@@ -8584,14 +8584,14 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>3.291</v>
       </c>
-      <c r="E45" t="n">
+      <c r="I45" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="J45" t="n">
         <v>0.706</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0.599</v>
       </c>
     </row>
     <row r="46">
@@ -8600,14 +8600,14 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>3.054</v>
       </c>
-      <c r="E46" t="n">
+      <c r="I46" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.6919999999999999</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.867</v>
       </c>
     </row>
     <row r="47">
@@ -8616,17 +8616,17 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="D47" t="n">
+        <v>3.762</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.113</v>
       </c>
-      <c r="C47" t="n">
-        <v>3.762</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="I47" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="J47" t="n">
         <v>0.614</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.602</v>
       </c>
     </row>
     <row r="48">
@@ -8635,17 +8635,17 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="D48" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.106</v>
       </c>
-      <c r="C48" t="n">
-        <v>3.551</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="I48" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.765</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.731</v>
       </c>
     </row>
     <row r="49">
@@ -8654,17 +8654,17 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="D49" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="G49" t="n">
         <v>0.248</v>
       </c>
-      <c r="C49" t="n">
-        <v>3.347</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="I49" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J49" t="n">
         <v>1.184</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0.731</v>
       </c>
     </row>
     <row r="50">
@@ -8673,17 +8673,17 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="D50" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="G50" t="n">
         <v>0.388</v>
       </c>
-      <c r="C50" t="n">
-        <v>2.696</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="I50" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="J50" t="n">
         <v>1.084</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0.699</v>
       </c>
     </row>
     <row r="51">
@@ -8692,20 +8692,20 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="D51" t="n">
+        <v>3.461</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="G51" t="n">
         <v>0.364</v>
       </c>
-      <c r="C51" t="n">
-        <v>3.461</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="I51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J51" t="n">
         <v>1.26</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.235</v>
       </c>
     </row>
     <row r="52">
@@ -8714,20 +8714,20 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="D52" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="G52" t="n">
         <v>0.379</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.775</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="I52" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="J52" t="n">
         <v>1.488</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.365</v>
       </c>
     </row>
     <row r="53">
@@ -8736,20 +8736,20 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="D53" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="G53" t="n">
         <v>0.507</v>
       </c>
-      <c r="C53" t="n">
-        <v>3.852</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="I53" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="J53" t="n">
         <v>1.357</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.353</v>
       </c>
     </row>
     <row r="54">
@@ -8758,23 +8758,23 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="D54" t="n">
+        <v>3.813</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.84</v>
       </c>
-      <c r="C54" t="n">
-        <v>3.813</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="H54" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="J54" t="n">
         <v>1.461</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.229</v>
       </c>
     </row>
     <row r="55">
@@ -8783,23 +8783,23 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="D55" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.98</v>
       </c>
-      <c r="C55" t="n">
-        <v>4.018</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="H55" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="J55" t="n">
         <v>1.426</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1.456</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.428</v>
       </c>
     </row>
     <row r="56">
@@ -8808,20 +8808,20 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="D56" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="G56" t="n">
         <v>1.044</v>
       </c>
-      <c r="C56" t="n">
-        <v>3.684</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="I56" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J56" t="n">
         <v>1.55</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1.446</v>
       </c>
     </row>
     <row r="57">
@@ -8830,20 +8830,20 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="D57" t="n">
+        <v>3.447</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="G57" t="n">
         <v>1.208</v>
       </c>
-      <c r="C57" t="n">
-        <v>3.447</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="I57" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J57" t="n">
         <v>1.462</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1.635</v>
       </c>
     </row>
     <row r="58">
@@ -8852,20 +8852,20 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="D58" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="G58" t="n">
         <v>1.301</v>
       </c>
-      <c r="C58" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="I58" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="J58" t="n">
         <v>1.245</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1.158</v>
       </c>
     </row>
     <row r="59">
@@ -8874,20 +8874,20 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="D59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="G59" t="n">
         <v>1.135</v>
       </c>
-      <c r="C59" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="I59" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J59" t="n">
         <v>0.831</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="I59" t="n">
-        <v>1.008</v>
       </c>
     </row>
     <row r="60">
@@ -8896,20 +8896,20 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="D60" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G60" t="n">
         <v>1.366</v>
       </c>
-      <c r="C60" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="I60" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.307</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.543</v>
       </c>
     </row>
     <row r="61">
@@ -8918,20 +8918,20 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="D61" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G61" t="n">
         <v>1.099</v>
       </c>
-      <c r="C61" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="I61" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.373</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.132</v>
       </c>
     </row>
     <row r="62">
@@ -8940,23 +8940,23 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="D62" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="G62" t="n">
         <v>1.117</v>
       </c>
-      <c r="C62" t="n">
-        <v>1.031</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="H62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="J62" t="n">
         <v>0.601</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.26</v>
       </c>
     </row>
     <row r="63">
@@ -8965,20 +8965,20 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>2.241</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="J63" t="n">
         <v>1.363</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1.127</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.271</v>
       </c>
     </row>
     <row r="64">
@@ -8987,23 +8987,23 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="D64" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="G64" t="n">
         <v>0.662</v>
       </c>
-      <c r="C64" t="n">
-        <v>3.106</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="H64" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="J64" t="n">
         <v>1.551</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1.892</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.52</v>
       </c>
     </row>
     <row r="65">
@@ -9012,23 +9012,23 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="D65" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="G65" t="n">
         <v>1.838</v>
       </c>
-      <c r="C65" t="n">
-        <v>3.684</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="H65" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="J65" t="n">
         <v>1.633</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1.953</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.469</v>
       </c>
     </row>
     <row r="66">
@@ -9037,23 +9037,23 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="D66" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="G66" t="n">
         <v>1.939</v>
       </c>
-      <c r="C66" t="n">
-        <v>3.845</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="H66" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J66" t="n">
         <v>1.821</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2.057</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.628</v>
       </c>
     </row>
     <row r="67">
@@ -9062,20 +9062,20 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="D67" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="G67" t="n">
         <v>1.943</v>
       </c>
-      <c r="C67" t="n">
-        <v>3.905</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="I67" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="J67" t="n">
         <v>2.012</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="I67" t="n">
-        <v>2.148</v>
       </c>
     </row>
     <row r="68">
@@ -9084,23 +9084,23 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="D68" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="G68" t="n">
         <v>1.42</v>
       </c>
-      <c r="C68" t="n">
-        <v>3.263</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="H68" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="J68" t="n">
         <v>1.297</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.541</v>
       </c>
     </row>
     <row r="69">
@@ -9109,23 +9109,23 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="D69" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.237</v>
+      </c>
+      <c r="G69" t="n">
         <v>1.755</v>
       </c>
-      <c r="C69" t="n">
-        <v>4.013</v>
-      </c>
-      <c r="E69" t="n">
+      <c r="H69" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="J69" t="n">
         <v>2.201</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="I69" t="n">
-        <v>2.237</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.468</v>
       </c>
     </row>
     <row r="70">
@@ -9134,23 +9134,23 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="D70" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="G70" t="n">
         <v>1.848</v>
       </c>
-      <c r="C70" t="n">
-        <v>3.955</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="H70" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="J70" t="n">
         <v>2.175</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="I70" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.68</v>
       </c>
     </row>
     <row r="71">
@@ -9159,23 +9159,23 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="D71" t="n">
+        <v>3.805</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="G71" t="n">
         <v>1.855</v>
       </c>
-      <c r="C71" t="n">
-        <v>3.805</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="H71" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="J71" t="n">
         <v>2.066</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2.223</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.662</v>
       </c>
     </row>
     <row r="72">
@@ -9184,23 +9184,23 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="D72" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="G72" t="n">
         <v>1.418</v>
       </c>
-      <c r="C72" t="n">
-        <v>3.118</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="H72" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="J72" t="n">
         <v>2.236</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2.127</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.524</v>
       </c>
     </row>
     <row r="73">
@@ -9209,23 +9209,23 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="D73" t="n">
+        <v>3.402</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="G73" t="n">
         <v>1.82</v>
       </c>
-      <c r="C73" t="n">
-        <v>3.402</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="H73" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J73" t="n">
         <v>2.126</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>2.141</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.493</v>
       </c>
     </row>
     <row r="74">
@@ -9234,23 +9234,23 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="D74" t="n">
+        <v>3.492</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="G74" t="n">
         <v>1.467</v>
       </c>
-      <c r="C74" t="n">
-        <v>3.492</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="H74" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J74" t="n">
         <v>2.171</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="I74" t="n">
-        <v>2.307</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0.507</v>
       </c>
     </row>
     <row r="75">
@@ -9259,23 +9259,23 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="D75" t="n">
+        <v>3.619</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="G75" t="n">
         <v>1.919</v>
       </c>
-      <c r="C75" t="n">
-        <v>3.619</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="H75" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="J75" t="n">
         <v>2.34</v>
-      </c>
-      <c r="G75" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1.764</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.396</v>
       </c>
     </row>
     <row r="76">
@@ -9284,23 +9284,23 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="D76" t="n">
+        <v>3.561</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="G76" t="n">
         <v>1.852</v>
       </c>
-      <c r="C76" t="n">
-        <v>3.561</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="H76" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="J76" t="n">
         <v>2.28</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="I76" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.639</v>
       </c>
     </row>
     <row r="77">
@@ -9309,23 +9309,23 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="D77" t="n">
+        <v>4.097</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="G77" t="n">
         <v>2.113</v>
       </c>
-      <c r="C77" t="n">
-        <v>4.097</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="H77" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="J77" t="n">
         <v>2.307</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="I77" t="n">
-        <v>1.597</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.423</v>
       </c>
     </row>
     <row r="78">
@@ -9334,23 +9334,23 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="D78" t="n">
+        <v>4.186</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="G78" t="n">
         <v>2.158</v>
       </c>
-      <c r="C78" t="n">
-        <v>4.186</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="H78" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J78" t="n">
         <v>2.249</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="I78" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.723</v>
       </c>
     </row>
     <row r="79">
@@ -9359,23 +9359,23 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="D79" t="n">
+        <v>4.576</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="G79" t="n">
         <v>2.151</v>
       </c>
-      <c r="C79" t="n">
-        <v>4.576</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="H79" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="J79" t="n">
         <v>2.347</v>
-      </c>
-      <c r="G79" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2.248</v>
-      </c>
-      <c r="J79" t="n">
-        <v>0.441</v>
       </c>
     </row>
     <row r="80">
@@ -9384,23 +9384,23 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="D80" t="n">
+        <v>4.318</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="G80" t="n">
         <v>2.116</v>
       </c>
-      <c r="C80" t="n">
-        <v>4.318</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="H80" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="J80" t="n">
         <v>2.654</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="I80" t="n">
-        <v>2.043</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.749</v>
       </c>
     </row>
     <row r="81">
@@ -9410,25 +9410,25 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4.588</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="G81" t="n">
         <v>2.123</v>
       </c>
-      <c r="C81" t="n">
-        <v>4.588</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1.279</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="H81" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="J81" t="n">
         <v>2.115</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="I81" t="n">
-        <v>2.268</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0.609</v>
       </c>
     </row>
     <row r="82">
@@ -9438,25 +9438,25 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="G82" t="n">
         <v>2.095</v>
       </c>
-      <c r="C82" t="n">
-        <v>4.526</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="H82" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="J82" t="n">
         <v>2.117</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1.427</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0.784</v>
       </c>
     </row>
     <row r="83">
@@ -9466,25 +9466,25 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4.597</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="G83" t="n">
         <v>1.426</v>
       </c>
-      <c r="C83" t="n">
-        <v>4.597</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.774</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="H83" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="J83" t="n">
         <v>2.179</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="I83" t="n">
-        <v>2.232</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0.488</v>
       </c>
     </row>
     <row r="84">
@@ -9494,25 +9494,25 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="G84" t="n">
         <v>1.86</v>
       </c>
-      <c r="C84" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2.334</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="H84" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="J84" t="n">
         <v>2.315</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.777</v>
       </c>
     </row>
     <row r="85">
@@ -9522,22 +9522,22 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="G85" t="n">
         <v>1.832</v>
       </c>
-      <c r="C85" t="n">
-        <v>4.168</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="H85" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="J85" t="n">
         <v>2.218</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0.64</v>
       </c>
     </row>
     <row r="86">
@@ -9547,22 +9547,22 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="D86" t="n">
+        <v>4.173</v>
+      </c>
+      <c r="G86" t="n">
         <v>1.88</v>
       </c>
-      <c r="C86" t="n">
-        <v>4.173</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="H86" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="J86" t="n">
         <v>2.23</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.647</v>
       </c>
     </row>
     <row r="87">
@@ -9572,22 +9572,22 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4.201</v>
+      </c>
+      <c r="G87" t="n">
         <v>1.912</v>
       </c>
-      <c r="C87" t="n">
-        <v>4.201</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2.796</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="H87" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J87" t="n">
         <v>2.173</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0.708</v>
       </c>
     </row>
     <row r="88">
@@ -9597,19 +9597,19 @@
         </is>
       </c>
       <c r="B88" t="n">
+        <v>3.186</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4.586</v>
+      </c>
+      <c r="G88" t="n">
         <v>2.094</v>
       </c>
-      <c r="C88" t="n">
-        <v>4.586</v>
-      </c>
-      <c r="D88" t="n">
-        <v>3.186</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="H88" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J88" t="n">
         <v>2.348</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0.519</v>
       </c>
     </row>
     <row r="89">
@@ -9619,22 +9619,22 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="G89" t="n">
         <v>2.107</v>
       </c>
-      <c r="C89" t="n">
-        <v>4.363</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="H89" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="J89" t="n">
         <v>2.072</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0.773</v>
       </c>
     </row>
     <row r="90">
@@ -9644,22 +9644,22 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="D90" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="G90" t="n">
         <v>2.088</v>
       </c>
-      <c r="C90" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="H90" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="J90" t="n">
         <v>2.255</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1.047</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0.66</v>
       </c>
     </row>
     <row r="91">
@@ -9669,22 +9669,22 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>3.007</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="G91" t="n">
         <v>2.183</v>
       </c>
-      <c r="C91" t="n">
-        <v>4.896</v>
-      </c>
-      <c r="D91" t="n">
-        <v>3.007</v>
-      </c>
-      <c r="E91" t="n">
+      <c r="H91" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="J91" t="n">
         <v>2.2</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0.663</v>
       </c>
     </row>
     <row r="92">
@@ -9694,25 +9694,25 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>3.501</v>
+      </c>
+      <c r="D92" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G92" t="n">
         <v>2.175</v>
       </c>
-      <c r="C92" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="D92" t="n">
-        <v>3.501</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="H92" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="J92" t="n">
         <v>2.496</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0.823</v>
       </c>
     </row>
     <row r="93">
@@ -9722,25 +9722,25 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="D93" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="G93" t="n">
         <v>2.176</v>
       </c>
-      <c r="C93" t="n">
-        <v>4.605</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="H93" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="J93" t="n">
         <v>2.361</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="J93" t="n">
-        <v>0.803</v>
       </c>
     </row>
     <row r="94">
@@ -9750,25 +9750,25 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="D94" t="n">
+        <v>4.977</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="G94" t="n">
         <v>1.992</v>
       </c>
-      <c r="C94" t="n">
-        <v>4.977</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2.883</v>
-      </c>
-      <c r="E94" t="n">
+      <c r="H94" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J94" t="n">
         <v>2.018</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="I94" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0.532</v>
       </c>
     </row>
     <row r="95">
@@ -9778,25 +9778,25 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4.436</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="G95" t="n">
         <v>1.368</v>
       </c>
-      <c r="C95" t="n">
-        <v>4.436</v>
-      </c>
-      <c r="D95" t="n">
-        <v>2.943</v>
-      </c>
-      <c r="E95" t="n">
+      <c r="H95" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="J95" t="n">
         <v>2.03</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="I95" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0.519</v>
       </c>
     </row>
     <row r="96">
@@ -9806,25 +9806,25 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="G96" t="n">
         <v>1.896</v>
       </c>
-      <c r="C96" t="n">
-        <v>3.043</v>
-      </c>
-      <c r="D96" t="n">
-        <v>2.169</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="H96" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="J96" t="n">
         <v>2.269</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="I96" t="n">
-        <v>2.299</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0.944</v>
       </c>
     </row>
     <row r="97">
@@ -9834,25 +9834,25 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3.985</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="G97" t="n">
         <v>1.751</v>
       </c>
-      <c r="C97" t="n">
-        <v>3.985</v>
-      </c>
-      <c r="D97" t="n">
-        <v>2.723</v>
-      </c>
-      <c r="E97" t="n">
+      <c r="H97" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="J97" t="n">
         <v>2.062</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="I97" t="n">
-        <v>2.093</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0.651</v>
       </c>
     </row>
     <row r="98">
@@ -9862,25 +9862,25 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>2.508</v>
+      </c>
+      <c r="D98" t="n">
+        <v>4.166</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G98" t="n">
         <v>1.761</v>
       </c>
-      <c r="C98" t="n">
-        <v>4.166</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2.508</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="H98" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="J98" t="n">
         <v>2.195</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="I98" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J98" t="n">
-        <v>0.207</v>
       </c>
     </row>
     <row r="99">
@@ -9890,25 +9890,25 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4.193</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="G99" t="n">
         <v>1.793</v>
       </c>
-      <c r="C99" t="n">
-        <v>4.193</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2.834</v>
-      </c>
-      <c r="E99" t="n">
+      <c r="H99" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="J99" t="n">
         <v>2.157</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1.963</v>
-      </c>
-      <c r="J99" t="n">
-        <v>0.863</v>
       </c>
     </row>
     <row r="100">
@@ -9918,25 +9918,25 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>3.366</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4.656</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="G100" t="n">
         <v>2.094</v>
       </c>
-      <c r="C100" t="n">
-        <v>4.656</v>
-      </c>
-      <c r="D100" t="n">
-        <v>3.366</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="H100" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J100" t="n">
         <v>2.229</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="I100" t="n">
-        <v>2.249</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0.456</v>
       </c>
     </row>
     <row r="101">
@@ -9946,25 +9946,25 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4.739</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="G101" t="n">
         <v>2.022</v>
       </c>
-      <c r="C101" t="n">
-        <v>4.739</v>
-      </c>
-      <c r="D101" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="E101" t="n">
+      <c r="H101" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="J101" t="n">
         <v>2.342</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="I101" t="n">
-        <v>2.184</v>
-      </c>
-      <c r="J101" t="n">
-        <v>0.588</v>
       </c>
     </row>
     <row r="102">
@@ -9974,25 +9974,25 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="D102" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="G102" t="n">
         <v>2.334</v>
       </c>
-      <c r="C102" t="n">
-        <v>4.976</v>
-      </c>
-      <c r="D102" t="n">
-        <v>3.175</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="H102" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="J102" t="n">
         <v>2.257</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="I102" t="n">
-        <v>2.504</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0.77</v>
       </c>
     </row>
     <row r="103">
@@ -10002,25 +10002,25 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4.844</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="G103" t="n">
         <v>2.178</v>
       </c>
-      <c r="C103" t="n">
-        <v>4.844</v>
-      </c>
-      <c r="D103" t="n">
-        <v>3.573</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="H103" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="J103" t="n">
         <v>2.148</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="I103" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0.739</v>
       </c>
     </row>
     <row r="104">
@@ -10030,25 +10030,25 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>3.334</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4.822</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G104" t="n">
         <v>2.229</v>
       </c>
-      <c r="C104" t="n">
-        <v>4.822</v>
-      </c>
-      <c r="D104" t="n">
-        <v>3.334</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="H104" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="J104" t="n">
         <v>2.096</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="I104" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0.527</v>
       </c>
     </row>
     <row r="105">
@@ -10058,25 +10058,25 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="G105" t="n">
         <v>2.072</v>
       </c>
-      <c r="C105" t="n">
-        <v>4.861</v>
-      </c>
-      <c r="D105" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="H105" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="J105" t="n">
         <v>2.154</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0.903</v>
       </c>
     </row>
     <row r="106">
@@ -10086,25 +10086,25 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G106" t="n">
         <v>1.946</v>
       </c>
-      <c r="C106" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="D106" t="n">
-        <v>2.768</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="H106" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="J106" t="n">
         <v>1.821</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0.522</v>
       </c>
     </row>
     <row r="107">
@@ -10114,25 +10114,25 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="G107" t="n">
         <v>1.528</v>
       </c>
-      <c r="C107" t="n">
-        <v>4.624</v>
-      </c>
-      <c r="D107" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="H107" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="J107" t="n">
         <v>2.163</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="I107" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0.411</v>
       </c>
     </row>
     <row r="108">
@@ -10142,25 +10142,25 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.944</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G108" t="n">
         <v>1.849</v>
       </c>
-      <c r="C108" t="n">
-        <v>3.944</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3.038</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="H108" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="J108" t="n">
         <v>2.346</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="I108" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0.466</v>
       </c>
     </row>
     <row r="109">
@@ -10170,25 +10170,25 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="D109" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="G109" t="n">
         <v>1.815</v>
       </c>
-      <c r="C109" t="n">
-        <v>4.213</v>
-      </c>
-      <c r="D109" t="n">
-        <v>2.762</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="H109" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="J109" t="n">
         <v>2.018</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="110">
@@ -10198,25 +10198,25 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="D110" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="G110" t="n">
         <v>1.829</v>
       </c>
-      <c r="C110" t="n">
-        <v>4.164</v>
-      </c>
-      <c r="D110" t="n">
-        <v>2.298</v>
-      </c>
-      <c r="E110" t="n">
+      <c r="H110" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="J110" t="n">
         <v>2.234</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="I110" t="n">
-        <v>2.212</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0.957</v>
       </c>
     </row>
     <row r="111">
@@ -10226,25 +10226,25 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="D111" t="n">
+        <v>4.401</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="G111" t="n">
         <v>1.885</v>
       </c>
-      <c r="C111" t="n">
-        <v>4.401</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="H111" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="J111" t="n">
         <v>2.349</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="I111" t="n">
-        <v>2.288</v>
-      </c>
-      <c r="J111" t="n">
-        <v>0.499</v>
       </c>
     </row>
     <row r="112">
@@ -10254,25 +10254,25 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.427</v>
+      </c>
+      <c r="G112" t="n">
         <v>1.887</v>
       </c>
-      <c r="C112" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D112" t="n">
-        <v>2.711</v>
-      </c>
-      <c r="E112" t="n">
+      <c r="H112" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="J112" t="n">
         <v>2.348</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="I112" t="n">
-        <v>2.427</v>
-      </c>
-      <c r="J112" t="n">
-        <v>0.447</v>
       </c>
     </row>
     <row r="113">
@@ -10282,25 +10282,25 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4.609</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="G113" t="n">
         <v>2.183</v>
       </c>
-      <c r="C113" t="n">
-        <v>4.609</v>
-      </c>
-      <c r="D113" t="n">
-        <v>2.838</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="H113" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="J113" t="n">
         <v>2.38</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="I113" t="n">
-        <v>2.021</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0.381</v>
       </c>
     </row>
     <row r="114">
@@ -10310,28 +10310,28 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="D114" t="n">
+        <v>4.677</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="G114" t="n">
         <v>2.291</v>
       </c>
-      <c r="C114" t="n">
-        <v>4.677</v>
-      </c>
-      <c r="D114" t="n">
-        <v>2.751</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="H114" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="J114" t="n">
         <v>2.365</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="I114" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0.6870000000000001</v>
       </c>
     </row>
     <row r="115">
@@ -10341,28 +10341,28 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>2.754</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4.853</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="G115" t="n">
         <v>2.193</v>
       </c>
-      <c r="C115" t="n">
-        <v>4.853</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2.754</v>
-      </c>
-      <c r="E115" t="n">
+      <c r="H115" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" t="n">
         <v>2.185</v>
-      </c>
-      <c r="G115" t="n">
-        <v>1</v>
-      </c>
-      <c r="H115" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0.427</v>
       </c>
     </row>
     <row r="116">
@@ -10372,28 +10372,28 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="D116" t="n">
+        <v>4.574</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.404</v>
+      </c>
+      <c r="G116" t="n">
         <v>2.343</v>
       </c>
-      <c r="C116" t="n">
-        <v>4.574</v>
-      </c>
-      <c r="D116" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="H116" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="J116" t="n">
         <v>2.582</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="H116" t="n">
-        <v>2.461</v>
-      </c>
-      <c r="I116" t="n">
-        <v>2.404</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0.761</v>
       </c>
     </row>
     <row r="117">
@@ -10403,28 +10403,28 @@
         </is>
       </c>
       <c r="B117" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3.473</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="G117" t="n">
         <v>2.107</v>
       </c>
-      <c r="C117" t="n">
-        <v>4.818</v>
-      </c>
-      <c r="D117" t="n">
-        <v>3.251</v>
-      </c>
-      <c r="E117" t="n">
+      <c r="H117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="J117" t="n">
         <v>2.341</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="H117" t="n">
-        <v>3.473</v>
-      </c>
-      <c r="I117" t="n">
-        <v>2.257</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0.2</v>
       </c>
     </row>
     <row r="118">
@@ -10434,28 +10434,28 @@
         </is>
       </c>
       <c r="B118" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3.886</v>
+      </c>
+      <c r="D118" t="n">
+        <v>4.631</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="G118" t="n">
         <v>2.195</v>
       </c>
-      <c r="C118" t="n">
-        <v>4.631</v>
-      </c>
-      <c r="D118" t="n">
-        <v>3.347</v>
-      </c>
-      <c r="E118" t="n">
+      <c r="H118" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="J118" t="n">
         <v>2.317</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="H118" t="n">
-        <v>3.886</v>
-      </c>
-      <c r="I118" t="n">
-        <v>2.502</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0.525</v>
       </c>
     </row>
     <row r="119">
@@ -10465,28 +10465,28 @@
         </is>
       </c>
       <c r="B119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="D119" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G119" t="n">
         <v>1.442</v>
       </c>
-      <c r="C119" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="D119" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="H119" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="J119" t="n">
         <v>2.196</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="H119" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0.61</v>
       </c>
     </row>
     <row r="120">
@@ -10496,28 +10496,28 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3.084</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="G120" t="n">
         <v>1.677</v>
       </c>
-      <c r="C120" t="n">
-        <v>3.084</v>
-      </c>
-      <c r="D120" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="H120" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="J120" t="n">
         <v>2.259</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="H120" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="I120" t="n">
-        <v>2.442</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0.754</v>
       </c>
     </row>
     <row r="121">
@@ -10527,28 +10527,28 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="D121" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="G121" t="n">
         <v>1.91</v>
       </c>
-      <c r="C121" t="n">
-        <v>4.035</v>
-      </c>
-      <c r="D121" t="n">
-        <v>3.043</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="H121" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J121" t="n">
         <v>2.388</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H121" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="I121" t="n">
-        <v>2.109</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0.255</v>
       </c>
     </row>
     <row r="122">
@@ -10558,28 +10558,28 @@
         </is>
       </c>
       <c r="B122" t="n">
+        <v>3.144</v>
+      </c>
+      <c r="C122" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="D122" t="n">
+        <v>4.155</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.134</v>
+      </c>
+      <c r="G122" t="n">
         <v>1.936</v>
       </c>
-      <c r="C122" t="n">
-        <v>4.155</v>
-      </c>
-      <c r="D122" t="n">
-        <v>3.144</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="H122" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="J122" t="n">
         <v>2.334</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="H122" t="n">
-        <v>5.517</v>
-      </c>
-      <c r="I122" t="n">
-        <v>2.134</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0.469</v>
       </c>
     </row>
     <row r="123">
@@ -10589,28 +10589,28 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="C123" t="n">
+        <v>5.711</v>
+      </c>
+      <c r="D123" t="n">
+        <v>4.221</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.179</v>
+      </c>
+      <c r="G123" t="n">
         <v>2.012</v>
       </c>
-      <c r="C123" t="n">
-        <v>4.221</v>
-      </c>
-      <c r="D123" t="n">
-        <v>3.132</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="H123" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="J123" t="n">
         <v>2.546</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="H123" t="n">
-        <v>5.711</v>
-      </c>
-      <c r="I123" t="n">
-        <v>2.179</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0.726</v>
       </c>
     </row>
     <row r="124">
@@ -10620,28 +10620,28 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="C124" t="n">
+        <v>7.541</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.459</v>
+      </c>
+      <c r="G124" t="n">
         <v>1.997</v>
       </c>
-      <c r="C124" t="n">
-        <v>4.489</v>
-      </c>
-      <c r="D124" t="n">
-        <v>2.748</v>
-      </c>
-      <c r="E124" t="n">
+      <c r="H124" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="J124" t="n">
         <v>2.684</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="H124" t="n">
-        <v>7.541</v>
-      </c>
-      <c r="I124" t="n">
-        <v>2.459</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0.496</v>
       </c>
     </row>
     <row r="125">
@@ -10651,28 +10651,28 @@
         </is>
       </c>
       <c r="B125" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="C125" t="n">
+        <v>7.614</v>
+      </c>
+      <c r="D125" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.326</v>
+      </c>
+      <c r="G125" t="n">
         <v>2.14</v>
       </c>
-      <c r="C125" t="n">
-        <v>4.926</v>
-      </c>
-      <c r="D125" t="n">
-        <v>3.385</v>
-      </c>
-      <c r="E125" t="n">
+      <c r="H125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J125" t="n">
         <v>3.095</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="H125" t="n">
-        <v>7.614</v>
-      </c>
-      <c r="I125" t="n">
-        <v>2.326</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0.531</v>
       </c>
     </row>
     <row r="126">
@@ -10682,28 +10682,28 @@
         </is>
       </c>
       <c r="B126" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="C126" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="G126" t="n">
         <v>2.463</v>
       </c>
-      <c r="C126" t="n">
-        <v>4.725</v>
-      </c>
-      <c r="D126" t="n">
-        <v>3.581</v>
-      </c>
-      <c r="E126" t="n">
+      <c r="H126" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="I126" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="J126" t="n">
         <v>3.189</v>
-      </c>
-      <c r="G126" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="H126" t="n">
-        <v>7.775</v>
-      </c>
-      <c r="I126" t="n">
-        <v>2.438</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0.805</v>
       </c>
     </row>
     <row r="127">
@@ -10713,28 +10713,28 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>3.321</v>
+      </c>
+      <c r="C127" t="n">
+        <v>8.148</v>
+      </c>
+      <c r="D127" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="G127" t="n">
         <v>2.253</v>
       </c>
-      <c r="C127" t="n">
-        <v>4.649</v>
-      </c>
-      <c r="D127" t="n">
-        <v>3.321</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="H127" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="J127" t="n">
         <v>2.945</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="H127" t="n">
-        <v>8.148</v>
-      </c>
-      <c r="I127" t="n">
-        <v>2.232</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0.361</v>
       </c>
     </row>
     <row r="128">
@@ -10744,28 +10744,28 @@
         </is>
       </c>
       <c r="B128" t="n">
+        <v>3.384</v>
+      </c>
+      <c r="C128" t="n">
+        <v>7.524</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="G128" t="n">
         <v>2.269</v>
       </c>
-      <c r="C128" t="n">
-        <v>4.756</v>
-      </c>
-      <c r="D128" t="n">
-        <v>3.384</v>
-      </c>
-      <c r="E128" t="n">
+      <c r="H128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="J128" t="n">
         <v>3.317</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="H128" t="n">
-        <v>7.524</v>
-      </c>
-      <c r="I128" t="n">
-        <v>2.441</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0.294</v>
       </c>
     </row>
     <row r="129">
@@ -10775,28 +10775,28 @@
         </is>
       </c>
       <c r="B129" t="n">
+        <v>3.317</v>
+      </c>
+      <c r="C129" t="n">
+        <v>8.334</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="G129" t="n">
         <v>2.284</v>
       </c>
-      <c r="C129" t="n">
-        <v>4.918</v>
-      </c>
-      <c r="D129" t="n">
-        <v>3.317</v>
-      </c>
-      <c r="E129" t="n">
+      <c r="H129" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="J129" t="n">
         <v>3.361</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="H129" t="n">
-        <v>8.334</v>
-      </c>
-      <c r="I129" t="n">
-        <v>2.455</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0.518</v>
       </c>
     </row>
     <row r="130">
@@ -10806,31 +10806,31 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>3.437</v>
+      </c>
+      <c r="C130" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4.745</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="G130" t="n">
         <v>2.113</v>
       </c>
-      <c r="C130" t="n">
-        <v>4.745</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3.437</v>
-      </c>
-      <c r="E130" t="n">
+      <c r="H130" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="J130" t="n">
         <v>3.154</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="H130" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="I130" t="n">
-        <v>2.511</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0.555</v>
       </c>
     </row>
     <row r="131">
@@ -10840,31 +10840,31 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="C131" t="n">
+        <v>7.846</v>
+      </c>
+      <c r="D131" t="n">
+        <v>4.314</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="G131" t="n">
         <v>1.546</v>
       </c>
-      <c r="C131" t="n">
-        <v>4.314</v>
-      </c>
-      <c r="D131" t="n">
-        <v>3.066</v>
-      </c>
-      <c r="E131" t="n">
+      <c r="H131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="J131" t="n">
         <v>3.122</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="H131" t="n">
-        <v>7.846</v>
-      </c>
-      <c r="I131" t="n">
-        <v>1.993</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0.331</v>
       </c>
     </row>
     <row r="132">
@@ -10874,31 +10874,31 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D132" t="n">
+        <v>4.436</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G132" t="n">
         <v>2.187</v>
       </c>
-      <c r="C132" t="n">
-        <v>4.436</v>
-      </c>
-      <c r="D132" t="n">
-        <v>3.177</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="H132" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="J132" t="n">
         <v>3.271</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="H132" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="I132" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0.9419999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -514,21 +514,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plaquemines: Near complete - Gator Express is fed by Tennessee Gas and Texas Eastern.</t>
+          <t>Plaquemines: Complete - Gator Express's three feeds: Tennessee Gas, Texas Eastern and Columbia Gulf.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cameron: Complete - Cameron Interstate's delivery meter into the terminal.</t>
+          <t>Cameron: Complete - Cameron Interstate's delivery meter into the terminal plus Columbia Gulf's direct feed.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Calcasieu Pass: Partial - TransCameron is intrastate; only Texas Eastern's delivery into it is seen.</t>
+          <t>Calcasieu Pass: Mostly complete - ANR (Grand Chenier XPress) and Texas Eastern deliveries into TransCameron; Sabine Pipe Line's, if any, not yet seen.</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Freeport: Partial - Stratton Ridge only; BIG Pipeline and Gulf South meters not yet covered. Stratton Ridge is a hub, so check against Freeport's reported output.</t>
+          <t>Freeport: Partial - Texas Eastern's deliveries at Stratton Ridge and into BIG Pipeline only; Texas intrastate supply is invisible, so use the calibrated estimate. Stratton Ridge also serves Dow's Freeport complex.</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cove Point: Not yet covered - Transco, Columbia and DETI.</t>
+          <t>Cove Point: Complete - Cove Point pipeline's delivery meter into the plant.</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -691,6 +691,11 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>Cove Point</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
@@ -715,7 +720,7 @@
         <v>2.432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.183</v>
+        <v>0.395</v>
       </c>
       <c r="H2" t="n">
         <v>0.362</v>
@@ -724,7 +729,10 @@
         <v>0.746</v>
       </c>
       <c r="J2" t="n">
-        <v>12.052</v>
+        <v>0.014</v>
+      </c>
+      <c r="K2" t="n">
+        <v>12.278</v>
       </c>
     </row>
   </sheetData>
@@ -792,7 +800,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cove Point (EIA 2026-06, unmetered)</t>
+          <t>Cove Point</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -826,7 +834,7 @@
         <v>2.432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.183</v>
+        <v>0.395</v>
       </c>
       <c r="H2" t="n">
         <v>0.362</v>
@@ -835,13 +843,13 @@
         <v>0.746</v>
       </c>
       <c r="J2" t="n">
-        <v>0.765</v>
+        <v>0.014</v>
       </c>
       <c r="K2" t="n">
-        <v>12.816</v>
+        <v>12.277</v>
       </c>
       <c r="L2" t="n">
-        <v>12.051</v>
+        <v>12.277</v>
       </c>
     </row>
   </sheetData>
@@ -855,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -899,32 +907,57 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Plaquemines | Columbia Gulf -&gt; Wilkinson Bayou (Gator Express) (CGT 4267)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Cameron | Cameron Interstate -&gt; Cameron LNG (CAMERON 772300)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Cameron | Columbia Gulf -&gt; Cameron LNG (CGT 4246)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>Calcasieu Pass | Texas Eastern -&gt; TransCameron, Oak Grove (TE 74529)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Calcasieu Pass | ANR -&gt; TransCameron (Grand Chenier XPress), Mermentau River (ANR 523094)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>Corpus Christi | Corpus Christi Pipeline -&gt; Corpus Christi Liquefaction (400 CC200221)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Freeport | Texas Eastern -&gt; Stratton Ridge (TE 79999)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Freeport | Texas Eastern -&gt; BIG Pipeline, Angleton (TE 73912)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Elba Island | Elba Express -&gt; Elba Liquefaction, Chatham (EEC 660700)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Golden Pass | Gulf Run -&gt; Golden Pass Pipeline (GR 808311)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Cove Point | Cove Point pipeline -&gt; Cove Point plant (cpl 10001)</t>
         </is>
       </c>
     </row>
@@ -950,23 +983,29 @@
       <c r="G2" t="n">
         <v>1468619</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>1428275</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>310625</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>2522392</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>189475</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P2" t="n">
         <v>375660</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>773586</v>
+      </c>
+      <c r="R2" t="n">
+        <v>15000</v>
       </c>
     </row>
   </sheetData>
@@ -8059,47 +8098,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cove Point</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Calcasieu Pass</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Plaquemines</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Golden Pass</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Freeport</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Cameron</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Cove Point</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
         </is>
       </c>
     </row>
@@ -8419,12 +8458,12 @@
           <t>2018-03</t>
         </is>
       </c>
+      <c r="C33" t="n">
+        <v>0.105</v>
+      </c>
       <c r="D33" t="n">
         <v>3.11</v>
       </c>
-      <c r="I33" t="n">
-        <v>0.105</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8432,12 +8471,12 @@
           <t>2018-04</t>
         </is>
       </c>
+      <c r="C34" t="n">
+        <v>0.325</v>
+      </c>
       <c r="D34" t="n">
         <v>2.788</v>
       </c>
-      <c r="I34" t="n">
-        <v>0.325</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8445,12 +8484,12 @@
           <t>2018-05</t>
         </is>
       </c>
+      <c r="C35" t="n">
+        <v>0.77</v>
+      </c>
       <c r="D35" t="n">
         <v>2.562</v>
       </c>
-      <c r="I35" t="n">
-        <v>0.77</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8458,12 +8497,12 @@
           <t>2018-06</t>
         </is>
       </c>
+      <c r="C36" t="n">
+        <v>0.457</v>
+      </c>
       <c r="D36" t="n">
         <v>2.213</v>
       </c>
-      <c r="I36" t="n">
-        <v>0.457</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8471,12 +8510,12 @@
           <t>2018-07</t>
         </is>
       </c>
+      <c r="C37" t="n">
+        <v>0.675</v>
+      </c>
       <c r="D37" t="n">
         <v>2.778</v>
       </c>
-      <c r="I37" t="n">
-        <v>0.675</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8484,12 +8523,12 @@
           <t>2018-08</t>
         </is>
       </c>
+      <c r="C38" t="n">
+        <v>0.676</v>
+      </c>
       <c r="D38" t="n">
         <v>2.54</v>
       </c>
-      <c r="I38" t="n">
-        <v>0.676</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8497,12 +8536,12 @@
           <t>2018-09</t>
         </is>
       </c>
+      <c r="C39" t="n">
+        <v>0.449</v>
+      </c>
       <c r="D39" t="n">
         <v>2.507</v>
       </c>
-      <c r="I39" t="n">
-        <v>0.449</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8510,12 +8549,12 @@
           <t>2018-10</t>
         </is>
       </c>
+      <c r="C40" t="n">
+        <v>0.226</v>
+      </c>
       <c r="D40" t="n">
         <v>2.932</v>
       </c>
-      <c r="I40" t="n">
-        <v>0.226</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8523,12 +8562,12 @@
           <t>2018-11</t>
         </is>
       </c>
+      <c r="C41" t="n">
+        <v>0.701</v>
+      </c>
       <c r="D41" t="n">
         <v>3.202</v>
       </c>
-      <c r="I41" t="n">
-        <v>0.701</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8536,15 +8575,15 @@
           <t>2018-12</t>
         </is>
       </c>
+      <c r="B42" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.711</v>
+      </c>
       <c r="D42" t="n">
         <v>3.36</v>
       </c>
-      <c r="I42" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.241</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -8552,15 +8591,15 @@
           <t>2019-01</t>
         </is>
       </c>
+      <c r="B43" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.714</v>
+      </c>
       <c r="D43" t="n">
         <v>3.367</v>
       </c>
-      <c r="I43" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8568,15 +8607,15 @@
           <t>2019-02</t>
         </is>
       </c>
+      <c r="B44" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.915</v>
+      </c>
       <c r="D44" t="n">
         <v>2.942</v>
       </c>
-      <c r="I44" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.145</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8584,15 +8623,15 @@
           <t>2019-03</t>
         </is>
       </c>
+      <c r="B45" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.599</v>
+      </c>
       <c r="D45" t="n">
         <v>3.291</v>
       </c>
-      <c r="I45" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.706</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8600,15 +8639,15 @@
           <t>2019-04</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.867</v>
+      </c>
       <c r="D46" t="n">
         <v>3.054</v>
       </c>
-      <c r="I46" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.6919999999999999</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8616,17 +8655,17 @@
           <t>2019-05</t>
         </is>
       </c>
+      <c r="B47" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.602</v>
+      </c>
       <c r="D47" t="n">
         <v>3.762</v>
       </c>
-      <c r="G47" t="n">
+      <c r="J47" t="n">
         <v>0.113</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.614</v>
       </c>
     </row>
     <row r="48">
@@ -8635,17 +8674,17 @@
           <t>2019-06</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.731</v>
+      </c>
       <c r="D48" t="n">
         <v>3.551</v>
       </c>
-      <c r="G48" t="n">
+      <c r="J48" t="n">
         <v>0.106</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.765</v>
       </c>
     </row>
     <row r="49">
@@ -8654,17 +8693,17 @@
           <t>2019-07</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.731</v>
+      </c>
       <c r="D49" t="n">
         <v>3.347</v>
       </c>
-      <c r="G49" t="n">
+      <c r="J49" t="n">
         <v>0.248</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.184</v>
       </c>
     </row>
     <row r="50">
@@ -8673,17 +8712,17 @@
           <t>2019-08</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.699</v>
+      </c>
       <c r="D50" t="n">
         <v>2.696</v>
       </c>
-      <c r="G50" t="n">
+      <c r="J50" t="n">
         <v>0.388</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.084</v>
       </c>
     </row>
     <row r="51">
@@ -8692,20 +8731,20 @@
           <t>2019-09</t>
         </is>
       </c>
+      <c r="B51" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.5</v>
+      </c>
       <c r="D51" t="n">
         <v>3.461</v>
       </c>
       <c r="F51" t="n">
         <v>0.235</v>
       </c>
-      <c r="G51" t="n">
+      <c r="J51" t="n">
         <v>0.364</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.26</v>
       </c>
     </row>
     <row r="52">
@@ -8714,20 +8753,20 @@
           <t>2019-10</t>
         </is>
       </c>
+      <c r="B52" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.244</v>
+      </c>
       <c r="D52" t="n">
         <v>3.775</v>
       </c>
       <c r="F52" t="n">
         <v>0.365</v>
       </c>
-      <c r="G52" t="n">
+      <c r="J52" t="n">
         <v>0.379</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.488</v>
       </c>
     </row>
     <row r="53">
@@ -8736,20 +8775,20 @@
           <t>2019-11</t>
         </is>
       </c>
+      <c r="B53" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.852</v>
+      </c>
       <c r="D53" t="n">
         <v>3.852</v>
       </c>
       <c r="F53" t="n">
         <v>0.353</v>
       </c>
-      <c r="G53" t="n">
+      <c r="J53" t="n">
         <v>0.507</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.357</v>
       </c>
     </row>
     <row r="54">
@@ -8758,6 +8797,12 @@
           <t>2019-12</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.729</v>
+      </c>
       <c r="D54" t="n">
         <v>3.813</v>
       </c>
@@ -8765,16 +8810,10 @@
         <v>0.79</v>
       </c>
       <c r="G54" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.84</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.461</v>
       </c>
     </row>
     <row r="55">
@@ -8783,6 +8822,12 @@
           <t>2020-01</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.722</v>
+      </c>
       <c r="D55" t="n">
         <v>4.018</v>
       </c>
@@ -8790,16 +8835,10 @@
         <v>1.456</v>
       </c>
       <c r="G55" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.98</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.426</v>
       </c>
     </row>
     <row r="56">
@@ -8808,20 +8847,20 @@
           <t>2020-02</t>
         </is>
       </c>
+      <c r="B56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.758</v>
+      </c>
       <c r="D56" t="n">
         <v>3.684</v>
       </c>
       <c r="F56" t="n">
         <v>1.446</v>
       </c>
-      <c r="G56" t="n">
+      <c r="J56" t="n">
         <v>1.044</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="57">
@@ -8830,20 +8869,20 @@
           <t>2020-03</t>
         </is>
       </c>
+      <c r="B57" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.831</v>
+      </c>
       <c r="D57" t="n">
         <v>3.447</v>
       </c>
       <c r="F57" t="n">
         <v>1.635</v>
       </c>
-      <c r="G57" t="n">
+      <c r="J57" t="n">
         <v>1.208</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.462</v>
       </c>
     </row>
     <row r="58">
@@ -8852,20 +8891,20 @@
           <t>2020-04</t>
         </is>
       </c>
+      <c r="B58" t="n">
+        <v>1.245</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.608</v>
+      </c>
       <c r="D58" t="n">
         <v>3.333</v>
       </c>
       <c r="F58" t="n">
         <v>1.158</v>
       </c>
-      <c r="G58" t="n">
+      <c r="J58" t="n">
         <v>1.301</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.245</v>
       </c>
     </row>
     <row r="59">
@@ -8874,20 +8913,20 @@
           <t>2020-05</t>
         </is>
       </c>
+      <c r="B59" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.708</v>
+      </c>
       <c r="D59" t="n">
         <v>2.73</v>
       </c>
       <c r="F59" t="n">
         <v>1.008</v>
       </c>
-      <c r="G59" t="n">
+      <c r="J59" t="n">
         <v>1.135</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.831</v>
       </c>
     </row>
     <row r="60">
@@ -8896,20 +8935,20 @@
           <t>2020-06</t>
         </is>
       </c>
+      <c r="B60" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.763</v>
+      </c>
       <c r="D60" t="n">
         <v>0.978</v>
       </c>
       <c r="F60" t="n">
         <v>0.543</v>
       </c>
-      <c r="G60" t="n">
+      <c r="J60" t="n">
         <v>1.366</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.307</v>
       </c>
     </row>
     <row r="61">
@@ -8918,20 +8957,20 @@
           <t>2020-07</t>
         </is>
       </c>
+      <c r="B61" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.711</v>
+      </c>
       <c r="D61" t="n">
         <v>1.063</v>
       </c>
       <c r="F61" t="n">
         <v>0.132</v>
       </c>
-      <c r="G61" t="n">
+      <c r="J61" t="n">
         <v>1.099</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.373</v>
       </c>
     </row>
     <row r="62">
@@ -8940,6 +8979,12 @@
           <t>2020-08</t>
         </is>
       </c>
+      <c r="B62" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0.596</v>
+      </c>
       <c r="D62" t="n">
         <v>1.031</v>
       </c>
@@ -8947,16 +8992,10 @@
         <v>0.399</v>
       </c>
       <c r="G62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J62" t="n">
         <v>1.117</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.601</v>
       </c>
     </row>
     <row r="63">
@@ -8965,20 +9004,20 @@
           <t>2020-09</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0.621</v>
+      </c>
       <c r="D63" t="n">
         <v>2.241</v>
       </c>
       <c r="F63" t="n">
         <v>1.127</v>
       </c>
-      <c r="H63" t="n">
+      <c r="G63" t="n">
         <v>0.271</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.363</v>
       </c>
     </row>
     <row r="64">
@@ -8987,6 +9026,12 @@
           <t>2020-10</t>
         </is>
       </c>
+      <c r="B64" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0.373</v>
+      </c>
       <c r="D64" t="n">
         <v>3.106</v>
       </c>
@@ -8994,16 +9039,10 @@
         <v>1.892</v>
       </c>
       <c r="G64" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J64" t="n">
         <v>0.662</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.551</v>
       </c>
     </row>
     <row r="65">
@@ -9012,6 +9051,12 @@
           <t>2020-11</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.852</v>
+      </c>
       <c r="D65" t="n">
         <v>3.684</v>
       </c>
@@ -9019,16 +9064,10 @@
         <v>1.953</v>
       </c>
       <c r="G65" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="J65" t="n">
         <v>1.838</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.633</v>
       </c>
     </row>
     <row r="66">
@@ -9037,6 +9076,12 @@
           <t>2020-12</t>
         </is>
       </c>
+      <c r="B66" t="n">
+        <v>1.821</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.718</v>
+      </c>
       <c r="D66" t="n">
         <v>3.845</v>
       </c>
@@ -9044,16 +9089,10 @@
         <v>2.057</v>
       </c>
       <c r="G66" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="J66" t="n">
         <v>1.939</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1.821</v>
       </c>
     </row>
     <row r="67">
@@ -9062,20 +9101,20 @@
           <t>2021-01</t>
         </is>
       </c>
+      <c r="B67" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0.718</v>
+      </c>
       <c r="D67" t="n">
         <v>3.905</v>
       </c>
       <c r="F67" t="n">
         <v>2.148</v>
       </c>
-      <c r="G67" t="n">
+      <c r="J67" t="n">
         <v>1.943</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2.012</v>
       </c>
     </row>
     <row r="68">
@@ -9084,6 +9123,12 @@
           <t>2021-02</t>
         </is>
       </c>
+      <c r="B68" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0.671</v>
+      </c>
       <c r="D68" t="n">
         <v>3.263</v>
       </c>
@@ -9091,16 +9136,10 @@
         <v>1.186</v>
       </c>
       <c r="G68" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="J68" t="n">
         <v>1.42</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1.297</v>
       </c>
     </row>
     <row r="69">
@@ -9109,6 +9148,12 @@
           <t>2021-03</t>
         </is>
       </c>
+      <c r="B69" t="n">
+        <v>2.201</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.845</v>
+      </c>
       <c r="D69" t="n">
         <v>4.013</v>
       </c>
@@ -9116,16 +9161,10 @@
         <v>2.237</v>
       </c>
       <c r="G69" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="J69" t="n">
         <v>1.755</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.201</v>
       </c>
     </row>
     <row r="70">
@@ -9134,6 +9173,12 @@
           <t>2021-04</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0.622</v>
+      </c>
       <c r="D70" t="n">
         <v>3.955</v>
       </c>
@@ -9141,16 +9186,10 @@
         <v>2.203</v>
       </c>
       <c r="G70" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J70" t="n">
         <v>1.848</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.175</v>
       </c>
     </row>
     <row r="71">
@@ -9159,6 +9198,12 @@
           <t>2021-05</t>
         </is>
       </c>
+      <c r="B71" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.787</v>
+      </c>
       <c r="D71" t="n">
         <v>3.805</v>
       </c>
@@ -9166,16 +9211,10 @@
         <v>2.223</v>
       </c>
       <c r="G71" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="J71" t="n">
         <v>1.855</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.787</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.066</v>
       </c>
     </row>
     <row r="72">
@@ -9184,6 +9223,12 @@
           <t>2021-06</t>
         </is>
       </c>
+      <c r="B72" t="n">
+        <v>2.236</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0.6919999999999999</v>
+      </c>
       <c r="D72" t="n">
         <v>3.118</v>
       </c>
@@ -9191,16 +9236,10 @@
         <v>2.127</v>
       </c>
       <c r="G72" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="J72" t="n">
         <v>1.418</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2.236</v>
       </c>
     </row>
     <row r="73">
@@ -9209,6 +9248,12 @@
           <t>2021-07</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="D73" t="n">
         <v>3.402</v>
       </c>
@@ -9216,16 +9261,10 @@
         <v>2.141</v>
       </c>
       <c r="G73" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="J73" t="n">
         <v>1.82</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2.126</v>
       </c>
     </row>
     <row r="74">
@@ -9234,6 +9273,12 @@
           <t>2021-08</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>2.171</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0.785</v>
+      </c>
       <c r="D74" t="n">
         <v>3.492</v>
       </c>
@@ -9241,16 +9286,10 @@
         <v>2.307</v>
       </c>
       <c r="G74" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="J74" t="n">
         <v>1.467</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.171</v>
       </c>
     </row>
     <row r="75">
@@ -9259,6 +9298,12 @@
           <t>2021-09</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.499</v>
+      </c>
       <c r="D75" t="n">
         <v>3.619</v>
       </c>
@@ -9266,16 +9311,10 @@
         <v>1.764</v>
       </c>
       <c r="G75" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="J75" t="n">
         <v>1.919</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2.34</v>
       </c>
     </row>
     <row r="76">
@@ -9284,6 +9323,12 @@
           <t>2021-10</t>
         </is>
       </c>
+      <c r="B76" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0.348</v>
+      </c>
       <c r="D76" t="n">
         <v>3.561</v>
       </c>
@@ -9291,16 +9336,10 @@
         <v>2.111</v>
       </c>
       <c r="G76" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="J76" t="n">
         <v>1.852</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.348</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2.28</v>
       </c>
     </row>
     <row r="77">
@@ -9309,6 +9348,12 @@
           <t>2021-11</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.797</v>
+      </c>
       <c r="D77" t="n">
         <v>4.097</v>
       </c>
@@ -9316,16 +9361,10 @@
         <v>1.597</v>
       </c>
       <c r="G77" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="J77" t="n">
         <v>2.113</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="J77" t="n">
-        <v>2.307</v>
       </c>
     </row>
     <row r="78">
@@ -9334,6 +9373,12 @@
           <t>2021-12</t>
         </is>
       </c>
+      <c r="B78" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0.8100000000000001</v>
+      </c>
       <c r="D78" t="n">
         <v>4.186</v>
       </c>
@@ -9341,16 +9386,10 @@
         <v>2.365</v>
       </c>
       <c r="G78" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="J78" t="n">
         <v>2.158</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.249</v>
       </c>
     </row>
     <row r="79">
@@ -9359,6 +9398,12 @@
           <t>2022-01</t>
         </is>
       </c>
+      <c r="B79" t="n">
+        <v>2.347</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.886</v>
+      </c>
       <c r="D79" t="n">
         <v>4.576</v>
       </c>
@@ -9366,16 +9411,10 @@
         <v>2.248</v>
       </c>
       <c r="G79" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="J79" t="n">
         <v>2.151</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.347</v>
       </c>
     </row>
     <row r="80">
@@ -9384,6 +9423,12 @@
           <t>2022-02</t>
         </is>
       </c>
+      <c r="B80" t="n">
+        <v>2.654</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0.8120000000000001</v>
+      </c>
       <c r="D80" t="n">
         <v>4.318</v>
       </c>
@@ -9391,16 +9436,10 @@
         <v>2.043</v>
       </c>
       <c r="G80" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="J80" t="n">
         <v>2.116</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2.654</v>
       </c>
     </row>
     <row r="81">
@@ -9410,25 +9449,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.279</v>
+        <v>2.115</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.754</v>
       </c>
       <c r="D81" t="n">
         <v>4.588</v>
       </c>
+      <c r="E81" t="n">
+        <v>1.279</v>
+      </c>
       <c r="F81" t="n">
         <v>2.268</v>
       </c>
       <c r="G81" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J81" t="n">
         <v>2.123</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.115</v>
       </c>
     </row>
     <row r="82">
@@ -9438,25 +9477,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.289</v>
+        <v>2.117</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0.794</v>
       </c>
       <c r="D82" t="n">
         <v>4.526</v>
       </c>
+      <c r="E82" t="n">
+        <v>1.289</v>
+      </c>
       <c r="F82" t="n">
         <v>1.427</v>
       </c>
       <c r="G82" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="J82" t="n">
         <v>2.095</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="J82" t="n">
-        <v>2.117</v>
       </c>
     </row>
     <row r="83">
@@ -9466,25 +9505,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.774</v>
+        <v>2.179</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.781</v>
       </c>
       <c r="D83" t="n">
         <v>4.597</v>
       </c>
+      <c r="E83" t="n">
+        <v>1.774</v>
+      </c>
       <c r="F83" t="n">
         <v>2.232</v>
       </c>
       <c r="G83" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="J83" t="n">
         <v>1.426</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.179</v>
       </c>
     </row>
     <row r="84">
@@ -9494,25 +9533,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.334</v>
+        <v>2.315</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.716</v>
       </c>
       <c r="D84" t="n">
         <v>3.84</v>
       </c>
+      <c r="E84" t="n">
+        <v>2.334</v>
+      </c>
       <c r="F84" t="n">
         <v>0.629</v>
       </c>
       <c r="G84" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="J84" t="n">
         <v>1.86</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.716</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2.315</v>
       </c>
     </row>
     <row r="85">
@@ -9522,22 +9561,22 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.33</v>
+        <v>2.218</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0.851</v>
       </c>
       <c r="D85" t="n">
         <v>4.168</v>
       </c>
+      <c r="E85" t="n">
+        <v>2.33</v>
+      </c>
       <c r="G85" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J85" t="n">
         <v>1.832</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2.218</v>
       </c>
     </row>
     <row r="86">
@@ -9547,22 +9586,22 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.375</v>
+        <v>2.23</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0.753</v>
       </c>
       <c r="D86" t="n">
         <v>4.173</v>
       </c>
+      <c r="E86" t="n">
+        <v>2.375</v>
+      </c>
       <c r="G86" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J86" t="n">
         <v>1.88</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.753</v>
-      </c>
-      <c r="J86" t="n">
-        <v>2.23</v>
       </c>
     </row>
     <row r="87">
@@ -9572,22 +9611,22 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.796</v>
+        <v>2.173</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="D87" t="n">
         <v>4.201</v>
       </c>
+      <c r="E87" t="n">
+        <v>2.796</v>
+      </c>
       <c r="G87" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J87" t="n">
         <v>1.912</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.173</v>
       </c>
     </row>
     <row r="88">
@@ -9597,19 +9636,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.186</v>
+        <v>2.348</v>
       </c>
       <c r="D88" t="n">
         <v>4.586</v>
       </c>
+      <c r="E88" t="n">
+        <v>3.186</v>
+      </c>
       <c r="G88" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J88" t="n">
         <v>2.094</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="J88" t="n">
-        <v>2.348</v>
       </c>
     </row>
     <row r="89">
@@ -9619,22 +9658,22 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.625</v>
+        <v>2.072</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.742</v>
       </c>
       <c r="D89" t="n">
         <v>4.363</v>
       </c>
+      <c r="E89" t="n">
+        <v>2.625</v>
+      </c>
       <c r="G89" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="J89" t="n">
         <v>2.107</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.742</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.072</v>
       </c>
     </row>
     <row r="90">
@@ -9644,22 +9683,22 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2.655</v>
+        <v>2.255</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1.047</v>
       </c>
       <c r="D90" t="n">
         <v>4.893</v>
       </c>
+      <c r="E90" t="n">
+        <v>2.655</v>
+      </c>
       <c r="G90" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J90" t="n">
         <v>2.088</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1.047</v>
-      </c>
-      <c r="J90" t="n">
-        <v>2.255</v>
       </c>
     </row>
     <row r="91">
@@ -9669,22 +9708,22 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.007</v>
+        <v>2.2</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.731</v>
       </c>
       <c r="D91" t="n">
         <v>4.896</v>
       </c>
+      <c r="E91" t="n">
+        <v>3.007</v>
+      </c>
       <c r="G91" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J91" t="n">
         <v>2.183</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="92">
@@ -9694,25 +9733,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3.501</v>
+        <v>2.496</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.756</v>
       </c>
       <c r="D92" t="n">
         <v>4.65</v>
       </c>
+      <c r="E92" t="n">
+        <v>3.501</v>
+      </c>
       <c r="F92" t="n">
         <v>0.45</v>
       </c>
       <c r="G92" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="J92" t="n">
         <v>2.175</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="J92" t="n">
-        <v>2.496</v>
       </c>
     </row>
     <row r="93">
@@ -9722,25 +9761,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.682</v>
+        <v>2.361</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0.976</v>
       </c>
       <c r="D93" t="n">
         <v>4.605</v>
       </c>
+      <c r="E93" t="n">
+        <v>2.682</v>
+      </c>
       <c r="F93" t="n">
         <v>1.019</v>
       </c>
       <c r="G93" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="J93" t="n">
         <v>2.176</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="J93" t="n">
-        <v>2.361</v>
       </c>
     </row>
     <row r="94">
@@ -9750,25 +9789,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.883</v>
+        <v>2.018</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="D94" t="n">
         <v>4.977</v>
       </c>
+      <c r="E94" t="n">
+        <v>2.883</v>
+      </c>
       <c r="F94" t="n">
         <v>2.271</v>
       </c>
       <c r="G94" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="J94" t="n">
         <v>1.992</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2.018</v>
       </c>
     </row>
     <row r="95">
@@ -9778,25 +9817,25 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.943</v>
+        <v>2.03</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.924</v>
       </c>
       <c r="D95" t="n">
         <v>4.436</v>
       </c>
+      <c r="E95" t="n">
+        <v>2.943</v>
+      </c>
       <c r="F95" t="n">
         <v>2.405</v>
       </c>
       <c r="G95" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J95" t="n">
         <v>1.368</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="J95" t="n">
-        <v>2.03</v>
       </c>
     </row>
     <row r="96">
@@ -9806,25 +9845,25 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.169</v>
+        <v>2.269</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0.845</v>
       </c>
       <c r="D96" t="n">
         <v>3.043</v>
       </c>
+      <c r="E96" t="n">
+        <v>2.169</v>
+      </c>
       <c r="F96" t="n">
         <v>2.299</v>
       </c>
       <c r="G96" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="J96" t="n">
         <v>1.896</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="J96" t="n">
-        <v>2.269</v>
       </c>
     </row>
     <row r="97">
@@ -9834,25 +9873,25 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2.723</v>
+        <v>2.062</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.701</v>
       </c>
       <c r="D97" t="n">
         <v>3.985</v>
       </c>
+      <c r="E97" t="n">
+        <v>2.723</v>
+      </c>
       <c r="F97" t="n">
         <v>2.093</v>
       </c>
       <c r="G97" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="J97" t="n">
         <v>1.751</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.701</v>
-      </c>
-      <c r="J97" t="n">
-        <v>2.062</v>
       </c>
     </row>
     <row r="98">
@@ -9862,25 +9901,25 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.508</v>
+        <v>2.195</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.771</v>
       </c>
       <c r="D98" t="n">
         <v>4.166</v>
       </c>
+      <c r="E98" t="n">
+        <v>2.508</v>
+      </c>
       <c r="F98" t="n">
         <v>2.16</v>
       </c>
       <c r="G98" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="J98" t="n">
         <v>1.761</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0.771</v>
-      </c>
-      <c r="J98" t="n">
-        <v>2.195</v>
       </c>
     </row>
     <row r="99">
@@ -9890,25 +9929,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.834</v>
+        <v>2.157</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.635</v>
       </c>
       <c r="D99" t="n">
         <v>4.193</v>
       </c>
+      <c r="E99" t="n">
+        <v>2.834</v>
+      </c>
       <c r="F99" t="n">
         <v>1.963</v>
       </c>
       <c r="G99" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="J99" t="n">
         <v>1.793</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="J99" t="n">
-        <v>2.157</v>
       </c>
     </row>
     <row r="100">
@@ -9918,25 +9957,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.366</v>
+        <v>2.229</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0.375</v>
       </c>
       <c r="D100" t="n">
         <v>4.656</v>
       </c>
+      <c r="E100" t="n">
+        <v>3.366</v>
+      </c>
       <c r="F100" t="n">
         <v>2.249</v>
       </c>
       <c r="G100" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="J100" t="n">
         <v>2.094</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J100" t="n">
-        <v>2.229</v>
       </c>
     </row>
     <row r="101">
@@ -9946,25 +9985,25 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3.38</v>
+        <v>2.342</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.761</v>
       </c>
       <c r="D101" t="n">
         <v>4.739</v>
       </c>
+      <c r="E101" t="n">
+        <v>3.38</v>
+      </c>
       <c r="F101" t="n">
         <v>2.184</v>
       </c>
       <c r="G101" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J101" t="n">
         <v>2.022</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2.342</v>
       </c>
     </row>
     <row r="102">
@@ -9974,25 +10013,25 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3.175</v>
+        <v>2.257</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.824</v>
       </c>
       <c r="D102" t="n">
         <v>4.976</v>
       </c>
+      <c r="E102" t="n">
+        <v>3.175</v>
+      </c>
       <c r="F102" t="n">
         <v>2.504</v>
       </c>
       <c r="G102" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J102" t="n">
         <v>2.334</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2.257</v>
       </c>
     </row>
     <row r="103">
@@ -10002,25 +10041,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.573</v>
+        <v>2.148</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.749</v>
       </c>
       <c r="D103" t="n">
         <v>4.844</v>
       </c>
+      <c r="E103" t="n">
+        <v>3.573</v>
+      </c>
       <c r="F103" t="n">
         <v>1.855</v>
       </c>
       <c r="G103" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="J103" t="n">
         <v>2.178</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="J103" t="n">
-        <v>2.148</v>
       </c>
     </row>
     <row r="104">
@@ -10030,25 +10069,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3.334</v>
+        <v>2.096</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.898</v>
       </c>
       <c r="D104" t="n">
         <v>4.822</v>
       </c>
+      <c r="E104" t="n">
+        <v>3.334</v>
+      </c>
       <c r="F104" t="n">
         <v>1.559</v>
       </c>
       <c r="G104" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="J104" t="n">
         <v>2.229</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="J104" t="n">
-        <v>2.096</v>
       </c>
     </row>
     <row r="105">
@@ -10058,25 +10097,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3.31</v>
+        <v>2.154</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.886</v>
       </c>
       <c r="D105" t="n">
         <v>4.861</v>
       </c>
+      <c r="E105" t="n">
+        <v>3.31</v>
+      </c>
       <c r="F105" t="n">
         <v>0.923</v>
       </c>
       <c r="G105" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="J105" t="n">
         <v>2.072</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="J105" t="n">
-        <v>2.154</v>
       </c>
     </row>
     <row r="106">
@@ -10086,25 +10125,25 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.768</v>
+        <v>1.821</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.882</v>
       </c>
       <c r="D106" t="n">
         <v>4.35</v>
       </c>
+      <c r="E106" t="n">
+        <v>2.768</v>
+      </c>
       <c r="F106" t="n">
         <v>0.39</v>
       </c>
       <c r="G106" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="J106" t="n">
         <v>1.946</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="J106" t="n">
-        <v>1.821</v>
       </c>
     </row>
     <row r="107">
@@ -10114,25 +10153,25 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3.158</v>
+        <v>2.163</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.885</v>
       </c>
       <c r="D107" t="n">
         <v>4.624</v>
       </c>
+      <c r="E107" t="n">
+        <v>3.158</v>
+      </c>
       <c r="F107" t="n">
         <v>1.942</v>
       </c>
       <c r="G107" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="J107" t="n">
         <v>1.528</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2.163</v>
       </c>
     </row>
     <row r="108">
@@ -10142,25 +10181,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.038</v>
+        <v>2.346</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.695</v>
       </c>
       <c r="D108" t="n">
         <v>3.944</v>
       </c>
+      <c r="E108" t="n">
+        <v>3.038</v>
+      </c>
       <c r="F108" t="n">
         <v>2.36</v>
       </c>
       <c r="G108" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="J108" t="n">
         <v>1.849</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2.346</v>
       </c>
     </row>
     <row r="109">
@@ -10170,25 +10209,25 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2.762</v>
+        <v>2.018</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.745</v>
       </c>
       <c r="D109" t="n">
         <v>4.213</v>
       </c>
+      <c r="E109" t="n">
+        <v>2.762</v>
+      </c>
       <c r="F109" t="n">
         <v>0.871</v>
       </c>
       <c r="G109" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="J109" t="n">
         <v>1.815</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="J109" t="n">
-        <v>2.018</v>
       </c>
     </row>
     <row r="110">
@@ -10198,25 +10237,25 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.298</v>
+        <v>2.234</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.6870000000000001</v>
       </c>
       <c r="D110" t="n">
         <v>4.164</v>
       </c>
+      <c r="E110" t="n">
+        <v>2.298</v>
+      </c>
       <c r="F110" t="n">
         <v>2.212</v>
       </c>
       <c r="G110" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="J110" t="n">
         <v>1.829</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="J110" t="n">
-        <v>2.234</v>
       </c>
     </row>
     <row r="111">
@@ -10226,25 +10265,25 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2.537</v>
+        <v>2.349</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0.639</v>
       </c>
       <c r="D111" t="n">
         <v>4.401</v>
       </c>
+      <c r="E111" t="n">
+        <v>2.537</v>
+      </c>
       <c r="F111" t="n">
         <v>2.288</v>
       </c>
       <c r="G111" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="J111" t="n">
         <v>1.885</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="J111" t="n">
-        <v>2.349</v>
       </c>
     </row>
     <row r="112">
@@ -10254,25 +10293,25 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.711</v>
+        <v>2.348</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.448</v>
       </c>
       <c r="D112" t="n">
         <v>4.533</v>
       </c>
+      <c r="E112" t="n">
+        <v>2.711</v>
+      </c>
       <c r="F112" t="n">
         <v>2.427</v>
       </c>
       <c r="G112" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="J112" t="n">
         <v>1.887</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="J112" t="n">
-        <v>2.348</v>
       </c>
     </row>
     <row r="113">
@@ -10282,25 +10321,25 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.838</v>
+        <v>2.38</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.831</v>
       </c>
       <c r="D113" t="n">
         <v>4.609</v>
       </c>
+      <c r="E113" t="n">
+        <v>2.838</v>
+      </c>
       <c r="F113" t="n">
         <v>2.021</v>
       </c>
       <c r="G113" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="J113" t="n">
         <v>2.183</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0.831</v>
-      </c>
-      <c r="J113" t="n">
-        <v>2.38</v>
       </c>
     </row>
     <row r="114">
@@ -10310,28 +10349,28 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.751</v>
+        <v>2.365</v>
       </c>
       <c r="C114" t="n">
-        <v>0.257</v>
+        <v>0.785</v>
       </c>
       <c r="D114" t="n">
         <v>4.677</v>
       </c>
+      <c r="E114" t="n">
+        <v>2.751</v>
+      </c>
       <c r="F114" t="n">
         <v>2.395</v>
       </c>
       <c r="G114" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="J114" t="n">
         <v>2.291</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="J114" t="n">
-        <v>2.365</v>
       </c>
     </row>
     <row r="115">
@@ -10341,28 +10380,28 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2.754</v>
+        <v>2.185</v>
       </c>
       <c r="C115" t="n">
-        <v>1.511</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
         <v>4.853</v>
       </c>
+      <c r="E115" t="n">
+        <v>2.754</v>
+      </c>
       <c r="F115" t="n">
         <v>1.969</v>
       </c>
       <c r="G115" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="H115" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="J115" t="n">
         <v>2.193</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" t="n">
-        <v>2.185</v>
       </c>
     </row>
     <row r="116">
@@ -10372,28 +10411,28 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2.85</v>
+        <v>2.582</v>
       </c>
       <c r="C116" t="n">
-        <v>2.461</v>
+        <v>0.868</v>
       </c>
       <c r="D116" t="n">
         <v>4.574</v>
       </c>
+      <c r="E116" t="n">
+        <v>2.85</v>
+      </c>
       <c r="F116" t="n">
         <v>2.404</v>
       </c>
       <c r="G116" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="J116" t="n">
         <v>2.343</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="J116" t="n">
-        <v>2.582</v>
       </c>
     </row>
     <row r="117">
@@ -10403,28 +10442,28 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3.251</v>
+        <v>2.341</v>
       </c>
       <c r="C117" t="n">
-        <v>3.473</v>
+        <v>0.882</v>
       </c>
       <c r="D117" t="n">
         <v>4.818</v>
       </c>
+      <c r="E117" t="n">
+        <v>3.251</v>
+      </c>
       <c r="F117" t="n">
         <v>2.257</v>
       </c>
       <c r="G117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3.473</v>
+      </c>
+      <c r="J117" t="n">
         <v>2.107</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="J117" t="n">
-        <v>2.341</v>
       </c>
     </row>
     <row r="118">
@@ -10434,28 +10473,28 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3.347</v>
+        <v>2.317</v>
       </c>
       <c r="C118" t="n">
-        <v>3.886</v>
+        <v>0.758</v>
       </c>
       <c r="D118" t="n">
         <v>4.631</v>
       </c>
+      <c r="E118" t="n">
+        <v>3.347</v>
+      </c>
       <c r="F118" t="n">
         <v>2.502</v>
       </c>
       <c r="G118" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3.886</v>
+      </c>
+      <c r="J118" t="n">
         <v>2.195</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0.758</v>
-      </c>
-      <c r="J118" t="n">
-        <v>2.317</v>
       </c>
     </row>
     <row r="119">
@@ -10465,28 +10504,28 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3.3</v>
+        <v>2.196</v>
       </c>
       <c r="C119" t="n">
-        <v>4.23</v>
+        <v>0.847</v>
       </c>
       <c r="D119" t="n">
         <v>4.39</v>
       </c>
+      <c r="E119" t="n">
+        <v>3.3</v>
+      </c>
       <c r="F119" t="n">
         <v>2.3</v>
       </c>
       <c r="G119" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="J119" t="n">
         <v>1.442</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="J119" t="n">
-        <v>2.196</v>
       </c>
     </row>
     <row r="120">
@@ -10496,28 +10535,28 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3.13</v>
+        <v>2.259</v>
       </c>
       <c r="C120" t="n">
-        <v>4.893</v>
+        <v>0.899</v>
       </c>
       <c r="D120" t="n">
         <v>3.084</v>
       </c>
+      <c r="E120" t="n">
+        <v>3.13</v>
+      </c>
       <c r="F120" t="n">
         <v>2.442</v>
       </c>
       <c r="G120" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="H120" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="J120" t="n">
         <v>1.677</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="J120" t="n">
-        <v>2.259</v>
       </c>
     </row>
     <row r="121">
@@ -10527,28 +10566,28 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3.043</v>
+        <v>2.388</v>
       </c>
       <c r="C121" t="n">
-        <v>4.92</v>
+        <v>0.75</v>
       </c>
       <c r="D121" t="n">
         <v>4.035</v>
       </c>
+      <c r="E121" t="n">
+        <v>3.043</v>
+      </c>
       <c r="F121" t="n">
         <v>2.109</v>
       </c>
       <c r="G121" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="H121" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="J121" t="n">
         <v>1.91</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J121" t="n">
-        <v>2.388</v>
       </c>
     </row>
     <row r="122">
@@ -10558,28 +10597,28 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3.144</v>
+        <v>2.334</v>
       </c>
       <c r="C122" t="n">
-        <v>5.517</v>
+        <v>0.798</v>
       </c>
       <c r="D122" t="n">
         <v>4.155</v>
       </c>
+      <c r="E122" t="n">
+        <v>3.144</v>
+      </c>
       <c r="F122" t="n">
         <v>2.134</v>
       </c>
       <c r="G122" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="H122" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="J122" t="n">
         <v>1.936</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0.798</v>
-      </c>
-      <c r="J122" t="n">
-        <v>2.334</v>
       </c>
     </row>
     <row r="123">
@@ -10589,28 +10628,28 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3.132</v>
+        <v>2.546</v>
       </c>
       <c r="C123" t="n">
-        <v>5.711</v>
+        <v>0.541</v>
       </c>
       <c r="D123" t="n">
         <v>4.221</v>
       </c>
+      <c r="E123" t="n">
+        <v>3.132</v>
+      </c>
       <c r="F123" t="n">
         <v>2.179</v>
       </c>
       <c r="G123" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5.711</v>
+      </c>
+      <c r="J123" t="n">
         <v>2.012</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="J123" t="n">
-        <v>2.546</v>
       </c>
     </row>
     <row r="124">
@@ -10620,28 +10659,28 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2.748</v>
+        <v>2.684</v>
       </c>
       <c r="C124" t="n">
-        <v>7.541</v>
+        <v>0.546</v>
       </c>
       <c r="D124" t="n">
         <v>4.489</v>
       </c>
+      <c r="E124" t="n">
+        <v>2.748</v>
+      </c>
       <c r="F124" t="n">
         <v>2.459</v>
       </c>
       <c r="G124" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="H124" t="n">
+        <v>7.541</v>
+      </c>
+      <c r="J124" t="n">
         <v>1.997</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.546</v>
-      </c>
-      <c r="J124" t="n">
-        <v>2.684</v>
       </c>
     </row>
     <row r="125">
@@ -10651,28 +10690,28 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3.385</v>
+        <v>3.095</v>
       </c>
       <c r="C125" t="n">
-        <v>7.614</v>
+        <v>0.723</v>
       </c>
       <c r="D125" t="n">
         <v>4.926</v>
       </c>
+      <c r="E125" t="n">
+        <v>3.385</v>
+      </c>
       <c r="F125" t="n">
         <v>2.326</v>
       </c>
       <c r="G125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H125" t="n">
+        <v>7.614</v>
+      </c>
+      <c r="J125" t="n">
         <v>2.14</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="J125" t="n">
-        <v>3.095</v>
       </c>
     </row>
     <row r="126">
@@ -10682,28 +10721,28 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3.581</v>
+        <v>3.189</v>
       </c>
       <c r="C126" t="n">
-        <v>7.775</v>
+        <v>1.007</v>
       </c>
       <c r="D126" t="n">
         <v>4.725</v>
       </c>
+      <c r="E126" t="n">
+        <v>3.581</v>
+      </c>
       <c r="F126" t="n">
         <v>2.438</v>
       </c>
       <c r="G126" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="J126" t="n">
         <v>2.463</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="I126" t="n">
-        <v>1.007</v>
-      </c>
-      <c r="J126" t="n">
-        <v>3.189</v>
       </c>
     </row>
     <row r="127">
@@ -10713,28 +10752,28 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3.321</v>
+        <v>2.945</v>
       </c>
       <c r="C127" t="n">
-        <v>8.148</v>
+        <v>0.838</v>
       </c>
       <c r="D127" t="n">
         <v>4.649</v>
       </c>
+      <c r="E127" t="n">
+        <v>3.321</v>
+      </c>
       <c r="F127" t="n">
         <v>2.232</v>
       </c>
       <c r="G127" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="H127" t="n">
+        <v>8.148</v>
+      </c>
+      <c r="J127" t="n">
         <v>2.253</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0.838</v>
-      </c>
-      <c r="J127" t="n">
-        <v>2.945</v>
       </c>
     </row>
     <row r="128">
@@ -10744,28 +10783,28 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3.384</v>
+        <v>3.317</v>
       </c>
       <c r="C128" t="n">
-        <v>7.524</v>
+        <v>0.719</v>
       </c>
       <c r="D128" t="n">
         <v>4.756</v>
       </c>
+      <c r="E128" t="n">
+        <v>3.384</v>
+      </c>
       <c r="F128" t="n">
         <v>2.441</v>
       </c>
       <c r="G128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="H128" t="n">
+        <v>7.524</v>
+      </c>
+      <c r="J128" t="n">
         <v>2.269</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="J128" t="n">
-        <v>3.317</v>
       </c>
     </row>
     <row r="129">
@@ -10775,28 +10814,28 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3.317</v>
+        <v>3.361</v>
       </c>
       <c r="C129" t="n">
-        <v>8.334</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="D129" t="n">
         <v>4.918</v>
       </c>
+      <c r="E129" t="n">
+        <v>3.317</v>
+      </c>
       <c r="F129" t="n">
         <v>2.455</v>
       </c>
       <c r="G129" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H129" t="n">
+        <v>8.334</v>
+      </c>
+      <c r="J129" t="n">
         <v>2.284</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="J129" t="n">
-        <v>3.361</v>
       </c>
     </row>
     <row r="130">
@@ -10806,31 +10845,31 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3.437</v>
+        <v>3.154</v>
       </c>
       <c r="C130" t="n">
-        <v>7.89</v>
+        <v>0.762</v>
       </c>
       <c r="D130" t="n">
         <v>4.745</v>
       </c>
       <c r="E130" t="n">
-        <v>0.263</v>
+        <v>3.437</v>
       </c>
       <c r="F130" t="n">
         <v>2.511</v>
       </c>
       <c r="G130" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="H130" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="J130" t="n">
         <v>2.113</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="J130" t="n">
-        <v>3.154</v>
       </c>
     </row>
     <row r="131">
@@ -10840,31 +10879,31 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3.066</v>
+        <v>3.122</v>
       </c>
       <c r="C131" t="n">
-        <v>7.846</v>
+        <v>0.883</v>
       </c>
       <c r="D131" t="n">
         <v>4.314</v>
       </c>
       <c r="E131" t="n">
-        <v>0.244</v>
+        <v>3.066</v>
       </c>
       <c r="F131" t="n">
         <v>1.993</v>
       </c>
       <c r="G131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H131" t="n">
+        <v>7.846</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="J131" t="n">
         <v>1.546</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.883</v>
-      </c>
-      <c r="J131" t="n">
-        <v>3.122</v>
       </c>
     </row>
     <row r="132">
@@ -10874,31 +10913,31 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3.177</v>
+        <v>3.271</v>
       </c>
       <c r="C132" t="n">
-        <v>7.62</v>
+        <v>0.765</v>
       </c>
       <c r="D132" t="n">
         <v>4.436</v>
       </c>
       <c r="E132" t="n">
-        <v>0.251</v>
+        <v>3.177</v>
       </c>
       <c r="F132" t="n">
         <v>2.16</v>
       </c>
       <c r="G132" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="J132" t="n">
         <v>2.187</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="J132" t="n">
-        <v>3.271</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -8098,19 +8098,19 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Golden Pass</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Corpus Christi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Cove Point</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>Calcasieu Pass</t>
@@ -8118,27 +8118,27 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Freeport</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Plaquemines</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Golden Pass</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Cameron</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="J3" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="J4" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8188,7 +8188,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8198,7 +8198,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="J7" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="I8" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="I9" t="n">
         <v>0.373</v>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="I10" t="n">
         <v>0.364</v>
       </c>
     </row>
@@ -8238,7 +8238,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="I11" t="n">
         <v>0.346</v>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="I12" t="n">
         <v>0.597</v>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="I13" t="n">
         <v>0.552</v>
       </c>
     </row>
@@ -8268,7 +8268,7 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="I14" t="n">
         <v>0.966</v>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="I15" t="n">
         <v>0.607</v>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="I16" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="I17" t="n">
         <v>1.196</v>
       </c>
     </row>
@@ -8308,7 +8308,7 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="I18" t="n">
         <v>1.468</v>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="I19" t="n">
         <v>1.801</v>
       </c>
     </row>
@@ -8328,7 +8328,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="I20" t="n">
         <v>2.024</v>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="I21" t="n">
         <v>1.528</v>
       </c>
     </row>
@@ -8348,7 +8348,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="I22" t="n">
         <v>1.838</v>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="I23" t="n">
         <v>2.136</v>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="I24" t="n">
         <v>1.905</v>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="I25" t="n">
         <v>1.883</v>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="I26" t="n">
         <v>1.597</v>
       </c>
     </row>
@@ -8398,7 +8398,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="I27" t="n">
         <v>1.986</v>
       </c>
     </row>
@@ -8408,7 +8408,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="I28" t="n">
         <v>2.832</v>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="I29" t="n">
         <v>2.906</v>
       </c>
     </row>
@@ -8428,7 +8428,7 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="I30" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="I31" t="n">
         <v>2.543</v>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="I32" t="n">
         <v>2.864</v>
       </c>
     </row>
@@ -8458,10 +8458,10 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>0.105</v>
       </c>
-      <c r="D33" t="n">
+      <c r="I33" t="n">
         <v>3.11</v>
       </c>
     </row>
@@ -8471,10 +8471,10 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>0.325</v>
       </c>
-      <c r="D34" t="n">
+      <c r="I34" t="n">
         <v>2.788</v>
       </c>
     </row>
@@ -8484,10 +8484,10 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="D35" t="n">
         <v>0.77</v>
       </c>
-      <c r="D35" t="n">
+      <c r="I35" t="n">
         <v>2.562</v>
       </c>
     </row>
@@ -8497,10 +8497,10 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>0.457</v>
       </c>
-      <c r="D36" t="n">
+      <c r="I36" t="n">
         <v>2.213</v>
       </c>
     </row>
@@ -8510,10 +8510,10 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>0.675</v>
       </c>
-      <c r="D37" t="n">
+      <c r="I37" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -8523,10 +8523,10 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>0.676</v>
       </c>
-      <c r="D38" t="n">
+      <c r="I38" t="n">
         <v>2.54</v>
       </c>
     </row>
@@ -8536,10 +8536,10 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>0.449</v>
       </c>
-      <c r="D39" t="n">
+      <c r="I39" t="n">
         <v>2.507</v>
       </c>
     </row>
@@ -8549,10 +8549,10 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>0.226</v>
       </c>
-      <c r="D40" t="n">
+      <c r="I40" t="n">
         <v>2.932</v>
       </c>
     </row>
@@ -8562,10 +8562,10 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>0.701</v>
       </c>
-      <c r="D41" t="n">
+      <c r="I41" t="n">
         <v>3.202</v>
       </c>
     </row>
@@ -8575,13 +8575,13 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="C42" t="n">
         <v>0.241</v>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>0.711</v>
       </c>
-      <c r="D42" t="n">
+      <c r="I42" t="n">
         <v>3.36</v>
       </c>
     </row>
@@ -8591,13 +8591,13 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="C43" t="n">
         <v>0.378</v>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>0.714</v>
       </c>
-      <c r="D43" t="n">
+      <c r="I43" t="n">
         <v>3.367</v>
       </c>
     </row>
@@ -8607,13 +8607,13 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="C44" t="n">
         <v>0.145</v>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>0.915</v>
       </c>
-      <c r="D44" t="n">
+      <c r="I44" t="n">
         <v>2.942</v>
       </c>
     </row>
@@ -8623,13 +8623,13 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="C45" t="n">
         <v>0.706</v>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>0.599</v>
       </c>
-      <c r="D45" t="n">
+      <c r="I45" t="n">
         <v>3.291</v>
       </c>
     </row>
@@ -8639,13 +8639,13 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="C46" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>0.867</v>
       </c>
-      <c r="D46" t="n">
+      <c r="I46" t="n">
         <v>3.054</v>
       </c>
     </row>
@@ -8655,17 +8655,17 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="C47" t="n">
         <v>0.614</v>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>0.602</v>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="I47" t="n">
         <v>3.762</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.113</v>
       </c>
     </row>
     <row r="48">
@@ -8674,17 +8674,17 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="C48" t="n">
         <v>0.765</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>0.731</v>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="I48" t="n">
         <v>3.551</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.106</v>
       </c>
     </row>
     <row r="49">
@@ -8693,17 +8693,17 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="C49" t="n">
         <v>1.184</v>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>0.731</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="I49" t="n">
         <v>3.347</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.248</v>
       </c>
     </row>
     <row r="50">
@@ -8712,17 +8712,17 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="C50" t="n">
         <v>1.084</v>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>0.699</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="I50" t="n">
         <v>2.696</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.388</v>
       </c>
     </row>
     <row r="51">
@@ -8731,20 +8731,20 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="C51" t="n">
         <v>1.26</v>
       </c>
-      <c r="C51" t="n">
+      <c r="D51" t="n">
         <v>0.5</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I51" t="n">
         <v>3.461</v>
       </c>
-      <c r="F51" t="n">
+      <c r="J51" t="n">
         <v>0.235</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.364</v>
       </c>
     </row>
     <row r="52">
@@ -8753,20 +8753,20 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="C52" t="n">
         <v>1.488</v>
       </c>
-      <c r="C52" t="n">
+      <c r="D52" t="n">
         <v>0.244</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I52" t="n">
         <v>3.775</v>
       </c>
-      <c r="F52" t="n">
+      <c r="J52" t="n">
         <v>0.365</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.379</v>
       </c>
     </row>
     <row r="53">
@@ -8775,20 +8775,20 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="C53" t="n">
         <v>1.357</v>
       </c>
-      <c r="C53" t="n">
+      <c r="D53" t="n">
         <v>0.852</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I53" t="n">
         <v>3.852</v>
       </c>
-      <c r="F53" t="n">
+      <c r="J53" t="n">
         <v>0.353</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.507</v>
       </c>
     </row>
     <row r="54">
@@ -8797,23 +8797,23 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="C54" t="n">
         <v>1.461</v>
       </c>
-      <c r="C54" t="n">
+      <c r="D54" t="n">
         <v>0.729</v>
       </c>
-      <c r="D54" t="n">
-        <v>3.813</v>
-      </c>
       <c r="F54" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="G54" t="n">
         <v>0.229</v>
       </c>
+      <c r="I54" t="n">
+        <v>3.813</v>
+      </c>
       <c r="J54" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="55">
@@ -8822,23 +8822,23 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="C55" t="n">
         <v>1.426</v>
       </c>
-      <c r="C55" t="n">
+      <c r="D55" t="n">
         <v>0.722</v>
       </c>
-      <c r="D55" t="n">
-        <v>4.018</v>
-      </c>
       <c r="F55" t="n">
-        <v>1.456</v>
+        <v>0.98</v>
       </c>
       <c r="G55" t="n">
         <v>0.428</v>
       </c>
+      <c r="I55" t="n">
+        <v>4.018</v>
+      </c>
       <c r="J55" t="n">
-        <v>0.98</v>
+        <v>1.456</v>
       </c>
     </row>
     <row r="56">
@@ -8847,20 +8847,20 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="C56" t="n">
         <v>1.55</v>
       </c>
-      <c r="C56" t="n">
+      <c r="D56" t="n">
         <v>0.758</v>
       </c>
-      <c r="D56" t="n">
+      <c r="F56" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="I56" t="n">
         <v>3.684</v>
       </c>
-      <c r="F56" t="n">
+      <c r="J56" t="n">
         <v>1.446</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.044</v>
       </c>
     </row>
     <row r="57">
@@ -8869,20 +8869,20 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="C57" t="n">
         <v>1.462</v>
       </c>
-      <c r="C57" t="n">
+      <c r="D57" t="n">
         <v>0.831</v>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="I57" t="n">
         <v>3.447</v>
       </c>
-      <c r="F57" t="n">
+      <c r="J57" t="n">
         <v>1.635</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.208</v>
       </c>
     </row>
     <row r="58">
@@ -8891,20 +8891,20 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="C58" t="n">
         <v>1.245</v>
       </c>
-      <c r="C58" t="n">
+      <c r="D58" t="n">
         <v>0.608</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="I58" t="n">
         <v>3.333</v>
       </c>
-      <c r="F58" t="n">
+      <c r="J58" t="n">
         <v>1.158</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.301</v>
       </c>
     </row>
     <row r="59">
@@ -8913,20 +8913,20 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="C59" t="n">
         <v>0.831</v>
       </c>
-      <c r="C59" t="n">
+      <c r="D59" t="n">
         <v>0.708</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="I59" t="n">
         <v>2.73</v>
       </c>
-      <c r="F59" t="n">
+      <c r="J59" t="n">
         <v>1.008</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.135</v>
       </c>
     </row>
     <row r="60">
@@ -8935,20 +8935,20 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="C60" t="n">
         <v>0.307</v>
       </c>
-      <c r="C60" t="n">
+      <c r="D60" t="n">
         <v>0.763</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.978</v>
       </c>
-      <c r="F60" t="n">
+      <c r="J60" t="n">
         <v>0.543</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1.366</v>
       </c>
     </row>
     <row r="61">
@@ -8957,20 +8957,20 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="C61" t="n">
         <v>0.373</v>
       </c>
-      <c r="C61" t="n">
+      <c r="D61" t="n">
         <v>0.711</v>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="I61" t="n">
         <v>1.063</v>
       </c>
-      <c r="F61" t="n">
+      <c r="J61" t="n">
         <v>0.132</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.099</v>
       </c>
     </row>
     <row r="62">
@@ -8979,23 +8979,23 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="C62" t="n">
         <v>0.601</v>
       </c>
-      <c r="C62" t="n">
+      <c r="D62" t="n">
         <v>0.596</v>
       </c>
-      <c r="D62" t="n">
-        <v>1.031</v>
-      </c>
       <c r="F62" t="n">
-        <v>0.399</v>
+        <v>1.117</v>
       </c>
       <c r="G62" t="n">
         <v>0.26</v>
       </c>
+      <c r="I62" t="n">
+        <v>1.031</v>
+      </c>
       <c r="J62" t="n">
-        <v>1.117</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="63">
@@ -9004,21 +9004,21 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="C63" t="n">
         <v>1.363</v>
       </c>
-      <c r="C63" t="n">
+      <c r="D63" t="n">
         <v>0.621</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.241</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.127</v>
       </c>
       <c r="G63" t="n">
         <v>0.271</v>
       </c>
+      <c r="I63" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1.127</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9026,23 +9026,23 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="C64" t="n">
         <v>1.551</v>
       </c>
-      <c r="C64" t="n">
+      <c r="D64" t="n">
         <v>0.373</v>
       </c>
-      <c r="D64" t="n">
-        <v>3.106</v>
-      </c>
       <c r="F64" t="n">
-        <v>1.892</v>
+        <v>0.662</v>
       </c>
       <c r="G64" t="n">
         <v>0.52</v>
       </c>
+      <c r="I64" t="n">
+        <v>3.106</v>
+      </c>
       <c r="J64" t="n">
-        <v>0.662</v>
+        <v>1.892</v>
       </c>
     </row>
     <row r="65">
@@ -9051,23 +9051,23 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="C65" t="n">
         <v>1.633</v>
       </c>
-      <c r="C65" t="n">
+      <c r="D65" t="n">
         <v>0.852</v>
       </c>
-      <c r="D65" t="n">
-        <v>3.684</v>
-      </c>
       <c r="F65" t="n">
-        <v>1.953</v>
+        <v>1.838</v>
       </c>
       <c r="G65" t="n">
         <v>0.469</v>
       </c>
+      <c r="I65" t="n">
+        <v>3.684</v>
+      </c>
       <c r="J65" t="n">
-        <v>1.838</v>
+        <v>1.953</v>
       </c>
     </row>
     <row r="66">
@@ -9076,23 +9076,23 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="C66" t="n">
         <v>1.821</v>
       </c>
-      <c r="C66" t="n">
+      <c r="D66" t="n">
         <v>0.718</v>
       </c>
-      <c r="D66" t="n">
-        <v>3.845</v>
-      </c>
       <c r="F66" t="n">
-        <v>2.057</v>
+        <v>1.939</v>
       </c>
       <c r="G66" t="n">
         <v>0.628</v>
       </c>
+      <c r="I66" t="n">
+        <v>3.845</v>
+      </c>
       <c r="J66" t="n">
-        <v>1.939</v>
+        <v>2.057</v>
       </c>
     </row>
     <row r="67">
@@ -9101,20 +9101,20 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="C67" t="n">
         <v>2.012</v>
       </c>
-      <c r="C67" t="n">
+      <c r="D67" t="n">
         <v>0.718</v>
       </c>
-      <c r="D67" t="n">
+      <c r="F67" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="I67" t="n">
         <v>3.905</v>
       </c>
-      <c r="F67" t="n">
+      <c r="J67" t="n">
         <v>2.148</v>
-      </c>
-      <c r="J67" t="n">
-        <v>1.943</v>
       </c>
     </row>
     <row r="68">
@@ -9123,23 +9123,23 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="C68" t="n">
         <v>1.297</v>
       </c>
-      <c r="C68" t="n">
+      <c r="D68" t="n">
         <v>0.671</v>
       </c>
-      <c r="D68" t="n">
-        <v>3.263</v>
-      </c>
       <c r="F68" t="n">
-        <v>1.186</v>
+        <v>1.42</v>
       </c>
       <c r="G68" t="n">
         <v>0.541</v>
       </c>
+      <c r="I68" t="n">
+        <v>3.263</v>
+      </c>
       <c r="J68" t="n">
-        <v>1.42</v>
+        <v>1.186</v>
       </c>
     </row>
     <row r="69">
@@ -9148,23 +9148,23 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="C69" t="n">
         <v>2.201</v>
       </c>
-      <c r="C69" t="n">
+      <c r="D69" t="n">
         <v>0.845</v>
       </c>
-      <c r="D69" t="n">
-        <v>4.013</v>
-      </c>
       <c r="F69" t="n">
-        <v>2.237</v>
+        <v>1.755</v>
       </c>
       <c r="G69" t="n">
         <v>0.468</v>
       </c>
+      <c r="I69" t="n">
+        <v>4.013</v>
+      </c>
       <c r="J69" t="n">
-        <v>1.755</v>
+        <v>2.237</v>
       </c>
     </row>
     <row r="70">
@@ -9173,23 +9173,23 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="C70" t="n">
         <v>2.175</v>
       </c>
-      <c r="C70" t="n">
+      <c r="D70" t="n">
         <v>0.622</v>
       </c>
-      <c r="D70" t="n">
-        <v>3.955</v>
-      </c>
       <c r="F70" t="n">
-        <v>2.203</v>
+        <v>1.848</v>
       </c>
       <c r="G70" t="n">
         <v>0.68</v>
       </c>
+      <c r="I70" t="n">
+        <v>3.955</v>
+      </c>
       <c r="J70" t="n">
-        <v>1.848</v>
+        <v>2.203</v>
       </c>
     </row>
     <row r="71">
@@ -9198,23 +9198,23 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="C71" t="n">
         <v>2.066</v>
       </c>
-      <c r="C71" t="n">
+      <c r="D71" t="n">
         <v>0.787</v>
       </c>
-      <c r="D71" t="n">
-        <v>3.805</v>
-      </c>
       <c r="F71" t="n">
-        <v>2.223</v>
+        <v>1.855</v>
       </c>
       <c r="G71" t="n">
         <v>0.662</v>
       </c>
+      <c r="I71" t="n">
+        <v>3.805</v>
+      </c>
       <c r="J71" t="n">
-        <v>1.855</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="72">
@@ -9223,23 +9223,23 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="C72" t="n">
         <v>2.236</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="D72" t="n">
-        <v>3.118</v>
-      </c>
       <c r="F72" t="n">
-        <v>2.127</v>
+        <v>1.418</v>
       </c>
       <c r="G72" t="n">
         <v>0.524</v>
       </c>
+      <c r="I72" t="n">
+        <v>3.118</v>
+      </c>
       <c r="J72" t="n">
-        <v>1.418</v>
+        <v>2.127</v>
       </c>
     </row>
     <row r="73">
@@ -9248,23 +9248,23 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="C73" t="n">
         <v>2.126</v>
       </c>
-      <c r="C73" t="n">
+      <c r="D73" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D73" t="n">
-        <v>3.402</v>
-      </c>
       <c r="F73" t="n">
-        <v>2.141</v>
+        <v>1.82</v>
       </c>
       <c r="G73" t="n">
         <v>0.493</v>
       </c>
+      <c r="I73" t="n">
+        <v>3.402</v>
+      </c>
       <c r="J73" t="n">
-        <v>1.82</v>
+        <v>2.141</v>
       </c>
     </row>
     <row r="74">
@@ -9273,23 +9273,23 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="C74" t="n">
         <v>2.171</v>
       </c>
-      <c r="C74" t="n">
+      <c r="D74" t="n">
         <v>0.785</v>
       </c>
-      <c r="D74" t="n">
-        <v>3.492</v>
-      </c>
       <c r="F74" t="n">
-        <v>2.307</v>
+        <v>1.467</v>
       </c>
       <c r="G74" t="n">
         <v>0.507</v>
       </c>
+      <c r="I74" t="n">
+        <v>3.492</v>
+      </c>
       <c r="J74" t="n">
-        <v>1.467</v>
+        <v>2.307</v>
       </c>
     </row>
     <row r="75">
@@ -9298,23 +9298,23 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="C75" t="n">
         <v>2.34</v>
       </c>
-      <c r="C75" t="n">
+      <c r="D75" t="n">
         <v>0.499</v>
       </c>
-      <c r="D75" t="n">
-        <v>3.619</v>
-      </c>
       <c r="F75" t="n">
-        <v>1.764</v>
+        <v>1.919</v>
       </c>
       <c r="G75" t="n">
         <v>0.396</v>
       </c>
+      <c r="I75" t="n">
+        <v>3.619</v>
+      </c>
       <c r="J75" t="n">
-        <v>1.919</v>
+        <v>1.764</v>
       </c>
     </row>
     <row r="76">
@@ -9323,23 +9323,23 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="C76" t="n">
         <v>2.28</v>
       </c>
-      <c r="C76" t="n">
+      <c r="D76" t="n">
         <v>0.348</v>
       </c>
-      <c r="D76" t="n">
-        <v>3.561</v>
-      </c>
       <c r="F76" t="n">
-        <v>2.111</v>
+        <v>1.852</v>
       </c>
       <c r="G76" t="n">
         <v>0.639</v>
       </c>
+      <c r="I76" t="n">
+        <v>3.561</v>
+      </c>
       <c r="J76" t="n">
-        <v>1.852</v>
+        <v>2.111</v>
       </c>
     </row>
     <row r="77">
@@ -9348,23 +9348,23 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="C77" t="n">
         <v>2.307</v>
       </c>
-      <c r="C77" t="n">
+      <c r="D77" t="n">
         <v>0.797</v>
       </c>
-      <c r="D77" t="n">
-        <v>4.097</v>
-      </c>
       <c r="F77" t="n">
-        <v>1.597</v>
+        <v>2.113</v>
       </c>
       <c r="G77" t="n">
         <v>0.423</v>
       </c>
+      <c r="I77" t="n">
+        <v>4.097</v>
+      </c>
       <c r="J77" t="n">
-        <v>2.113</v>
+        <v>1.597</v>
       </c>
     </row>
     <row r="78">
@@ -9373,23 +9373,23 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="C78" t="n">
         <v>2.249</v>
       </c>
-      <c r="C78" t="n">
+      <c r="D78" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D78" t="n">
-        <v>4.186</v>
-      </c>
       <c r="F78" t="n">
-        <v>2.365</v>
+        <v>2.158</v>
       </c>
       <c r="G78" t="n">
         <v>0.723</v>
       </c>
+      <c r="I78" t="n">
+        <v>4.186</v>
+      </c>
       <c r="J78" t="n">
-        <v>2.158</v>
+        <v>2.365</v>
       </c>
     </row>
     <row r="79">
@@ -9398,23 +9398,23 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="C79" t="n">
         <v>2.347</v>
       </c>
-      <c r="C79" t="n">
+      <c r="D79" t="n">
         <v>0.886</v>
       </c>
-      <c r="D79" t="n">
-        <v>4.576</v>
-      </c>
       <c r="F79" t="n">
-        <v>2.248</v>
+        <v>2.151</v>
       </c>
       <c r="G79" t="n">
         <v>0.441</v>
       </c>
+      <c r="I79" t="n">
+        <v>4.576</v>
+      </c>
       <c r="J79" t="n">
-        <v>2.151</v>
+        <v>2.248</v>
       </c>
     </row>
     <row r="80">
@@ -9423,23 +9423,23 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="C80" t="n">
         <v>2.654</v>
       </c>
-      <c r="C80" t="n">
+      <c r="D80" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="D80" t="n">
-        <v>4.318</v>
-      </c>
       <c r="F80" t="n">
-        <v>2.043</v>
+        <v>2.116</v>
       </c>
       <c r="G80" t="n">
         <v>0.749</v>
       </c>
+      <c r="I80" t="n">
+        <v>4.318</v>
+      </c>
       <c r="J80" t="n">
-        <v>2.116</v>
+        <v>2.043</v>
       </c>
     </row>
     <row r="81">
@@ -9448,26 +9448,26 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="C81" t="n">
         <v>2.115</v>
       </c>
-      <c r="C81" t="n">
+      <c r="D81" t="n">
         <v>0.754</v>
-      </c>
-      <c r="D81" t="n">
-        <v>4.588</v>
       </c>
       <c r="E81" t="n">
         <v>1.279</v>
       </c>
       <c r="F81" t="n">
-        <v>2.268</v>
+        <v>2.123</v>
       </c>
       <c r="G81" t="n">
         <v>0.609</v>
       </c>
+      <c r="I81" t="n">
+        <v>4.588</v>
+      </c>
       <c r="J81" t="n">
-        <v>2.123</v>
+        <v>2.268</v>
       </c>
     </row>
     <row r="82">
@@ -9476,26 +9476,26 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="C82" t="n">
         <v>2.117</v>
       </c>
-      <c r="C82" t="n">
+      <c r="D82" t="n">
         <v>0.794</v>
-      </c>
-      <c r="D82" t="n">
-        <v>4.526</v>
       </c>
       <c r="E82" t="n">
         <v>1.289</v>
       </c>
       <c r="F82" t="n">
-        <v>1.427</v>
+        <v>2.095</v>
       </c>
       <c r="G82" t="n">
         <v>0.784</v>
       </c>
+      <c r="I82" t="n">
+        <v>4.526</v>
+      </c>
       <c r="J82" t="n">
-        <v>2.095</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="83">
@@ -9504,26 +9504,26 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="C83" t="n">
         <v>2.179</v>
       </c>
-      <c r="C83" t="n">
+      <c r="D83" t="n">
         <v>0.781</v>
-      </c>
-      <c r="D83" t="n">
-        <v>4.597</v>
       </c>
       <c r="E83" t="n">
         <v>1.774</v>
       </c>
       <c r="F83" t="n">
-        <v>2.232</v>
+        <v>1.426</v>
       </c>
       <c r="G83" t="n">
         <v>0.488</v>
       </c>
+      <c r="I83" t="n">
+        <v>4.597</v>
+      </c>
       <c r="J83" t="n">
-        <v>1.426</v>
+        <v>2.232</v>
       </c>
     </row>
     <row r="84">
@@ -9532,26 +9532,26 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="C84" t="n">
         <v>2.315</v>
       </c>
-      <c r="C84" t="n">
+      <c r="D84" t="n">
         <v>0.716</v>
-      </c>
-      <c r="D84" t="n">
-        <v>3.84</v>
       </c>
       <c r="E84" t="n">
         <v>2.334</v>
       </c>
       <c r="F84" t="n">
-        <v>0.629</v>
+        <v>1.86</v>
       </c>
       <c r="G84" t="n">
         <v>0.777</v>
       </c>
+      <c r="I84" t="n">
+        <v>3.84</v>
+      </c>
       <c r="J84" t="n">
-        <v>1.86</v>
+        <v>0.629</v>
       </c>
     </row>
     <row r="85">
@@ -9560,23 +9560,23 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="C85" t="n">
         <v>2.218</v>
       </c>
-      <c r="C85" t="n">
+      <c r="D85" t="n">
         <v>0.851</v>
-      </c>
-      <c r="D85" t="n">
-        <v>4.168</v>
       </c>
       <c r="E85" t="n">
         <v>2.33</v>
       </c>
+      <c r="F85" t="n">
+        <v>1.832</v>
+      </c>
       <c r="G85" t="n">
         <v>0.64</v>
       </c>
-      <c r="J85" t="n">
-        <v>1.832</v>
+      <c r="I85" t="n">
+        <v>4.168</v>
       </c>
     </row>
     <row r="86">
@@ -9585,23 +9585,23 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="C86" t="n">
         <v>2.23</v>
       </c>
-      <c r="C86" t="n">
+      <c r="D86" t="n">
         <v>0.753</v>
-      </c>
-      <c r="D86" t="n">
-        <v>4.173</v>
       </c>
       <c r="E86" t="n">
         <v>2.375</v>
       </c>
+      <c r="F86" t="n">
+        <v>1.88</v>
+      </c>
       <c r="G86" t="n">
         <v>0.647</v>
       </c>
-      <c r="J86" t="n">
-        <v>1.88</v>
+      <c r="I86" t="n">
+        <v>4.173</v>
       </c>
     </row>
     <row r="87">
@@ -9610,23 +9610,23 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="C87" t="n">
         <v>2.173</v>
       </c>
-      <c r="C87" t="n">
+      <c r="D87" t="n">
         <v>0.6840000000000001</v>
-      </c>
-      <c r="D87" t="n">
-        <v>4.201</v>
       </c>
       <c r="E87" t="n">
         <v>2.796</v>
       </c>
+      <c r="F87" t="n">
+        <v>1.912</v>
+      </c>
       <c r="G87" t="n">
         <v>0.708</v>
       </c>
-      <c r="J87" t="n">
-        <v>1.912</v>
+      <c r="I87" t="n">
+        <v>4.201</v>
       </c>
     </row>
     <row r="88">
@@ -9635,20 +9635,20 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="C88" t="n">
         <v>2.348</v>
-      </c>
-      <c r="D88" t="n">
-        <v>4.586</v>
       </c>
       <c r="E88" t="n">
         <v>3.186</v>
       </c>
+      <c r="F88" t="n">
+        <v>2.094</v>
+      </c>
       <c r="G88" t="n">
         <v>0.519</v>
       </c>
-      <c r="J88" t="n">
-        <v>2.094</v>
+      <c r="I88" t="n">
+        <v>4.586</v>
       </c>
     </row>
     <row r="89">
@@ -9657,23 +9657,23 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="C89" t="n">
         <v>2.072</v>
       </c>
-      <c r="C89" t="n">
+      <c r="D89" t="n">
         <v>0.742</v>
-      </c>
-      <c r="D89" t="n">
-        <v>4.363</v>
       </c>
       <c r="E89" t="n">
         <v>2.625</v>
       </c>
+      <c r="F89" t="n">
+        <v>2.107</v>
+      </c>
       <c r="G89" t="n">
         <v>0.773</v>
       </c>
-      <c r="J89" t="n">
-        <v>2.107</v>
+      <c r="I89" t="n">
+        <v>4.363</v>
       </c>
     </row>
     <row r="90">
@@ -9682,23 +9682,23 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="C90" t="n">
         <v>2.255</v>
       </c>
-      <c r="C90" t="n">
+      <c r="D90" t="n">
         <v>1.047</v>
-      </c>
-      <c r="D90" t="n">
-        <v>4.893</v>
       </c>
       <c r="E90" t="n">
         <v>2.655</v>
       </c>
+      <c r="F90" t="n">
+        <v>2.088</v>
+      </c>
       <c r="G90" t="n">
         <v>0.66</v>
       </c>
-      <c r="J90" t="n">
-        <v>2.088</v>
+      <c r="I90" t="n">
+        <v>4.893</v>
       </c>
     </row>
     <row r="91">
@@ -9707,23 +9707,23 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="C91" t="n">
         <v>2.2</v>
       </c>
-      <c r="C91" t="n">
+      <c r="D91" t="n">
         <v>0.731</v>
-      </c>
-      <c r="D91" t="n">
-        <v>4.896</v>
       </c>
       <c r="E91" t="n">
         <v>3.007</v>
       </c>
+      <c r="F91" t="n">
+        <v>2.183</v>
+      </c>
       <c r="G91" t="n">
         <v>0.663</v>
       </c>
-      <c r="J91" t="n">
-        <v>2.183</v>
+      <c r="I91" t="n">
+        <v>4.896</v>
       </c>
     </row>
     <row r="92">
@@ -9732,26 +9732,26 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="C92" t="n">
         <v>2.496</v>
       </c>
-      <c r="C92" t="n">
+      <c r="D92" t="n">
         <v>0.756</v>
-      </c>
-      <c r="D92" t="n">
-        <v>4.65</v>
       </c>
       <c r="E92" t="n">
         <v>3.501</v>
       </c>
       <c r="F92" t="n">
-        <v>0.45</v>
+        <v>2.175</v>
       </c>
       <c r="G92" t="n">
         <v>0.823</v>
       </c>
+      <c r="I92" t="n">
+        <v>4.65</v>
+      </c>
       <c r="J92" t="n">
-        <v>2.175</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="93">
@@ -9760,26 +9760,26 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="C93" t="n">
         <v>2.361</v>
       </c>
-      <c r="C93" t="n">
+      <c r="D93" t="n">
         <v>0.976</v>
-      </c>
-      <c r="D93" t="n">
-        <v>4.605</v>
       </c>
       <c r="E93" t="n">
         <v>2.682</v>
       </c>
       <c r="F93" t="n">
-        <v>1.019</v>
+        <v>2.176</v>
       </c>
       <c r="G93" t="n">
         <v>0.803</v>
       </c>
+      <c r="I93" t="n">
+        <v>4.605</v>
+      </c>
       <c r="J93" t="n">
-        <v>2.176</v>
+        <v>1.019</v>
       </c>
     </row>
     <row r="94">
@@ -9788,26 +9788,26 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="C94" t="n">
         <v>2.018</v>
       </c>
-      <c r="C94" t="n">
+      <c r="D94" t="n">
         <v>0.6840000000000001</v>
-      </c>
-      <c r="D94" t="n">
-        <v>4.977</v>
       </c>
       <c r="E94" t="n">
         <v>2.883</v>
       </c>
       <c r="F94" t="n">
-        <v>2.271</v>
+        <v>1.992</v>
       </c>
       <c r="G94" t="n">
         <v>0.532</v>
       </c>
+      <c r="I94" t="n">
+        <v>4.977</v>
+      </c>
       <c r="J94" t="n">
-        <v>1.992</v>
+        <v>2.271</v>
       </c>
     </row>
     <row r="95">
@@ -9816,26 +9816,26 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="C95" t="n">
         <v>2.03</v>
       </c>
-      <c r="C95" t="n">
+      <c r="D95" t="n">
         <v>0.924</v>
-      </c>
-      <c r="D95" t="n">
-        <v>4.436</v>
       </c>
       <c r="E95" t="n">
         <v>2.943</v>
       </c>
       <c r="F95" t="n">
-        <v>2.405</v>
+        <v>1.368</v>
       </c>
       <c r="G95" t="n">
         <v>0.519</v>
       </c>
+      <c r="I95" t="n">
+        <v>4.436</v>
+      </c>
       <c r="J95" t="n">
-        <v>1.368</v>
+        <v>2.405</v>
       </c>
     </row>
     <row r="96">
@@ -9844,26 +9844,26 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="C96" t="n">
         <v>2.269</v>
       </c>
-      <c r="C96" t="n">
+      <c r="D96" t="n">
         <v>0.845</v>
-      </c>
-      <c r="D96" t="n">
-        <v>3.043</v>
       </c>
       <c r="E96" t="n">
         <v>2.169</v>
       </c>
       <c r="F96" t="n">
-        <v>2.299</v>
+        <v>1.896</v>
       </c>
       <c r="G96" t="n">
         <v>0.944</v>
       </c>
+      <c r="I96" t="n">
+        <v>3.043</v>
+      </c>
       <c r="J96" t="n">
-        <v>1.896</v>
+        <v>2.299</v>
       </c>
     </row>
     <row r="97">
@@ -9872,26 +9872,26 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="C97" t="n">
         <v>2.062</v>
       </c>
-      <c r="C97" t="n">
+      <c r="D97" t="n">
         <v>0.701</v>
-      </c>
-      <c r="D97" t="n">
-        <v>3.985</v>
       </c>
       <c r="E97" t="n">
         <v>2.723</v>
       </c>
       <c r="F97" t="n">
-        <v>2.093</v>
+        <v>1.751</v>
       </c>
       <c r="G97" t="n">
         <v>0.651</v>
       </c>
+      <c r="I97" t="n">
+        <v>3.985</v>
+      </c>
       <c r="J97" t="n">
-        <v>1.751</v>
+        <v>2.093</v>
       </c>
     </row>
     <row r="98">
@@ -9900,26 +9900,26 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="C98" t="n">
         <v>2.195</v>
       </c>
-      <c r="C98" t="n">
+      <c r="D98" t="n">
         <v>0.771</v>
-      </c>
-      <c r="D98" t="n">
-        <v>4.166</v>
       </c>
       <c r="E98" t="n">
         <v>2.508</v>
       </c>
       <c r="F98" t="n">
-        <v>2.16</v>
+        <v>1.761</v>
       </c>
       <c r="G98" t="n">
         <v>0.207</v>
       </c>
+      <c r="I98" t="n">
+        <v>4.166</v>
+      </c>
       <c r="J98" t="n">
-        <v>1.761</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="99">
@@ -9928,26 +9928,26 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="C99" t="n">
         <v>2.157</v>
       </c>
-      <c r="C99" t="n">
+      <c r="D99" t="n">
         <v>0.635</v>
-      </c>
-      <c r="D99" t="n">
-        <v>4.193</v>
       </c>
       <c r="E99" t="n">
         <v>2.834</v>
       </c>
       <c r="F99" t="n">
-        <v>1.963</v>
+        <v>1.793</v>
       </c>
       <c r="G99" t="n">
         <v>0.863</v>
       </c>
+      <c r="I99" t="n">
+        <v>4.193</v>
+      </c>
       <c r="J99" t="n">
-        <v>1.793</v>
+        <v>1.963</v>
       </c>
     </row>
     <row r="100">
@@ -9956,26 +9956,26 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="C100" t="n">
         <v>2.229</v>
       </c>
-      <c r="C100" t="n">
+      <c r="D100" t="n">
         <v>0.375</v>
-      </c>
-      <c r="D100" t="n">
-        <v>4.656</v>
       </c>
       <c r="E100" t="n">
         <v>3.366</v>
       </c>
       <c r="F100" t="n">
-        <v>2.249</v>
+        <v>2.094</v>
       </c>
       <c r="G100" t="n">
         <v>0.456</v>
       </c>
+      <c r="I100" t="n">
+        <v>4.656</v>
+      </c>
       <c r="J100" t="n">
-        <v>2.094</v>
+        <v>2.249</v>
       </c>
     </row>
     <row r="101">
@@ -9984,26 +9984,26 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="C101" t="n">
         <v>2.342</v>
       </c>
-      <c r="C101" t="n">
+      <c r="D101" t="n">
         <v>0.761</v>
-      </c>
-      <c r="D101" t="n">
-        <v>4.739</v>
       </c>
       <c r="E101" t="n">
         <v>3.38</v>
       </c>
       <c r="F101" t="n">
-        <v>2.184</v>
+        <v>2.022</v>
       </c>
       <c r="G101" t="n">
         <v>0.588</v>
       </c>
+      <c r="I101" t="n">
+        <v>4.739</v>
+      </c>
       <c r="J101" t="n">
-        <v>2.022</v>
+        <v>2.184</v>
       </c>
     </row>
     <row r="102">
@@ -10012,26 +10012,26 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="C102" t="n">
         <v>2.257</v>
       </c>
-      <c r="C102" t="n">
+      <c r="D102" t="n">
         <v>0.824</v>
-      </c>
-      <c r="D102" t="n">
-        <v>4.976</v>
       </c>
       <c r="E102" t="n">
         <v>3.175</v>
       </c>
       <c r="F102" t="n">
-        <v>2.504</v>
+        <v>2.334</v>
       </c>
       <c r="G102" t="n">
         <v>0.77</v>
       </c>
+      <c r="I102" t="n">
+        <v>4.976</v>
+      </c>
       <c r="J102" t="n">
-        <v>2.334</v>
+        <v>2.504</v>
       </c>
     </row>
     <row r="103">
@@ -10040,26 +10040,26 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="C103" t="n">
         <v>2.148</v>
       </c>
-      <c r="C103" t="n">
+      <c r="D103" t="n">
         <v>0.749</v>
-      </c>
-      <c r="D103" t="n">
-        <v>4.844</v>
       </c>
       <c r="E103" t="n">
         <v>3.573</v>
       </c>
       <c r="F103" t="n">
-        <v>1.855</v>
+        <v>2.178</v>
       </c>
       <c r="G103" t="n">
         <v>0.739</v>
       </c>
+      <c r="I103" t="n">
+        <v>4.844</v>
+      </c>
       <c r="J103" t="n">
-        <v>2.178</v>
+        <v>1.855</v>
       </c>
     </row>
     <row r="104">
@@ -10068,26 +10068,26 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="C104" t="n">
         <v>2.096</v>
       </c>
-      <c r="C104" t="n">
+      <c r="D104" t="n">
         <v>0.898</v>
-      </c>
-      <c r="D104" t="n">
-        <v>4.822</v>
       </c>
       <c r="E104" t="n">
         <v>3.334</v>
       </c>
       <c r="F104" t="n">
-        <v>1.559</v>
+        <v>2.229</v>
       </c>
       <c r="G104" t="n">
         <v>0.527</v>
       </c>
+      <c r="I104" t="n">
+        <v>4.822</v>
+      </c>
       <c r="J104" t="n">
-        <v>2.229</v>
+        <v>1.559</v>
       </c>
     </row>
     <row r="105">
@@ -10096,26 +10096,26 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="C105" t="n">
         <v>2.154</v>
       </c>
-      <c r="C105" t="n">
+      <c r="D105" t="n">
         <v>0.886</v>
-      </c>
-      <c r="D105" t="n">
-        <v>4.861</v>
       </c>
       <c r="E105" t="n">
         <v>3.31</v>
       </c>
       <c r="F105" t="n">
-        <v>0.923</v>
+        <v>2.072</v>
       </c>
       <c r="G105" t="n">
         <v>0.903</v>
       </c>
+      <c r="I105" t="n">
+        <v>4.861</v>
+      </c>
       <c r="J105" t="n">
-        <v>2.072</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="106">
@@ -10124,26 +10124,26 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="C106" t="n">
         <v>1.821</v>
       </c>
-      <c r="C106" t="n">
+      <c r="D106" t="n">
         <v>0.882</v>
-      </c>
-      <c r="D106" t="n">
-        <v>4.35</v>
       </c>
       <c r="E106" t="n">
         <v>2.768</v>
       </c>
       <c r="F106" t="n">
-        <v>0.39</v>
+        <v>1.946</v>
       </c>
       <c r="G106" t="n">
         <v>0.522</v>
       </c>
+      <c r="I106" t="n">
+        <v>4.35</v>
+      </c>
       <c r="J106" t="n">
-        <v>1.946</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="107">
@@ -10152,26 +10152,26 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="C107" t="n">
         <v>2.163</v>
       </c>
-      <c r="C107" t="n">
+      <c r="D107" t="n">
         <v>0.885</v>
-      </c>
-      <c r="D107" t="n">
-        <v>4.624</v>
       </c>
       <c r="E107" t="n">
         <v>3.158</v>
       </c>
       <c r="F107" t="n">
-        <v>1.942</v>
+        <v>1.528</v>
       </c>
       <c r="G107" t="n">
         <v>0.411</v>
       </c>
+      <c r="I107" t="n">
+        <v>4.624</v>
+      </c>
       <c r="J107" t="n">
-        <v>1.528</v>
+        <v>1.942</v>
       </c>
     </row>
     <row r="108">
@@ -10180,26 +10180,26 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="C108" t="n">
         <v>2.346</v>
       </c>
-      <c r="C108" t="n">
+      <c r="D108" t="n">
         <v>0.695</v>
-      </c>
-      <c r="D108" t="n">
-        <v>3.944</v>
       </c>
       <c r="E108" t="n">
         <v>3.038</v>
       </c>
       <c r="F108" t="n">
-        <v>2.36</v>
+        <v>1.849</v>
       </c>
       <c r="G108" t="n">
         <v>0.466</v>
       </c>
+      <c r="I108" t="n">
+        <v>3.944</v>
+      </c>
       <c r="J108" t="n">
-        <v>1.849</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="109">
@@ -10208,26 +10208,26 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="C109" t="n">
         <v>2.018</v>
       </c>
-      <c r="C109" t="n">
+      <c r="D109" t="n">
         <v>0.745</v>
-      </c>
-      <c r="D109" t="n">
-        <v>4.213</v>
       </c>
       <c r="E109" t="n">
         <v>2.762</v>
       </c>
       <c r="F109" t="n">
-        <v>0.871</v>
+        <v>1.815</v>
       </c>
       <c r="G109" t="n">
         <v>0.6850000000000001</v>
       </c>
+      <c r="I109" t="n">
+        <v>4.213</v>
+      </c>
       <c r="J109" t="n">
-        <v>1.815</v>
+        <v>0.871</v>
       </c>
     </row>
     <row r="110">
@@ -10236,26 +10236,26 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="C110" t="n">
         <v>2.234</v>
       </c>
-      <c r="C110" t="n">
+      <c r="D110" t="n">
         <v>0.6870000000000001</v>
-      </c>
-      <c r="D110" t="n">
-        <v>4.164</v>
       </c>
       <c r="E110" t="n">
         <v>2.298</v>
       </c>
       <c r="F110" t="n">
-        <v>2.212</v>
+        <v>1.829</v>
       </c>
       <c r="G110" t="n">
         <v>0.957</v>
       </c>
+      <c r="I110" t="n">
+        <v>4.164</v>
+      </c>
       <c r="J110" t="n">
-        <v>1.829</v>
+        <v>2.212</v>
       </c>
     </row>
     <row r="111">
@@ -10264,26 +10264,26 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="C111" t="n">
         <v>2.349</v>
       </c>
-      <c r="C111" t="n">
+      <c r="D111" t="n">
         <v>0.639</v>
-      </c>
-      <c r="D111" t="n">
-        <v>4.401</v>
       </c>
       <c r="E111" t="n">
         <v>2.537</v>
       </c>
       <c r="F111" t="n">
-        <v>2.288</v>
+        <v>1.885</v>
       </c>
       <c r="G111" t="n">
         <v>0.499</v>
       </c>
+      <c r="I111" t="n">
+        <v>4.401</v>
+      </c>
       <c r="J111" t="n">
-        <v>1.885</v>
+        <v>2.288</v>
       </c>
     </row>
     <row r="112">
@@ -10292,26 +10292,26 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="C112" t="n">
         <v>2.348</v>
       </c>
-      <c r="C112" t="n">
+      <c r="D112" t="n">
         <v>0.448</v>
-      </c>
-      <c r="D112" t="n">
-        <v>4.533</v>
       </c>
       <c r="E112" t="n">
         <v>2.711</v>
       </c>
       <c r="F112" t="n">
-        <v>2.427</v>
+        <v>1.887</v>
       </c>
       <c r="G112" t="n">
         <v>0.447</v>
       </c>
+      <c r="I112" t="n">
+        <v>4.533</v>
+      </c>
       <c r="J112" t="n">
-        <v>1.887</v>
+        <v>2.427</v>
       </c>
     </row>
     <row r="113">
@@ -10320,26 +10320,26 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="C113" t="n">
         <v>2.38</v>
       </c>
-      <c r="C113" t="n">
+      <c r="D113" t="n">
         <v>0.831</v>
-      </c>
-      <c r="D113" t="n">
-        <v>4.609</v>
       </c>
       <c r="E113" t="n">
         <v>2.838</v>
       </c>
       <c r="F113" t="n">
-        <v>2.021</v>
+        <v>2.183</v>
       </c>
       <c r="G113" t="n">
         <v>0.381</v>
       </c>
+      <c r="I113" t="n">
+        <v>4.609</v>
+      </c>
       <c r="J113" t="n">
-        <v>2.183</v>
+        <v>2.021</v>
       </c>
     </row>
     <row r="114">
@@ -10348,20 +10348,17 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="C114" t="n">
         <v>2.365</v>
       </c>
-      <c r="C114" t="n">
+      <c r="D114" t="n">
         <v>0.785</v>
-      </c>
-      <c r="D114" t="n">
-        <v>4.677</v>
       </c>
       <c r="E114" t="n">
         <v>2.751</v>
       </c>
       <c r="F114" t="n">
-        <v>2.395</v>
+        <v>2.291</v>
       </c>
       <c r="G114" t="n">
         <v>0.6870000000000001</v>
@@ -10369,8 +10366,11 @@
       <c r="H114" t="n">
         <v>0.257</v>
       </c>
+      <c r="I114" t="n">
+        <v>4.677</v>
+      </c>
       <c r="J114" t="n">
-        <v>2.291</v>
+        <v>2.395</v>
       </c>
     </row>
     <row r="115">
@@ -10379,20 +10379,17 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="C115" t="n">
         <v>2.185</v>
       </c>
-      <c r="C115" t="n">
+      <c r="D115" t="n">
         <v>1</v>
-      </c>
-      <c r="D115" t="n">
-        <v>4.853</v>
       </c>
       <c r="E115" t="n">
         <v>2.754</v>
       </c>
       <c r="F115" t="n">
-        <v>1.969</v>
+        <v>2.193</v>
       </c>
       <c r="G115" t="n">
         <v>0.427</v>
@@ -10400,8 +10397,11 @@
       <c r="H115" t="n">
         <v>1.511</v>
       </c>
+      <c r="I115" t="n">
+        <v>4.853</v>
+      </c>
       <c r="J115" t="n">
-        <v>2.193</v>
+        <v>1.969</v>
       </c>
     </row>
     <row r="116">
@@ -10410,20 +10410,17 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="C116" t="n">
         <v>2.582</v>
       </c>
-      <c r="C116" t="n">
+      <c r="D116" t="n">
         <v>0.868</v>
-      </c>
-      <c r="D116" t="n">
-        <v>4.574</v>
       </c>
       <c r="E116" t="n">
         <v>2.85</v>
       </c>
       <c r="F116" t="n">
-        <v>2.404</v>
+        <v>2.343</v>
       </c>
       <c r="G116" t="n">
         <v>0.761</v>
@@ -10431,8 +10428,11 @@
       <c r="H116" t="n">
         <v>2.461</v>
       </c>
+      <c r="I116" t="n">
+        <v>4.574</v>
+      </c>
       <c r="J116" t="n">
-        <v>2.343</v>
+        <v>2.404</v>
       </c>
     </row>
     <row r="117">
@@ -10441,20 +10441,17 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="C117" t="n">
         <v>2.341</v>
       </c>
-      <c r="C117" t="n">
+      <c r="D117" t="n">
         <v>0.882</v>
-      </c>
-      <c r="D117" t="n">
-        <v>4.818</v>
       </c>
       <c r="E117" t="n">
         <v>3.251</v>
       </c>
       <c r="F117" t="n">
-        <v>2.257</v>
+        <v>2.107</v>
       </c>
       <c r="G117" t="n">
         <v>0.2</v>
@@ -10462,8 +10459,11 @@
       <c r="H117" t="n">
         <v>3.473</v>
       </c>
+      <c r="I117" t="n">
+        <v>4.818</v>
+      </c>
       <c r="J117" t="n">
-        <v>2.107</v>
+        <v>2.257</v>
       </c>
     </row>
     <row r="118">
@@ -10472,20 +10472,17 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="C118" t="n">
         <v>2.317</v>
       </c>
-      <c r="C118" t="n">
+      <c r="D118" t="n">
         <v>0.758</v>
-      </c>
-      <c r="D118" t="n">
-        <v>4.631</v>
       </c>
       <c r="E118" t="n">
         <v>3.347</v>
       </c>
       <c r="F118" t="n">
-        <v>2.502</v>
+        <v>2.195</v>
       </c>
       <c r="G118" t="n">
         <v>0.525</v>
@@ -10493,8 +10490,11 @@
       <c r="H118" t="n">
         <v>3.886</v>
       </c>
+      <c r="I118" t="n">
+        <v>4.631</v>
+      </c>
       <c r="J118" t="n">
-        <v>2.195</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="119">
@@ -10503,20 +10503,17 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="C119" t="n">
         <v>2.196</v>
       </c>
-      <c r="C119" t="n">
+      <c r="D119" t="n">
         <v>0.847</v>
-      </c>
-      <c r="D119" t="n">
-        <v>4.39</v>
       </c>
       <c r="E119" t="n">
         <v>3.3</v>
       </c>
       <c r="F119" t="n">
-        <v>2.3</v>
+        <v>1.442</v>
       </c>
       <c r="G119" t="n">
         <v>0.61</v>
@@ -10524,8 +10521,11 @@
       <c r="H119" t="n">
         <v>4.23</v>
       </c>
+      <c r="I119" t="n">
+        <v>4.39</v>
+      </c>
       <c r="J119" t="n">
-        <v>1.442</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="120">
@@ -10534,20 +10534,17 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="C120" t="n">
         <v>2.259</v>
       </c>
-      <c r="C120" t="n">
+      <c r="D120" t="n">
         <v>0.899</v>
-      </c>
-      <c r="D120" t="n">
-        <v>3.084</v>
       </c>
       <c r="E120" t="n">
         <v>3.13</v>
       </c>
       <c r="F120" t="n">
-        <v>2.442</v>
+        <v>1.677</v>
       </c>
       <c r="G120" t="n">
         <v>0.754</v>
@@ -10555,8 +10552,11 @@
       <c r="H120" t="n">
         <v>4.893</v>
       </c>
+      <c r="I120" t="n">
+        <v>3.084</v>
+      </c>
       <c r="J120" t="n">
-        <v>1.677</v>
+        <v>2.442</v>
       </c>
     </row>
     <row r="121">
@@ -10565,20 +10565,17 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="C121" t="n">
         <v>2.388</v>
       </c>
-      <c r="C121" t="n">
+      <c r="D121" t="n">
         <v>0.75</v>
-      </c>
-      <c r="D121" t="n">
-        <v>4.035</v>
       </c>
       <c r="E121" t="n">
         <v>3.043</v>
       </c>
       <c r="F121" t="n">
-        <v>2.109</v>
+        <v>1.91</v>
       </c>
       <c r="G121" t="n">
         <v>0.255</v>
@@ -10586,8 +10583,11 @@
       <c r="H121" t="n">
         <v>4.92</v>
       </c>
+      <c r="I121" t="n">
+        <v>4.035</v>
+      </c>
       <c r="J121" t="n">
-        <v>1.91</v>
+        <v>2.109</v>
       </c>
     </row>
     <row r="122">
@@ -10596,20 +10596,17 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="C122" t="n">
         <v>2.334</v>
       </c>
-      <c r="C122" t="n">
+      <c r="D122" t="n">
         <v>0.798</v>
-      </c>
-      <c r="D122" t="n">
-        <v>4.155</v>
       </c>
       <c r="E122" t="n">
         <v>3.144</v>
       </c>
       <c r="F122" t="n">
-        <v>2.134</v>
+        <v>1.936</v>
       </c>
       <c r="G122" t="n">
         <v>0.469</v>
@@ -10617,8 +10614,11 @@
       <c r="H122" t="n">
         <v>5.517</v>
       </c>
+      <c r="I122" t="n">
+        <v>4.155</v>
+      </c>
       <c r="J122" t="n">
-        <v>1.936</v>
+        <v>2.134</v>
       </c>
     </row>
     <row r="123">
@@ -10627,20 +10627,17 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="C123" t="n">
         <v>2.546</v>
       </c>
-      <c r="C123" t="n">
+      <c r="D123" t="n">
         <v>0.541</v>
-      </c>
-      <c r="D123" t="n">
-        <v>4.221</v>
       </c>
       <c r="E123" t="n">
         <v>3.132</v>
       </c>
       <c r="F123" t="n">
-        <v>2.179</v>
+        <v>2.012</v>
       </c>
       <c r="G123" t="n">
         <v>0.726</v>
@@ -10648,8 +10645,11 @@
       <c r="H123" t="n">
         <v>5.711</v>
       </c>
+      <c r="I123" t="n">
+        <v>4.221</v>
+      </c>
       <c r="J123" t="n">
-        <v>2.012</v>
+        <v>2.179</v>
       </c>
     </row>
     <row r="124">
@@ -10658,20 +10658,17 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="C124" t="n">
         <v>2.684</v>
       </c>
-      <c r="C124" t="n">
+      <c r="D124" t="n">
         <v>0.546</v>
-      </c>
-      <c r="D124" t="n">
-        <v>4.489</v>
       </c>
       <c r="E124" t="n">
         <v>2.748</v>
       </c>
       <c r="F124" t="n">
-        <v>2.459</v>
+        <v>1.997</v>
       </c>
       <c r="G124" t="n">
         <v>0.496</v>
@@ -10679,8 +10676,11 @@
       <c r="H124" t="n">
         <v>7.541</v>
       </c>
+      <c r="I124" t="n">
+        <v>4.489</v>
+      </c>
       <c r="J124" t="n">
-        <v>1.997</v>
+        <v>2.459</v>
       </c>
     </row>
     <row r="125">
@@ -10689,20 +10689,17 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="C125" t="n">
         <v>3.095</v>
       </c>
-      <c r="C125" t="n">
+      <c r="D125" t="n">
         <v>0.723</v>
-      </c>
-      <c r="D125" t="n">
-        <v>4.926</v>
       </c>
       <c r="E125" t="n">
         <v>3.385</v>
       </c>
       <c r="F125" t="n">
-        <v>2.326</v>
+        <v>2.14</v>
       </c>
       <c r="G125" t="n">
         <v>0.531</v>
@@ -10710,8 +10707,11 @@
       <c r="H125" t="n">
         <v>7.614</v>
       </c>
+      <c r="I125" t="n">
+        <v>4.926</v>
+      </c>
       <c r="J125" t="n">
-        <v>2.14</v>
+        <v>2.326</v>
       </c>
     </row>
     <row r="126">
@@ -10720,20 +10720,17 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="C126" t="n">
         <v>3.189</v>
       </c>
-      <c r="C126" t="n">
+      <c r="D126" t="n">
         <v>1.007</v>
-      </c>
-      <c r="D126" t="n">
-        <v>4.725</v>
       </c>
       <c r="E126" t="n">
         <v>3.581</v>
       </c>
       <c r="F126" t="n">
-        <v>2.438</v>
+        <v>2.463</v>
       </c>
       <c r="G126" t="n">
         <v>0.805</v>
@@ -10741,8 +10738,11 @@
       <c r="H126" t="n">
         <v>7.775</v>
       </c>
+      <c r="I126" t="n">
+        <v>4.725</v>
+      </c>
       <c r="J126" t="n">
-        <v>2.463</v>
+        <v>2.438</v>
       </c>
     </row>
     <row r="127">
@@ -10751,20 +10751,17 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="C127" t="n">
         <v>2.945</v>
       </c>
-      <c r="C127" t="n">
+      <c r="D127" t="n">
         <v>0.838</v>
-      </c>
-      <c r="D127" t="n">
-        <v>4.649</v>
       </c>
       <c r="E127" t="n">
         <v>3.321</v>
       </c>
       <c r="F127" t="n">
-        <v>2.232</v>
+        <v>2.253</v>
       </c>
       <c r="G127" t="n">
         <v>0.361</v>
@@ -10772,8 +10769,11 @@
       <c r="H127" t="n">
         <v>8.148</v>
       </c>
+      <c r="I127" t="n">
+        <v>4.649</v>
+      </c>
       <c r="J127" t="n">
-        <v>2.253</v>
+        <v>2.232</v>
       </c>
     </row>
     <row r="128">
@@ -10782,20 +10782,17 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="C128" t="n">
         <v>3.317</v>
       </c>
-      <c r="C128" t="n">
+      <c r="D128" t="n">
         <v>0.719</v>
-      </c>
-      <c r="D128" t="n">
-        <v>4.756</v>
       </c>
       <c r="E128" t="n">
         <v>3.384</v>
       </c>
       <c r="F128" t="n">
-        <v>2.441</v>
+        <v>2.269</v>
       </c>
       <c r="G128" t="n">
         <v>0.294</v>
@@ -10803,8 +10800,11 @@
       <c r="H128" t="n">
         <v>7.524</v>
       </c>
+      <c r="I128" t="n">
+        <v>4.756</v>
+      </c>
       <c r="J128" t="n">
-        <v>2.269</v>
+        <v>2.441</v>
       </c>
     </row>
     <row r="129">
@@ -10813,20 +10813,17 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="C129" t="n">
         <v>3.361</v>
       </c>
-      <c r="C129" t="n">
+      <c r="D129" t="n">
         <v>0.9379999999999999</v>
-      </c>
-      <c r="D129" t="n">
-        <v>4.918</v>
       </c>
       <c r="E129" t="n">
         <v>3.317</v>
       </c>
       <c r="F129" t="n">
-        <v>2.455</v>
+        <v>2.284</v>
       </c>
       <c r="G129" t="n">
         <v>0.518</v>
@@ -10834,8 +10831,11 @@
       <c r="H129" t="n">
         <v>8.334</v>
       </c>
+      <c r="I129" t="n">
+        <v>4.918</v>
+      </c>
       <c r="J129" t="n">
-        <v>2.284</v>
+        <v>2.455</v>
       </c>
     </row>
     <row r="130">
@@ -10845,19 +10845,19 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="C130" t="n">
         <v>3.154</v>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>0.762</v>
-      </c>
-      <c r="D130" t="n">
-        <v>4.745</v>
       </c>
       <c r="E130" t="n">
         <v>3.437</v>
       </c>
       <c r="F130" t="n">
-        <v>2.511</v>
+        <v>2.113</v>
       </c>
       <c r="G130" t="n">
         <v>0.555</v>
@@ -10866,10 +10866,10 @@
         <v>7.89</v>
       </c>
       <c r="I130" t="n">
-        <v>0.263</v>
+        <v>4.745</v>
       </c>
       <c r="J130" t="n">
-        <v>2.113</v>
+        <v>2.511</v>
       </c>
     </row>
     <row r="131">
@@ -10879,19 +10879,19 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="C131" t="n">
         <v>3.122</v>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>0.883</v>
-      </c>
-      <c r="D131" t="n">
-        <v>4.314</v>
       </c>
       <c r="E131" t="n">
         <v>3.066</v>
       </c>
       <c r="F131" t="n">
-        <v>1.993</v>
+        <v>1.546</v>
       </c>
       <c r="G131" t="n">
         <v>0.331</v>
@@ -10900,10 +10900,10 @@
         <v>7.846</v>
       </c>
       <c r="I131" t="n">
-        <v>0.244</v>
+        <v>4.314</v>
       </c>
       <c r="J131" t="n">
-        <v>1.546</v>
+        <v>1.993</v>
       </c>
     </row>
     <row r="132">
@@ -10913,19 +10913,19 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="C132" t="n">
         <v>3.271</v>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>0.765</v>
-      </c>
-      <c r="D132" t="n">
-        <v>4.436</v>
       </c>
       <c r="E132" t="n">
         <v>3.177</v>
       </c>
       <c r="F132" t="n">
-        <v>2.16</v>
+        <v>2.187</v>
       </c>
       <c r="G132" t="n">
         <v>0.9419999999999999</v>
@@ -10934,10 +10934,10 @@
         <v>7.62</v>
       </c>
       <c r="I132" t="n">
-        <v>0.251</v>
+        <v>4.436</v>
       </c>
       <c r="J132" t="n">
-        <v>2.187</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -571,56 +571,127 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>CALIBRATION</t>
+          <t>PLANT START DATES (approximate first feedgas; blanks before these = not operating yet)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>'EIA exports (Bcfd)': EIA monthly LNG exports by terminal (point of exit), converted to Bcf/d and grossed up by 1.09 for liquefaction fuel and shrinkage (an assumed ~9%) - i.e. the feedgas each plant actually needed. About 2-3 months behind.</t>
+          <t>Sabine Pass: Jan 2016 (meters treated as live from Jul 2015, 6 months earlier, to catch pre-commissioning feedgas)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>'Monthly check': for each month with 20+ metered days, metered average vs EIA-implied feedgas; seen_share = the part of each plant's supply our meters see.</t>
+          <t>Cove Point: Feb 2018 (meters treated as live from Aug 2017, 6 months earlier, to catch pre-commissioning feedgas)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>'Estimated (calibrated)': daily metered / the plant's latest seen_share - fills the gas we can't see (Freeport's Texas intrastate supply above all). Plants with no share yet (the first 2-3 months, until EIA catches up with our history) carry their metered value. 'Estimated total' vs 'Metered total' shows how much is inferred.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t>Corpus Christi: Nov 2018 (meters treated as live from May 2018, 6 months earlier, to catch pre-commissioning feedgas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cameron: May 2019 (meters treated as live from Nov 2018, 6 months earlier, to catch pre-commissioning feedgas)</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>POINTS</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Freeport: Aug 2019 (meters treated as live from Feb 2019, 6 months earlier, to catch pre-commissioning feedgas)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Each 'Points (Dth)' column is 'Plant | meter (pipeline code, location id)'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t>Elba Island: Oct 2019 (meters treated as live from Apr 2019, 6 months earlier, to catch pre-commissioning feedgas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Calcasieu Pass: Jan 2022 (meters treated as live from Jul 2021, 6 months earlier, to catch pre-commissioning feedgas)</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>SOURCE</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Plaquemines: Dec 2024 (meters treated as live from Jun 2024, 6 months earlier, to catch pre-commissioning feedgas)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Golden Pass: Jan 2026 (meters treated as live from Jul 2025, 6 months earlier, to catch pre-commissioning feedgas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>CALIBRATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>'EIA exports (Bcfd)': EIA monthly LNG exports by terminal (point of exit), converted to Bcf/d and grossed up by 1.09 for liquefaction fuel and shrinkage (an assumed ~9%) - i.e. the feedgas each plant actually needed. About 2-3 months behind.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>'Monthly check': for each month with 20+ metered days, metered average vs EIA-implied feedgas; seen_share = the part of each plant's supply our meters see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>'Estimated (calibrated)': daily metered / the plant's latest seen_share - fills the gas we can't see (Freeport's Texas intrastate supply above all). Plants with no share yet (the first 2-3 months, until EIA catches up with our history) carry their metered value. 'Estimated total' vs 'Metered total' shows how much is inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>POINTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Each 'Points (Dth)' column is 'Plant | meter (pipeline code, location id)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate), Energy Transfer Messenger+ and Cheniere LNG Connection equivalents - all operator-hosted.</t>
         </is>
@@ -8098,47 +8169,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Cove Point</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Golden Pass</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Corpus Christi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Cove Point</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Calcasieu Pass</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Cameron</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Elba Island</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Plaquemines</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Freeport</t>
+          <t>Sabine Pass</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8219,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="F2" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8158,7 +8229,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="F3" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8168,7 +8239,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="F4" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8178,7 +8249,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="F5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8188,7 +8259,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="F6" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8198,7 +8269,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="F7" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8208,7 +8279,7 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -8218,7 +8289,7 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.373</v>
       </c>
     </row>
@@ -8228,7 +8299,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>0.364</v>
       </c>
     </row>
@@ -8238,7 +8309,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>0.346</v>
       </c>
     </row>
@@ -8248,7 +8319,7 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>0.597</v>
       </c>
     </row>
@@ -8258,7 +8329,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>0.552</v>
       </c>
     </row>
@@ -8268,7 +8339,7 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>0.966</v>
       </c>
     </row>
@@ -8278,7 +8349,7 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.607</v>
       </c>
     </row>
@@ -8288,7 +8359,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -8298,7 +8369,7 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>1.196</v>
       </c>
     </row>
@@ -8308,7 +8379,7 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1.468</v>
       </c>
     </row>
@@ -8318,7 +8389,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1.801</v>
       </c>
     </row>
@@ -8328,7 +8399,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>2.024</v>
       </c>
     </row>
@@ -8338,7 +8409,7 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>1.528</v>
       </c>
     </row>
@@ -8348,7 +8419,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1.838</v>
       </c>
     </row>
@@ -8358,7 +8429,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>2.136</v>
       </c>
     </row>
@@ -8368,7 +8439,7 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1.905</v>
       </c>
     </row>
@@ -8378,7 +8449,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>1.883</v>
       </c>
     </row>
@@ -8388,7 +8459,7 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>1.597</v>
       </c>
     </row>
@@ -8398,7 +8469,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>1.986</v>
       </c>
     </row>
@@ -8408,7 +8479,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>2.832</v>
       </c>
     </row>
@@ -8418,7 +8489,7 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>2.906</v>
       </c>
     </row>
@@ -8428,7 +8499,7 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -8438,7 +8509,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2.543</v>
       </c>
     </row>
@@ -8448,7 +8519,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>2.864</v>
       </c>
     </row>
@@ -8458,10 +8529,10 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="B33" t="n">
         <v>0.105</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>3.11</v>
       </c>
     </row>
@@ -8471,10 +8542,10 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="B34" t="n">
         <v>0.325</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>2.788</v>
       </c>
     </row>
@@ -8484,10 +8555,10 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="B35" t="n">
         <v>0.77</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2.562</v>
       </c>
     </row>
@@ -8497,10 +8568,10 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="B36" t="n">
         <v>0.457</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>2.213</v>
       </c>
     </row>
@@ -8510,10 +8581,10 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="B37" t="n">
         <v>0.675</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>2.778</v>
       </c>
     </row>
@@ -8523,10 +8594,10 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="B38" t="n">
         <v>0.676</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>2.54</v>
       </c>
     </row>
@@ -8536,10 +8607,10 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="B39" t="n">
         <v>0.449</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>2.507</v>
       </c>
     </row>
@@ -8549,10 +8620,10 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="B40" t="n">
         <v>0.226</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>2.932</v>
       </c>
     </row>
@@ -8562,10 +8633,10 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="B41" t="n">
         <v>0.701</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>3.202</v>
       </c>
     </row>
@@ -8575,13 +8646,13 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="B42" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D42" t="n">
         <v>0.241</v>
       </c>
-      <c r="D42" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>3.36</v>
       </c>
     </row>
@@ -8591,13 +8662,13 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="B43" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="D43" t="n">
         <v>0.378</v>
       </c>
-      <c r="D43" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>3.367</v>
       </c>
     </row>
@@ -8607,13 +8678,13 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="B44" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="D44" t="n">
         <v>0.145</v>
       </c>
-      <c r="D44" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>2.942</v>
       </c>
     </row>
@@ -8623,13 +8694,13 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="B45" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="D45" t="n">
         <v>0.706</v>
       </c>
-      <c r="D45" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>3.291</v>
       </c>
     </row>
@@ -8639,13 +8710,13 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="B46" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D46" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="D46" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>3.054</v>
       </c>
     </row>
@@ -8655,16 +8726,16 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="B47" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="D47" t="n">
         <v>0.614</v>
       </c>
-      <c r="D47" t="n">
-        <v>0.602</v>
-      </c>
-      <c r="F47" t="n">
+      <c r="E47" t="n">
         <v>0.113</v>
       </c>
-      <c r="I47" t="n">
+      <c r="J47" t="n">
         <v>3.762</v>
       </c>
     </row>
@@ -8674,16 +8745,16 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="B48" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.765</v>
       </c>
-      <c r="D48" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="F48" t="n">
+      <c r="E48" t="n">
         <v>0.106</v>
       </c>
-      <c r="I48" t="n">
+      <c r="J48" t="n">
         <v>3.551</v>
       </c>
     </row>
@@ -8693,16 +8764,16 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="B49" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="D49" t="n">
         <v>1.184</v>
       </c>
-      <c r="D49" t="n">
-        <v>0.731</v>
-      </c>
-      <c r="F49" t="n">
+      <c r="E49" t="n">
         <v>0.248</v>
       </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
         <v>3.347</v>
       </c>
     </row>
@@ -8712,16 +8783,16 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="B50" t="n">
+        <v>0.699</v>
+      </c>
+      <c r="D50" t="n">
         <v>1.084</v>
       </c>
-      <c r="D50" t="n">
-        <v>0.699</v>
-      </c>
-      <c r="F50" t="n">
+      <c r="E50" t="n">
         <v>0.388</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
         <v>2.696</v>
       </c>
     </row>
@@ -8731,20 +8802,20 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="B51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D51" t="n">
         <v>1.26</v>
       </c>
-      <c r="D51" t="n">
-        <v>0.5</v>
+      <c r="E51" t="n">
+        <v>0.364</v>
       </c>
       <c r="F51" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="I51" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J51" t="n">
         <v>3.461</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.235</v>
       </c>
     </row>
     <row r="52">
@@ -8753,20 +8824,20 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="B52" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="D52" t="n">
         <v>1.488</v>
       </c>
-      <c r="D52" t="n">
-        <v>0.244</v>
+      <c r="E52" t="n">
+        <v>0.379</v>
       </c>
       <c r="F52" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="I52" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="J52" t="n">
         <v>3.775</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.365</v>
       </c>
     </row>
     <row r="53">
@@ -8775,20 +8846,20 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="B53" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D53" t="n">
         <v>1.357</v>
       </c>
-      <c r="D53" t="n">
-        <v>0.852</v>
+      <c r="E53" t="n">
+        <v>0.507</v>
       </c>
       <c r="F53" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I53" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="J53" t="n">
         <v>3.852</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.353</v>
       </c>
     </row>
     <row r="54">
@@ -8797,23 +8868,23 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="B54" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="D54" t="n">
         <v>1.461</v>
       </c>
-      <c r="D54" t="n">
-        <v>0.729</v>
+      <c r="E54" t="n">
+        <v>0.84</v>
       </c>
       <c r="F54" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G54" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H54" t="n">
         <v>0.229</v>
       </c>
-      <c r="I54" t="n">
+      <c r="J54" t="n">
         <v>3.813</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.79</v>
       </c>
     </row>
     <row r="55">
@@ -8822,23 +8893,23 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="B55" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="D55" t="n">
         <v>1.426</v>
       </c>
-      <c r="D55" t="n">
-        <v>0.722</v>
+      <c r="E55" t="n">
+        <v>0.98</v>
       </c>
       <c r="F55" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="G55" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="H55" t="n">
         <v>0.428</v>
       </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>4.018</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.456</v>
       </c>
     </row>
     <row r="56">
@@ -8847,20 +8918,20 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="B56" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="D56" t="n">
         <v>1.55</v>
       </c>
-      <c r="D56" t="n">
-        <v>0.758</v>
+      <c r="E56" t="n">
+        <v>1.044</v>
       </c>
       <c r="F56" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="I56" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="J56" t="n">
         <v>3.684</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.446</v>
       </c>
     </row>
     <row r="57">
@@ -8869,20 +8940,20 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="B57" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D57" t="n">
         <v>1.462</v>
       </c>
-      <c r="D57" t="n">
-        <v>0.831</v>
+      <c r="E57" t="n">
+        <v>1.208</v>
       </c>
       <c r="F57" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="I57" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="J57" t="n">
         <v>3.447</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.635</v>
       </c>
     </row>
     <row r="58">
@@ -8891,20 +8962,20 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="C58" t="n">
+      <c r="B58" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="D58" t="n">
         <v>1.245</v>
       </c>
-      <c r="D58" t="n">
-        <v>0.608</v>
+      <c r="E58" t="n">
+        <v>1.301</v>
       </c>
       <c r="F58" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="I58" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="J58" t="n">
         <v>3.333</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.158</v>
       </c>
     </row>
     <row r="59">
@@ -8913,20 +8984,20 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="C59" t="n">
+      <c r="B59" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="D59" t="n">
         <v>0.831</v>
       </c>
-      <c r="D59" t="n">
-        <v>0.708</v>
+      <c r="E59" t="n">
+        <v>1.135</v>
       </c>
       <c r="F59" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="I59" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="J59" t="n">
         <v>2.73</v>
-      </c>
-      <c r="J59" t="n">
-        <v>1.008</v>
       </c>
     </row>
     <row r="60">
@@ -8935,20 +9006,20 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="C60" t="n">
+      <c r="B60" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="D60" t="n">
         <v>0.307</v>
       </c>
-      <c r="D60" t="n">
-        <v>0.763</v>
+      <c r="E60" t="n">
+        <v>1.366</v>
       </c>
       <c r="F60" t="n">
-        <v>1.366</v>
-      </c>
-      <c r="I60" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.978</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.543</v>
       </c>
     </row>
     <row r="61">
@@ -8957,20 +9028,20 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="B61" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="D61" t="n">
         <v>0.373</v>
       </c>
-      <c r="D61" t="n">
-        <v>0.711</v>
+      <c r="E61" t="n">
+        <v>1.099</v>
       </c>
       <c r="F61" t="n">
-        <v>1.099</v>
-      </c>
-      <c r="I61" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J61" t="n">
         <v>1.063</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.132</v>
       </c>
     </row>
     <row r="62">
@@ -8979,23 +9050,23 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="C62" t="n">
+      <c r="B62" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="D62" t="n">
         <v>0.601</v>
       </c>
-      <c r="D62" t="n">
-        <v>0.596</v>
+      <c r="E62" t="n">
+        <v>1.117</v>
       </c>
       <c r="F62" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="G62" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="H62" t="n">
         <v>0.26</v>
       </c>
-      <c r="I62" t="n">
+      <c r="J62" t="n">
         <v>1.031</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.399</v>
       </c>
     </row>
     <row r="63">
@@ -9004,20 +9075,20 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="C63" t="n">
+      <c r="B63" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="D63" t="n">
         <v>1.363</v>
       </c>
-      <c r="D63" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="G63" t="n">
+      <c r="F63" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="H63" t="n">
         <v>0.271</v>
       </c>
-      <c r="I63" t="n">
+      <c r="J63" t="n">
         <v>2.241</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.127</v>
       </c>
     </row>
     <row r="64">
@@ -9026,23 +9097,23 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="C64" t="n">
+      <c r="B64" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="D64" t="n">
         <v>1.551</v>
       </c>
-      <c r="D64" t="n">
-        <v>0.373</v>
+      <c r="E64" t="n">
+        <v>0.662</v>
       </c>
       <c r="F64" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="G64" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.52</v>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>3.106</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.892</v>
       </c>
     </row>
     <row r="65">
@@ -9051,23 +9122,23 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="C65" t="n">
+      <c r="B65" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D65" t="n">
         <v>1.633</v>
       </c>
-      <c r="D65" t="n">
-        <v>0.852</v>
+      <c r="E65" t="n">
+        <v>1.838</v>
       </c>
       <c r="F65" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="G65" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="H65" t="n">
         <v>0.469</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>3.684</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.953</v>
       </c>
     </row>
     <row r="66">
@@ -9076,23 +9147,23 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="C66" t="n">
+      <c r="B66" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="D66" t="n">
         <v>1.821</v>
       </c>
-      <c r="D66" t="n">
-        <v>0.718</v>
+      <c r="E66" t="n">
+        <v>1.939</v>
       </c>
       <c r="F66" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="G66" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="H66" t="n">
         <v>0.628</v>
       </c>
-      <c r="I66" t="n">
+      <c r="J66" t="n">
         <v>3.845</v>
-      </c>
-      <c r="J66" t="n">
-        <v>2.057</v>
       </c>
     </row>
     <row r="67">
@@ -9101,20 +9172,20 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="C67" t="n">
+      <c r="B67" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="D67" t="n">
         <v>2.012</v>
       </c>
-      <c r="D67" t="n">
-        <v>0.718</v>
+      <c r="E67" t="n">
+        <v>1.943</v>
       </c>
       <c r="F67" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="I67" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="J67" t="n">
         <v>3.905</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2.148</v>
       </c>
     </row>
     <row r="68">
@@ -9123,23 +9194,23 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="C68" t="n">
+      <c r="B68" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="D68" t="n">
         <v>1.297</v>
       </c>
-      <c r="D68" t="n">
-        <v>0.671</v>
+      <c r="E68" t="n">
+        <v>1.42</v>
       </c>
       <c r="F68" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G68" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.541</v>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>3.263</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1.186</v>
       </c>
     </row>
     <row r="69">
@@ -9148,23 +9219,23 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="C69" t="n">
+      <c r="B69" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="D69" t="n">
         <v>2.201</v>
       </c>
-      <c r="D69" t="n">
-        <v>0.845</v>
+      <c r="E69" t="n">
+        <v>1.755</v>
       </c>
       <c r="F69" t="n">
-        <v>1.755</v>
-      </c>
-      <c r="G69" t="n">
+        <v>2.237</v>
+      </c>
+      <c r="H69" t="n">
         <v>0.468</v>
       </c>
-      <c r="I69" t="n">
+      <c r="J69" t="n">
         <v>4.013</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.237</v>
       </c>
     </row>
     <row r="70">
@@ -9173,23 +9244,23 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="B70" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="D70" t="n">
         <v>2.175</v>
       </c>
-      <c r="D70" t="n">
-        <v>0.622</v>
+      <c r="E70" t="n">
+        <v>1.848</v>
       </c>
       <c r="F70" t="n">
-        <v>1.848</v>
-      </c>
-      <c r="G70" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="H70" t="n">
         <v>0.68</v>
       </c>
-      <c r="I70" t="n">
+      <c r="J70" t="n">
         <v>3.955</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.203</v>
       </c>
     </row>
     <row r="71">
@@ -9198,23 +9269,23 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="C71" t="n">
+      <c r="B71" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="D71" t="n">
         <v>2.066</v>
       </c>
-      <c r="D71" t="n">
-        <v>0.787</v>
+      <c r="E71" t="n">
+        <v>1.855</v>
       </c>
       <c r="F71" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="G71" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="H71" t="n">
         <v>0.662</v>
       </c>
-      <c r="I71" t="n">
+      <c r="J71" t="n">
         <v>3.805</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.223</v>
       </c>
     </row>
     <row r="72">
@@ -9223,23 +9294,23 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="C72" t="n">
+      <c r="B72" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="D72" t="n">
         <v>2.236</v>
       </c>
-      <c r="D72" t="n">
-        <v>0.6919999999999999</v>
+      <c r="E72" t="n">
+        <v>1.418</v>
       </c>
       <c r="F72" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="G72" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="H72" t="n">
         <v>0.524</v>
       </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
         <v>3.118</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2.127</v>
       </c>
     </row>
     <row r="73">
@@ -9248,23 +9319,23 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="B73" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D73" t="n">
         <v>2.126</v>
       </c>
-      <c r="D73" t="n">
-        <v>0.8100000000000001</v>
+      <c r="E73" t="n">
+        <v>1.82</v>
       </c>
       <c r="F73" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G73" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="H73" t="n">
         <v>0.493</v>
       </c>
-      <c r="I73" t="n">
+      <c r="J73" t="n">
         <v>3.402</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2.141</v>
       </c>
     </row>
     <row r="74">
@@ -9273,23 +9344,23 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="C74" t="n">
+      <c r="B74" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="D74" t="n">
         <v>2.171</v>
       </c>
-      <c r="D74" t="n">
-        <v>0.785</v>
+      <c r="E74" t="n">
+        <v>1.467</v>
       </c>
       <c r="F74" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="G74" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.507</v>
       </c>
-      <c r="I74" t="n">
+      <c r="J74" t="n">
         <v>3.492</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.307</v>
       </c>
     </row>
     <row r="75">
@@ -9298,23 +9369,23 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="C75" t="n">
+      <c r="B75" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="D75" t="n">
         <v>2.34</v>
       </c>
-      <c r="D75" t="n">
-        <v>0.499</v>
+      <c r="E75" t="n">
+        <v>1.919</v>
       </c>
       <c r="F75" t="n">
-        <v>1.919</v>
-      </c>
-      <c r="G75" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="H75" t="n">
         <v>0.396</v>
       </c>
-      <c r="I75" t="n">
+      <c r="J75" t="n">
         <v>3.619</v>
-      </c>
-      <c r="J75" t="n">
-        <v>1.764</v>
       </c>
     </row>
     <row r="76">
@@ -9323,23 +9394,23 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="C76" t="n">
+      <c r="B76" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="D76" t="n">
         <v>2.28</v>
       </c>
-      <c r="D76" t="n">
-        <v>0.348</v>
+      <c r="E76" t="n">
+        <v>1.852</v>
       </c>
       <c r="F76" t="n">
-        <v>1.852</v>
-      </c>
-      <c r="G76" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="H76" t="n">
         <v>0.639</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>3.561</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2.111</v>
       </c>
     </row>
     <row r="77">
@@ -9348,23 +9419,23 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="C77" t="n">
+      <c r="B77" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="D77" t="n">
         <v>2.307</v>
       </c>
-      <c r="D77" t="n">
-        <v>0.797</v>
+      <c r="E77" t="n">
+        <v>2.113</v>
       </c>
       <c r="F77" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="G77" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="H77" t="n">
         <v>0.423</v>
       </c>
-      <c r="I77" t="n">
+      <c r="J77" t="n">
         <v>4.097</v>
-      </c>
-      <c r="J77" t="n">
-        <v>1.597</v>
       </c>
     </row>
     <row r="78">
@@ -9373,23 +9444,23 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="C78" t="n">
+      <c r="B78" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D78" t="n">
         <v>2.249</v>
       </c>
-      <c r="D78" t="n">
-        <v>0.8100000000000001</v>
+      <c r="E78" t="n">
+        <v>2.158</v>
       </c>
       <c r="F78" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="G78" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="H78" t="n">
         <v>0.723</v>
       </c>
-      <c r="I78" t="n">
+      <c r="J78" t="n">
         <v>4.186</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.365</v>
       </c>
     </row>
     <row r="79">
@@ -9398,23 +9469,23 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="C79" t="n">
+      <c r="B79" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="D79" t="n">
         <v>2.347</v>
       </c>
-      <c r="D79" t="n">
-        <v>0.886</v>
+      <c r="E79" t="n">
+        <v>2.151</v>
       </c>
       <c r="F79" t="n">
-        <v>2.151</v>
-      </c>
-      <c r="G79" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="H79" t="n">
         <v>0.441</v>
       </c>
-      <c r="I79" t="n">
+      <c r="J79" t="n">
         <v>4.576</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.248</v>
       </c>
     </row>
     <row r="80">
@@ -9423,23 +9494,23 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="C80" t="n">
+      <c r="B80" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="D80" t="n">
         <v>2.654</v>
       </c>
-      <c r="D80" t="n">
-        <v>0.8120000000000001</v>
+      <c r="E80" t="n">
+        <v>2.116</v>
       </c>
       <c r="F80" t="n">
-        <v>2.116</v>
-      </c>
-      <c r="G80" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="H80" t="n">
         <v>0.749</v>
       </c>
-      <c r="I80" t="n">
+      <c r="J80" t="n">
         <v>4.318</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2.043</v>
       </c>
     </row>
     <row r="81">
@@ -9448,26 +9519,26 @@
           <t>2022-03</t>
         </is>
       </c>
-      <c r="C81" t="n">
+      <c r="B81" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="D81" t="n">
         <v>2.115</v>
       </c>
-      <c r="D81" t="n">
-        <v>0.754</v>
-      </c>
       <c r="E81" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="G81" t="n">
         <v>1.279</v>
       </c>
-      <c r="F81" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>0.609</v>
       </c>
-      <c r="I81" t="n">
+      <c r="J81" t="n">
         <v>4.588</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.268</v>
       </c>
     </row>
     <row r="82">
@@ -9476,26 +9547,26 @@
           <t>2022-04</t>
         </is>
       </c>
-      <c r="C82" t="n">
+      <c r="B82" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="D82" t="n">
         <v>2.117</v>
       </c>
-      <c r="D82" t="n">
-        <v>0.794</v>
-      </c>
       <c r="E82" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="G82" t="n">
         <v>1.289</v>
       </c>
-      <c r="F82" t="n">
-        <v>2.095</v>
-      </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>0.784</v>
       </c>
-      <c r="I82" t="n">
+      <c r="J82" t="n">
         <v>4.526</v>
-      </c>
-      <c r="J82" t="n">
-        <v>1.427</v>
       </c>
     </row>
     <row r="83">
@@ -9504,26 +9575,26 @@
           <t>2022-05</t>
         </is>
       </c>
-      <c r="C83" t="n">
+      <c r="B83" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="D83" t="n">
         <v>2.179</v>
       </c>
-      <c r="D83" t="n">
-        <v>0.781</v>
-      </c>
       <c r="E83" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="G83" t="n">
         <v>1.774</v>
       </c>
-      <c r="F83" t="n">
-        <v>1.426</v>
-      </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>0.488</v>
       </c>
-      <c r="I83" t="n">
+      <c r="J83" t="n">
         <v>4.597</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.232</v>
       </c>
     </row>
     <row r="84">
@@ -9532,26 +9603,26 @@
           <t>2022-06</t>
         </is>
       </c>
-      <c r="C84" t="n">
+      <c r="B84" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="D84" t="n">
         <v>2.315</v>
       </c>
-      <c r="D84" t="n">
-        <v>0.716</v>
-      </c>
       <c r="E84" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="G84" t="n">
         <v>2.334</v>
       </c>
-      <c r="F84" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>0.777</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>3.84</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.629</v>
       </c>
     </row>
     <row r="85">
@@ -9560,22 +9631,22 @@
           <t>2022-07</t>
         </is>
       </c>
-      <c r="C85" t="n">
+      <c r="B85" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="D85" t="n">
         <v>2.218</v>
       </c>
-      <c r="D85" t="n">
-        <v>0.851</v>
-      </c>
       <c r="E85" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="G85" t="n">
         <v>2.33</v>
       </c>
-      <c r="F85" t="n">
-        <v>1.832</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>0.64</v>
       </c>
-      <c r="I85" t="n">
+      <c r="J85" t="n">
         <v>4.168</v>
       </c>
     </row>
@@ -9585,22 +9656,22 @@
           <t>2022-08</t>
         </is>
       </c>
-      <c r="C86" t="n">
+      <c r="B86" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="D86" t="n">
         <v>2.23</v>
       </c>
-      <c r="D86" t="n">
-        <v>0.753</v>
-      </c>
       <c r="E86" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G86" t="n">
         <v>2.375</v>
       </c>
-      <c r="F86" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>0.647</v>
       </c>
-      <c r="I86" t="n">
+      <c r="J86" t="n">
         <v>4.173</v>
       </c>
     </row>
@@ -9610,22 +9681,22 @@
           <t>2022-09</t>
         </is>
       </c>
-      <c r="C87" t="n">
+      <c r="B87" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="D87" t="n">
         <v>2.173</v>
       </c>
-      <c r="D87" t="n">
-        <v>0.6840000000000001</v>
-      </c>
       <c r="E87" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="G87" t="n">
         <v>2.796</v>
       </c>
-      <c r="F87" t="n">
-        <v>1.912</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>0.708</v>
       </c>
-      <c r="I87" t="n">
+      <c r="J87" t="n">
         <v>4.201</v>
       </c>
     </row>
@@ -9635,19 +9706,19 @@
           <t>2022-10</t>
         </is>
       </c>
-      <c r="C88" t="n">
+      <c r="D88" t="n">
         <v>2.348</v>
       </c>
       <c r="E88" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="G88" t="n">
         <v>3.186</v>
       </c>
-      <c r="F88" t="n">
-        <v>2.094</v>
-      </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>0.519</v>
       </c>
-      <c r="I88" t="n">
+      <c r="J88" t="n">
         <v>4.586</v>
       </c>
     </row>
@@ -9657,22 +9728,22 @@
           <t>2022-11</t>
         </is>
       </c>
-      <c r="C89" t="n">
+      <c r="B89" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="D89" t="n">
         <v>2.072</v>
       </c>
-      <c r="D89" t="n">
-        <v>0.742</v>
-      </c>
       <c r="E89" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="G89" t="n">
         <v>2.625</v>
       </c>
-      <c r="F89" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>0.773</v>
       </c>
-      <c r="I89" t="n">
+      <c r="J89" t="n">
         <v>4.363</v>
       </c>
     </row>
@@ -9682,22 +9753,22 @@
           <t>2022-12</t>
         </is>
       </c>
-      <c r="C90" t="n">
+      <c r="B90" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="D90" t="n">
         <v>2.255</v>
       </c>
-      <c r="D90" t="n">
-        <v>1.047</v>
-      </c>
       <c r="E90" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="G90" t="n">
         <v>2.655</v>
       </c>
-      <c r="F90" t="n">
-        <v>2.088</v>
-      </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>0.66</v>
       </c>
-      <c r="I90" t="n">
+      <c r="J90" t="n">
         <v>4.893</v>
       </c>
     </row>
@@ -9707,22 +9778,22 @@
           <t>2023-01</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="B91" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="D91" t="n">
         <v>2.2</v>
       </c>
-      <c r="D91" t="n">
-        <v>0.731</v>
-      </c>
       <c r="E91" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="G91" t="n">
         <v>3.007</v>
       </c>
-      <c r="F91" t="n">
-        <v>2.183</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>0.663</v>
       </c>
-      <c r="I91" t="n">
+      <c r="J91" t="n">
         <v>4.896</v>
       </c>
     </row>
@@ -9732,26 +9803,26 @@
           <t>2023-02</t>
         </is>
       </c>
-      <c r="C92" t="n">
+      <c r="B92" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="D92" t="n">
         <v>2.496</v>
       </c>
-      <c r="D92" t="n">
-        <v>0.756</v>
-      </c>
       <c r="E92" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G92" t="n">
         <v>3.501</v>
       </c>
-      <c r="F92" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>0.823</v>
       </c>
-      <c r="I92" t="n">
+      <c r="J92" t="n">
         <v>4.65</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0.45</v>
       </c>
     </row>
     <row r="93">
@@ -9760,26 +9831,26 @@
           <t>2023-03</t>
         </is>
       </c>
-      <c r="C93" t="n">
+      <c r="B93" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="D93" t="n">
         <v>2.361</v>
       </c>
-      <c r="D93" t="n">
-        <v>0.976</v>
-      </c>
       <c r="E93" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="G93" t="n">
         <v>2.682</v>
       </c>
-      <c r="F93" t="n">
-        <v>2.176</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>0.803</v>
       </c>
-      <c r="I93" t="n">
+      <c r="J93" t="n">
         <v>4.605</v>
-      </c>
-      <c r="J93" t="n">
-        <v>1.019</v>
       </c>
     </row>
     <row r="94">
@@ -9788,26 +9859,26 @@
           <t>2023-04</t>
         </is>
       </c>
-      <c r="C94" t="n">
+      <c r="B94" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="D94" t="n">
         <v>2.018</v>
       </c>
-      <c r="D94" t="n">
-        <v>0.6840000000000001</v>
-      </c>
       <c r="E94" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="G94" t="n">
         <v>2.883</v>
       </c>
-      <c r="F94" t="n">
-        <v>1.992</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>0.532</v>
       </c>
-      <c r="I94" t="n">
+      <c r="J94" t="n">
         <v>4.977</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2.271</v>
       </c>
     </row>
     <row r="95">
@@ -9816,26 +9887,26 @@
           <t>2023-05</t>
         </is>
       </c>
-      <c r="C95" t="n">
+      <c r="B95" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="D95" t="n">
         <v>2.03</v>
       </c>
-      <c r="D95" t="n">
-        <v>0.924</v>
-      </c>
       <c r="E95" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="G95" t="n">
         <v>2.943</v>
       </c>
-      <c r="F95" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>0.519</v>
       </c>
-      <c r="I95" t="n">
+      <c r="J95" t="n">
         <v>4.436</v>
-      </c>
-      <c r="J95" t="n">
-        <v>2.405</v>
       </c>
     </row>
     <row r="96">
@@ -9844,26 +9915,26 @@
           <t>2023-06</t>
         </is>
       </c>
-      <c r="C96" t="n">
+      <c r="B96" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="D96" t="n">
         <v>2.269</v>
       </c>
-      <c r="D96" t="n">
-        <v>0.845</v>
-      </c>
       <c r="E96" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="G96" t="n">
         <v>2.169</v>
       </c>
-      <c r="F96" t="n">
-        <v>1.896</v>
-      </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>0.944</v>
       </c>
-      <c r="I96" t="n">
+      <c r="J96" t="n">
         <v>3.043</v>
-      </c>
-      <c r="J96" t="n">
-        <v>2.299</v>
       </c>
     </row>
     <row r="97">
@@ -9872,26 +9943,26 @@
           <t>2023-07</t>
         </is>
       </c>
-      <c r="C97" t="n">
+      <c r="B97" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="D97" t="n">
         <v>2.062</v>
       </c>
-      <c r="D97" t="n">
-        <v>0.701</v>
-      </c>
       <c r="E97" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="G97" t="n">
         <v>2.723</v>
       </c>
-      <c r="F97" t="n">
-        <v>1.751</v>
-      </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>0.651</v>
       </c>
-      <c r="I97" t="n">
+      <c r="J97" t="n">
         <v>3.985</v>
-      </c>
-      <c r="J97" t="n">
-        <v>2.093</v>
       </c>
     </row>
     <row r="98">
@@ -9900,26 +9971,26 @@
           <t>2023-08</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="B98" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="D98" t="n">
         <v>2.195</v>
       </c>
-      <c r="D98" t="n">
-        <v>0.771</v>
-      </c>
       <c r="E98" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G98" t="n">
         <v>2.508</v>
       </c>
-      <c r="F98" t="n">
-        <v>1.761</v>
-      </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>0.207</v>
       </c>
-      <c r="I98" t="n">
+      <c r="J98" t="n">
         <v>4.166</v>
-      </c>
-      <c r="J98" t="n">
-        <v>2.16</v>
       </c>
     </row>
     <row r="99">
@@ -9928,26 +9999,26 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="C99" t="n">
+      <c r="B99" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="D99" t="n">
         <v>2.157</v>
       </c>
-      <c r="D99" t="n">
-        <v>0.635</v>
-      </c>
       <c r="E99" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="G99" t="n">
         <v>2.834</v>
       </c>
-      <c r="F99" t="n">
-        <v>1.793</v>
-      </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>0.863</v>
       </c>
-      <c r="I99" t="n">
+      <c r="J99" t="n">
         <v>4.193</v>
-      </c>
-      <c r="J99" t="n">
-        <v>1.963</v>
       </c>
     </row>
     <row r="100">
@@ -9956,26 +10027,26 @@
           <t>2023-10</t>
         </is>
       </c>
-      <c r="C100" t="n">
+      <c r="B100" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="D100" t="n">
         <v>2.229</v>
       </c>
-      <c r="D100" t="n">
-        <v>0.375</v>
-      </c>
       <c r="E100" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="G100" t="n">
         <v>3.366</v>
       </c>
-      <c r="F100" t="n">
-        <v>2.094</v>
-      </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>0.456</v>
       </c>
-      <c r="I100" t="n">
+      <c r="J100" t="n">
         <v>4.656</v>
-      </c>
-      <c r="J100" t="n">
-        <v>2.249</v>
       </c>
     </row>
     <row r="101">
@@ -9984,26 +10055,26 @@
           <t>2023-11</t>
         </is>
       </c>
-      <c r="C101" t="n">
+      <c r="B101" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="D101" t="n">
         <v>2.342</v>
       </c>
-      <c r="D101" t="n">
-        <v>0.761</v>
-      </c>
       <c r="E101" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="G101" t="n">
         <v>3.38</v>
       </c>
-      <c r="F101" t="n">
-        <v>2.022</v>
-      </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>0.588</v>
       </c>
-      <c r="I101" t="n">
+      <c r="J101" t="n">
         <v>4.739</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2.184</v>
       </c>
     </row>
     <row r="102">
@@ -10012,26 +10083,26 @@
           <t>2023-12</t>
         </is>
       </c>
-      <c r="C102" t="n">
+      <c r="B102" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D102" t="n">
         <v>2.257</v>
       </c>
-      <c r="D102" t="n">
-        <v>0.824</v>
-      </c>
       <c r="E102" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="G102" t="n">
         <v>3.175</v>
       </c>
-      <c r="F102" t="n">
-        <v>2.334</v>
-      </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>0.77</v>
       </c>
-      <c r="I102" t="n">
+      <c r="J102" t="n">
         <v>4.976</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2.504</v>
       </c>
     </row>
     <row r="103">
@@ -10040,26 +10111,26 @@
           <t>2024-01</t>
         </is>
       </c>
-      <c r="C103" t="n">
+      <c r="B103" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="D103" t="n">
         <v>2.148</v>
       </c>
-      <c r="D103" t="n">
-        <v>0.749</v>
-      </c>
       <c r="E103" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="G103" t="n">
         <v>3.573</v>
       </c>
-      <c r="F103" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>0.739</v>
       </c>
-      <c r="I103" t="n">
+      <c r="J103" t="n">
         <v>4.844</v>
-      </c>
-      <c r="J103" t="n">
-        <v>1.855</v>
       </c>
     </row>
     <row r="104">
@@ -10068,26 +10139,26 @@
           <t>2024-02</t>
         </is>
       </c>
-      <c r="C104" t="n">
+      <c r="B104" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="D104" t="n">
         <v>2.096</v>
       </c>
-      <c r="D104" t="n">
-        <v>0.898</v>
-      </c>
       <c r="E104" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="G104" t="n">
         <v>3.334</v>
       </c>
-      <c r="F104" t="n">
-        <v>2.229</v>
-      </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>0.527</v>
       </c>
-      <c r="I104" t="n">
+      <c r="J104" t="n">
         <v>4.822</v>
-      </c>
-      <c r="J104" t="n">
-        <v>1.559</v>
       </c>
     </row>
     <row r="105">
@@ -10096,26 +10167,26 @@
           <t>2024-03</t>
         </is>
       </c>
-      <c r="C105" t="n">
+      <c r="B105" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="D105" t="n">
         <v>2.154</v>
       </c>
-      <c r="D105" t="n">
-        <v>0.886</v>
-      </c>
       <c r="E105" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="G105" t="n">
         <v>3.31</v>
       </c>
-      <c r="F105" t="n">
-        <v>2.072</v>
-      </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>0.903</v>
       </c>
-      <c r="I105" t="n">
+      <c r="J105" t="n">
         <v>4.861</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0.923</v>
       </c>
     </row>
     <row r="106">
@@ -10124,26 +10195,26 @@
           <t>2024-04</t>
         </is>
       </c>
-      <c r="C106" t="n">
+      <c r="B106" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="D106" t="n">
         <v>1.821</v>
       </c>
-      <c r="D106" t="n">
-        <v>0.882</v>
-      </c>
       <c r="E106" t="n">
+        <v>1.946</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G106" t="n">
         <v>2.768</v>
       </c>
-      <c r="F106" t="n">
-        <v>1.946</v>
-      </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>0.522</v>
       </c>
-      <c r="I106" t="n">
+      <c r="J106" t="n">
         <v>4.35</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0.39</v>
       </c>
     </row>
     <row r="107">
@@ -10152,26 +10223,26 @@
           <t>2024-05</t>
         </is>
       </c>
-      <c r="C107" t="n">
+      <c r="B107" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="D107" t="n">
         <v>2.163</v>
       </c>
-      <c r="D107" t="n">
-        <v>0.885</v>
-      </c>
       <c r="E107" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="G107" t="n">
         <v>3.158</v>
       </c>
-      <c r="F107" t="n">
-        <v>1.528</v>
-      </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>0.411</v>
       </c>
-      <c r="I107" t="n">
+      <c r="J107" t="n">
         <v>4.624</v>
-      </c>
-      <c r="J107" t="n">
-        <v>1.942</v>
       </c>
     </row>
     <row r="108">
@@ -10180,26 +10251,26 @@
           <t>2024-06</t>
         </is>
       </c>
-      <c r="C108" t="n">
+      <c r="B108" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="D108" t="n">
         <v>2.346</v>
       </c>
-      <c r="D108" t="n">
-        <v>0.695</v>
-      </c>
       <c r="E108" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G108" t="n">
         <v>3.038</v>
       </c>
-      <c r="F108" t="n">
-        <v>1.849</v>
-      </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>0.466</v>
       </c>
-      <c r="I108" t="n">
+      <c r="J108" t="n">
         <v>3.944</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2.36</v>
       </c>
     </row>
     <row r="109">
@@ -10208,26 +10279,26 @@
           <t>2024-07</t>
         </is>
       </c>
-      <c r="C109" t="n">
+      <c r="B109" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="D109" t="n">
         <v>2.018</v>
       </c>
-      <c r="D109" t="n">
-        <v>0.745</v>
-      </c>
       <c r="E109" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="G109" t="n">
         <v>2.762</v>
       </c>
-      <c r="F109" t="n">
-        <v>1.815</v>
-      </c>
-      <c r="G109" t="n">
+      <c r="H109" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="I109" t="n">
+      <c r="J109" t="n">
         <v>4.213</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0.871</v>
       </c>
     </row>
     <row r="110">
@@ -10236,26 +10307,26 @@
           <t>2024-08</t>
         </is>
       </c>
-      <c r="C110" t="n">
+      <c r="B110" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="D110" t="n">
         <v>2.234</v>
       </c>
-      <c r="D110" t="n">
-        <v>0.6870000000000001</v>
-      </c>
       <c r="E110" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="G110" t="n">
         <v>2.298</v>
       </c>
-      <c r="F110" t="n">
-        <v>1.829</v>
-      </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>0.957</v>
       </c>
-      <c r="I110" t="n">
+      <c r="J110" t="n">
         <v>4.164</v>
-      </c>
-      <c r="J110" t="n">
-        <v>2.212</v>
       </c>
     </row>
     <row r="111">
@@ -10264,26 +10335,26 @@
           <t>2024-09</t>
         </is>
       </c>
-      <c r="C111" t="n">
+      <c r="B111" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="D111" t="n">
         <v>2.349</v>
       </c>
-      <c r="D111" t="n">
-        <v>0.639</v>
-      </c>
       <c r="E111" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="G111" t="n">
         <v>2.537</v>
       </c>
-      <c r="F111" t="n">
-        <v>1.885</v>
-      </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>0.499</v>
       </c>
-      <c r="I111" t="n">
+      <c r="J111" t="n">
         <v>4.401</v>
-      </c>
-      <c r="J111" t="n">
-        <v>2.288</v>
       </c>
     </row>
     <row r="112">
@@ -10292,26 +10363,26 @@
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C112" t="n">
+      <c r="B112" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="D112" t="n">
         <v>2.348</v>
       </c>
-      <c r="D112" t="n">
-        <v>0.448</v>
-      </c>
       <c r="E112" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.427</v>
+      </c>
+      <c r="G112" t="n">
         <v>2.711</v>
       </c>
-      <c r="F112" t="n">
-        <v>1.887</v>
-      </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>0.447</v>
       </c>
-      <c r="I112" t="n">
+      <c r="J112" t="n">
         <v>4.533</v>
-      </c>
-      <c r="J112" t="n">
-        <v>2.427</v>
       </c>
     </row>
     <row r="113">
@@ -10320,26 +10391,26 @@
           <t>2024-11</t>
         </is>
       </c>
-      <c r="C113" t="n">
+      <c r="B113" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D113" t="n">
         <v>2.38</v>
       </c>
-      <c r="D113" t="n">
-        <v>0.831</v>
-      </c>
       <c r="E113" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="G113" t="n">
         <v>2.838</v>
       </c>
-      <c r="F113" t="n">
-        <v>2.183</v>
-      </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>0.381</v>
       </c>
-      <c r="I113" t="n">
+      <c r="J113" t="n">
         <v>4.609</v>
-      </c>
-      <c r="J113" t="n">
-        <v>2.021</v>
       </c>
     </row>
     <row r="114">
@@ -10348,29 +10419,29 @@
           <t>2024-12</t>
         </is>
       </c>
-      <c r="C114" t="n">
+      <c r="B114" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="D114" t="n">
         <v>2.365</v>
       </c>
-      <c r="D114" t="n">
-        <v>0.785</v>
-      </c>
       <c r="E114" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="G114" t="n">
         <v>2.751</v>
       </c>
-      <c r="F114" t="n">
-        <v>2.291</v>
-      </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>0.257</v>
       </c>
-      <c r="I114" t="n">
+      <c r="J114" t="n">
         <v>4.677</v>
-      </c>
-      <c r="J114" t="n">
-        <v>2.395</v>
       </c>
     </row>
     <row r="115">
@@ -10379,29 +10450,29 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="C115" t="n">
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
         <v>2.185</v>
       </c>
-      <c r="D115" t="n">
-        <v>1</v>
-      </c>
       <c r="E115" t="n">
+        <v>2.193</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="G115" t="n">
         <v>2.754</v>
       </c>
-      <c r="F115" t="n">
-        <v>2.193</v>
-      </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>0.427</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>1.511</v>
       </c>
-      <c r="I115" t="n">
+      <c r="J115" t="n">
         <v>4.853</v>
-      </c>
-      <c r="J115" t="n">
-        <v>1.969</v>
       </c>
     </row>
     <row r="116">
@@ -10410,29 +10481,29 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="C116" t="n">
+      <c r="B116" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="D116" t="n">
         <v>2.582</v>
       </c>
-      <c r="D116" t="n">
-        <v>0.868</v>
-      </c>
       <c r="E116" t="n">
+        <v>2.343</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.404</v>
+      </c>
+      <c r="G116" t="n">
         <v>2.85</v>
       </c>
-      <c r="F116" t="n">
-        <v>2.343</v>
-      </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>0.761</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>2.461</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
         <v>4.574</v>
-      </c>
-      <c r="J116" t="n">
-        <v>2.404</v>
       </c>
     </row>
     <row r="117">
@@ -10441,29 +10512,29 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="B117" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="D117" t="n">
         <v>2.341</v>
       </c>
-      <c r="D117" t="n">
-        <v>0.882</v>
-      </c>
       <c r="E117" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="G117" t="n">
         <v>3.251</v>
       </c>
-      <c r="F117" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>0.2</v>
       </c>
-      <c r="H117" t="n">
+      <c r="I117" t="n">
         <v>3.473</v>
       </c>
-      <c r="I117" t="n">
+      <c r="J117" t="n">
         <v>4.818</v>
-      </c>
-      <c r="J117" t="n">
-        <v>2.257</v>
       </c>
     </row>
     <row r="118">
@@ -10472,29 +10543,29 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="C118" t="n">
+      <c r="B118" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="D118" t="n">
         <v>2.317</v>
       </c>
-      <c r="D118" t="n">
-        <v>0.758</v>
-      </c>
       <c r="E118" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="G118" t="n">
         <v>3.347</v>
       </c>
-      <c r="F118" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>0.525</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>3.886</v>
       </c>
-      <c r="I118" t="n">
+      <c r="J118" t="n">
         <v>4.631</v>
-      </c>
-      <c r="J118" t="n">
-        <v>2.502</v>
       </c>
     </row>
     <row r="119">
@@ -10503,29 +10574,29 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="C119" t="n">
+      <c r="B119" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="D119" t="n">
         <v>2.196</v>
       </c>
-      <c r="D119" t="n">
-        <v>0.847</v>
-      </c>
       <c r="E119" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G119" t="n">
         <v>3.3</v>
       </c>
-      <c r="F119" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="G119" t="n">
+      <c r="H119" t="n">
         <v>0.61</v>
       </c>
-      <c r="H119" t="n">
+      <c r="I119" t="n">
         <v>4.23</v>
       </c>
-      <c r="I119" t="n">
+      <c r="J119" t="n">
         <v>4.39</v>
-      </c>
-      <c r="J119" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="120">
@@ -10534,29 +10605,29 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="C120" t="n">
+      <c r="B120" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="D120" t="n">
         <v>2.259</v>
       </c>
-      <c r="D120" t="n">
-        <v>0.899</v>
-      </c>
       <c r="E120" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="G120" t="n">
         <v>3.13</v>
       </c>
-      <c r="F120" t="n">
-        <v>1.677</v>
-      </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>0.754</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>4.893</v>
       </c>
-      <c r="I120" t="n">
+      <c r="J120" t="n">
         <v>3.084</v>
-      </c>
-      <c r="J120" t="n">
-        <v>2.442</v>
       </c>
     </row>
     <row r="121">
@@ -10565,29 +10636,29 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="C121" t="n">
+      <c r="B121" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D121" t="n">
         <v>2.388</v>
       </c>
-      <c r="D121" t="n">
-        <v>0.75</v>
-      </c>
       <c r="E121" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="G121" t="n">
         <v>3.043</v>
       </c>
-      <c r="F121" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>0.255</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>4.92</v>
       </c>
-      <c r="I121" t="n">
+      <c r="J121" t="n">
         <v>4.035</v>
-      </c>
-      <c r="J121" t="n">
-        <v>2.109</v>
       </c>
     </row>
     <row r="122">
@@ -10596,29 +10667,29 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="C122" t="n">
+      <c r="B122" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="D122" t="n">
         <v>2.334</v>
       </c>
-      <c r="D122" t="n">
-        <v>0.798</v>
-      </c>
       <c r="E122" t="n">
+        <v>1.936</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.134</v>
+      </c>
+      <c r="G122" t="n">
         <v>3.144</v>
       </c>
-      <c r="F122" t="n">
-        <v>1.936</v>
-      </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>0.469</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>5.517</v>
       </c>
-      <c r="I122" t="n">
+      <c r="J122" t="n">
         <v>4.155</v>
-      </c>
-      <c r="J122" t="n">
-        <v>2.134</v>
       </c>
     </row>
     <row r="123">
@@ -10627,29 +10698,29 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="C123" t="n">
+      <c r="B123" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="D123" t="n">
         <v>2.546</v>
       </c>
-      <c r="D123" t="n">
-        <v>0.541</v>
-      </c>
       <c r="E123" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.179</v>
+      </c>
+      <c r="G123" t="n">
         <v>3.132</v>
       </c>
-      <c r="F123" t="n">
-        <v>2.012</v>
-      </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>0.726</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>5.711</v>
       </c>
-      <c r="I123" t="n">
+      <c r="J123" t="n">
         <v>4.221</v>
-      </c>
-      <c r="J123" t="n">
-        <v>2.179</v>
       </c>
     </row>
     <row r="124">
@@ -10658,29 +10729,29 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="C124" t="n">
+      <c r="B124" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="D124" t="n">
         <v>2.684</v>
       </c>
-      <c r="D124" t="n">
-        <v>0.546</v>
-      </c>
       <c r="E124" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.459</v>
+      </c>
+      <c r="G124" t="n">
         <v>2.748</v>
       </c>
-      <c r="F124" t="n">
-        <v>1.997</v>
-      </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>0.496</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>7.541</v>
       </c>
-      <c r="I124" t="n">
+      <c r="J124" t="n">
         <v>4.489</v>
-      </c>
-      <c r="J124" t="n">
-        <v>2.459</v>
       </c>
     </row>
     <row r="125">
@@ -10689,29 +10760,29 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="C125" t="n">
+      <c r="B125" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="D125" t="n">
         <v>3.095</v>
       </c>
-      <c r="D125" t="n">
-        <v>0.723</v>
-      </c>
       <c r="E125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.326</v>
+      </c>
+      <c r="G125" t="n">
         <v>3.385</v>
       </c>
-      <c r="F125" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>0.531</v>
       </c>
-      <c r="H125" t="n">
+      <c r="I125" t="n">
         <v>7.614</v>
       </c>
-      <c r="I125" t="n">
+      <c r="J125" t="n">
         <v>4.926</v>
-      </c>
-      <c r="J125" t="n">
-        <v>2.326</v>
       </c>
     </row>
     <row r="126">
@@ -10720,29 +10791,29 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="C126" t="n">
+      <c r="B126" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="D126" t="n">
         <v>3.189</v>
       </c>
-      <c r="D126" t="n">
-        <v>1.007</v>
-      </c>
       <c r="E126" t="n">
+        <v>2.463</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="G126" t="n">
         <v>3.581</v>
       </c>
-      <c r="F126" t="n">
-        <v>2.463</v>
-      </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>0.805</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>7.775</v>
       </c>
-      <c r="I126" t="n">
+      <c r="J126" t="n">
         <v>4.725</v>
-      </c>
-      <c r="J126" t="n">
-        <v>2.438</v>
       </c>
     </row>
     <row r="127">
@@ -10751,29 +10822,29 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="C127" t="n">
+      <c r="B127" t="n">
+        <v>0.838</v>
+      </c>
+      <c r="D127" t="n">
         <v>2.945</v>
       </c>
-      <c r="D127" t="n">
-        <v>0.838</v>
-      </c>
       <c r="E127" t="n">
+        <v>2.253</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="G127" t="n">
         <v>3.321</v>
       </c>
-      <c r="F127" t="n">
-        <v>2.253</v>
-      </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>0.361</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>8.148</v>
       </c>
-      <c r="I127" t="n">
+      <c r="J127" t="n">
         <v>4.649</v>
-      </c>
-      <c r="J127" t="n">
-        <v>2.232</v>
       </c>
     </row>
     <row r="128">
@@ -10782,29 +10853,29 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="C128" t="n">
+      <c r="B128" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="D128" t="n">
         <v>3.317</v>
       </c>
-      <c r="D128" t="n">
-        <v>0.719</v>
-      </c>
       <c r="E128" t="n">
+        <v>2.269</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="G128" t="n">
         <v>3.384</v>
       </c>
-      <c r="F128" t="n">
-        <v>2.269</v>
-      </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>0.294</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>7.524</v>
       </c>
-      <c r="I128" t="n">
+      <c r="J128" t="n">
         <v>4.756</v>
-      </c>
-      <c r="J128" t="n">
-        <v>2.441</v>
       </c>
     </row>
     <row r="129">
@@ -10813,29 +10884,29 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="C129" t="n">
+      <c r="B129" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="D129" t="n">
         <v>3.361</v>
       </c>
-      <c r="D129" t="n">
-        <v>0.9379999999999999</v>
-      </c>
       <c r="E129" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="G129" t="n">
         <v>3.317</v>
       </c>
-      <c r="F129" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>0.518</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>8.334</v>
       </c>
-      <c r="I129" t="n">
+      <c r="J129" t="n">
         <v>4.918</v>
-      </c>
-      <c r="J129" t="n">
-        <v>2.455</v>
       </c>
     </row>
     <row r="130">
@@ -10845,31 +10916,31 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="C130" t="n">
         <v>0.263</v>
       </c>
-      <c r="C130" t="n">
+      <c r="D130" t="n">
         <v>3.154</v>
       </c>
-      <c r="D130" t="n">
-        <v>0.762</v>
-      </c>
       <c r="E130" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="G130" t="n">
         <v>3.437</v>
       </c>
-      <c r="F130" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>0.555</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>7.89</v>
       </c>
-      <c r="I130" t="n">
+      <c r="J130" t="n">
         <v>4.745</v>
-      </c>
-      <c r="J130" t="n">
-        <v>2.511</v>
       </c>
     </row>
     <row r="131">
@@ -10879,31 +10950,31 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="C131" t="n">
         <v>0.244</v>
       </c>
-      <c r="C131" t="n">
+      <c r="D131" t="n">
         <v>3.122</v>
       </c>
-      <c r="D131" t="n">
-        <v>0.883</v>
-      </c>
       <c r="E131" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="G131" t="n">
         <v>3.066</v>
       </c>
-      <c r="F131" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>0.331</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>7.846</v>
       </c>
-      <c r="I131" t="n">
+      <c r="J131" t="n">
         <v>4.314</v>
-      </c>
-      <c r="J131" t="n">
-        <v>1.993</v>
       </c>
     </row>
     <row r="132">
@@ -10913,31 +10984,31 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="C132" t="n">
         <v>0.251</v>
       </c>
-      <c r="C132" t="n">
+      <c r="D132" t="n">
         <v>3.271</v>
       </c>
-      <c r="D132" t="n">
-        <v>0.765</v>
-      </c>
       <c r="E132" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G132" t="n">
         <v>3.177</v>
       </c>
-      <c r="F132" t="n">
-        <v>2.187</v>
-      </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>7.62</v>
       </c>
-      <c r="I132" t="n">
+      <c r="J132" t="n">
         <v>4.436</v>
-      </c>
-      <c r="J132" t="n">
-        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -8169,47 +8169,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Calcasieu Pass</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Cove Point</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>Golden Pass</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>Corpus Christi</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Cameron</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Freeport</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Calcasieu Pass</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Plaquemines</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="C8" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="C9" t="n">
         <v>0.373</v>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="C10" t="n">
         <v>0.364</v>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="C11" t="n">
         <v>0.346</v>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="C12" t="n">
         <v>0.597</v>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="C13" t="n">
         <v>0.552</v>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="C14" t="n">
         <v>0.966</v>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="C15" t="n">
         <v>0.607</v>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="C16" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="C17" t="n">
         <v>1.196</v>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="C18" t="n">
         <v>1.468</v>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="C19" t="n">
         <v>1.801</v>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="C20" t="n">
         <v>2.024</v>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="C21" t="n">
         <v>1.528</v>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="C22" t="n">
         <v>1.838</v>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="C23" t="n">
         <v>2.136</v>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="C24" t="n">
         <v>1.905</v>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="C25" t="n">
         <v>1.883</v>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="C26" t="n">
         <v>1.597</v>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="C27" t="n">
         <v>1.986</v>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="C28" t="n">
         <v>2.832</v>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="C29" t="n">
         <v>2.906</v>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="C30" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="C31" t="n">
         <v>2.543</v>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="C32" t="n">
         <v>2.864</v>
       </c>
     </row>
@@ -8529,11 +8529,11 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="C33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="E33" t="n">
         <v>0.105</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.11</v>
       </c>
     </row>
     <row r="34">
@@ -8542,11 +8542,11 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="C34" t="n">
+        <v>2.788</v>
+      </c>
+      <c r="E34" t="n">
         <v>0.325</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2.788</v>
       </c>
     </row>
     <row r="35">
@@ -8555,11 +8555,11 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="C35" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.77</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2.562</v>
       </c>
     </row>
     <row r="36">
@@ -8568,11 +8568,11 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="C36" t="n">
+        <v>2.213</v>
+      </c>
+      <c r="E36" t="n">
         <v>0.457</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2.213</v>
       </c>
     </row>
     <row r="37">
@@ -8581,11 +8581,11 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="C37" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="E37" t="n">
         <v>0.675</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2.778</v>
       </c>
     </row>
     <row r="38">
@@ -8594,11 +8594,11 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="C38" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.676</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.54</v>
       </c>
     </row>
     <row r="39">
@@ -8607,11 +8607,11 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="C39" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="E39" t="n">
         <v>0.449</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2.507</v>
       </c>
     </row>
     <row r="40">
@@ -8620,11 +8620,11 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="C40" t="n">
+        <v>2.932</v>
+      </c>
+      <c r="E40" t="n">
         <v>0.226</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2.932</v>
       </c>
     </row>
     <row r="41">
@@ -8633,11 +8633,11 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="C41" t="n">
+        <v>3.202</v>
+      </c>
+      <c r="E41" t="n">
         <v>0.701</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.202</v>
       </c>
     </row>
     <row r="42">
@@ -8646,14 +8646,14 @@
           <t>2018-12</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="C42" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E42" t="n">
         <v>0.711</v>
       </c>
-      <c r="D42" t="n">
+      <c r="J42" t="n">
         <v>0.241</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.36</v>
       </c>
     </row>
     <row r="43">
@@ -8662,14 +8662,14 @@
           <t>2019-01</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="C43" t="n">
+        <v>3.367</v>
+      </c>
+      <c r="E43" t="n">
         <v>0.714</v>
       </c>
-      <c r="D43" t="n">
+      <c r="J43" t="n">
         <v>0.378</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.367</v>
       </c>
     </row>
     <row r="44">
@@ -8678,14 +8678,14 @@
           <t>2019-02</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="C44" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="E44" t="n">
         <v>0.915</v>
       </c>
-      <c r="D44" t="n">
+      <c r="J44" t="n">
         <v>0.145</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.942</v>
       </c>
     </row>
     <row r="45">
@@ -8694,14 +8694,14 @@
           <t>2019-03</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="C45" t="n">
+        <v>3.291</v>
+      </c>
+      <c r="E45" t="n">
         <v>0.599</v>
       </c>
-      <c r="D45" t="n">
+      <c r="J45" t="n">
         <v>0.706</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.291</v>
       </c>
     </row>
     <row r="46">
@@ -8710,14 +8710,14 @@
           <t>2019-04</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="C46" t="n">
+        <v>3.054</v>
+      </c>
+      <c r="E46" t="n">
         <v>0.867</v>
       </c>
-      <c r="D46" t="n">
+      <c r="J46" t="n">
         <v>0.6919999999999999</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.054</v>
       </c>
     </row>
     <row r="47">
@@ -8726,17 +8726,17 @@
           <t>2019-05</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="C47" t="n">
+        <v>3.762</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="E47" t="n">
         <v>0.602</v>
       </c>
-      <c r="D47" t="n">
+      <c r="J47" t="n">
         <v>0.614</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.762</v>
       </c>
     </row>
     <row r="48">
@@ -8745,17 +8745,17 @@
           <t>2019-06</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="C48" t="n">
+        <v>3.551</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="E48" t="n">
         <v>0.731</v>
       </c>
-      <c r="D48" t="n">
+      <c r="J48" t="n">
         <v>0.765</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.551</v>
       </c>
     </row>
     <row r="49">
@@ -8764,17 +8764,17 @@
           <t>2019-07</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="C49" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="E49" t="n">
         <v>0.731</v>
       </c>
-      <c r="D49" t="n">
+      <c r="J49" t="n">
         <v>1.184</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.248</v>
-      </c>
-      <c r="J49" t="n">
-        <v>3.347</v>
       </c>
     </row>
     <row r="50">
@@ -8783,17 +8783,17 @@
           <t>2019-08</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="C50" t="n">
+        <v>2.696</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="E50" t="n">
         <v>0.699</v>
       </c>
-      <c r="D50" t="n">
+      <c r="J50" t="n">
         <v>1.084</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2.696</v>
       </c>
     </row>
     <row r="51">
@@ -8802,20 +8802,20 @@
           <t>2019-09</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="C51" t="n">
+        <v>3.461</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E51" t="n">
         <v>0.5</v>
       </c>
-      <c r="D51" t="n">
+      <c r="I51" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="J51" t="n">
         <v>1.26</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3.461</v>
       </c>
     </row>
     <row r="52">
@@ -8824,20 +8824,20 @@
           <t>2019-10</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="C52" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="E52" t="n">
         <v>0.244</v>
       </c>
-      <c r="D52" t="n">
+      <c r="I52" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="J52" t="n">
         <v>1.488</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="J52" t="n">
-        <v>3.775</v>
       </c>
     </row>
     <row r="53">
@@ -8846,20 +8846,20 @@
           <t>2019-11</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="C53" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="E53" t="n">
         <v>0.852</v>
       </c>
-      <c r="D53" t="n">
+      <c r="I53" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="J53" t="n">
         <v>1.357</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3.852</v>
       </c>
     </row>
     <row r="54">
@@ -8868,23 +8868,23 @@
           <t>2019-12</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="C54" t="n">
+        <v>3.813</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E54" t="n">
         <v>0.729</v>
       </c>
-      <c r="D54" t="n">
+      <c r="G54" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J54" t="n">
         <v>1.461</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="J54" t="n">
-        <v>3.813</v>
       </c>
     </row>
     <row r="55">
@@ -8893,23 +8893,23 @@
           <t>2020-01</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="C55" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="E55" t="n">
         <v>0.722</v>
       </c>
-      <c r="D55" t="n">
+      <c r="G55" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="J55" t="n">
         <v>1.426</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1.456</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="J55" t="n">
-        <v>4.018</v>
       </c>
     </row>
     <row r="56">
@@ -8918,20 +8918,20 @@
           <t>2020-02</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="C56" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="E56" t="n">
         <v>0.758</v>
       </c>
-      <c r="D56" t="n">
+      <c r="I56" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="J56" t="n">
         <v>1.55</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1.446</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.684</v>
       </c>
     </row>
     <row r="57">
@@ -8940,20 +8940,20 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="C57" t="n">
+        <v>3.447</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="E57" t="n">
         <v>0.831</v>
       </c>
-      <c r="D57" t="n">
+      <c r="I57" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="J57" t="n">
         <v>1.462</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1.635</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.447</v>
       </c>
     </row>
     <row r="58">
@@ -8962,20 +8962,20 @@
           <t>2020-04</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="C58" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="E58" t="n">
         <v>0.608</v>
       </c>
-      <c r="D58" t="n">
+      <c r="I58" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="J58" t="n">
         <v>1.245</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3.333</v>
       </c>
     </row>
     <row r="59">
@@ -8984,20 +8984,20 @@
           <t>2020-05</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="C59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="E59" t="n">
         <v>0.708</v>
       </c>
-      <c r="D59" t="n">
+      <c r="I59" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="J59" t="n">
         <v>0.831</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2.73</v>
       </c>
     </row>
     <row r="60">
@@ -9006,20 +9006,20 @@
           <t>2020-06</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="C60" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="E60" t="n">
         <v>0.763</v>
       </c>
-      <c r="D60" t="n">
+      <c r="I60" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.307</v>
-      </c>
-      <c r="E60" t="n">
-        <v>1.366</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.978</v>
       </c>
     </row>
     <row r="61">
@@ -9028,20 +9028,20 @@
           <t>2020-07</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="C61" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="E61" t="n">
         <v>0.711</v>
       </c>
-      <c r="D61" t="n">
+      <c r="I61" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.373</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1.099</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="J61" t="n">
-        <v>1.063</v>
       </c>
     </row>
     <row r="62">
@@ -9050,23 +9050,23 @@
           <t>2020-08</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="C62" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="E62" t="n">
         <v>0.596</v>
       </c>
-      <c r="D62" t="n">
+      <c r="G62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="J62" t="n">
         <v>0.601</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1.031</v>
       </c>
     </row>
     <row r="63">
@@ -9075,20 +9075,20 @@
           <t>2020-09</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="C63" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="E63" t="n">
         <v>0.621</v>
       </c>
-      <c r="D63" t="n">
+      <c r="G63" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="J63" t="n">
         <v>1.363</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1.127</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="J63" t="n">
-        <v>2.241</v>
       </c>
     </row>
     <row r="64">
@@ -9097,23 +9097,23 @@
           <t>2020-10</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="C64" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="E64" t="n">
         <v>0.373</v>
       </c>
-      <c r="D64" t="n">
+      <c r="G64" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="J64" t="n">
         <v>1.551</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1.892</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3.106</v>
       </c>
     </row>
     <row r="65">
@@ -9122,23 +9122,23 @@
           <t>2020-11</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="C65" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.838</v>
+      </c>
+      <c r="E65" t="n">
         <v>0.852</v>
       </c>
-      <c r="D65" t="n">
+      <c r="G65" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I65" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="J65" t="n">
         <v>1.633</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="F65" t="n">
-        <v>1.953</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="J65" t="n">
-        <v>3.684</v>
       </c>
     </row>
     <row r="66">
@@ -9147,23 +9147,23 @@
           <t>2020-12</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="C66" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.939</v>
+      </c>
+      <c r="E66" t="n">
         <v>0.718</v>
       </c>
-      <c r="D66" t="n">
+      <c r="G66" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.057</v>
+      </c>
+      <c r="J66" t="n">
         <v>1.821</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1.939</v>
-      </c>
-      <c r="F66" t="n">
-        <v>2.057</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="J66" t="n">
-        <v>3.845</v>
       </c>
     </row>
     <row r="67">
@@ -9172,20 +9172,20 @@
           <t>2021-01</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="C67" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="E67" t="n">
         <v>0.718</v>
       </c>
-      <c r="D67" t="n">
+      <c r="I67" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="J67" t="n">
         <v>2.012</v>
-      </c>
-      <c r="E67" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="F67" t="n">
-        <v>2.148</v>
-      </c>
-      <c r="J67" t="n">
-        <v>3.905</v>
       </c>
     </row>
     <row r="68">
@@ -9194,23 +9194,23 @@
           <t>2021-02</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="C68" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E68" t="n">
         <v>0.671</v>
       </c>
-      <c r="D68" t="n">
+      <c r="G68" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="J68" t="n">
         <v>1.297</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1.186</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="J68" t="n">
-        <v>3.263</v>
       </c>
     </row>
     <row r="69">
@@ -9219,23 +9219,23 @@
           <t>2021-03</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="C69" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="E69" t="n">
         <v>0.845</v>
       </c>
-      <c r="D69" t="n">
+      <c r="G69" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="I69" t="n">
+        <v>2.237</v>
+      </c>
+      <c r="J69" t="n">
         <v>2.201</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1.755</v>
-      </c>
-      <c r="F69" t="n">
-        <v>2.237</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="J69" t="n">
-        <v>4.013</v>
       </c>
     </row>
     <row r="70">
@@ -9244,23 +9244,23 @@
           <t>2021-04</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="C70" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.848</v>
+      </c>
+      <c r="E70" t="n">
         <v>0.622</v>
       </c>
-      <c r="D70" t="n">
+      <c r="G70" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2.203</v>
+      </c>
+      <c r="J70" t="n">
         <v>2.175</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1.848</v>
-      </c>
-      <c r="F70" t="n">
-        <v>2.203</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J70" t="n">
-        <v>3.955</v>
       </c>
     </row>
     <row r="71">
@@ -9269,23 +9269,23 @@
           <t>2021-05</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="C71" t="n">
+        <v>3.805</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="E71" t="n">
         <v>0.787</v>
       </c>
-      <c r="D71" t="n">
+      <c r="G71" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2.223</v>
+      </c>
+      <c r="J71" t="n">
         <v>2.066</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="F71" t="n">
-        <v>2.223</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="J71" t="n">
-        <v>3.805</v>
       </c>
     </row>
     <row r="72">
@@ -9294,23 +9294,23 @@
           <t>2021-06</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="C72" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1.418</v>
+      </c>
+      <c r="E72" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="D72" t="n">
+      <c r="G72" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2.127</v>
+      </c>
+      <c r="J72" t="n">
         <v>2.236</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1.418</v>
-      </c>
-      <c r="F72" t="n">
-        <v>2.127</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="J72" t="n">
-        <v>3.118</v>
       </c>
     </row>
     <row r="73">
@@ -9319,23 +9319,23 @@
           <t>2021-07</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="C73" t="n">
+        <v>3.402</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E73" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D73" t="n">
+      <c r="G73" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="I73" t="n">
+        <v>2.141</v>
+      </c>
+      <c r="J73" t="n">
         <v>2.126</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="F73" t="n">
-        <v>2.141</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="J73" t="n">
-        <v>3.402</v>
       </c>
     </row>
     <row r="74">
@@ -9344,23 +9344,23 @@
           <t>2021-08</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="C74" t="n">
+        <v>3.492</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1.467</v>
+      </c>
+      <c r="E74" t="n">
         <v>0.785</v>
       </c>
-      <c r="D74" t="n">
+      <c r="G74" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="J74" t="n">
         <v>2.171</v>
-      </c>
-      <c r="E74" t="n">
-        <v>1.467</v>
-      </c>
-      <c r="F74" t="n">
-        <v>2.307</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="J74" t="n">
-        <v>3.492</v>
       </c>
     </row>
     <row r="75">
@@ -9369,23 +9369,23 @@
           <t>2021-09</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="C75" t="n">
+        <v>3.619</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="E75" t="n">
         <v>0.499</v>
       </c>
-      <c r="D75" t="n">
+      <c r="G75" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="J75" t="n">
         <v>2.34</v>
-      </c>
-      <c r="E75" t="n">
-        <v>1.919</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1.764</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="J75" t="n">
-        <v>3.619</v>
       </c>
     </row>
     <row r="76">
@@ -9394,23 +9394,23 @@
           <t>2021-10</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="C76" t="n">
+        <v>3.561</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="E76" t="n">
         <v>0.348</v>
       </c>
-      <c r="D76" t="n">
+      <c r="G76" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="I76" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="J76" t="n">
         <v>2.28</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1.852</v>
-      </c>
-      <c r="F76" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="J76" t="n">
-        <v>3.561</v>
       </c>
     </row>
     <row r="77">
@@ -9419,23 +9419,23 @@
           <t>2021-11</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="C77" t="n">
+        <v>4.097</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="E77" t="n">
         <v>0.797</v>
       </c>
-      <c r="D77" t="n">
+      <c r="G77" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.597</v>
+      </c>
+      <c r="J77" t="n">
         <v>2.307</v>
-      </c>
-      <c r="E77" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1.597</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="J77" t="n">
-        <v>4.097</v>
       </c>
     </row>
     <row r="78">
@@ -9444,23 +9444,23 @@
           <t>2021-12</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="C78" t="n">
+        <v>4.186</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2.158</v>
+      </c>
+      <c r="E78" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D78" t="n">
+      <c r="G78" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2.365</v>
+      </c>
+      <c r="J78" t="n">
         <v>2.249</v>
-      </c>
-      <c r="E78" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="F78" t="n">
-        <v>2.365</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="J78" t="n">
-        <v>4.186</v>
       </c>
     </row>
     <row r="79">
@@ -9469,23 +9469,23 @@
           <t>2022-01</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="C79" t="n">
+        <v>4.576</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2.151</v>
+      </c>
+      <c r="E79" t="n">
         <v>0.886</v>
       </c>
-      <c r="D79" t="n">
+      <c r="G79" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2.248</v>
+      </c>
+      <c r="J79" t="n">
         <v>2.347</v>
-      </c>
-      <c r="E79" t="n">
-        <v>2.151</v>
-      </c>
-      <c r="F79" t="n">
-        <v>2.248</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="J79" t="n">
-        <v>4.576</v>
       </c>
     </row>
     <row r="80">
@@ -9494,23 +9494,23 @@
           <t>2022-02</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="C80" t="n">
+        <v>4.318</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2.116</v>
+      </c>
+      <c r="E80" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="D80" t="n">
+      <c r="G80" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2.043</v>
+      </c>
+      <c r="J80" t="n">
         <v>2.654</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2.116</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2.043</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="J80" t="n">
-        <v>4.318</v>
       </c>
     </row>
     <row r="81">
@@ -9520,25 +9520,25 @@
         </is>
       </c>
       <c r="B81" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4.588</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="E81" t="n">
         <v>0.754</v>
       </c>
-      <c r="D81" t="n">
+      <c r="G81" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2.268</v>
+      </c>
+      <c r="J81" t="n">
         <v>2.115</v>
-      </c>
-      <c r="E81" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="F81" t="n">
-        <v>2.268</v>
-      </c>
-      <c r="G81" t="n">
-        <v>1.279</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="J81" t="n">
-        <v>4.588</v>
       </c>
     </row>
     <row r="82">
@@ -9548,25 +9548,25 @@
         </is>
       </c>
       <c r="B82" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4.526</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2.095</v>
+      </c>
+      <c r="E82" t="n">
         <v>0.794</v>
       </c>
-      <c r="D82" t="n">
+      <c r="G82" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.427</v>
+      </c>
+      <c r="J82" t="n">
         <v>2.117</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2.095</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.427</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.784</v>
-      </c>
-      <c r="J82" t="n">
-        <v>4.526</v>
       </c>
     </row>
     <row r="83">
@@ -9576,25 +9576,25 @@
         </is>
       </c>
       <c r="B83" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4.597</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="E83" t="n">
         <v>0.781</v>
       </c>
-      <c r="D83" t="n">
+      <c r="G83" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="J83" t="n">
         <v>2.179</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1.426</v>
-      </c>
-      <c r="F83" t="n">
-        <v>2.232</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1.774</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="J83" t="n">
-        <v>4.597</v>
       </c>
     </row>
     <row r="84">
@@ -9604,25 +9604,25 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E84" t="n">
         <v>0.716</v>
       </c>
-      <c r="D84" t="n">
+      <c r="G84" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="J84" t="n">
         <v>2.315</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2.334</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.777</v>
-      </c>
-      <c r="J84" t="n">
-        <v>3.84</v>
       </c>
     </row>
     <row r="85">
@@ -9632,22 +9632,22 @@
         </is>
       </c>
       <c r="B85" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1.832</v>
+      </c>
+      <c r="E85" t="n">
         <v>0.851</v>
       </c>
-      <c r="D85" t="n">
+      <c r="G85" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J85" t="n">
         <v>2.218</v>
-      </c>
-      <c r="E85" t="n">
-        <v>1.832</v>
-      </c>
-      <c r="G85" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J85" t="n">
-        <v>4.168</v>
       </c>
     </row>
     <row r="86">
@@ -9657,22 +9657,22 @@
         </is>
       </c>
       <c r="B86" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4.173</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E86" t="n">
         <v>0.753</v>
       </c>
-      <c r="D86" t="n">
+      <c r="G86" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="J86" t="n">
         <v>2.23</v>
-      </c>
-      <c r="E86" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="G86" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="J86" t="n">
-        <v>4.173</v>
       </c>
     </row>
     <row r="87">
@@ -9682,22 +9682,22 @@
         </is>
       </c>
       <c r="B87" t="n">
+        <v>2.796</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4.201</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1.912</v>
+      </c>
+      <c r="E87" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D87" t="n">
+      <c r="G87" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="J87" t="n">
         <v>2.173</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1.912</v>
-      </c>
-      <c r="G87" t="n">
-        <v>2.796</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="J87" t="n">
-        <v>4.201</v>
       </c>
     </row>
     <row r="88">
@@ -9706,20 +9706,20 @@
           <t>2022-10</t>
         </is>
       </c>
+      <c r="B88" t="n">
+        <v>3.186</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.586</v>
+      </c>
       <c r="D88" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="J88" t="n">
         <v>2.348</v>
-      </c>
-      <c r="E88" t="n">
-        <v>2.094</v>
-      </c>
-      <c r="G88" t="n">
-        <v>3.186</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="J88" t="n">
-        <v>4.586</v>
       </c>
     </row>
     <row r="89">
@@ -9729,22 +9729,22 @@
         </is>
       </c>
       <c r="B89" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="E89" t="n">
         <v>0.742</v>
       </c>
-      <c r="D89" t="n">
+      <c r="G89" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="J89" t="n">
         <v>2.072</v>
-      </c>
-      <c r="E89" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="G89" t="n">
-        <v>2.625</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="J89" t="n">
-        <v>4.363</v>
       </c>
     </row>
     <row r="90">
@@ -9754,22 +9754,22 @@
         </is>
       </c>
       <c r="B90" t="n">
+        <v>2.655</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="E90" t="n">
         <v>1.047</v>
       </c>
-      <c r="D90" t="n">
+      <c r="G90" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J90" t="n">
         <v>2.255</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2.088</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2.655</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J90" t="n">
-        <v>4.893</v>
       </c>
     </row>
     <row r="91">
@@ -9779,22 +9779,22 @@
         </is>
       </c>
       <c r="B91" t="n">
+        <v>3.007</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="E91" t="n">
         <v>0.731</v>
       </c>
-      <c r="D91" t="n">
+      <c r="G91" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="J91" t="n">
         <v>2.2</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2.183</v>
-      </c>
-      <c r="G91" t="n">
-        <v>3.007</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="J91" t="n">
-        <v>4.896</v>
       </c>
     </row>
     <row r="92">
@@ -9804,25 +9804,25 @@
         </is>
       </c>
       <c r="B92" t="n">
+        <v>3.501</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="E92" t="n">
         <v>0.756</v>
       </c>
-      <c r="D92" t="n">
+      <c r="G92" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J92" t="n">
         <v>2.496</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="G92" t="n">
-        <v>3.501</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.823</v>
-      </c>
-      <c r="J92" t="n">
-        <v>4.65</v>
       </c>
     </row>
     <row r="93">
@@ -9832,25 +9832,25 @@
         </is>
       </c>
       <c r="B93" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2.176</v>
+      </c>
+      <c r="E93" t="n">
         <v>0.976</v>
       </c>
-      <c r="D93" t="n">
+      <c r="G93" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.019</v>
+      </c>
+      <c r="J93" t="n">
         <v>2.361</v>
-      </c>
-      <c r="E93" t="n">
-        <v>2.176</v>
-      </c>
-      <c r="F93" t="n">
-        <v>1.019</v>
-      </c>
-      <c r="G93" t="n">
-        <v>2.682</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.803</v>
-      </c>
-      <c r="J93" t="n">
-        <v>4.605</v>
       </c>
     </row>
     <row r="94">
@@ -9860,25 +9860,25 @@
         </is>
       </c>
       <c r="B94" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4.977</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="E94" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D94" t="n">
+      <c r="G94" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2.271</v>
+      </c>
+      <c r="J94" t="n">
         <v>2.018</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1.992</v>
-      </c>
-      <c r="F94" t="n">
-        <v>2.271</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2.883</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="J94" t="n">
-        <v>4.977</v>
       </c>
     </row>
     <row r="95">
@@ -9888,25 +9888,25 @@
         </is>
       </c>
       <c r="B95" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4.436</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.368</v>
+      </c>
+      <c r="E95" t="n">
         <v>0.924</v>
       </c>
-      <c r="D95" t="n">
+      <c r="G95" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.405</v>
+      </c>
+      <c r="J95" t="n">
         <v>2.03</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="F95" t="n">
-        <v>2.405</v>
-      </c>
-      <c r="G95" t="n">
-        <v>2.943</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="J95" t="n">
-        <v>4.436</v>
       </c>
     </row>
     <row r="96">
@@ -9916,25 +9916,25 @@
         </is>
       </c>
       <c r="B96" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="E96" t="n">
         <v>0.845</v>
       </c>
-      <c r="D96" t="n">
+      <c r="G96" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="J96" t="n">
         <v>2.269</v>
-      </c>
-      <c r="E96" t="n">
-        <v>1.896</v>
-      </c>
-      <c r="F96" t="n">
-        <v>2.299</v>
-      </c>
-      <c r="G96" t="n">
-        <v>2.169</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="J96" t="n">
-        <v>3.043</v>
       </c>
     </row>
     <row r="97">
@@ -9944,25 +9944,25 @@
         </is>
       </c>
       <c r="B97" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="C97" t="n">
+        <v>3.985</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.751</v>
+      </c>
+      <c r="E97" t="n">
         <v>0.701</v>
       </c>
-      <c r="D97" t="n">
+      <c r="G97" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2.093</v>
+      </c>
+      <c r="J97" t="n">
         <v>2.062</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1.751</v>
-      </c>
-      <c r="F97" t="n">
-        <v>2.093</v>
-      </c>
-      <c r="G97" t="n">
-        <v>2.723</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0.651</v>
-      </c>
-      <c r="J97" t="n">
-        <v>3.985</v>
       </c>
     </row>
     <row r="98">
@@ -9972,25 +9972,25 @@
         </is>
       </c>
       <c r="B98" t="n">
+        <v>2.508</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.166</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="E98" t="n">
         <v>0.771</v>
       </c>
-      <c r="D98" t="n">
+      <c r="G98" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="I98" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J98" t="n">
         <v>2.195</v>
-      </c>
-      <c r="E98" t="n">
-        <v>1.761</v>
-      </c>
-      <c r="F98" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="G98" t="n">
-        <v>2.508</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="J98" t="n">
-        <v>4.166</v>
       </c>
     </row>
     <row r="99">
@@ -10000,25 +10000,25 @@
         </is>
       </c>
       <c r="B99" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4.193</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="E99" t="n">
         <v>0.635</v>
       </c>
-      <c r="D99" t="n">
+      <c r="G99" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="J99" t="n">
         <v>2.157</v>
-      </c>
-      <c r="E99" t="n">
-        <v>1.793</v>
-      </c>
-      <c r="F99" t="n">
-        <v>1.963</v>
-      </c>
-      <c r="G99" t="n">
-        <v>2.834</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.863</v>
-      </c>
-      <c r="J99" t="n">
-        <v>4.193</v>
       </c>
     </row>
     <row r="100">
@@ -10028,25 +10028,25 @@
         </is>
       </c>
       <c r="B100" t="n">
+        <v>3.366</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4.656</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="E100" t="n">
         <v>0.375</v>
       </c>
-      <c r="D100" t="n">
+      <c r="G100" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2.249</v>
+      </c>
+      <c r="J100" t="n">
         <v>2.229</v>
-      </c>
-      <c r="E100" t="n">
-        <v>2.094</v>
-      </c>
-      <c r="F100" t="n">
-        <v>2.249</v>
-      </c>
-      <c r="G100" t="n">
-        <v>3.366</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="J100" t="n">
-        <v>4.656</v>
       </c>
     </row>
     <row r="101">
@@ -10056,25 +10056,25 @@
         </is>
       </c>
       <c r="B101" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4.739</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="E101" t="n">
         <v>0.761</v>
       </c>
-      <c r="D101" t="n">
+      <c r="G101" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="I101" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="J101" t="n">
         <v>2.342</v>
-      </c>
-      <c r="E101" t="n">
-        <v>2.022</v>
-      </c>
-      <c r="F101" t="n">
-        <v>2.184</v>
-      </c>
-      <c r="G101" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.588</v>
-      </c>
-      <c r="J101" t="n">
-        <v>4.739</v>
       </c>
     </row>
     <row r="102">
@@ -10084,25 +10084,25 @@
         </is>
       </c>
       <c r="B102" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4.976</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="E102" t="n">
         <v>0.824</v>
       </c>
-      <c r="D102" t="n">
+      <c r="G102" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I102" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="J102" t="n">
         <v>2.257</v>
-      </c>
-      <c r="E102" t="n">
-        <v>2.334</v>
-      </c>
-      <c r="F102" t="n">
-        <v>2.504</v>
-      </c>
-      <c r="G102" t="n">
-        <v>3.175</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="J102" t="n">
-        <v>4.976</v>
       </c>
     </row>
     <row r="103">
@@ -10112,25 +10112,25 @@
         </is>
       </c>
       <c r="B103" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4.844</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2.178</v>
+      </c>
+      <c r="E103" t="n">
         <v>0.749</v>
       </c>
-      <c r="D103" t="n">
+      <c r="G103" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="J103" t="n">
         <v>2.148</v>
-      </c>
-      <c r="E103" t="n">
-        <v>2.178</v>
-      </c>
-      <c r="F103" t="n">
-        <v>1.855</v>
-      </c>
-      <c r="G103" t="n">
-        <v>3.573</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="J103" t="n">
-        <v>4.844</v>
       </c>
     </row>
     <row r="104">
@@ -10140,25 +10140,25 @@
         </is>
       </c>
       <c r="B104" t="n">
+        <v>3.334</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4.822</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.229</v>
+      </c>
+      <c r="E104" t="n">
         <v>0.898</v>
       </c>
-      <c r="D104" t="n">
+      <c r="G104" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="I104" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="J104" t="n">
         <v>2.096</v>
-      </c>
-      <c r="E104" t="n">
-        <v>2.229</v>
-      </c>
-      <c r="F104" t="n">
-        <v>1.559</v>
-      </c>
-      <c r="G104" t="n">
-        <v>3.334</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0.527</v>
-      </c>
-      <c r="J104" t="n">
-        <v>4.822</v>
       </c>
     </row>
     <row r="105">
@@ -10168,25 +10168,25 @@
         </is>
       </c>
       <c r="B105" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4.861</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="E105" t="n">
         <v>0.886</v>
       </c>
-      <c r="D105" t="n">
+      <c r="G105" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="J105" t="n">
         <v>2.154</v>
-      </c>
-      <c r="E105" t="n">
-        <v>2.072</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="G105" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="J105" t="n">
-        <v>4.861</v>
       </c>
     </row>
     <row r="106">
@@ -10196,25 +10196,25 @@
         </is>
       </c>
       <c r="B106" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1.946</v>
+      </c>
+      <c r="E106" t="n">
         <v>0.882</v>
       </c>
-      <c r="D106" t="n">
+      <c r="G106" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="J106" t="n">
         <v>1.821</v>
-      </c>
-      <c r="E106" t="n">
-        <v>1.946</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="G106" t="n">
-        <v>2.768</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="J106" t="n">
-        <v>4.35</v>
       </c>
     </row>
     <row r="107">
@@ -10224,25 +10224,25 @@
         </is>
       </c>
       <c r="B107" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="E107" t="n">
         <v>0.885</v>
       </c>
-      <c r="D107" t="n">
+      <c r="G107" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="J107" t="n">
         <v>2.163</v>
-      </c>
-      <c r="E107" t="n">
-        <v>1.528</v>
-      </c>
-      <c r="F107" t="n">
-        <v>1.942</v>
-      </c>
-      <c r="G107" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="J107" t="n">
-        <v>4.624</v>
       </c>
     </row>
     <row r="108">
@@ -10252,25 +10252,25 @@
         </is>
       </c>
       <c r="B108" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3.944</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1.849</v>
+      </c>
+      <c r="E108" t="n">
         <v>0.695</v>
       </c>
-      <c r="D108" t="n">
+      <c r="G108" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J108" t="n">
         <v>2.346</v>
-      </c>
-      <c r="E108" t="n">
-        <v>1.849</v>
-      </c>
-      <c r="F108" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="G108" t="n">
-        <v>3.038</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0.466</v>
-      </c>
-      <c r="J108" t="n">
-        <v>3.944</v>
       </c>
     </row>
     <row r="109">
@@ -10280,25 +10280,25 @@
         </is>
       </c>
       <c r="B109" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="E109" t="n">
         <v>0.745</v>
       </c>
-      <c r="D109" t="n">
+      <c r="G109" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="J109" t="n">
         <v>2.018</v>
-      </c>
-      <c r="E109" t="n">
-        <v>1.815</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="G109" t="n">
-        <v>2.762</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="J109" t="n">
-        <v>4.213</v>
       </c>
     </row>
     <row r="110">
@@ -10308,25 +10308,25 @@
         </is>
       </c>
       <c r="B110" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="C110" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.829</v>
+      </c>
+      <c r="E110" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="D110" t="n">
+      <c r="G110" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2.212</v>
+      </c>
+      <c r="J110" t="n">
         <v>2.234</v>
-      </c>
-      <c r="E110" t="n">
-        <v>1.829</v>
-      </c>
-      <c r="F110" t="n">
-        <v>2.212</v>
-      </c>
-      <c r="G110" t="n">
-        <v>2.298</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="J110" t="n">
-        <v>4.164</v>
       </c>
     </row>
     <row r="111">
@@ -10336,25 +10336,25 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.401</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1.885</v>
+      </c>
+      <c r="E111" t="n">
         <v>0.639</v>
       </c>
-      <c r="D111" t="n">
+      <c r="G111" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="I111" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="J111" t="n">
         <v>2.349</v>
-      </c>
-      <c r="E111" t="n">
-        <v>1.885</v>
-      </c>
-      <c r="F111" t="n">
-        <v>2.288</v>
-      </c>
-      <c r="G111" t="n">
-        <v>2.537</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="J111" t="n">
-        <v>4.401</v>
       </c>
     </row>
     <row r="112">
@@ -10364,25 +10364,25 @@
         </is>
       </c>
       <c r="B112" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.887</v>
+      </c>
+      <c r="E112" t="n">
         <v>0.448</v>
       </c>
-      <c r="D112" t="n">
+      <c r="G112" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2.427</v>
+      </c>
+      <c r="J112" t="n">
         <v>2.348</v>
-      </c>
-      <c r="E112" t="n">
-        <v>1.887</v>
-      </c>
-      <c r="F112" t="n">
-        <v>2.427</v>
-      </c>
-      <c r="G112" t="n">
-        <v>2.711</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.447</v>
-      </c>
-      <c r="J112" t="n">
-        <v>4.533</v>
       </c>
     </row>
     <row r="113">
@@ -10392,25 +10392,25 @@
         </is>
       </c>
       <c r="B113" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.609</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="E113" t="n">
         <v>0.831</v>
       </c>
-      <c r="D113" t="n">
+      <c r="G113" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="J113" t="n">
         <v>2.38</v>
-      </c>
-      <c r="E113" t="n">
-        <v>2.183</v>
-      </c>
-      <c r="F113" t="n">
-        <v>2.021</v>
-      </c>
-      <c r="G113" t="n">
-        <v>2.838</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="J113" t="n">
-        <v>4.609</v>
       </c>
     </row>
     <row r="114">
@@ -10420,28 +10420,28 @@
         </is>
       </c>
       <c r="B114" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.677</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="E114" t="n">
         <v>0.785</v>
       </c>
-      <c r="D114" t="n">
+      <c r="F114" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2.395</v>
+      </c>
+      <c r="J114" t="n">
         <v>2.365</v>
-      </c>
-      <c r="E114" t="n">
-        <v>2.291</v>
-      </c>
-      <c r="F114" t="n">
-        <v>2.395</v>
-      </c>
-      <c r="G114" t="n">
-        <v>2.751</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.6870000000000001</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="J114" t="n">
-        <v>4.677</v>
       </c>
     </row>
     <row r="115">
@@ -10451,28 +10451,28 @@
         </is>
       </c>
       <c r="B115" t="n">
+        <v>2.754</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.853</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2.193</v>
+      </c>
+      <c r="E115" t="n">
         <v>1</v>
       </c>
-      <c r="D115" t="n">
+      <c r="F115" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="I115" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="J115" t="n">
         <v>2.185</v>
-      </c>
-      <c r="E115" t="n">
-        <v>2.193</v>
-      </c>
-      <c r="F115" t="n">
-        <v>1.969</v>
-      </c>
-      <c r="G115" t="n">
-        <v>2.754</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="I115" t="n">
-        <v>1.511</v>
-      </c>
-      <c r="J115" t="n">
-        <v>4.853</v>
       </c>
     </row>
     <row r="116">
@@ -10482,28 +10482,28 @@
         </is>
       </c>
       <c r="B116" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4.574</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2.343</v>
+      </c>
+      <c r="E116" t="n">
         <v>0.868</v>
       </c>
-      <c r="D116" t="n">
+      <c r="F116" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="I116" t="n">
+        <v>2.404</v>
+      </c>
+      <c r="J116" t="n">
         <v>2.582</v>
-      </c>
-      <c r="E116" t="n">
-        <v>2.343</v>
-      </c>
-      <c r="F116" t="n">
-        <v>2.404</v>
-      </c>
-      <c r="G116" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="I116" t="n">
-        <v>2.461</v>
-      </c>
-      <c r="J116" t="n">
-        <v>4.574</v>
       </c>
     </row>
     <row r="117">
@@ -10513,28 +10513,28 @@
         </is>
       </c>
       <c r="B117" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="E117" t="n">
         <v>0.882</v>
       </c>
-      <c r="D117" t="n">
+      <c r="F117" t="n">
+        <v>3.473</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="J117" t="n">
         <v>2.341</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="F117" t="n">
-        <v>2.257</v>
-      </c>
-      <c r="G117" t="n">
-        <v>3.251</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I117" t="n">
-        <v>3.473</v>
-      </c>
-      <c r="J117" t="n">
-        <v>4.818</v>
       </c>
     </row>
     <row r="118">
@@ -10544,28 +10544,28 @@
         </is>
       </c>
       <c r="B118" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.631</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2.195</v>
+      </c>
+      <c r="E118" t="n">
         <v>0.758</v>
       </c>
-      <c r="D118" t="n">
+      <c r="F118" t="n">
+        <v>3.886</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I118" t="n">
+        <v>2.502</v>
+      </c>
+      <c r="J118" t="n">
         <v>2.317</v>
-      </c>
-      <c r="E118" t="n">
-        <v>2.195</v>
-      </c>
-      <c r="F118" t="n">
-        <v>2.502</v>
-      </c>
-      <c r="G118" t="n">
-        <v>3.347</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I118" t="n">
-        <v>3.886</v>
-      </c>
-      <c r="J118" t="n">
-        <v>4.631</v>
       </c>
     </row>
     <row r="119">
@@ -10575,28 +10575,28 @@
         </is>
       </c>
       <c r="B119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="E119" t="n">
         <v>0.847</v>
       </c>
-      <c r="D119" t="n">
+      <c r="F119" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J119" t="n">
         <v>2.196</v>
-      </c>
-      <c r="E119" t="n">
-        <v>1.442</v>
-      </c>
-      <c r="F119" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G119" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I119" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="J119" t="n">
-        <v>4.39</v>
       </c>
     </row>
     <row r="120">
@@ -10606,28 +10606,28 @@
         </is>
       </c>
       <c r="B120" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="C120" t="n">
+        <v>3.084</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="E120" t="n">
         <v>0.899</v>
       </c>
-      <c r="D120" t="n">
+      <c r="F120" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2.442</v>
+      </c>
+      <c r="J120" t="n">
         <v>2.259</v>
-      </c>
-      <c r="E120" t="n">
-        <v>1.677</v>
-      </c>
-      <c r="F120" t="n">
-        <v>2.442</v>
-      </c>
-      <c r="G120" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0.754</v>
-      </c>
-      <c r="I120" t="n">
-        <v>4.893</v>
-      </c>
-      <c r="J120" t="n">
-        <v>3.084</v>
       </c>
     </row>
     <row r="121">
@@ -10637,28 +10637,28 @@
         </is>
       </c>
       <c r="B121" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E121" t="n">
         <v>0.75</v>
       </c>
-      <c r="D121" t="n">
+      <c r="F121" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="J121" t="n">
         <v>2.388</v>
-      </c>
-      <c r="E121" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F121" t="n">
-        <v>2.109</v>
-      </c>
-      <c r="G121" t="n">
-        <v>3.043</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="I121" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="J121" t="n">
-        <v>4.035</v>
       </c>
     </row>
     <row r="122">
@@ -10668,28 +10668,28 @@
         </is>
       </c>
       <c r="B122" t="n">
+        <v>3.144</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.155</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1.936</v>
+      </c>
+      <c r="E122" t="n">
         <v>0.798</v>
       </c>
-      <c r="D122" t="n">
+      <c r="F122" t="n">
+        <v>5.517</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I122" t="n">
+        <v>2.134</v>
+      </c>
+      <c r="J122" t="n">
         <v>2.334</v>
-      </c>
-      <c r="E122" t="n">
-        <v>1.936</v>
-      </c>
-      <c r="F122" t="n">
-        <v>2.134</v>
-      </c>
-      <c r="G122" t="n">
-        <v>3.144</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="I122" t="n">
-        <v>5.517</v>
-      </c>
-      <c r="J122" t="n">
-        <v>4.155</v>
       </c>
     </row>
     <row r="123">
@@ -10699,28 +10699,28 @@
         </is>
       </c>
       <c r="B123" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.221</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="E123" t="n">
         <v>0.541</v>
       </c>
-      <c r="D123" t="n">
+      <c r="F123" t="n">
+        <v>5.711</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="I123" t="n">
+        <v>2.179</v>
+      </c>
+      <c r="J123" t="n">
         <v>2.546</v>
-      </c>
-      <c r="E123" t="n">
-        <v>2.012</v>
-      </c>
-      <c r="F123" t="n">
-        <v>2.179</v>
-      </c>
-      <c r="G123" t="n">
-        <v>3.132</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="I123" t="n">
-        <v>5.711</v>
-      </c>
-      <c r="J123" t="n">
-        <v>4.221</v>
       </c>
     </row>
     <row r="124">
@@ -10730,28 +10730,28 @@
         </is>
       </c>
       <c r="B124" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="E124" t="n">
         <v>0.546</v>
       </c>
-      <c r="D124" t="n">
+      <c r="F124" t="n">
+        <v>7.541</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2.459</v>
+      </c>
+      <c r="J124" t="n">
         <v>2.684</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1.997</v>
-      </c>
-      <c r="F124" t="n">
-        <v>2.459</v>
-      </c>
-      <c r="G124" t="n">
-        <v>2.748</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="I124" t="n">
-        <v>7.541</v>
-      </c>
-      <c r="J124" t="n">
-        <v>4.489</v>
       </c>
     </row>
     <row r="125">
@@ -10761,28 +10761,28 @@
         </is>
       </c>
       <c r="B125" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E125" t="n">
         <v>0.723</v>
       </c>
-      <c r="D125" t="n">
+      <c r="F125" t="n">
+        <v>7.614</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2.326</v>
+      </c>
+      <c r="J125" t="n">
         <v>3.095</v>
-      </c>
-      <c r="E125" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="F125" t="n">
-        <v>2.326</v>
-      </c>
-      <c r="G125" t="n">
-        <v>3.385</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="I125" t="n">
-        <v>7.614</v>
-      </c>
-      <c r="J125" t="n">
-        <v>4.926</v>
       </c>
     </row>
     <row r="126">
@@ -10792,28 +10792,28 @@
         </is>
       </c>
       <c r="B126" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2.463</v>
+      </c>
+      <c r="E126" t="n">
         <v>1.007</v>
       </c>
-      <c r="D126" t="n">
+      <c r="F126" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="I126" t="n">
+        <v>2.438</v>
+      </c>
+      <c r="J126" t="n">
         <v>3.189</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2.463</v>
-      </c>
-      <c r="F126" t="n">
-        <v>2.438</v>
-      </c>
-      <c r="G126" t="n">
-        <v>3.581</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="I126" t="n">
-        <v>7.775</v>
-      </c>
-      <c r="J126" t="n">
-        <v>4.725</v>
       </c>
     </row>
     <row r="127">
@@ -10823,28 +10823,28 @@
         </is>
       </c>
       <c r="B127" t="n">
+        <v>3.321</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.253</v>
+      </c>
+      <c r="E127" t="n">
         <v>0.838</v>
       </c>
-      <c r="D127" t="n">
+      <c r="F127" t="n">
+        <v>8.148</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="J127" t="n">
         <v>2.945</v>
-      </c>
-      <c r="E127" t="n">
-        <v>2.253</v>
-      </c>
-      <c r="F127" t="n">
-        <v>2.232</v>
-      </c>
-      <c r="G127" t="n">
-        <v>3.321</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="I127" t="n">
-        <v>8.148</v>
-      </c>
-      <c r="J127" t="n">
-        <v>4.649</v>
       </c>
     </row>
     <row r="128">
@@ -10854,28 +10854,28 @@
         </is>
       </c>
       <c r="B128" t="n">
+        <v>3.384</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2.269</v>
+      </c>
+      <c r="E128" t="n">
         <v>0.719</v>
       </c>
-      <c r="D128" t="n">
+      <c r="F128" t="n">
+        <v>7.524</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2.441</v>
+      </c>
+      <c r="J128" t="n">
         <v>3.317</v>
-      </c>
-      <c r="E128" t="n">
-        <v>2.269</v>
-      </c>
-      <c r="F128" t="n">
-        <v>2.441</v>
-      </c>
-      <c r="G128" t="n">
-        <v>3.384</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="I128" t="n">
-        <v>7.524</v>
-      </c>
-      <c r="J128" t="n">
-        <v>4.756</v>
       </c>
     </row>
     <row r="129">
@@ -10885,28 +10885,28 @@
         </is>
       </c>
       <c r="B129" t="n">
+        <v>3.317</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2.284</v>
+      </c>
+      <c r="E129" t="n">
         <v>0.9379999999999999</v>
       </c>
-      <c r="D129" t="n">
+      <c r="F129" t="n">
+        <v>8.334</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="J129" t="n">
         <v>3.361</v>
-      </c>
-      <c r="E129" t="n">
-        <v>2.284</v>
-      </c>
-      <c r="F129" t="n">
-        <v>2.455</v>
-      </c>
-      <c r="G129" t="n">
-        <v>3.317</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="I129" t="n">
-        <v>8.334</v>
-      </c>
-      <c r="J129" t="n">
-        <v>4.918</v>
       </c>
     </row>
     <row r="130">
@@ -10916,31 +10916,31 @@
         </is>
       </c>
       <c r="B130" t="n">
+        <v>3.437</v>
+      </c>
+      <c r="C130" t="n">
+        <v>4.745</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="E130" t="n">
         <v>0.762</v>
       </c>
-      <c r="C130" t="n">
+      <c r="F130" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="H130" t="n">
         <v>0.263</v>
       </c>
-      <c r="D130" t="n">
+      <c r="I130" t="n">
+        <v>2.511</v>
+      </c>
+      <c r="J130" t="n">
         <v>3.154</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2.113</v>
-      </c>
-      <c r="F130" t="n">
-        <v>2.511</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3.437</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="I130" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="J130" t="n">
-        <v>4.745</v>
       </c>
     </row>
     <row r="131">
@@ -10950,31 +10950,31 @@
         </is>
       </c>
       <c r="B131" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="C131" t="n">
+        <v>4.314</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="E131" t="n">
         <v>0.883</v>
       </c>
-      <c r="C131" t="n">
+      <c r="F131" t="n">
+        <v>7.846</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H131" t="n">
         <v>0.244</v>
       </c>
-      <c r="D131" t="n">
+      <c r="I131" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="J131" t="n">
         <v>3.122</v>
-      </c>
-      <c r="E131" t="n">
-        <v>1.546</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1.993</v>
-      </c>
-      <c r="G131" t="n">
-        <v>3.066</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="I131" t="n">
-        <v>7.846</v>
-      </c>
-      <c r="J131" t="n">
-        <v>4.314</v>
       </c>
     </row>
     <row r="132">
@@ -10984,31 +10984,31 @@
         </is>
       </c>
       <c r="B132" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4.436</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="E132" t="n">
         <v>0.765</v>
       </c>
-      <c r="C132" t="n">
+      <c r="F132" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="H132" t="n">
         <v>0.251</v>
       </c>
-      <c r="D132" t="n">
+      <c r="I132" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J132" t="n">
         <v>3.271</v>
-      </c>
-      <c r="E132" t="n">
-        <v>2.187</v>
-      </c>
-      <c r="F132" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="G132" t="n">
-        <v>3.177</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0.9419999999999999</v>
-      </c>
-      <c r="I132" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="J132" t="n">
-        <v>4.436</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -8169,47 +8169,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cove Point</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Golden Pass</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Calcasieu Pass</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Sabine Pass</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Cameron</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Cove Point</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Plaquemines</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Golden Pass</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Freeport</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Corpus Christi</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8239,7 +8239,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8249,7 +8249,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8279,7 +8279,7 @@
           <t>2016-02</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="F8" t="n">
         <v>0.172</v>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
           <t>2016-03</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="F9" t="n">
         <v>0.373</v>
       </c>
     </row>
@@ -8299,7 +8299,7 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="F10" t="n">
         <v>0.364</v>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="F11" t="n">
         <v>0.346</v>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
           <t>2016-06</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="F12" t="n">
         <v>0.597</v>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
           <t>2016-07</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="F13" t="n">
         <v>0.552</v>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
           <t>2016-08</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="F14" t="n">
         <v>0.966</v>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
           <t>2016-09</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="F15" t="n">
         <v>0.607</v>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
           <t>2016-10</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="F16" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
           <t>2016-11</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="F17" t="n">
         <v>1.196</v>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
           <t>2016-12</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="F18" t="n">
         <v>1.468</v>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
           <t>2017-01</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="F19" t="n">
         <v>1.801</v>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
           <t>2017-02</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="F20" t="n">
         <v>2.024</v>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
           <t>2017-03</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="F21" t="n">
         <v>1.528</v>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
           <t>2017-04</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="F22" t="n">
         <v>1.838</v>
       </c>
     </row>
@@ -8429,7 +8429,7 @@
           <t>2017-05</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="F23" t="n">
         <v>2.136</v>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
           <t>2017-06</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="F24" t="n">
         <v>1.905</v>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
           <t>2017-07</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="F25" t="n">
         <v>1.883</v>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
           <t>2017-08</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="F26" t="n">
         <v>1.597</v>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
           <t>2017-09</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="F27" t="n">
         <v>1.986</v>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
           <t>2017-10</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="F28" t="n">
         <v>2.832</v>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
           <t>2017-11</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="F29" t="n">
         <v>2.906</v>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
           <t>2017-12</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="F30" t="n">
         <v>2.9</v>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
           <t>2018-01</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="F31" t="n">
         <v>2.543</v>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
           <t>2018-02</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="F32" t="n">
         <v>2.864</v>
       </c>
     </row>
@@ -8529,12 +8529,12 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>3.11</v>
-      </c>
       <c r="E33" t="n">
         <v>0.105</v>
       </c>
+      <c r="F33" t="n">
+        <v>3.11</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8542,12 +8542,12 @@
           <t>2018-04</t>
         </is>
       </c>
-      <c r="C34" t="n">
-        <v>2.788</v>
-      </c>
       <c r="E34" t="n">
         <v>0.325</v>
       </c>
+      <c r="F34" t="n">
+        <v>2.788</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -8555,12 +8555,12 @@
           <t>2018-05</t>
         </is>
       </c>
-      <c r="C35" t="n">
-        <v>2.562</v>
-      </c>
       <c r="E35" t="n">
         <v>0.77</v>
       </c>
+      <c r="F35" t="n">
+        <v>2.562</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -8568,12 +8568,12 @@
           <t>2018-06</t>
         </is>
       </c>
-      <c r="C36" t="n">
-        <v>2.213</v>
-      </c>
       <c r="E36" t="n">
         <v>0.457</v>
       </c>
+      <c r="F36" t="n">
+        <v>2.213</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -8581,12 +8581,12 @@
           <t>2018-07</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>2.778</v>
-      </c>
       <c r="E37" t="n">
         <v>0.675</v>
       </c>
+      <c r="F37" t="n">
+        <v>2.778</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -8594,12 +8594,12 @@
           <t>2018-08</t>
         </is>
       </c>
-      <c r="C38" t="n">
-        <v>2.54</v>
-      </c>
       <c r="E38" t="n">
         <v>0.676</v>
       </c>
+      <c r="F38" t="n">
+        <v>2.54</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -8607,12 +8607,12 @@
           <t>2018-09</t>
         </is>
       </c>
-      <c r="C39" t="n">
-        <v>2.507</v>
-      </c>
       <c r="E39" t="n">
         <v>0.449</v>
       </c>
+      <c r="F39" t="n">
+        <v>2.507</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8620,12 +8620,12 @@
           <t>2018-10</t>
         </is>
       </c>
-      <c r="C40" t="n">
-        <v>2.932</v>
-      </c>
       <c r="E40" t="n">
         <v>0.226</v>
       </c>
+      <c r="F40" t="n">
+        <v>2.932</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -8633,12 +8633,12 @@
           <t>2018-11</t>
         </is>
       </c>
-      <c r="C41" t="n">
-        <v>3.202</v>
-      </c>
       <c r="E41" t="n">
         <v>0.701</v>
       </c>
+      <c r="F41" t="n">
+        <v>3.202</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -8647,13 +8647,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3.36</v>
+        <v>0.241</v>
       </c>
       <c r="E42" t="n">
         <v>0.711</v>
       </c>
-      <c r="J42" t="n">
-        <v>0.241</v>
+      <c r="F42" t="n">
+        <v>3.36</v>
       </c>
     </row>
     <row r="43">
@@ -8663,13 +8663,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.367</v>
+        <v>0.378</v>
       </c>
       <c r="E43" t="n">
         <v>0.714</v>
       </c>
-      <c r="J43" t="n">
-        <v>0.378</v>
+      <c r="F43" t="n">
+        <v>3.367</v>
       </c>
     </row>
     <row r="44">
@@ -8679,13 +8679,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.942</v>
+        <v>0.145</v>
       </c>
       <c r="E44" t="n">
         <v>0.915</v>
       </c>
-      <c r="J44" t="n">
-        <v>0.145</v>
+      <c r="F44" t="n">
+        <v>2.942</v>
       </c>
     </row>
     <row r="45">
@@ -8695,13 +8695,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.291</v>
+        <v>0.706</v>
       </c>
       <c r="E45" t="n">
         <v>0.599</v>
       </c>
-      <c r="J45" t="n">
-        <v>0.706</v>
+      <c r="F45" t="n">
+        <v>3.291</v>
       </c>
     </row>
     <row r="46">
@@ -8711,13 +8711,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.054</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="E46" t="n">
         <v>0.867</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.6919999999999999</v>
+      <c r="F46" t="n">
+        <v>3.054</v>
       </c>
     </row>
     <row r="47">
@@ -8727,7 +8727,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.762</v>
+        <v>0.614</v>
       </c>
       <c r="D47" t="n">
         <v>0.113</v>
@@ -8735,8 +8735,8 @@
       <c r="E47" t="n">
         <v>0.602</v>
       </c>
-      <c r="J47" t="n">
-        <v>0.614</v>
+      <c r="F47" t="n">
+        <v>3.762</v>
       </c>
     </row>
     <row r="48">
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.551</v>
+        <v>0.765</v>
       </c>
       <c r="D48" t="n">
         <v>0.106</v>
@@ -8754,8 +8754,8 @@
       <c r="E48" t="n">
         <v>0.731</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.765</v>
+      <c r="F48" t="n">
+        <v>3.551</v>
       </c>
     </row>
     <row r="49">
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.347</v>
+        <v>1.184</v>
       </c>
       <c r="D49" t="n">
         <v>0.248</v>
@@ -8773,8 +8773,8 @@
       <c r="E49" t="n">
         <v>0.731</v>
       </c>
-      <c r="J49" t="n">
-        <v>1.184</v>
+      <c r="F49" t="n">
+        <v>3.347</v>
       </c>
     </row>
     <row r="50">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.696</v>
+        <v>1.084</v>
       </c>
       <c r="D50" t="n">
         <v>0.388</v>
@@ -8792,8 +8792,8 @@
       <c r="E50" t="n">
         <v>0.699</v>
       </c>
-      <c r="J50" t="n">
-        <v>1.084</v>
+      <c r="F50" t="n">
+        <v>2.696</v>
       </c>
     </row>
     <row r="51">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.461</v>
+        <v>1.26</v>
       </c>
       <c r="D51" t="n">
         <v>0.364</v>
@@ -8811,11 +8811,11 @@
       <c r="E51" t="n">
         <v>0.5</v>
       </c>
-      <c r="I51" t="n">
+      <c r="F51" t="n">
+        <v>3.461</v>
+      </c>
+      <c r="J51" t="n">
         <v>0.235</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1.26</v>
       </c>
     </row>
     <row r="52">
@@ -8825,7 +8825,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.775</v>
+        <v>1.488</v>
       </c>
       <c r="D52" t="n">
         <v>0.379</v>
@@ -8833,11 +8833,11 @@
       <c r="E52" t="n">
         <v>0.244</v>
       </c>
-      <c r="I52" t="n">
+      <c r="F52" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="J52" t="n">
         <v>0.365</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1.488</v>
       </c>
     </row>
     <row r="53">
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.852</v>
+        <v>1.357</v>
       </c>
       <c r="D53" t="n">
         <v>0.507</v>
@@ -8855,11 +8855,11 @@
       <c r="E53" t="n">
         <v>0.852</v>
       </c>
-      <c r="I53" t="n">
+      <c r="F53" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="J53" t="n">
         <v>0.353</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1.357</v>
       </c>
     </row>
     <row r="54">
@@ -8868,8 +8868,11 @@
           <t>2019-12</t>
         </is>
       </c>
+      <c r="B54" t="n">
+        <v>0.229</v>
+      </c>
       <c r="C54" t="n">
-        <v>3.813</v>
+        <v>1.461</v>
       </c>
       <c r="D54" t="n">
         <v>0.84</v>
@@ -8877,14 +8880,11 @@
       <c r="E54" t="n">
         <v>0.729</v>
       </c>
-      <c r="G54" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="I54" t="n">
+      <c r="F54" t="n">
+        <v>3.813</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.79</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1.461</v>
       </c>
     </row>
     <row r="55">
@@ -8893,8 +8893,11 @@
           <t>2020-01</t>
         </is>
       </c>
+      <c r="B55" t="n">
+        <v>0.428</v>
+      </c>
       <c r="C55" t="n">
-        <v>4.018</v>
+        <v>1.426</v>
       </c>
       <c r="D55" t="n">
         <v>0.98</v>
@@ -8902,14 +8905,11 @@
       <c r="E55" t="n">
         <v>0.722</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="F55" t="n">
+        <v>4.018</v>
+      </c>
+      <c r="J55" t="n">
         <v>1.456</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1.426</v>
       </c>
     </row>
     <row r="56">
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3.684</v>
+        <v>1.55</v>
       </c>
       <c r="D56" t="n">
         <v>1.044</v>
@@ -8927,11 +8927,11 @@
       <c r="E56" t="n">
         <v>0.758</v>
       </c>
-      <c r="I56" t="n">
+      <c r="F56" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="J56" t="n">
         <v>1.446</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="57">
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.447</v>
+        <v>1.462</v>
       </c>
       <c r="D57" t="n">
         <v>1.208</v>
@@ -8949,11 +8949,11 @@
       <c r="E57" t="n">
         <v>0.831</v>
       </c>
-      <c r="I57" t="n">
+      <c r="F57" t="n">
+        <v>3.447</v>
+      </c>
+      <c r="J57" t="n">
         <v>1.635</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1.462</v>
       </c>
     </row>
     <row r="58">
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3.333</v>
+        <v>1.245</v>
       </c>
       <c r="D58" t="n">
         <v>1.301</v>
@@ -8971,11 +8971,11 @@
       <c r="E58" t="n">
         <v>0.608</v>
       </c>
-      <c r="I58" t="n">
+      <c r="F58" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="J58" t="n">
         <v>1.158</v>
-      </c>
-      <c r="J58" t="n">
-        <v>1.245</v>
       </c>
     </row>
     <row r="59">
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2.73</v>
+        <v>0.831</v>
       </c>
       <c r="D59" t="n">
         <v>1.135</v>
@@ -8993,11 +8993,11 @@
       <c r="E59" t="n">
         <v>0.708</v>
       </c>
-      <c r="I59" t="n">
+      <c r="F59" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J59" t="n">
         <v>1.008</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.831</v>
       </c>
     </row>
     <row r="60">
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.978</v>
+        <v>0.307</v>
       </c>
       <c r="D60" t="n">
         <v>1.366</v>
@@ -9015,11 +9015,11 @@
       <c r="E60" t="n">
         <v>0.763</v>
       </c>
-      <c r="I60" t="n">
+      <c r="F60" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="J60" t="n">
         <v>0.543</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.307</v>
       </c>
     </row>
     <row r="61">
@@ -9029,7 +9029,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.063</v>
+        <v>0.373</v>
       </c>
       <c r="D61" t="n">
         <v>1.099</v>
@@ -9037,11 +9037,11 @@
       <c r="E61" t="n">
         <v>0.711</v>
       </c>
-      <c r="I61" t="n">
+      <c r="F61" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.132</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.373</v>
       </c>
     </row>
     <row r="62">
@@ -9050,8 +9050,11 @@
           <t>2020-08</t>
         </is>
       </c>
+      <c r="B62" t="n">
+        <v>0.26</v>
+      </c>
       <c r="C62" t="n">
-        <v>1.031</v>
+        <v>0.601</v>
       </c>
       <c r="D62" t="n">
         <v>1.117</v>
@@ -9059,14 +9062,11 @@
       <c r="E62" t="n">
         <v>0.596</v>
       </c>
-      <c r="G62" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="I62" t="n">
+      <c r="F62" t="n">
+        <v>1.031</v>
+      </c>
+      <c r="J62" t="n">
         <v>0.399</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.601</v>
       </c>
     </row>
     <row r="63">
@@ -9075,20 +9075,20 @@
           <t>2020-09</t>
         </is>
       </c>
+      <c r="B63" t="n">
+        <v>0.271</v>
+      </c>
       <c r="C63" t="n">
-        <v>2.241</v>
+        <v>1.363</v>
       </c>
       <c r="E63" t="n">
         <v>0.621</v>
       </c>
-      <c r="G63" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="F63" t="n">
+        <v>2.241</v>
+      </c>
+      <c r="J63" t="n">
         <v>1.127</v>
-      </c>
-      <c r="J63" t="n">
-        <v>1.363</v>
       </c>
     </row>
     <row r="64">
@@ -9097,8 +9097,11 @@
           <t>2020-10</t>
         </is>
       </c>
+      <c r="B64" t="n">
+        <v>0.52</v>
+      </c>
       <c r="C64" t="n">
-        <v>3.106</v>
+        <v>1.551</v>
       </c>
       <c r="D64" t="n">
         <v>0.662</v>
@@ -9106,14 +9109,11 @@
       <c r="E64" t="n">
         <v>0.373</v>
       </c>
-      <c r="G64" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I64" t="n">
+      <c r="F64" t="n">
+        <v>3.106</v>
+      </c>
+      <c r="J64" t="n">
         <v>1.892</v>
-      </c>
-      <c r="J64" t="n">
-        <v>1.551</v>
       </c>
     </row>
     <row r="65">
@@ -9122,8 +9122,11 @@
           <t>2020-11</t>
         </is>
       </c>
+      <c r="B65" t="n">
+        <v>0.469</v>
+      </c>
       <c r="C65" t="n">
-        <v>3.684</v>
+        <v>1.633</v>
       </c>
       <c r="D65" t="n">
         <v>1.838</v>
@@ -9131,14 +9134,11 @@
       <c r="E65" t="n">
         <v>0.852</v>
       </c>
-      <c r="G65" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="I65" t="n">
+      <c r="F65" t="n">
+        <v>3.684</v>
+      </c>
+      <c r="J65" t="n">
         <v>1.953</v>
-      </c>
-      <c r="J65" t="n">
-        <v>1.633</v>
       </c>
     </row>
     <row r="66">
@@ -9147,8 +9147,11 @@
           <t>2020-12</t>
         </is>
       </c>
+      <c r="B66" t="n">
+        <v>0.628</v>
+      </c>
       <c r="C66" t="n">
-        <v>3.845</v>
+        <v>1.821</v>
       </c>
       <c r="D66" t="n">
         <v>1.939</v>
@@ -9156,14 +9159,11 @@
       <c r="E66" t="n">
         <v>0.718</v>
       </c>
-      <c r="G66" t="n">
-        <v>0.628</v>
-      </c>
-      <c r="I66" t="n">
+      <c r="F66" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="J66" t="n">
         <v>2.057</v>
-      </c>
-      <c r="J66" t="n">
-        <v>1.821</v>
       </c>
     </row>
     <row r="67">
@@ -9173,7 +9173,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3.905</v>
+        <v>2.012</v>
       </c>
       <c r="D67" t="n">
         <v>1.943</v>
@@ -9181,11 +9181,11 @@
       <c r="E67" t="n">
         <v>0.718</v>
       </c>
-      <c r="I67" t="n">
+      <c r="F67" t="n">
+        <v>3.905</v>
+      </c>
+      <c r="J67" t="n">
         <v>2.148</v>
-      </c>
-      <c r="J67" t="n">
-        <v>2.012</v>
       </c>
     </row>
     <row r="68">
@@ -9194,8 +9194,11 @@
           <t>2021-02</t>
         </is>
       </c>
+      <c r="B68" t="n">
+        <v>0.541</v>
+      </c>
       <c r="C68" t="n">
-        <v>3.263</v>
+        <v>1.297</v>
       </c>
       <c r="D68" t="n">
         <v>1.42</v>
@@ -9203,14 +9206,11 @@
       <c r="E68" t="n">
         <v>0.671</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="I68" t="n">
+      <c r="F68" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="J68" t="n">
         <v>1.186</v>
-      </c>
-      <c r="J68" t="n">
-        <v>1.297</v>
       </c>
     </row>
     <row r="69">
@@ -9219,8 +9219,11 @@
           <t>2021-03</t>
         </is>
       </c>
+      <c r="B69" t="n">
+        <v>0.468</v>
+      </c>
       <c r="C69" t="n">
-        <v>4.013</v>
+        <v>2.201</v>
       </c>
       <c r="D69" t="n">
         <v>1.755</v>
@@ -9228,14 +9231,11 @@
       <c r="E69" t="n">
         <v>0.845</v>
       </c>
-      <c r="G69" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="I69" t="n">
+      <c r="F69" t="n">
+        <v>4.013</v>
+      </c>
+      <c r="J69" t="n">
         <v>2.237</v>
-      </c>
-      <c r="J69" t="n">
-        <v>2.201</v>
       </c>
     </row>
     <row r="70">
@@ -9244,8 +9244,11 @@
           <t>2021-04</t>
         </is>
       </c>
+      <c r="B70" t="n">
+        <v>0.68</v>
+      </c>
       <c r="C70" t="n">
-        <v>3.955</v>
+        <v>2.175</v>
       </c>
       <c r="D70" t="n">
         <v>1.848</v>
@@ -9253,14 +9256,11 @@
       <c r="E70" t="n">
         <v>0.622</v>
       </c>
-      <c r="G70" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I70" t="n">
+      <c r="F70" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="J70" t="n">
         <v>2.203</v>
-      </c>
-      <c r="J70" t="n">
-        <v>2.175</v>
       </c>
     </row>
     <row r="71">
@@ -9269,8 +9269,11 @@
           <t>2021-05</t>
         </is>
       </c>
+      <c r="B71" t="n">
+        <v>0.662</v>
+      </c>
       <c r="C71" t="n">
-        <v>3.805</v>
+        <v>2.066</v>
       </c>
       <c r="D71" t="n">
         <v>1.855</v>
@@ -9278,14 +9281,11 @@
       <c r="E71" t="n">
         <v>0.787</v>
       </c>
-      <c r="G71" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="I71" t="n">
+      <c r="F71" t="n">
+        <v>3.805</v>
+      </c>
+      <c r="J71" t="n">
         <v>2.223</v>
-      </c>
-      <c r="J71" t="n">
-        <v>2.066</v>
       </c>
     </row>
     <row r="72">
@@ -9294,8 +9294,11 @@
           <t>2021-06</t>
         </is>
       </c>
+      <c r="B72" t="n">
+        <v>0.524</v>
+      </c>
       <c r="C72" t="n">
-        <v>3.118</v>
+        <v>2.236</v>
       </c>
       <c r="D72" t="n">
         <v>1.418</v>
@@ -9303,14 +9306,11 @@
       <c r="E72" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="G72" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="F72" t="n">
+        <v>3.118</v>
+      </c>
+      <c r="J72" t="n">
         <v>2.127</v>
-      </c>
-      <c r="J72" t="n">
-        <v>2.236</v>
       </c>
     </row>
     <row r="73">
@@ -9319,8 +9319,11 @@
           <t>2021-07</t>
         </is>
       </c>
+      <c r="B73" t="n">
+        <v>0.493</v>
+      </c>
       <c r="C73" t="n">
-        <v>3.402</v>
+        <v>2.126</v>
       </c>
       <c r="D73" t="n">
         <v>1.82</v>
@@ -9328,14 +9331,11 @@
       <c r="E73" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G73" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="I73" t="n">
+      <c r="F73" t="n">
+        <v>3.402</v>
+      </c>
+      <c r="J73" t="n">
         <v>2.141</v>
-      </c>
-      <c r="J73" t="n">
-        <v>2.126</v>
       </c>
     </row>
     <row r="74">
@@ -9344,8 +9344,11 @@
           <t>2021-08</t>
         </is>
       </c>
+      <c r="B74" t="n">
+        <v>0.507</v>
+      </c>
       <c r="C74" t="n">
-        <v>3.492</v>
+        <v>2.171</v>
       </c>
       <c r="D74" t="n">
         <v>1.467</v>
@@ -9353,14 +9356,11 @@
       <c r="E74" t="n">
         <v>0.785</v>
       </c>
-      <c r="G74" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I74" t="n">
+      <c r="F74" t="n">
+        <v>3.492</v>
+      </c>
+      <c r="J74" t="n">
         <v>2.307</v>
-      </c>
-      <c r="J74" t="n">
-        <v>2.171</v>
       </c>
     </row>
     <row r="75">
@@ -9369,8 +9369,11 @@
           <t>2021-09</t>
         </is>
       </c>
+      <c r="B75" t="n">
+        <v>0.396</v>
+      </c>
       <c r="C75" t="n">
-        <v>3.619</v>
+        <v>2.34</v>
       </c>
       <c r="D75" t="n">
         <v>1.919</v>
@@ -9378,14 +9381,11 @@
       <c r="E75" t="n">
         <v>0.499</v>
       </c>
-      <c r="G75" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="I75" t="n">
+      <c r="F75" t="n">
+        <v>3.619</v>
+      </c>
+      <c r="J75" t="n">
         <v>1.764</v>
-      </c>
-      <c r="J75" t="n">
-        <v>2.34</v>
       </c>
     </row>
     <row r="76">
@@ -9394,8 +9394,11 @@
           <t>2021-10</t>
         </is>
       </c>
+      <c r="B76" t="n">
+        <v>0.639</v>
+      </c>
       <c r="C76" t="n">
-        <v>3.561</v>
+        <v>2.28</v>
       </c>
       <c r="D76" t="n">
         <v>1.852</v>
@@ -9403,14 +9406,11 @@
       <c r="E76" t="n">
         <v>0.348</v>
       </c>
-      <c r="G76" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="I76" t="n">
+      <c r="F76" t="n">
+        <v>3.561</v>
+      </c>
+      <c r="J76" t="n">
         <v>2.111</v>
-      </c>
-      <c r="J76" t="n">
-        <v>2.28</v>
       </c>
     </row>
     <row r="77">
@@ -9419,8 +9419,11 @@
           <t>2021-11</t>
         </is>
       </c>
+      <c r="B77" t="n">
+        <v>0.423</v>
+      </c>
       <c r="C77" t="n">
-        <v>4.097</v>
+        <v>2.307</v>
       </c>
       <c r="D77" t="n">
         <v>2.113</v>
@@ -9428,14 +9431,11 @@
       <c r="E77" t="n">
         <v>0.797</v>
       </c>
-      <c r="G77" t="n">
-        <v>0.423</v>
-      </c>
-      <c r="I77" t="n">
+      <c r="F77" t="n">
+        <v>4.097</v>
+      </c>
+      <c r="J77" t="n">
         <v>1.597</v>
-      </c>
-      <c r="J77" t="n">
-        <v>2.307</v>
       </c>
     </row>
     <row r="78">
@@ -9444,8 +9444,11 @@
           <t>2021-12</t>
         </is>
       </c>
+      <c r="B78" t="n">
+        <v>0.723</v>
+      </c>
       <c r="C78" t="n">
-        <v>4.186</v>
+        <v>2.249</v>
       </c>
       <c r="D78" t="n">
         <v>2.158</v>
@@ -9453,14 +9456,11 @@
       <c r="E78" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G78" t="n">
-        <v>0.723</v>
-      </c>
-      <c r="I78" t="n">
+      <c r="F78" t="n">
+        <v>4.186</v>
+      </c>
+      <c r="J78" t="n">
         <v>2.365</v>
-      </c>
-      <c r="J78" t="n">
-        <v>2.249</v>
       </c>
     </row>
     <row r="79">
@@ -9469,8 +9469,11 @@
           <t>2022-01</t>
         </is>
       </c>
+      <c r="B79" t="n">
+        <v>0.441</v>
+      </c>
       <c r="C79" t="n">
-        <v>4.576</v>
+        <v>2.347</v>
       </c>
       <c r="D79" t="n">
         <v>2.151</v>
@@ -9478,14 +9481,11 @@
       <c r="E79" t="n">
         <v>0.886</v>
       </c>
-      <c r="G79" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="I79" t="n">
+      <c r="F79" t="n">
+        <v>4.576</v>
+      </c>
+      <c r="J79" t="n">
         <v>2.248</v>
-      </c>
-      <c r="J79" t="n">
-        <v>2.347</v>
       </c>
     </row>
     <row r="80">
@@ -9494,8 +9494,11 @@
           <t>2022-02</t>
         </is>
       </c>
+      <c r="B80" t="n">
+        <v>0.749</v>
+      </c>
       <c r="C80" t="n">
-        <v>4.318</v>
+        <v>2.654</v>
       </c>
       <c r="D80" t="n">
         <v>2.116</v>
@@ -9503,14 +9506,11 @@
       <c r="E80" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="G80" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="I80" t="n">
+      <c r="F80" t="n">
+        <v>4.318</v>
+      </c>
+      <c r="J80" t="n">
         <v>2.043</v>
-      </c>
-      <c r="J80" t="n">
-        <v>2.654</v>
       </c>
     </row>
     <row r="81">
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.279</v>
+        <v>0.609</v>
       </c>
       <c r="C81" t="n">
-        <v>4.588</v>
+        <v>2.115</v>
       </c>
       <c r="D81" t="n">
         <v>2.123</v>
@@ -9531,14 +9531,14 @@
       <c r="E81" t="n">
         <v>0.754</v>
       </c>
-      <c r="G81" t="n">
-        <v>0.609</v>
+      <c r="F81" t="n">
+        <v>4.588</v>
       </c>
       <c r="I81" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="J81" t="n">
         <v>2.268</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2.115</v>
       </c>
     </row>
     <row r="82">
@@ -9548,10 +9548,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.289</v>
+        <v>0.784</v>
       </c>
       <c r="C82" t="n">
-        <v>4.526</v>
+        <v>2.117</v>
       </c>
       <c r="D82" t="n">
         <v>2.095</v>
@@ -9559,14 +9559,14 @@
       <c r="E82" t="n">
         <v>0.794</v>
       </c>
-      <c r="G82" t="n">
-        <v>0.784</v>
+      <c r="F82" t="n">
+        <v>4.526</v>
       </c>
       <c r="I82" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="J82" t="n">
         <v>1.427</v>
-      </c>
-      <c r="J82" t="n">
-        <v>2.117</v>
       </c>
     </row>
     <row r="83">
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.774</v>
+        <v>0.488</v>
       </c>
       <c r="C83" t="n">
-        <v>4.597</v>
+        <v>2.179</v>
       </c>
       <c r="D83" t="n">
         <v>1.426</v>
@@ -9587,14 +9587,14 @@
       <c r="E83" t="n">
         <v>0.781</v>
       </c>
-      <c r="G83" t="n">
-        <v>0.488</v>
+      <c r="F83" t="n">
+        <v>4.597</v>
       </c>
       <c r="I83" t="n">
+        <v>1.774</v>
+      </c>
+      <c r="J83" t="n">
         <v>2.232</v>
-      </c>
-      <c r="J83" t="n">
-        <v>2.179</v>
       </c>
     </row>
     <row r="84">
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2.334</v>
+        <v>0.777</v>
       </c>
       <c r="C84" t="n">
-        <v>3.84</v>
+        <v>2.315</v>
       </c>
       <c r="D84" t="n">
         <v>1.86</v>
@@ -9615,14 +9615,14 @@
       <c r="E84" t="n">
         <v>0.716</v>
       </c>
-      <c r="G84" t="n">
-        <v>0.777</v>
+      <c r="F84" t="n">
+        <v>3.84</v>
       </c>
       <c r="I84" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="J84" t="n">
         <v>0.629</v>
-      </c>
-      <c r="J84" t="n">
-        <v>2.315</v>
       </c>
     </row>
     <row r="85">
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.33</v>
+        <v>0.64</v>
       </c>
       <c r="C85" t="n">
-        <v>4.168</v>
+        <v>2.218</v>
       </c>
       <c r="D85" t="n">
         <v>1.832</v>
@@ -9643,11 +9643,11 @@
       <c r="E85" t="n">
         <v>0.851</v>
       </c>
-      <c r="G85" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2.218</v>
+      <c r="F85" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.33</v>
       </c>
     </row>
     <row r="86">
@@ -9657,10 +9657,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.375</v>
+        <v>0.647</v>
       </c>
       <c r="C86" t="n">
-        <v>4.173</v>
+        <v>2.23</v>
       </c>
       <c r="D86" t="n">
         <v>1.88</v>
@@ -9668,11 +9668,11 @@
       <c r="E86" t="n">
         <v>0.753</v>
       </c>
-      <c r="G86" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="J86" t="n">
-        <v>2.23</v>
+      <c r="F86" t="n">
+        <v>4.173</v>
+      </c>
+      <c r="I86" t="n">
+        <v>2.375</v>
       </c>
     </row>
     <row r="87">
@@ -9682,10 +9682,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.796</v>
+        <v>0.708</v>
       </c>
       <c r="C87" t="n">
-        <v>4.201</v>
+        <v>2.173</v>
       </c>
       <c r="D87" t="n">
         <v>1.912</v>
@@ -9693,11 +9693,11 @@
       <c r="E87" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="G87" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="J87" t="n">
-        <v>2.173</v>
+      <c r="F87" t="n">
+        <v>4.201</v>
+      </c>
+      <c r="I87" t="n">
+        <v>2.796</v>
       </c>
     </row>
     <row r="88">
@@ -9707,19 +9707,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.186</v>
+        <v>0.519</v>
       </c>
       <c r="C88" t="n">
-        <v>4.586</v>
+        <v>2.348</v>
       </c>
       <c r="D88" t="n">
         <v>2.094</v>
       </c>
-      <c r="G88" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="J88" t="n">
-        <v>2.348</v>
+      <c r="F88" t="n">
+        <v>4.586</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3.186</v>
       </c>
     </row>
     <row r="89">
@@ -9729,10 +9729,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.625</v>
+        <v>0.773</v>
       </c>
       <c r="C89" t="n">
-        <v>4.363</v>
+        <v>2.072</v>
       </c>
       <c r="D89" t="n">
         <v>2.107</v>
@@ -9740,11 +9740,11 @@
       <c r="E89" t="n">
         <v>0.742</v>
       </c>
-      <c r="G89" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="J89" t="n">
-        <v>2.072</v>
+      <c r="F89" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2.625</v>
       </c>
     </row>
     <row r="90">
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2.655</v>
+        <v>0.66</v>
       </c>
       <c r="C90" t="n">
-        <v>4.893</v>
+        <v>2.255</v>
       </c>
       <c r="D90" t="n">
         <v>2.088</v>
@@ -9765,11 +9765,11 @@
       <c r="E90" t="n">
         <v>1.047</v>
       </c>
-      <c r="G90" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="J90" t="n">
-        <v>2.255</v>
+      <c r="F90" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2.655</v>
       </c>
     </row>
     <row r="91">
@@ -9779,10 +9779,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.007</v>
+        <v>0.663</v>
       </c>
       <c r="C91" t="n">
-        <v>4.896</v>
+        <v>2.2</v>
       </c>
       <c r="D91" t="n">
         <v>2.183</v>
@@ -9790,11 +9790,11 @@
       <c r="E91" t="n">
         <v>0.731</v>
       </c>
-      <c r="G91" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="J91" t="n">
-        <v>2.2</v>
+      <c r="F91" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3.007</v>
       </c>
     </row>
     <row r="92">
@@ -9804,10 +9804,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3.501</v>
+        <v>0.823</v>
       </c>
       <c r="C92" t="n">
-        <v>4.65</v>
+        <v>2.496</v>
       </c>
       <c r="D92" t="n">
         <v>2.175</v>
@@ -9815,14 +9815,14 @@
       <c r="E92" t="n">
         <v>0.756</v>
       </c>
-      <c r="G92" t="n">
-        <v>0.823</v>
+      <c r="F92" t="n">
+        <v>4.65</v>
       </c>
       <c r="I92" t="n">
+        <v>3.501</v>
+      </c>
+      <c r="J92" t="n">
         <v>0.45</v>
-      </c>
-      <c r="J92" t="n">
-        <v>2.496</v>
       </c>
     </row>
     <row r="93">
@@ -9832,10 +9832,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.682</v>
+        <v>0.803</v>
       </c>
       <c r="C93" t="n">
-        <v>4.605</v>
+        <v>2.361</v>
       </c>
       <c r="D93" t="n">
         <v>2.176</v>
@@ -9843,14 +9843,14 @@
       <c r="E93" t="n">
         <v>0.976</v>
       </c>
-      <c r="G93" t="n">
-        <v>0.803</v>
+      <c r="F93" t="n">
+        <v>4.605</v>
       </c>
       <c r="I93" t="n">
+        <v>2.682</v>
+      </c>
+      <c r="J93" t="n">
         <v>1.019</v>
-      </c>
-      <c r="J93" t="n">
-        <v>2.361</v>
       </c>
     </row>
     <row r="94">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.883</v>
+        <v>0.532</v>
       </c>
       <c r="C94" t="n">
-        <v>4.977</v>
+        <v>2.018</v>
       </c>
       <c r="D94" t="n">
         <v>1.992</v>
@@ -9871,14 +9871,14 @@
       <c r="E94" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="G94" t="n">
-        <v>0.532</v>
+      <c r="F94" t="n">
+        <v>4.977</v>
       </c>
       <c r="I94" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="J94" t="n">
         <v>2.271</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2.018</v>
       </c>
     </row>
     <row r="95">
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.943</v>
+        <v>0.519</v>
       </c>
       <c r="C95" t="n">
-        <v>4.436</v>
+        <v>2.03</v>
       </c>
       <c r="D95" t="n">
         <v>1.368</v>
@@ -9899,14 +9899,14 @@
       <c r="E95" t="n">
         <v>0.924</v>
       </c>
-      <c r="G95" t="n">
-        <v>0.519</v>
+      <c r="F95" t="n">
+        <v>4.436</v>
       </c>
       <c r="I95" t="n">
+        <v>2.943</v>
+      </c>
+      <c r="J95" t="n">
         <v>2.405</v>
-      </c>
-      <c r="J95" t="n">
-        <v>2.03</v>
       </c>
     </row>
     <row r="96">
@@ -9916,10 +9916,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.169</v>
+        <v>0.944</v>
       </c>
       <c r="C96" t="n">
-        <v>3.043</v>
+        <v>2.269</v>
       </c>
       <c r="D96" t="n">
         <v>1.896</v>
@@ -9927,14 +9927,14 @@
       <c r="E96" t="n">
         <v>0.845</v>
       </c>
-      <c r="G96" t="n">
-        <v>0.944</v>
+      <c r="F96" t="n">
+        <v>3.043</v>
       </c>
       <c r="I96" t="n">
+        <v>2.169</v>
+      </c>
+      <c r="J96" t="n">
         <v>2.299</v>
-      </c>
-      <c r="J96" t="n">
-        <v>2.269</v>
       </c>
     </row>
     <row r="97">
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2.723</v>
+        <v>0.651</v>
       </c>
       <c r="C97" t="n">
-        <v>3.985</v>
+        <v>2.062</v>
       </c>
       <c r="D97" t="n">
         <v>1.751</v>
@@ -9955,14 +9955,14 @@
       <c r="E97" t="n">
         <v>0.701</v>
       </c>
-      <c r="G97" t="n">
-        <v>0.651</v>
+      <c r="F97" t="n">
+        <v>3.985</v>
       </c>
       <c r="I97" t="n">
+        <v>2.723</v>
+      </c>
+      <c r="J97" t="n">
         <v>2.093</v>
-      </c>
-      <c r="J97" t="n">
-        <v>2.062</v>
       </c>
     </row>
     <row r="98">
@@ -9972,10 +9972,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.508</v>
+        <v>0.207</v>
       </c>
       <c r="C98" t="n">
-        <v>4.166</v>
+        <v>2.195</v>
       </c>
       <c r="D98" t="n">
         <v>1.761</v>
@@ -9983,14 +9983,14 @@
       <c r="E98" t="n">
         <v>0.771</v>
       </c>
-      <c r="G98" t="n">
-        <v>0.207</v>
+      <c r="F98" t="n">
+        <v>4.166</v>
       </c>
       <c r="I98" t="n">
+        <v>2.508</v>
+      </c>
+      <c r="J98" t="n">
         <v>2.16</v>
-      </c>
-      <c r="J98" t="n">
-        <v>2.195</v>
       </c>
     </row>
     <row r="99">
@@ -10000,10 +10000,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.834</v>
+        <v>0.863</v>
       </c>
       <c r="C99" t="n">
-        <v>4.193</v>
+        <v>2.157</v>
       </c>
       <c r="D99" t="n">
         <v>1.793</v>
@@ -10011,14 +10011,14 @@
       <c r="E99" t="n">
         <v>0.635</v>
       </c>
-      <c r="G99" t="n">
-        <v>0.863</v>
+      <c r="F99" t="n">
+        <v>4.193</v>
       </c>
       <c r="I99" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="J99" t="n">
         <v>1.963</v>
-      </c>
-      <c r="J99" t="n">
-        <v>2.157</v>
       </c>
     </row>
     <row r="100">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>3.366</v>
+        <v>0.456</v>
       </c>
       <c r="C100" t="n">
-        <v>4.656</v>
+        <v>2.229</v>
       </c>
       <c r="D100" t="n">
         <v>2.094</v>
@@ -10039,14 +10039,14 @@
       <c r="E100" t="n">
         <v>0.375</v>
       </c>
-      <c r="G100" t="n">
-        <v>0.456</v>
+      <c r="F100" t="n">
+        <v>4.656</v>
       </c>
       <c r="I100" t="n">
+        <v>3.366</v>
+      </c>
+      <c r="J100" t="n">
         <v>2.249</v>
-      </c>
-      <c r="J100" t="n">
-        <v>2.229</v>
       </c>
     </row>
     <row r="101">
@@ -10056,10 +10056,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>3.38</v>
+        <v>0.588</v>
       </c>
       <c r="C101" t="n">
-        <v>4.739</v>
+        <v>2.342</v>
       </c>
       <c r="D101" t="n">
         <v>2.022</v>
@@ -10067,14 +10067,14 @@
       <c r="E101" t="n">
         <v>0.761</v>
       </c>
-      <c r="G101" t="n">
-        <v>0.588</v>
+      <c r="F101" t="n">
+        <v>4.739</v>
       </c>
       <c r="I101" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="J101" t="n">
         <v>2.184</v>
-      </c>
-      <c r="J101" t="n">
-        <v>2.342</v>
       </c>
     </row>
     <row r="102">
@@ -10084,10 +10084,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3.175</v>
+        <v>0.77</v>
       </c>
       <c r="C102" t="n">
-        <v>4.976</v>
+        <v>2.257</v>
       </c>
       <c r="D102" t="n">
         <v>2.334</v>
@@ -10095,14 +10095,14 @@
       <c r="E102" t="n">
         <v>0.824</v>
       </c>
-      <c r="G102" t="n">
-        <v>0.77</v>
+      <c r="F102" t="n">
+        <v>4.976</v>
       </c>
       <c r="I102" t="n">
+        <v>3.175</v>
+      </c>
+      <c r="J102" t="n">
         <v>2.504</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2.257</v>
       </c>
     </row>
     <row r="103">
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3.573</v>
+        <v>0.739</v>
       </c>
       <c r="C103" t="n">
-        <v>4.844</v>
+        <v>2.148</v>
       </c>
       <c r="D103" t="n">
         <v>2.178</v>
@@ -10123,14 +10123,14 @@
       <c r="E103" t="n">
         <v>0.749</v>
       </c>
-      <c r="G103" t="n">
-        <v>0.739</v>
+      <c r="F103" t="n">
+        <v>4.844</v>
       </c>
       <c r="I103" t="n">
+        <v>3.573</v>
+      </c>
+      <c r="J103" t="n">
         <v>1.855</v>
-      </c>
-      <c r="J103" t="n">
-        <v>2.148</v>
       </c>
     </row>
     <row r="104">
@@ -10140,10 +10140,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3.334</v>
+        <v>0.527</v>
       </c>
       <c r="C104" t="n">
-        <v>4.822</v>
+        <v>2.096</v>
       </c>
       <c r="D104" t="n">
         <v>2.229</v>
@@ -10151,14 +10151,14 @@
       <c r="E104" t="n">
         <v>0.898</v>
       </c>
-      <c r="G104" t="n">
-        <v>0.527</v>
+      <c r="F104" t="n">
+        <v>4.822</v>
       </c>
       <c r="I104" t="n">
+        <v>3.334</v>
+      </c>
+      <c r="J104" t="n">
         <v>1.559</v>
-      </c>
-      <c r="J104" t="n">
-        <v>2.096</v>
       </c>
     </row>
     <row r="105">
@@ -10168,10 +10168,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3.31</v>
+        <v>0.903</v>
       </c>
       <c r="C105" t="n">
-        <v>4.861</v>
+        <v>2.154</v>
       </c>
       <c r="D105" t="n">
         <v>2.072</v>
@@ -10179,14 +10179,14 @@
       <c r="E105" t="n">
         <v>0.886</v>
       </c>
-      <c r="G105" t="n">
-        <v>0.903</v>
+      <c r="F105" t="n">
+        <v>4.861</v>
       </c>
       <c r="I105" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J105" t="n">
         <v>0.923</v>
-      </c>
-      <c r="J105" t="n">
-        <v>2.154</v>
       </c>
     </row>
     <row r="106">
@@ -10196,10 +10196,10 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.768</v>
+        <v>0.522</v>
       </c>
       <c r="C106" t="n">
-        <v>4.35</v>
+        <v>1.821</v>
       </c>
       <c r="D106" t="n">
         <v>1.946</v>
@@ -10207,14 +10207,14 @@
       <c r="E106" t="n">
         <v>0.882</v>
       </c>
-      <c r="G106" t="n">
-        <v>0.522</v>
+      <c r="F106" t="n">
+        <v>4.35</v>
       </c>
       <c r="I106" t="n">
+        <v>2.768</v>
+      </c>
+      <c r="J106" t="n">
         <v>0.39</v>
-      </c>
-      <c r="J106" t="n">
-        <v>1.821</v>
       </c>
     </row>
     <row r="107">
@@ -10224,10 +10224,10 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3.158</v>
+        <v>0.411</v>
       </c>
       <c r="C107" t="n">
-        <v>4.624</v>
+        <v>2.163</v>
       </c>
       <c r="D107" t="n">
         <v>1.528</v>
@@ -10235,14 +10235,14 @@
       <c r="E107" t="n">
         <v>0.885</v>
       </c>
-      <c r="G107" t="n">
-        <v>0.411</v>
+      <c r="F107" t="n">
+        <v>4.624</v>
       </c>
       <c r="I107" t="n">
+        <v>3.158</v>
+      </c>
+      <c r="J107" t="n">
         <v>1.942</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2.163</v>
       </c>
     </row>
     <row r="108">
@@ -10252,10 +10252,10 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3.038</v>
+        <v>0.466</v>
       </c>
       <c r="C108" t="n">
-        <v>3.944</v>
+        <v>2.346</v>
       </c>
       <c r="D108" t="n">
         <v>1.849</v>
@@ -10263,14 +10263,14 @@
       <c r="E108" t="n">
         <v>0.695</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.466</v>
+      <c r="F108" t="n">
+        <v>3.944</v>
       </c>
       <c r="I108" t="n">
+        <v>3.038</v>
+      </c>
+      <c r="J108" t="n">
         <v>2.36</v>
-      </c>
-      <c r="J108" t="n">
-        <v>2.346</v>
       </c>
     </row>
     <row r="109">
@@ -10280,10 +10280,10 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2.762</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="C109" t="n">
-        <v>4.213</v>
+        <v>2.018</v>
       </c>
       <c r="D109" t="n">
         <v>1.815</v>
@@ -10291,14 +10291,14 @@
       <c r="E109" t="n">
         <v>0.745</v>
       </c>
-      <c r="G109" t="n">
-        <v>0.6850000000000001</v>
+      <c r="F109" t="n">
+        <v>4.213</v>
       </c>
       <c r="I109" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="J109" t="n">
         <v>0.871</v>
-      </c>
-      <c r="J109" t="n">
-        <v>2.018</v>
       </c>
     </row>
     <row r="110">
@@ -10308,10 +10308,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.298</v>
+        <v>0.957</v>
       </c>
       <c r="C110" t="n">
-        <v>4.164</v>
+        <v>2.234</v>
       </c>
       <c r="D110" t="n">
         <v>1.829</v>
@@ -10319,14 +10319,14 @@
       <c r="E110" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="G110" t="n">
-        <v>0.957</v>
+      <c r="F110" t="n">
+        <v>4.164</v>
       </c>
       <c r="I110" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="J110" t="n">
         <v>2.212</v>
-      </c>
-      <c r="J110" t="n">
-        <v>2.234</v>
       </c>
     </row>
     <row r="111">
@@ -10336,10 +10336,10 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2.537</v>
+        <v>0.499</v>
       </c>
       <c r="C111" t="n">
-        <v>4.401</v>
+        <v>2.349</v>
       </c>
       <c r="D111" t="n">
         <v>1.885</v>
@@ -10347,14 +10347,14 @@
       <c r="E111" t="n">
         <v>0.639</v>
       </c>
-      <c r="G111" t="n">
-        <v>0.499</v>
+      <c r="F111" t="n">
+        <v>4.401</v>
       </c>
       <c r="I111" t="n">
+        <v>2.537</v>
+      </c>
+      <c r="J111" t="n">
         <v>2.288</v>
-      </c>
-      <c r="J111" t="n">
-        <v>2.349</v>
       </c>
     </row>
     <row r="112">
@@ -10364,10 +10364,10 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.711</v>
+        <v>0.447</v>
       </c>
       <c r="C112" t="n">
-        <v>4.533</v>
+        <v>2.348</v>
       </c>
       <c r="D112" t="n">
         <v>1.887</v>
@@ -10375,14 +10375,14 @@
       <c r="E112" t="n">
         <v>0.448</v>
       </c>
-      <c r="G112" t="n">
-        <v>0.447</v>
+      <c r="F112" t="n">
+        <v>4.533</v>
       </c>
       <c r="I112" t="n">
+        <v>2.711</v>
+      </c>
+      <c r="J112" t="n">
         <v>2.427</v>
-      </c>
-      <c r="J112" t="n">
-        <v>2.348</v>
       </c>
     </row>
     <row r="113">
@@ -10392,10 +10392,10 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.838</v>
+        <v>0.381</v>
       </c>
       <c r="C113" t="n">
-        <v>4.609</v>
+        <v>2.38</v>
       </c>
       <c r="D113" t="n">
         <v>2.183</v>
@@ -10403,14 +10403,14 @@
       <c r="E113" t="n">
         <v>0.831</v>
       </c>
-      <c r="G113" t="n">
-        <v>0.381</v>
+      <c r="F113" t="n">
+        <v>4.609</v>
       </c>
       <c r="I113" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="J113" t="n">
         <v>2.021</v>
-      </c>
-      <c r="J113" t="n">
-        <v>2.38</v>
       </c>
     </row>
     <row r="114">
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.751</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>4.677</v>
+        <v>2.365</v>
       </c>
       <c r="D114" t="n">
         <v>2.291</v>
@@ -10432,16 +10432,16 @@
         <v>0.785</v>
       </c>
       <c r="F114" t="n">
+        <v>4.677</v>
+      </c>
+      <c r="G114" t="n">
         <v>0.257</v>
       </c>
-      <c r="G114" t="n">
-        <v>0.6870000000000001</v>
-      </c>
       <c r="I114" t="n">
+        <v>2.751</v>
+      </c>
+      <c r="J114" t="n">
         <v>2.395</v>
-      </c>
-      <c r="J114" t="n">
-        <v>2.365</v>
       </c>
     </row>
     <row r="115">
@@ -10451,10 +10451,10 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2.754</v>
+        <v>0.427</v>
       </c>
       <c r="C115" t="n">
-        <v>4.853</v>
+        <v>2.185</v>
       </c>
       <c r="D115" t="n">
         <v>2.193</v>
@@ -10463,16 +10463,16 @@
         <v>1</v>
       </c>
       <c r="F115" t="n">
+        <v>4.853</v>
+      </c>
+      <c r="G115" t="n">
         <v>1.511</v>
       </c>
-      <c r="G115" t="n">
-        <v>0.427</v>
-      </c>
       <c r="I115" t="n">
+        <v>2.754</v>
+      </c>
+      <c r="J115" t="n">
         <v>1.969</v>
-      </c>
-      <c r="J115" t="n">
-        <v>2.185</v>
       </c>
     </row>
     <row r="116">
@@ -10482,10 +10482,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2.85</v>
+        <v>0.761</v>
       </c>
       <c r="C116" t="n">
-        <v>4.574</v>
+        <v>2.582</v>
       </c>
       <c r="D116" t="n">
         <v>2.343</v>
@@ -10494,16 +10494,16 @@
         <v>0.868</v>
       </c>
       <c r="F116" t="n">
+        <v>4.574</v>
+      </c>
+      <c r="G116" t="n">
         <v>2.461</v>
       </c>
-      <c r="G116" t="n">
-        <v>0.761</v>
-      </c>
       <c r="I116" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="J116" t="n">
         <v>2.404</v>
-      </c>
-      <c r="J116" t="n">
-        <v>2.582</v>
       </c>
     </row>
     <row r="117">
@@ -10513,10 +10513,10 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3.251</v>
+        <v>0.2</v>
       </c>
       <c r="C117" t="n">
-        <v>4.818</v>
+        <v>2.341</v>
       </c>
       <c r="D117" t="n">
         <v>2.107</v>
@@ -10525,16 +10525,16 @@
         <v>0.882</v>
       </c>
       <c r="F117" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="G117" t="n">
         <v>3.473</v>
       </c>
-      <c r="G117" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I117" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="J117" t="n">
         <v>2.257</v>
-      </c>
-      <c r="J117" t="n">
-        <v>2.341</v>
       </c>
     </row>
     <row r="118">
@@ -10544,10 +10544,10 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3.347</v>
+        <v>0.525</v>
       </c>
       <c r="C118" t="n">
-        <v>4.631</v>
+        <v>2.317</v>
       </c>
       <c r="D118" t="n">
         <v>2.195</v>
@@ -10556,16 +10556,16 @@
         <v>0.758</v>
       </c>
       <c r="F118" t="n">
+        <v>4.631</v>
+      </c>
+      <c r="G118" t="n">
         <v>3.886</v>
       </c>
-      <c r="G118" t="n">
-        <v>0.525</v>
-      </c>
       <c r="I118" t="n">
+        <v>3.347</v>
+      </c>
+      <c r="J118" t="n">
         <v>2.502</v>
-      </c>
-      <c r="J118" t="n">
-        <v>2.317</v>
       </c>
     </row>
     <row r="119">
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3.3</v>
+        <v>0.61</v>
       </c>
       <c r="C119" t="n">
-        <v>4.39</v>
+        <v>2.196</v>
       </c>
       <c r="D119" t="n">
         <v>1.442</v>
@@ -10587,16 +10587,16 @@
         <v>0.847</v>
       </c>
       <c r="F119" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="G119" t="n">
         <v>4.23</v>
       </c>
-      <c r="G119" t="n">
-        <v>0.61</v>
-      </c>
       <c r="I119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J119" t="n">
         <v>2.3</v>
-      </c>
-      <c r="J119" t="n">
-        <v>2.196</v>
       </c>
     </row>
     <row r="120">
@@ -10606,10 +10606,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3.13</v>
+        <v>0.754</v>
       </c>
       <c r="C120" t="n">
-        <v>3.084</v>
+        <v>2.259</v>
       </c>
       <c r="D120" t="n">
         <v>1.677</v>
@@ -10618,16 +10618,16 @@
         <v>0.899</v>
       </c>
       <c r="F120" t="n">
+        <v>3.084</v>
+      </c>
+      <c r="G120" t="n">
         <v>4.893</v>
       </c>
-      <c r="G120" t="n">
-        <v>0.754</v>
-      </c>
       <c r="I120" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="J120" t="n">
         <v>2.442</v>
-      </c>
-      <c r="J120" t="n">
-        <v>2.259</v>
       </c>
     </row>
     <row r="121">
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3.043</v>
+        <v>0.255</v>
       </c>
       <c r="C121" t="n">
-        <v>4.035</v>
+        <v>2.388</v>
       </c>
       <c r="D121" t="n">
         <v>1.91</v>
@@ -10649,16 +10649,16 @@
         <v>0.75</v>
       </c>
       <c r="F121" t="n">
+        <v>4.035</v>
+      </c>
+      <c r="G121" t="n">
         <v>4.92</v>
       </c>
-      <c r="G121" t="n">
-        <v>0.255</v>
-      </c>
       <c r="I121" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="J121" t="n">
         <v>2.109</v>
-      </c>
-      <c r="J121" t="n">
-        <v>2.388</v>
       </c>
     </row>
     <row r="122">
@@ -10668,10 +10668,10 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>3.144</v>
+        <v>0.469</v>
       </c>
       <c r="C122" t="n">
-        <v>4.155</v>
+        <v>2.334</v>
       </c>
       <c r="D122" t="n">
         <v>1.936</v>
@@ -10680,16 +10680,16 @@
         <v>0.798</v>
       </c>
       <c r="F122" t="n">
+        <v>4.155</v>
+      </c>
+      <c r="G122" t="n">
         <v>5.517</v>
       </c>
-      <c r="G122" t="n">
-        <v>0.469</v>
-      </c>
       <c r="I122" t="n">
+        <v>3.144</v>
+      </c>
+      <c r="J122" t="n">
         <v>2.134</v>
-      </c>
-      <c r="J122" t="n">
-        <v>2.334</v>
       </c>
     </row>
     <row r="123">
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3.132</v>
+        <v>0.726</v>
       </c>
       <c r="C123" t="n">
-        <v>4.221</v>
+        <v>2.546</v>
       </c>
       <c r="D123" t="n">
         <v>2.012</v>
@@ -10711,16 +10711,16 @@
         <v>0.541</v>
       </c>
       <c r="F123" t="n">
+        <v>4.221</v>
+      </c>
+      <c r="G123" t="n">
         <v>5.711</v>
       </c>
-      <c r="G123" t="n">
-        <v>0.726</v>
-      </c>
       <c r="I123" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="J123" t="n">
         <v>2.179</v>
-      </c>
-      <c r="J123" t="n">
-        <v>2.546</v>
       </c>
     </row>
     <row r="124">
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>2.748</v>
+        <v>0.496</v>
       </c>
       <c r="C124" t="n">
-        <v>4.489</v>
+        <v>2.684</v>
       </c>
       <c r="D124" t="n">
         <v>1.997</v>
@@ -10742,16 +10742,16 @@
         <v>0.546</v>
       </c>
       <c r="F124" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="G124" t="n">
         <v>7.541</v>
       </c>
-      <c r="G124" t="n">
-        <v>0.496</v>
-      </c>
       <c r="I124" t="n">
+        <v>2.748</v>
+      </c>
+      <c r="J124" t="n">
         <v>2.459</v>
-      </c>
-      <c r="J124" t="n">
-        <v>2.684</v>
       </c>
     </row>
     <row r="125">
@@ -10761,10 +10761,10 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3.385</v>
+        <v>0.531</v>
       </c>
       <c r="C125" t="n">
-        <v>4.926</v>
+        <v>3.095</v>
       </c>
       <c r="D125" t="n">
         <v>2.14</v>
@@ -10773,16 +10773,16 @@
         <v>0.723</v>
       </c>
       <c r="F125" t="n">
+        <v>4.926</v>
+      </c>
+      <c r="G125" t="n">
         <v>7.614</v>
       </c>
-      <c r="G125" t="n">
-        <v>0.531</v>
-      </c>
       <c r="I125" t="n">
+        <v>3.385</v>
+      </c>
+      <c r="J125" t="n">
         <v>2.326</v>
-      </c>
-      <c r="J125" t="n">
-        <v>3.095</v>
       </c>
     </row>
     <row r="126">
@@ -10792,10 +10792,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3.581</v>
+        <v>0.805</v>
       </c>
       <c r="C126" t="n">
-        <v>4.725</v>
+        <v>3.189</v>
       </c>
       <c r="D126" t="n">
         <v>2.463</v>
@@ -10804,16 +10804,16 @@
         <v>1.007</v>
       </c>
       <c r="F126" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="G126" t="n">
         <v>7.775</v>
       </c>
-      <c r="G126" t="n">
-        <v>0.805</v>
-      </c>
       <c r="I126" t="n">
+        <v>3.581</v>
+      </c>
+      <c r="J126" t="n">
         <v>2.438</v>
-      </c>
-      <c r="J126" t="n">
-        <v>3.189</v>
       </c>
     </row>
     <row r="127">
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3.321</v>
+        <v>0.361</v>
       </c>
       <c r="C127" t="n">
-        <v>4.649</v>
+        <v>2.945</v>
       </c>
       <c r="D127" t="n">
         <v>2.253</v>
@@ -10835,16 +10835,16 @@
         <v>0.838</v>
       </c>
       <c r="F127" t="n">
+        <v>4.649</v>
+      </c>
+      <c r="G127" t="n">
         <v>8.148</v>
       </c>
-      <c r="G127" t="n">
-        <v>0.361</v>
-      </c>
       <c r="I127" t="n">
+        <v>3.321</v>
+      </c>
+      <c r="J127" t="n">
         <v>2.232</v>
-      </c>
-      <c r="J127" t="n">
-        <v>2.945</v>
       </c>
     </row>
     <row r="128">
@@ -10854,10 +10854,10 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3.384</v>
+        <v>0.294</v>
       </c>
       <c r="C128" t="n">
-        <v>4.756</v>
+        <v>3.317</v>
       </c>
       <c r="D128" t="n">
         <v>2.269</v>
@@ -10866,16 +10866,16 @@
         <v>0.719</v>
       </c>
       <c r="F128" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="G128" t="n">
         <v>7.524</v>
       </c>
-      <c r="G128" t="n">
-        <v>0.294</v>
-      </c>
       <c r="I128" t="n">
+        <v>3.384</v>
+      </c>
+      <c r="J128" t="n">
         <v>2.441</v>
-      </c>
-      <c r="J128" t="n">
-        <v>3.317</v>
       </c>
     </row>
     <row r="129">
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3.317</v>
+        <v>0.518</v>
       </c>
       <c r="C129" t="n">
-        <v>4.918</v>
+        <v>3.361</v>
       </c>
       <c r="D129" t="n">
         <v>2.284</v>
@@ -10897,16 +10897,16 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="F129" t="n">
+        <v>4.918</v>
+      </c>
+      <c r="G129" t="n">
         <v>8.334</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.518</v>
-      </c>
       <c r="I129" t="n">
+        <v>3.317</v>
+      </c>
+      <c r="J129" t="n">
         <v>2.455</v>
-      </c>
-      <c r="J129" t="n">
-        <v>3.361</v>
       </c>
     </row>
     <row r="130">
@@ -10916,10 +10916,10 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3.437</v>
+        <v>0.555</v>
       </c>
       <c r="C130" t="n">
-        <v>4.745</v>
+        <v>3.154</v>
       </c>
       <c r="D130" t="n">
         <v>2.113</v>
@@ -10928,19 +10928,19 @@
         <v>0.762</v>
       </c>
       <c r="F130" t="n">
+        <v>4.745</v>
+      </c>
+      <c r="G130" t="n">
         <v>7.89</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0.555</v>
       </c>
       <c r="H130" t="n">
         <v>0.263</v>
       </c>
       <c r="I130" t="n">
+        <v>3.437</v>
+      </c>
+      <c r="J130" t="n">
         <v>2.511</v>
-      </c>
-      <c r="J130" t="n">
-        <v>3.154</v>
       </c>
     </row>
     <row r="131">
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3.066</v>
+        <v>0.331</v>
       </c>
       <c r="C131" t="n">
-        <v>4.314</v>
+        <v>3.122</v>
       </c>
       <c r="D131" t="n">
         <v>1.546</v>
@@ -10962,19 +10962,19 @@
         <v>0.883</v>
       </c>
       <c r="F131" t="n">
+        <v>4.314</v>
+      </c>
+      <c r="G131" t="n">
         <v>7.846</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0.331</v>
       </c>
       <c r="H131" t="n">
         <v>0.244</v>
       </c>
       <c r="I131" t="n">
+        <v>3.066</v>
+      </c>
+      <c r="J131" t="n">
         <v>1.993</v>
-      </c>
-      <c r="J131" t="n">
-        <v>3.122</v>
       </c>
     </row>
     <row r="132">
@@ -10984,10 +10984,10 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>3.177</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>4.436</v>
+        <v>3.271</v>
       </c>
       <c r="D132" t="n">
         <v>2.187</v>
@@ -10996,19 +10996,19 @@
         <v>0.765</v>
       </c>
       <c r="F132" t="n">
+        <v>4.436</v>
+      </c>
+      <c r="G132" t="n">
         <v>7.62</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0.9419999999999999</v>
       </c>
       <c r="H132" t="n">
         <v>0.251</v>
       </c>
       <c r="I132" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="J132" t="n">
         <v>2.16</v>
-      </c>
-      <c r="J132" t="n">
-        <v>3.271</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Bcfd by plant" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Estimated (calibrated)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Points (Dth)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Monthly check" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="EIA exports (Bcfd)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TC next day (timely)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Monthly check" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="EIA exports (Bcfd)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -671,14 +672,14 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>POINTS</t>
+          <t>TC ENERGY METERS (ANR, COLUMBIA GULF)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Each 'Points (Dth)' column is 'Plant | meter (pipeline code, location id)'.</t>
+          <t>TC eConnects only serves its latest posting - by each morning run, the next gas day's Timely cycle. Each run caches it ('TC next day (timely)') and the next run uses it for that day, so TC's meters (Calcasieu Pass via ANR; Cameron and Plaquemines via Columbia Gulf) are Timely nominations, not the final cycle, and have no history before the cache started. A missed run leaves that day's TC meters blank.</t>
         </is>
       </c>
     </row>
@@ -686,14 +687,29 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SOURCE</t>
+          <t>POINTS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate), Energy Transfer Messenger+ and Cheniere LNG Connection equivalents - all operator-hosted.</t>
+          <t>Each 'Points (Dth)' column is 'Plant | meter (pipeline code, location id)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kinder Morgan (pipeline2.kindermorgan.com) and Enbridge LINK (rtba.enbridge.com) Operationally Available Capacity postings, Total Scheduled Quantity column; gasnom.com (Cameron Interstate), Energy Transfer Messenger+, Cheniere LNG Connection, TC eConnects and BHE GT&amp;S equivalents - all operator-hosted.</t>
         </is>
       </c>
     </row>
@@ -1085,6 +1101,59 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>gas_day</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Calcasieu Pass | ANR -&gt; TransCameron (Grand Chenier XPress), Mermentau River (ANR 523094)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Plaquemines | Columbia Gulf -&gt; Wilkinson Bayou (Gator Express) (CGT 4267)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cameron | Columbia Gulf -&gt; Cameron LNG (CGT 4246)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1097052</v>
+      </c>
+      <c r="C2" t="n">
+        <v>625127</v>
+      </c>
+      <c r="D2" t="n">
+        <v>668725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8453,7 +8522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8480,32 +8549,32 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Cove Point</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Elba Island</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Cameron</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Plaquemines</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Golden Pass</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Freeport</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -8523,7 +8592,7 @@
       <c r="C2" t="n">
         <v>0.329</v>
       </c>
-      <c r="I2" t="n">
+      <c r="D2" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -8533,7 +8602,7 @@
           <t>2011-02</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="D3" t="n">
         <v>0.121</v>
       </c>
     </row>
@@ -8556,7 +8625,7 @@
       <c r="C5" t="n">
         <v>0.105</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8569,11 +8638,11 @@
       <c r="C6" t="n">
         <v>0.059</v>
       </c>
-      <c r="F6" t="n">
+      <c r="D6" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.096</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.101</v>
       </c>
     </row>
     <row r="7">
@@ -8582,7 +8651,7 @@
           <t>2011-07</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="D7" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -8625,7 +8694,7 @@
       <c r="C11" t="n">
         <v>0.074</v>
       </c>
-      <c r="I11" t="n">
+      <c r="D11" t="n">
         <v>0.108</v>
       </c>
     </row>
@@ -8638,7 +8707,7 @@
       <c r="C12" t="n">
         <v>0.112</v>
       </c>
-      <c r="I12" t="n">
+      <c r="D12" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8658,7 +8727,7 @@
           <t>2012-03</t>
         </is>
       </c>
-      <c r="I14" t="n">
+      <c r="D14" t="n">
         <v>0.091</v>
       </c>
     </row>
@@ -8668,7 +8737,7 @@
           <t>2012-10</t>
         </is>
       </c>
-      <c r="I15" t="n">
+      <c r="D15" t="n">
         <v>0.093</v>
       </c>
     </row>
@@ -8681,7 +8750,7 @@
       <c r="C16" t="n">
         <v>0.092</v>
       </c>
-      <c r="I16" t="n">
+      <c r="D16" t="n">
         <v>0.102</v>
       </c>
     </row>
@@ -8691,7 +8760,7 @@
           <t>2013-11</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="D17" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8701,7 +8770,7 @@
           <t>2014-02</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="D18" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -8711,7 +8780,7 @@
           <t>2015-01</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="D19" t="n">
         <v>0.099</v>
       </c>
     </row>
@@ -8721,7 +8790,7 @@
           <t>2015-02</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="D20" t="n">
         <v>0.106</v>
       </c>
     </row>
@@ -8731,7 +8800,7 @@
           <t>2015-11</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="D21" t="n">
         <v>0.107</v>
       </c>
     </row>
@@ -8741,7 +8810,7 @@
           <t>2015-12</t>
         </is>
       </c>
-      <c r="I22" t="n">
+      <c r="D22" t="n">
         <v>0.111</v>
       </c>
     </row>
@@ -9004,7 +9073,7 @@
       <c r="C48" t="n">
         <v>3.11</v>
       </c>
-      <c r="D48" t="n">
+      <c r="H48" t="n">
         <v>0.105</v>
       </c>
     </row>
@@ -9017,7 +9086,7 @@
       <c r="C49" t="n">
         <v>2.788</v>
       </c>
-      <c r="D49" t="n">
+      <c r="H49" t="n">
         <v>0.325</v>
       </c>
     </row>
@@ -9030,7 +9099,7 @@
       <c r="C50" t="n">
         <v>2.562</v>
       </c>
-      <c r="D50" t="n">
+      <c r="H50" t="n">
         <v>0.77</v>
       </c>
     </row>
@@ -9043,7 +9112,7 @@
       <c r="C51" t="n">
         <v>2.213</v>
       </c>
-      <c r="D51" t="n">
+      <c r="H51" t="n">
         <v>0.457</v>
       </c>
     </row>
@@ -9056,7 +9125,7 @@
       <c r="C52" t="n">
         <v>2.778</v>
       </c>
-      <c r="D52" t="n">
+      <c r="H52" t="n">
         <v>0.675</v>
       </c>
     </row>
@@ -9069,7 +9138,7 @@
       <c r="C53" t="n">
         <v>2.54</v>
       </c>
-      <c r="D53" t="n">
+      <c r="H53" t="n">
         <v>0.676</v>
       </c>
     </row>
@@ -9082,7 +9151,7 @@
       <c r="C54" t="n">
         <v>2.507</v>
       </c>
-      <c r="D54" t="n">
+      <c r="H54" t="n">
         <v>0.449</v>
       </c>
     </row>
@@ -9095,7 +9164,7 @@
       <c r="C55" t="n">
         <v>2.932</v>
       </c>
-      <c r="D55" t="n">
+      <c r="H55" t="n">
         <v>0.226</v>
       </c>
     </row>
@@ -9108,7 +9177,7 @@
       <c r="C56" t="n">
         <v>3.202</v>
       </c>
-      <c r="D56" t="n">
+      <c r="H56" t="n">
         <v>0.701</v>
       </c>
     </row>
@@ -9121,7 +9190,7 @@
       <c r="C57" t="n">
         <v>3.36</v>
       </c>
-      <c r="D57" t="n">
+      <c r="H57" t="n">
         <v>0.711</v>
       </c>
       <c r="J57" t="n">
@@ -9137,7 +9206,7 @@
       <c r="C58" t="n">
         <v>3.367</v>
       </c>
-      <c r="D58" t="n">
+      <c r="H58" t="n">
         <v>0.714</v>
       </c>
       <c r="J58" t="n">
@@ -9153,7 +9222,7 @@
       <c r="C59" t="n">
         <v>2.942</v>
       </c>
-      <c r="D59" t="n">
+      <c r="H59" t="n">
         <v>0.915</v>
       </c>
       <c r="J59" t="n">
@@ -9169,7 +9238,7 @@
       <c r="C60" t="n">
         <v>3.291</v>
       </c>
-      <c r="D60" t="n">
+      <c r="H60" t="n">
         <v>0.599</v>
       </c>
       <c r="J60" t="n">
@@ -9185,7 +9254,7 @@
       <c r="C61" t="n">
         <v>3.054</v>
       </c>
-      <c r="D61" t="n">
+      <c r="H61" t="n">
         <v>0.867</v>
       </c>
       <c r="J61" t="n">
@@ -9201,11 +9270,11 @@
       <c r="C62" t="n">
         <v>3.762</v>
       </c>
-      <c r="D62" t="n">
+      <c r="G62" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="H62" t="n">
         <v>0.602</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.113</v>
       </c>
       <c r="J62" t="n">
         <v>0.614</v>
@@ -9220,11 +9289,11 @@
       <c r="C63" t="n">
         <v>3.551</v>
       </c>
-      <c r="D63" t="n">
+      <c r="G63" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="H63" t="n">
         <v>0.731</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.106</v>
       </c>
       <c r="J63" t="n">
         <v>0.765</v>
@@ -9239,11 +9308,11 @@
       <c r="C64" t="n">
         <v>3.347</v>
       </c>
-      <c r="D64" t="n">
+      <c r="G64" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.731</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.248</v>
       </c>
       <c r="J64" t="n">
         <v>1.184</v>
@@ -9258,11 +9327,11 @@
       <c r="C65" t="n">
         <v>2.696</v>
       </c>
-      <c r="D65" t="n">
+      <c r="G65" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="H65" t="n">
         <v>0.699</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.388</v>
       </c>
       <c r="J65" t="n">
         <v>1.084</v>
@@ -9278,13 +9347,13 @@
         <v>3.461</v>
       </c>
       <c r="D66" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="H66" t="n">
         <v>0.5</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.235</v>
       </c>
       <c r="J66" t="n">
         <v>1.26</v>
@@ -9300,13 +9369,13 @@
         <v>3.775</v>
       </c>
       <c r="D67" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="H67" t="n">
         <v>0.244</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.365</v>
       </c>
       <c r="J67" t="n">
         <v>1.488</v>
@@ -9322,13 +9391,13 @@
         <v>3.852</v>
       </c>
       <c r="D68" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.852</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.353</v>
       </c>
       <c r="J68" t="n">
         <v>1.357</v>
@@ -9344,16 +9413,16 @@
         <v>3.813</v>
       </c>
       <c r="D69" t="n">
-        <v>0.729</v>
+        <v>0.79</v>
       </c>
       <c r="E69" t="n">
         <v>0.114</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>0.84</v>
       </c>
-      <c r="I69" t="n">
-        <v>0.79</v>
+      <c r="H69" t="n">
+        <v>0.729</v>
       </c>
       <c r="J69" t="n">
         <v>1.461</v>
@@ -9369,16 +9438,16 @@
         <v>4.018</v>
       </c>
       <c r="D70" t="n">
-        <v>0.722</v>
+        <v>1.456</v>
       </c>
       <c r="E70" t="n">
         <v>0.214</v>
       </c>
-      <c r="F70" t="n">
+      <c r="G70" t="n">
         <v>0.98</v>
       </c>
-      <c r="I70" t="n">
-        <v>1.456</v>
+      <c r="H70" t="n">
+        <v>0.722</v>
       </c>
       <c r="J70" t="n">
         <v>1.426</v>
@@ -9394,13 +9463,13 @@
         <v>3.684</v>
       </c>
       <c r="D71" t="n">
+        <v>1.446</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="H71" t="n">
         <v>0.758</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1.446</v>
       </c>
       <c r="J71" t="n">
         <v>1.55</v>
@@ -9416,13 +9485,13 @@
         <v>3.447</v>
       </c>
       <c r="D72" t="n">
+        <v>1.635</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1.208</v>
+      </c>
+      <c r="H72" t="n">
         <v>0.831</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="I72" t="n">
-        <v>1.635</v>
       </c>
       <c r="J72" t="n">
         <v>1.462</v>
@@ -9438,13 +9507,13 @@
         <v>3.333</v>
       </c>
       <c r="D73" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="H73" t="n">
         <v>0.608</v>
-      </c>
-      <c r="F73" t="n">
-        <v>1.301</v>
-      </c>
-      <c r="I73" t="n">
-        <v>1.158</v>
       </c>
       <c r="J73" t="n">
         <v>1.245</v>
@@ -9460,13 +9529,13 @@
         <v>2.73</v>
       </c>
       <c r="D74" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="H74" t="n">
         <v>0.708</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="I74" t="n">
-        <v>1.008</v>
       </c>
       <c r="J74" t="n">
         <v>0.831</v>
@@ -9482,13 +9551,13 @@
         <v>0.978</v>
       </c>
       <c r="D75" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="H75" t="n">
         <v>0.763</v>
-      </c>
-      <c r="F75" t="n">
-        <v>1.366</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.543</v>
       </c>
       <c r="J75" t="n">
         <v>0.307</v>
@@ -9504,13 +9573,13 @@
         <v>1.063</v>
       </c>
       <c r="D76" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1.099</v>
+      </c>
+      <c r="H76" t="n">
         <v>0.711</v>
-      </c>
-      <c r="F76" t="n">
-        <v>1.099</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.132</v>
       </c>
       <c r="J76" t="n">
         <v>0.373</v>
@@ -9526,16 +9595,16 @@
         <v>1.031</v>
       </c>
       <c r="D77" t="n">
-        <v>0.596</v>
+        <v>0.399</v>
       </c>
       <c r="E77" t="n">
         <v>0.13</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>1.117</v>
       </c>
-      <c r="I77" t="n">
-        <v>0.399</v>
+      <c r="H77" t="n">
+        <v>0.596</v>
       </c>
       <c r="J77" t="n">
         <v>0.601</v>
@@ -9551,13 +9620,13 @@
         <v>2.241</v>
       </c>
       <c r="D78" t="n">
-        <v>0.621</v>
+        <v>1.127</v>
       </c>
       <c r="E78" t="n">
         <v>0.135</v>
       </c>
-      <c r="I78" t="n">
-        <v>1.127</v>
+      <c r="H78" t="n">
+        <v>0.621</v>
       </c>
       <c r="J78" t="n">
         <v>1.363</v>
@@ -9573,16 +9642,16 @@
         <v>3.106</v>
       </c>
       <c r="D79" t="n">
-        <v>0.373</v>
+        <v>1.892</v>
       </c>
       <c r="E79" t="n">
         <v>0.26</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>0.662</v>
       </c>
-      <c r="I79" t="n">
-        <v>1.892</v>
+      <c r="H79" t="n">
+        <v>0.373</v>
       </c>
       <c r="J79" t="n">
         <v>1.551</v>
@@ -9598,16 +9667,16 @@
         <v>3.684</v>
       </c>
       <c r="D80" t="n">
-        <v>0.852</v>
+        <v>1.953</v>
       </c>
       <c r="E80" t="n">
         <v>0.235</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>1.838</v>
       </c>
-      <c r="I80" t="n">
-        <v>1.953</v>
+      <c r="H80" t="n">
+        <v>0.852</v>
       </c>
       <c r="J80" t="n">
         <v>1.633</v>
@@ -9623,16 +9692,16 @@
         <v>3.845</v>
       </c>
       <c r="D81" t="n">
-        <v>0.718</v>
+        <v>2.057</v>
       </c>
       <c r="E81" t="n">
         <v>0.314</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>1.939</v>
       </c>
-      <c r="I81" t="n">
-        <v>2.057</v>
+      <c r="H81" t="n">
+        <v>0.718</v>
       </c>
       <c r="J81" t="n">
         <v>1.821</v>
@@ -9648,13 +9717,13 @@
         <v>3.905</v>
       </c>
       <c r="D82" t="n">
+        <v>2.148</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="H82" t="n">
         <v>0.718</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="I82" t="n">
-        <v>2.148</v>
       </c>
       <c r="J82" t="n">
         <v>2.012</v>
@@ -9670,16 +9739,16 @@
         <v>3.263</v>
       </c>
       <c r="D83" t="n">
-        <v>0.671</v>
+        <v>1.186</v>
       </c>
       <c r="E83" t="n">
         <v>0.27</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>1.42</v>
       </c>
-      <c r="I83" t="n">
-        <v>1.186</v>
+      <c r="H83" t="n">
+        <v>0.671</v>
       </c>
       <c r="J83" t="n">
         <v>1.297</v>
@@ -9695,16 +9764,16 @@
         <v>4.013</v>
       </c>
       <c r="D84" t="n">
-        <v>0.845</v>
+        <v>2.237</v>
       </c>
       <c r="E84" t="n">
         <v>0.234</v>
       </c>
-      <c r="F84" t="n">
+      <c r="G84" t="n">
         <v>1.755</v>
       </c>
-      <c r="I84" t="n">
-        <v>2.237</v>
+      <c r="H84" t="n">
+        <v>0.845</v>
       </c>
       <c r="J84" t="n">
         <v>2.201</v>
@@ -9720,16 +9789,16 @@
         <v>3.955</v>
       </c>
       <c r="D85" t="n">
-        <v>0.622</v>
+        <v>2.203</v>
       </c>
       <c r="E85" t="n">
         <v>0.34</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>1.848</v>
       </c>
-      <c r="I85" t="n">
-        <v>2.203</v>
+      <c r="H85" t="n">
+        <v>0.622</v>
       </c>
       <c r="J85" t="n">
         <v>2.175</v>
@@ -9745,16 +9814,16 @@
         <v>3.805</v>
       </c>
       <c r="D86" t="n">
-        <v>0.787</v>
+        <v>2.223</v>
       </c>
       <c r="E86" t="n">
         <v>0.331</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>1.855</v>
       </c>
-      <c r="I86" t="n">
-        <v>2.223</v>
+      <c r="H86" t="n">
+        <v>0.787</v>
       </c>
       <c r="J86" t="n">
         <v>2.066</v>
@@ -9770,16 +9839,16 @@
         <v>3.118</v>
       </c>
       <c r="D87" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.127</v>
       </c>
       <c r="E87" t="n">
         <v>0.262</v>
       </c>
-      <c r="F87" t="n">
+      <c r="G87" t="n">
         <v>1.418</v>
       </c>
-      <c r="I87" t="n">
-        <v>2.127</v>
+      <c r="H87" t="n">
+        <v>0.6919999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>2.236</v>
@@ -9795,16 +9864,16 @@
         <v>3.402</v>
       </c>
       <c r="D88" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.141</v>
       </c>
       <c r="E88" t="n">
         <v>0.246</v>
       </c>
-      <c r="F88" t="n">
+      <c r="G88" t="n">
         <v>1.82</v>
       </c>
-      <c r="I88" t="n">
-        <v>2.141</v>
+      <c r="H88" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="J88" t="n">
         <v>2.126</v>
@@ -9820,16 +9889,16 @@
         <v>3.492</v>
       </c>
       <c r="D89" t="n">
-        <v>0.785</v>
+        <v>2.307</v>
       </c>
       <c r="E89" t="n">
         <v>0.254</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>1.467</v>
       </c>
-      <c r="I89" t="n">
-        <v>2.307</v>
+      <c r="H89" t="n">
+        <v>0.785</v>
       </c>
       <c r="J89" t="n">
         <v>2.171</v>
@@ -9845,16 +9914,16 @@
         <v>3.619</v>
       </c>
       <c r="D90" t="n">
-        <v>0.499</v>
+        <v>1.764</v>
       </c>
       <c r="E90" t="n">
         <v>0.198</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>1.919</v>
       </c>
-      <c r="I90" t="n">
-        <v>1.764</v>
+      <c r="H90" t="n">
+        <v>0.499</v>
       </c>
       <c r="J90" t="n">
         <v>2.34</v>
@@ -9870,16 +9939,16 @@
         <v>3.561</v>
       </c>
       <c r="D91" t="n">
-        <v>0.348</v>
+        <v>2.111</v>
       </c>
       <c r="E91" t="n">
         <v>0.32</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>1.852</v>
       </c>
-      <c r="I91" t="n">
-        <v>2.111</v>
+      <c r="H91" t="n">
+        <v>0.348</v>
       </c>
       <c r="J91" t="n">
         <v>2.28</v>
@@ -9895,16 +9964,16 @@
         <v>4.097</v>
       </c>
       <c r="D92" t="n">
-        <v>0.797</v>
+        <v>1.597</v>
       </c>
       <c r="E92" t="n">
         <v>0.211</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>2.113</v>
       </c>
-      <c r="I92" t="n">
-        <v>1.597</v>
+      <c r="H92" t="n">
+        <v>0.797</v>
       </c>
       <c r="J92" t="n">
         <v>2.307</v>
@@ -9920,16 +9989,16 @@
         <v>4.186</v>
       </c>
       <c r="D93" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.365</v>
       </c>
       <c r="E93" t="n">
         <v>0.361</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>2.158</v>
       </c>
-      <c r="I93" t="n">
-        <v>2.365</v>
+      <c r="H93" t="n">
+        <v>0.8100000000000001</v>
       </c>
       <c r="J93" t="n">
         <v>2.249</v>
@@ -9945,16 +10014,16 @@
         <v>4.576</v>
       </c>
       <c r="D94" t="n">
-        <v>0.886</v>
+        <v>2.248</v>
       </c>
       <c r="E94" t="n">
         <v>0.221</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>2.151</v>
       </c>
-      <c r="I94" t="n">
-        <v>2.248</v>
+      <c r="H94" t="n">
+        <v>0.886</v>
       </c>
       <c r="J94" t="n">
         <v>2.347</v>
@@ -9970,16 +10039,16 @@
         <v>4.318</v>
       </c>
       <c r="D95" t="n">
-        <v>0.8120000000000001</v>
+        <v>2.043</v>
       </c>
       <c r="E95" t="n">
         <v>0.375</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>2.116</v>
       </c>
-      <c r="I95" t="n">
-        <v>2.043</v>
+      <c r="H95" t="n">
+        <v>0.8120000000000001</v>
       </c>
       <c r="J95" t="n">
         <v>2.654</v>
@@ -9998,16 +10067,16 @@
         <v>4.588</v>
       </c>
       <c r="D96" t="n">
-        <v>0.754</v>
+        <v>2.268</v>
       </c>
       <c r="E96" t="n">
         <v>0.305</v>
       </c>
-      <c r="F96" t="n">
+      <c r="G96" t="n">
         <v>2.123</v>
       </c>
-      <c r="I96" t="n">
-        <v>2.268</v>
+      <c r="H96" t="n">
+        <v>0.754</v>
       </c>
       <c r="J96" t="n">
         <v>2.115</v>
@@ -10026,16 +10095,16 @@
         <v>4.526</v>
       </c>
       <c r="D97" t="n">
-        <v>0.794</v>
+        <v>1.427</v>
       </c>
       <c r="E97" t="n">
         <v>0.392</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>2.095</v>
       </c>
-      <c r="I97" t="n">
-        <v>1.427</v>
+      <c r="H97" t="n">
+        <v>0.794</v>
       </c>
       <c r="J97" t="n">
         <v>2.117</v>
@@ -10054,16 +10123,16 @@
         <v>4.597</v>
       </c>
       <c r="D98" t="n">
-        <v>0.781</v>
+        <v>2.232</v>
       </c>
       <c r="E98" t="n">
         <v>0.244</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>1.426</v>
       </c>
-      <c r="I98" t="n">
-        <v>2.232</v>
+      <c r="H98" t="n">
+        <v>0.781</v>
       </c>
       <c r="J98" t="n">
         <v>2.179</v>
@@ -10082,16 +10151,16 @@
         <v>3.84</v>
       </c>
       <c r="D99" t="n">
-        <v>0.716</v>
+        <v>0.629</v>
       </c>
       <c r="E99" t="n">
         <v>0.388</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>1.86</v>
       </c>
-      <c r="I99" t="n">
-        <v>0.629</v>
+      <c r="H99" t="n">
+        <v>0.716</v>
       </c>
       <c r="J99" t="n">
         <v>2.315</v>
@@ -10109,14 +10178,14 @@
       <c r="C100" t="n">
         <v>4.168</v>
       </c>
-      <c r="D100" t="n">
-        <v>0.851</v>
-      </c>
       <c r="E100" t="n">
         <v>0.32</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>1.832</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.851</v>
       </c>
       <c r="J100" t="n">
         <v>2.218</v>
@@ -10134,14 +10203,14 @@
       <c r="C101" t="n">
         <v>4.173</v>
       </c>
-      <c r="D101" t="n">
-        <v>0.753</v>
-      </c>
       <c r="E101" t="n">
         <v>0.324</v>
       </c>
-      <c r="F101" t="n">
+      <c r="G101" t="n">
         <v>1.88</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.753</v>
       </c>
       <c r="J101" t="n">
         <v>2.23</v>
@@ -10159,14 +10228,14 @@
       <c r="C102" t="n">
         <v>4.201</v>
       </c>
-      <c r="D102" t="n">
-        <v>0.6840000000000001</v>
-      </c>
       <c r="E102" t="n">
         <v>0.354</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>1.912</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>2.173</v>
@@ -10187,7 +10256,7 @@
       <c r="E103" t="n">
         <v>0.259</v>
       </c>
-      <c r="F103" t="n">
+      <c r="G103" t="n">
         <v>2.094</v>
       </c>
       <c r="J103" t="n">
@@ -10206,14 +10275,14 @@
       <c r="C104" t="n">
         <v>4.363</v>
       </c>
-      <c r="D104" t="n">
-        <v>0.742</v>
-      </c>
       <c r="E104" t="n">
         <v>0.387</v>
       </c>
-      <c r="F104" t="n">
+      <c r="G104" t="n">
         <v>2.107</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.742</v>
       </c>
       <c r="J104" t="n">
         <v>2.072</v>
@@ -10231,14 +10300,14 @@
       <c r="C105" t="n">
         <v>4.893</v>
       </c>
-      <c r="D105" t="n">
-        <v>1.047</v>
-      </c>
       <c r="E105" t="n">
         <v>0.33</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>2.088</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.047</v>
       </c>
       <c r="J105" t="n">
         <v>2.255</v>
@@ -10256,14 +10325,14 @@
       <c r="C106" t="n">
         <v>4.896</v>
       </c>
-      <c r="D106" t="n">
-        <v>0.731</v>
-      </c>
       <c r="E106" t="n">
         <v>0.331</v>
       </c>
-      <c r="F106" t="n">
+      <c r="G106" t="n">
         <v>2.183</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.731</v>
       </c>
       <c r="J106" t="n">
         <v>2.2</v>
@@ -10282,16 +10351,16 @@
         <v>4.65</v>
       </c>
       <c r="D107" t="n">
-        <v>0.756</v>
+        <v>0.45</v>
       </c>
       <c r="E107" t="n">
         <v>0.412</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>2.175</v>
       </c>
-      <c r="I107" t="n">
-        <v>0.45</v>
+      <c r="H107" t="n">
+        <v>0.756</v>
       </c>
       <c r="J107" t="n">
         <v>2.496</v>
@@ -10310,16 +10379,16 @@
         <v>4.605</v>
       </c>
       <c r="D108" t="n">
-        <v>0.976</v>
+        <v>1.019</v>
       </c>
       <c r="E108" t="n">
         <v>0.401</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>2.176</v>
       </c>
-      <c r="I108" t="n">
-        <v>1.019</v>
+      <c r="H108" t="n">
+        <v>0.976</v>
       </c>
       <c r="J108" t="n">
         <v>2.361</v>
@@ -10338,16 +10407,16 @@
         <v>4.977</v>
       </c>
       <c r="D109" t="n">
-        <v>0.6840000000000001</v>
+        <v>2.271</v>
       </c>
       <c r="E109" t="n">
         <v>0.266</v>
       </c>
-      <c r="F109" t="n">
+      <c r="G109" t="n">
         <v>1.992</v>
       </c>
-      <c r="I109" t="n">
-        <v>2.271</v>
+      <c r="H109" t="n">
+        <v>0.6840000000000001</v>
       </c>
       <c r="J109" t="n">
         <v>2.018</v>
@@ -10366,16 +10435,16 @@
         <v>4.436</v>
       </c>
       <c r="D110" t="n">
-        <v>0.924</v>
+        <v>2.405</v>
       </c>
       <c r="E110" t="n">
         <v>0.259</v>
       </c>
-      <c r="F110" t="n">
+      <c r="G110" t="n">
         <v>1.368</v>
       </c>
-      <c r="I110" t="n">
-        <v>2.405</v>
+      <c r="H110" t="n">
+        <v>0.924</v>
       </c>
       <c r="J110" t="n">
         <v>2.03</v>
@@ -10394,16 +10463,16 @@
         <v>3.043</v>
       </c>
       <c r="D111" t="n">
-        <v>0.845</v>
+        <v>2.299</v>
       </c>
       <c r="E111" t="n">
         <v>0.472</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>1.896</v>
       </c>
-      <c r="I111" t="n">
-        <v>2.299</v>
+      <c r="H111" t="n">
+        <v>0.845</v>
       </c>
       <c r="J111" t="n">
         <v>2.269</v>
@@ -10422,16 +10491,16 @@
         <v>3.985</v>
       </c>
       <c r="D112" t="n">
-        <v>0.701</v>
+        <v>2.093</v>
       </c>
       <c r="E112" t="n">
         <v>0.325</v>
       </c>
-      <c r="F112" t="n">
+      <c r="G112" t="n">
         <v>1.751</v>
       </c>
-      <c r="I112" t="n">
-        <v>2.093</v>
+      <c r="H112" t="n">
+        <v>0.701</v>
       </c>
       <c r="J112" t="n">
         <v>2.062</v>
@@ -10450,16 +10519,16 @@
         <v>4.166</v>
       </c>
       <c r="D113" t="n">
-        <v>0.771</v>
+        <v>2.16</v>
       </c>
       <c r="E113" t="n">
         <v>0.104</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>1.761</v>
       </c>
-      <c r="I113" t="n">
-        <v>2.16</v>
+      <c r="H113" t="n">
+        <v>0.771</v>
       </c>
       <c r="J113" t="n">
         <v>2.195</v>
@@ -10478,16 +10547,16 @@
         <v>4.193</v>
       </c>
       <c r="D114" t="n">
-        <v>0.635</v>
+        <v>1.963</v>
       </c>
       <c r="E114" t="n">
         <v>0.432</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>1.793</v>
       </c>
-      <c r="I114" t="n">
-        <v>1.963</v>
+      <c r="H114" t="n">
+        <v>0.635</v>
       </c>
       <c r="J114" t="n">
         <v>2.157</v>
@@ -10506,16 +10575,16 @@
         <v>4.656</v>
       </c>
       <c r="D115" t="n">
-        <v>0.375</v>
+        <v>2.249</v>
       </c>
       <c r="E115" t="n">
         <v>0.228</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>2.094</v>
       </c>
-      <c r="I115" t="n">
-        <v>2.249</v>
+      <c r="H115" t="n">
+        <v>0.375</v>
       </c>
       <c r="J115" t="n">
         <v>2.229</v>
@@ -10534,16 +10603,16 @@
         <v>4.739</v>
       </c>
       <c r="D116" t="n">
-        <v>0.761</v>
+        <v>2.184</v>
       </c>
       <c r="E116" t="n">
         <v>0.294</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>2.022</v>
       </c>
-      <c r="I116" t="n">
-        <v>2.184</v>
+      <c r="H116" t="n">
+        <v>0.761</v>
       </c>
       <c r="J116" t="n">
         <v>2.342</v>
@@ -10562,16 +10631,16 @@
         <v>4.976</v>
       </c>
       <c r="D117" t="n">
-        <v>0.824</v>
+        <v>2.504</v>
       </c>
       <c r="E117" t="n">
         <v>0.385</v>
       </c>
-      <c r="F117" t="n">
+      <c r="G117" t="n">
         <v>2.334</v>
       </c>
-      <c r="I117" t="n">
-        <v>2.504</v>
+      <c r="H117" t="n">
+        <v>0.824</v>
       </c>
       <c r="J117" t="n">
         <v>2.257</v>
@@ -10590,16 +10659,16 @@
         <v>4.844</v>
       </c>
       <c r="D118" t="n">
-        <v>0.749</v>
+        <v>1.855</v>
       </c>
       <c r="E118" t="n">
         <v>0.37</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>2.178</v>
       </c>
-      <c r="I118" t="n">
-        <v>1.855</v>
+      <c r="H118" t="n">
+        <v>0.749</v>
       </c>
       <c r="J118" t="n">
         <v>2.148</v>
@@ -10618,16 +10687,16 @@
         <v>4.822</v>
       </c>
       <c r="D119" t="n">
-        <v>0.898</v>
+        <v>1.559</v>
       </c>
       <c r="E119" t="n">
         <v>0.263</v>
       </c>
-      <c r="F119" t="n">
+      <c r="G119" t="n">
         <v>2.229</v>
       </c>
-      <c r="I119" t="n">
-        <v>1.559</v>
+      <c r="H119" t="n">
+        <v>0.898</v>
       </c>
       <c r="J119" t="n">
         <v>2.096</v>
@@ -10646,16 +10715,16 @@
         <v>4.861</v>
       </c>
       <c r="D120" t="n">
-        <v>0.886</v>
+        <v>0.923</v>
       </c>
       <c r="E120" t="n">
         <v>0.451</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>2.072</v>
       </c>
-      <c r="I120" t="n">
-        <v>0.923</v>
+      <c r="H120" t="n">
+        <v>0.886</v>
       </c>
       <c r="J120" t="n">
         <v>2.154</v>
@@ -10674,16 +10743,16 @@
         <v>4.35</v>
       </c>
       <c r="D121" t="n">
-        <v>0.882</v>
+        <v>0.39</v>
       </c>
       <c r="E121" t="n">
         <v>0.261</v>
       </c>
-      <c r="F121" t="n">
+      <c r="G121" t="n">
         <v>1.946</v>
       </c>
-      <c r="I121" t="n">
-        <v>0.39</v>
+      <c r="H121" t="n">
+        <v>0.882</v>
       </c>
       <c r="J121" t="n">
         <v>1.821</v>
@@ -10702,16 +10771,16 @@
         <v>4.624</v>
       </c>
       <c r="D122" t="n">
-        <v>0.885</v>
+        <v>1.942</v>
       </c>
       <c r="E122" t="n">
         <v>0.206</v>
       </c>
-      <c r="F122" t="n">
+      <c r="G122" t="n">
         <v>1.528</v>
       </c>
-      <c r="I122" t="n">
-        <v>1.942</v>
+      <c r="H122" t="n">
+        <v>0.885</v>
       </c>
       <c r="J122" t="n">
         <v>2.163</v>
@@ -10730,16 +10799,16 @@
         <v>3.944</v>
       </c>
       <c r="D123" t="n">
-        <v>0.695</v>
+        <v>2.36</v>
       </c>
       <c r="E123" t="n">
         <v>0.233</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>1.849</v>
       </c>
-      <c r="I123" t="n">
-        <v>2.36</v>
+      <c r="H123" t="n">
+        <v>0.695</v>
       </c>
       <c r="J123" t="n">
         <v>2.346</v>
@@ -10758,16 +10827,16 @@
         <v>4.213</v>
       </c>
       <c r="D124" t="n">
-        <v>0.745</v>
+        <v>0.871</v>
       </c>
       <c r="E124" t="n">
         <v>0.342</v>
       </c>
-      <c r="F124" t="n">
+      <c r="G124" t="n">
         <v>1.815</v>
       </c>
-      <c r="I124" t="n">
-        <v>0.871</v>
+      <c r="H124" t="n">
+        <v>0.745</v>
       </c>
       <c r="J124" t="n">
         <v>2.018</v>
@@ -10786,16 +10855,16 @@
         <v>4.164</v>
       </c>
       <c r="D125" t="n">
-        <v>0.6870000000000001</v>
+        <v>2.212</v>
       </c>
       <c r="E125" t="n">
         <v>0.478</v>
       </c>
-      <c r="F125" t="n">
+      <c r="G125" t="n">
         <v>1.829</v>
       </c>
-      <c r="I125" t="n">
-        <v>2.212</v>
+      <c r="H125" t="n">
+        <v>0.6870000000000001</v>
       </c>
       <c r="J125" t="n">
         <v>2.234</v>
@@ -10814,16 +10883,16 @@
         <v>4.401</v>
       </c>
       <c r="D126" t="n">
-        <v>0.639</v>
+        <v>2.288</v>
       </c>
       <c r="E126" t="n">
         <v>0.25</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>1.885</v>
       </c>
-      <c r="I126" t="n">
-        <v>2.288</v>
+      <c r="H126" t="n">
+        <v>0.639</v>
       </c>
       <c r="J126" t="n">
         <v>2.349</v>
@@ -10842,16 +10911,16 @@
         <v>4.533</v>
       </c>
       <c r="D127" t="n">
-        <v>0.448</v>
+        <v>2.427</v>
       </c>
       <c r="E127" t="n">
         <v>0.224</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>1.887</v>
       </c>
-      <c r="I127" t="n">
-        <v>2.427</v>
+      <c r="H127" t="n">
+        <v>0.448</v>
       </c>
       <c r="J127" t="n">
         <v>2.348</v>
@@ -10870,16 +10939,16 @@
         <v>4.609</v>
       </c>
       <c r="D128" t="n">
-        <v>0.831</v>
+        <v>2.021</v>
       </c>
       <c r="E128" t="n">
         <v>0.19</v>
       </c>
-      <c r="F128" t="n">
+      <c r="G128" t="n">
         <v>2.183</v>
       </c>
-      <c r="I128" t="n">
-        <v>2.021</v>
+      <c r="H128" t="n">
+        <v>0.831</v>
       </c>
       <c r="J128" t="n">
         <v>2.38</v>
@@ -10898,19 +10967,19 @@
         <v>4.677</v>
       </c>
       <c r="D129" t="n">
-        <v>0.785</v>
+        <v>2.395</v>
       </c>
       <c r="E129" t="n">
         <v>0.343</v>
       </c>
       <c r="F129" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="G129" t="n">
         <v>2.291</v>
       </c>
-      <c r="G129" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="I129" t="n">
-        <v>2.395</v>
+      <c r="H129" t="n">
+        <v>0.785</v>
       </c>
       <c r="J129" t="n">
         <v>2.365</v>
@@ -10929,19 +10998,19 @@
         <v>4.853</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>1.969</v>
       </c>
       <c r="E130" t="n">
         <v>0.213</v>
       </c>
       <c r="F130" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="G130" t="n">
         <v>2.193</v>
       </c>
-      <c r="G130" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="I130" t="n">
-        <v>1.969</v>
+      <c r="H130" t="n">
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>2.185</v>
@@ -10960,19 +11029,19 @@
         <v>4.574</v>
       </c>
       <c r="D131" t="n">
-        <v>0.868</v>
+        <v>2.404</v>
       </c>
       <c r="E131" t="n">
         <v>0.381</v>
       </c>
       <c r="F131" t="n">
+        <v>1.231</v>
+      </c>
+      <c r="G131" t="n">
         <v>2.343</v>
       </c>
-      <c r="G131" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="I131" t="n">
-        <v>2.404</v>
+      <c r="H131" t="n">
+        <v>0.868</v>
       </c>
       <c r="J131" t="n">
         <v>2.582</v>
@@ -10991,19 +11060,19 @@
         <v>4.818</v>
       </c>
       <c r="D132" t="n">
-        <v>0.882</v>
+        <v>2.257</v>
       </c>
       <c r="E132" t="n">
         <v>0.1</v>
       </c>
       <c r="F132" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="G132" t="n">
         <v>2.107</v>
       </c>
-      <c r="G132" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="I132" t="n">
-        <v>2.257</v>
+      <c r="H132" t="n">
+        <v>0.882</v>
       </c>
       <c r="J132" t="n">
         <v>2.341</v>
@@ -11022,19 +11091,19 @@
         <v>4.631</v>
       </c>
       <c r="D133" t="n">
-        <v>0.758</v>
+        <v>2.502</v>
       </c>
       <c r="E133" t="n">
         <v>0.263</v>
       </c>
       <c r="F133" t="n">
+        <v>1.943</v>
+      </c>
+      <c r="G133" t="n">
         <v>2.195</v>
       </c>
-      <c r="G133" t="n">
-        <v>1.943</v>
-      </c>
-      <c r="I133" t="n">
-        <v>2.502</v>
+      <c r="H133" t="n">
+        <v>0.758</v>
       </c>
       <c r="J133" t="n">
         <v>2.317</v>
@@ -11053,19 +11122,19 @@
         <v>4.39</v>
       </c>
       <c r="D134" t="n">
-        <v>0.847</v>
+        <v>2.3</v>
       </c>
       <c r="E134" t="n">
         <v>0.305</v>
       </c>
       <c r="F134" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="G134" t="n">
         <v>1.442</v>
       </c>
-      <c r="G134" t="n">
-        <v>2.115</v>
-      </c>
-      <c r="I134" t="n">
-        <v>2.3</v>
+      <c r="H134" t="n">
+        <v>0.847</v>
       </c>
       <c r="J134" t="n">
         <v>2.196</v>
@@ -11084,19 +11153,19 @@
         <v>3.084</v>
       </c>
       <c r="D135" t="n">
-        <v>0.899</v>
+        <v>2.442</v>
       </c>
       <c r="E135" t="n">
         <v>0.377</v>
       </c>
       <c r="F135" t="n">
+        <v>2.446</v>
+      </c>
+      <c r="G135" t="n">
         <v>1.677</v>
       </c>
-      <c r="G135" t="n">
-        <v>2.446</v>
-      </c>
-      <c r="I135" t="n">
-        <v>2.442</v>
+      <c r="H135" t="n">
+        <v>0.899</v>
       </c>
       <c r="J135" t="n">
         <v>2.259</v>
@@ -11115,19 +11184,19 @@
         <v>4.035</v>
       </c>
       <c r="D136" t="n">
-        <v>0.75</v>
+        <v>2.109</v>
       </c>
       <c r="E136" t="n">
         <v>0.127</v>
       </c>
       <c r="F136" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G136" t="n">
         <v>1.91</v>
       </c>
-      <c r="G136" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="I136" t="n">
-        <v>2.109</v>
+      <c r="H136" t="n">
+        <v>0.75</v>
       </c>
       <c r="J136" t="n">
         <v>2.388</v>
@@ -11146,19 +11215,19 @@
         <v>4.155</v>
       </c>
       <c r="D137" t="n">
-        <v>0.798</v>
+        <v>2.134</v>
       </c>
       <c r="E137" t="n">
         <v>0.235</v>
       </c>
       <c r="F137" t="n">
+        <v>2.758</v>
+      </c>
+      <c r="G137" t="n">
         <v>1.936</v>
       </c>
-      <c r="G137" t="n">
-        <v>2.758</v>
-      </c>
-      <c r="I137" t="n">
-        <v>2.134</v>
+      <c r="H137" t="n">
+        <v>0.798</v>
       </c>
       <c r="J137" t="n">
         <v>2.334</v>
@@ -11177,19 +11246,19 @@
         <v>4.221</v>
       </c>
       <c r="D138" t="n">
-        <v>0.541</v>
+        <v>2.179</v>
       </c>
       <c r="E138" t="n">
         <v>0.363</v>
       </c>
       <c r="F138" t="n">
+        <v>2.856</v>
+      </c>
+      <c r="G138" t="n">
         <v>2.012</v>
       </c>
-      <c r="G138" t="n">
-        <v>2.856</v>
-      </c>
-      <c r="I138" t="n">
-        <v>2.179</v>
+      <c r="H138" t="n">
+        <v>0.541</v>
       </c>
       <c r="J138" t="n">
         <v>2.546</v>
@@ -11208,19 +11277,19 @@
         <v>4.489</v>
       </c>
       <c r="D139" t="n">
-        <v>0.546</v>
+        <v>2.459</v>
       </c>
       <c r="E139" t="n">
         <v>0.248</v>
       </c>
       <c r="F139" t="n">
+        <v>3.771</v>
+      </c>
+      <c r="G139" t="n">
         <v>1.997</v>
       </c>
-      <c r="G139" t="n">
-        <v>3.771</v>
-      </c>
-      <c r="I139" t="n">
-        <v>2.459</v>
+      <c r="H139" t="n">
+        <v>0.546</v>
       </c>
       <c r="J139" t="n">
         <v>2.684</v>
@@ -11239,19 +11308,19 @@
         <v>4.926</v>
       </c>
       <c r="D140" t="n">
-        <v>0.723</v>
+        <v>2.326</v>
       </c>
       <c r="E140" t="n">
         <v>0.265</v>
       </c>
       <c r="F140" t="n">
+        <v>3.807</v>
+      </c>
+      <c r="G140" t="n">
         <v>2.14</v>
       </c>
-      <c r="G140" t="n">
-        <v>3.807</v>
-      </c>
-      <c r="I140" t="n">
-        <v>2.326</v>
+      <c r="H140" t="n">
+        <v>0.723</v>
       </c>
       <c r="J140" t="n">
         <v>3.095</v>
@@ -11270,19 +11339,19 @@
         <v>4.725</v>
       </c>
       <c r="D141" t="n">
-        <v>1.007</v>
+        <v>2.438</v>
       </c>
       <c r="E141" t="n">
         <v>0.402</v>
       </c>
       <c r="F141" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="G141" t="n">
         <v>2.463</v>
       </c>
-      <c r="G141" t="n">
-        <v>3.887</v>
-      </c>
-      <c r="I141" t="n">
-        <v>2.438</v>
+      <c r="H141" t="n">
+        <v>1.007</v>
       </c>
       <c r="J141" t="n">
         <v>3.189</v>
@@ -11301,19 +11370,19 @@
         <v>4.649</v>
       </c>
       <c r="D142" t="n">
-        <v>0.838</v>
+        <v>2.232</v>
       </c>
       <c r="E142" t="n">
         <v>0.181</v>
       </c>
       <c r="F142" t="n">
+        <v>4.074</v>
+      </c>
+      <c r="G142" t="n">
         <v>2.253</v>
       </c>
-      <c r="G142" t="n">
-        <v>4.074</v>
-      </c>
-      <c r="I142" t="n">
-        <v>2.232</v>
+      <c r="H142" t="n">
+        <v>0.838</v>
       </c>
       <c r="J142" t="n">
         <v>2.945</v>
@@ -11332,19 +11401,19 @@
         <v>4.756</v>
       </c>
       <c r="D143" t="n">
-        <v>0.719</v>
+        <v>2.441</v>
       </c>
       <c r="E143" t="n">
         <v>0.147</v>
       </c>
       <c r="F143" t="n">
+        <v>3.752</v>
+      </c>
+      <c r="G143" t="n">
         <v>2.269</v>
       </c>
-      <c r="G143" t="n">
-        <v>3.752</v>
-      </c>
-      <c r="I143" t="n">
-        <v>2.441</v>
+      <c r="H143" t="n">
+        <v>0.719</v>
       </c>
       <c r="J143" t="n">
         <v>3.317</v>
@@ -11363,19 +11432,19 @@
         <v>4.918</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9379999999999999</v>
+        <v>2.455</v>
       </c>
       <c r="E144" t="n">
         <v>0.259</v>
       </c>
       <c r="F144" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="G144" t="n">
         <v>2.284</v>
       </c>
-      <c r="G144" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="I144" t="n">
-        <v>2.455</v>
+      <c r="H144" t="n">
+        <v>0.9379999999999999</v>
       </c>
       <c r="J144" t="n">
         <v>3.361</v>
@@ -11394,22 +11463,22 @@
         <v>4.745</v>
       </c>
       <c r="D145" t="n">
-        <v>0.762</v>
+        <v>2.511</v>
       </c>
       <c r="E145" t="n">
         <v>0.278</v>
       </c>
       <c r="F145" t="n">
+        <v>3.945</v>
+      </c>
+      <c r="G145" t="n">
         <v>2.113</v>
       </c>
-      <c r="G145" t="n">
-        <v>3.945</v>
-      </c>
       <c r="H145" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="I145" t="n">
         <v>0.131</v>
-      </c>
-      <c r="I145" t="n">
-        <v>2.511</v>
       </c>
       <c r="J145" t="n">
         <v>3.154</v>
@@ -11428,22 +11497,22 @@
         <v>4.314</v>
       </c>
       <c r="D146" t="n">
-        <v>0.883</v>
+        <v>1.993</v>
       </c>
       <c r="E146" t="n">
         <v>0.166</v>
       </c>
       <c r="F146" t="n">
+        <v>3.923</v>
+      </c>
+      <c r="G146" t="n">
         <v>1.546</v>
       </c>
-      <c r="G146" t="n">
-        <v>3.923</v>
-      </c>
       <c r="H146" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="I146" t="n">
         <v>0.122</v>
-      </c>
-      <c r="I146" t="n">
-        <v>1.993</v>
       </c>
       <c r="J146" t="n">
         <v>3.122</v>
@@ -11462,22 +11531,22 @@
         <v>4.436</v>
       </c>
       <c r="D147" t="n">
-        <v>0.765</v>
+        <v>2.16</v>
       </c>
       <c r="E147" t="n">
         <v>0.471</v>
       </c>
       <c r="F147" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="G147" t="n">
         <v>2.187</v>
       </c>
-      <c r="G147" t="n">
-        <v>3.81</v>
-      </c>
       <c r="H147" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="I147" t="n">
         <v>0.125</v>
-      </c>
-      <c r="I147" t="n">
-        <v>2.16</v>
       </c>
       <c r="J147" t="n">
         <v>3.271</v>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80553,9 +80553,39 @@
       <c r="A2462" s="4" t="n">
         <v>46291</v>
       </c>
+      <c r="B2462" t="n">
+        <v>3.361</v>
+      </c>
+      <c r="C2462" t="n">
+        <v>3.372</v>
+      </c>
+      <c r="D2462" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="E2462" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="F2462" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="G2462" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H2462" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I2462" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J2462" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K2462" t="n">
+        <v>12.642</v>
+      </c>
       <c r="L2462" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80610,7 +80640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80675,22 +80705,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C2" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F2" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G2" t="n">
         <v>0.395</v>
@@ -80705,6 +80735,41 @@
         <v>0.014</v>
       </c>
       <c r="K2" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K3" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -80719,7 +80784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80789,22 +80854,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C2" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D2" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F2" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G2" t="n">
         <v>0.395</v>
@@ -80819,9 +80884,47 @@
         <v>0.014</v>
       </c>
       <c r="K2" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K3" t="n">
         <v>12.277</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L3" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81262,7 +81365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81362,40 +81465,40 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B2" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C2" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D2" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E2" t="n">
         <v>9100</v>
       </c>
       <c r="F2" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G2" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I2" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K2" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M2" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N2" t="n">
         <v>189475</v>
       </c>
       <c r="O2" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P2" t="n">
         <v>375660</v>
@@ -81404,6 +81507,53 @@
         <v>773586</v>
       </c>
       <c r="R2" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C3" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K3" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N3" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O3" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P3" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R3" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80543,9 +80543,39 @@
       <c r="A2461" s="4" t="n">
         <v>46290</v>
       </c>
+      <c r="B2461" t="n">
+        <v>3.412</v>
+      </c>
+      <c r="C2461" t="n">
+        <v>3.251</v>
+      </c>
+      <c r="D2461" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="E2461" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F2461" t="n">
+        <v>2.274</v>
+      </c>
+      <c r="G2461" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="H2461" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I2461" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="J2461" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K2461" t="n">
+        <v>12.373</v>
+      </c>
       <c r="L2461" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80640,7 +80670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80705,57 +80735,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C2" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D2" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F2" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G2" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H2" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J2" t="n">
         <v>0.014</v>
       </c>
       <c r="K2" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B3" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C3" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D3" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F3" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G3" t="n">
         <v>0.395</v>
@@ -80770,6 +80800,41 @@
         <v>0.014</v>
       </c>
       <c r="K3" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K4" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -80784,7 +80849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80854,60 +80919,60 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C2" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D2" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F2" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G2" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H2" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I2" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J2" t="n">
         <v>0.014</v>
       </c>
       <c r="K2" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L2" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B3" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C3" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D3" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F3" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G3" t="n">
         <v>0.395</v>
@@ -80922,9 +80987,47 @@
         <v>0.014</v>
       </c>
       <c r="K3" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K4" t="n">
         <v>12.277</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81365,7 +81468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81465,46 +81568,46 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B2" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C2" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D2" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E2" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F2" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G2" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I2" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K2" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M2" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N2" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O2" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P2" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q2" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R2" t="n">
         <v>15000</v>
@@ -81512,40 +81615,40 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B3" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C3" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D3" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E3" t="n">
         <v>9100</v>
       </c>
       <c r="F3" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G3" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I3" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K3" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M3" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N3" t="n">
         <v>189475</v>
       </c>
       <c r="O3" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P3" t="n">
         <v>375660</v>
@@ -81554,6 +81657,53 @@
         <v>773586</v>
       </c>
       <c r="R3" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C4" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K4" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N4" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O4" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P4" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R4" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80533,9 +80533,36 @@
       <c r="A2460" s="4" t="n">
         <v>46289</v>
       </c>
+      <c r="B2460" t="n">
+        <v>3.365</v>
+      </c>
+      <c r="C2460" t="n">
+        <v>3.197</v>
+      </c>
+      <c r="D2460" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E2460" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="F2460" t="n">
+        <v>2.354</v>
+      </c>
+      <c r="G2460" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="H2460" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="I2460" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="K2460" t="n">
+        <v>12.118</v>
+      </c>
       <c r="L2460" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80670,7 +80697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80735,92 +80762,89 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C2" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D2" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F2" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H2" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K2" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C3" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D3" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F3" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J3" t="n">
         <v>0.014</v>
       </c>
       <c r="K3" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B4" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C4" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D4" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F4" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G4" t="n">
         <v>0.395</v>
@@ -80835,6 +80859,41 @@
         <v>0.014</v>
       </c>
       <c r="K4" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K5" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -80849,7 +80908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80919,98 +80978,95 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C2" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D2" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F2" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G2" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H2" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K2" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L2" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C3" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D3" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F3" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I3" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J3" t="n">
         <v>0.014</v>
       </c>
       <c r="K3" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L3" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B4" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C4" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D4" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F4" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G4" t="n">
         <v>0.395</v>
@@ -81025,9 +81081,47 @@
         <v>0.014</v>
       </c>
       <c r="K4" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L4" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K5" t="n">
         <v>12.277</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81468,7 +81562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81568,93 +81662,90 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B2" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C2" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D2" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E2" t="n">
         <v>9300</v>
       </c>
       <c r="F2" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G2" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I2" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K2" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M2" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N2" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P2" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q2" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B3" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C3" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D3" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E3" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F3" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G3" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I3" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K3" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M3" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N3" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O3" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P3" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q3" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R3" t="n">
         <v>15000</v>
@@ -81662,40 +81753,40 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B4" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C4" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D4" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E4" t="n">
         <v>9100</v>
       </c>
       <c r="F4" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G4" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I4" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K4" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M4" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N4" t="n">
         <v>189475</v>
       </c>
       <c r="O4" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P4" t="n">
         <v>375660</v>
@@ -81704,6 +81795,53 @@
         <v>773586</v>
       </c>
       <c r="R4" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C5" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K5" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N5" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O5" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P5" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R5" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80523,9 +80523,36 @@
       <c r="A2459" s="4" t="n">
         <v>46288</v>
       </c>
+      <c r="B2459" t="n">
+        <v>3.277</v>
+      </c>
+      <c r="C2459" t="n">
+        <v>3.153</v>
+      </c>
+      <c r="D2459" t="n">
+        <v>1.426</v>
+      </c>
+      <c r="E2459" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="F2459" t="n">
+        <v>2.454</v>
+      </c>
+      <c r="G2459" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="H2459" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="I2459" t="n">
+        <v>0.728</v>
+      </c>
+      <c r="K2459" t="n">
+        <v>12.08</v>
+      </c>
       <c r="L2459" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80697,7 +80724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80762,22 +80789,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C2" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F2" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G2" t="n">
         <v>0.462</v>
@@ -80786,100 +80813,97 @@
         <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K2" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C3" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F3" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G3" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K3" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C4" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D4" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E4" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F4" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G4" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H4" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I4" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J4" t="n">
         <v>0.014</v>
       </c>
       <c r="K4" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B5" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C5" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D5" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F5" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G5" t="n">
         <v>0.395</v>
@@ -80894,6 +80918,41 @@
         <v>0.014</v>
       </c>
       <c r="K5" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K6" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -80908,7 +80967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80978,22 +81037,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C2" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F2" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G2" t="n">
         <v>0.462</v>
@@ -81002,109 +81061,106 @@
         <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K2" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L2" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C3" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F3" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G3" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H3" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K3" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L3" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C4" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D4" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E4" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F4" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G4" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H4" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I4" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J4" t="n">
         <v>0.014</v>
       </c>
       <c r="K4" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L4" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B5" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C5" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D5" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F5" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G5" t="n">
         <v>0.395</v>
@@ -81119,9 +81175,47 @@
         <v>0.014</v>
       </c>
       <c r="K5" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K6" t="n">
         <v>12.277</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81562,7 +81656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81662,34 +81756,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B2" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C2" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D2" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E2" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G2" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I2" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K2" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M2" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -81698,101 +81792,98 @@
         <v>264857</v>
       </c>
       <c r="P2" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q2" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B3" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C3" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D3" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E3" t="n">
         <v>9300</v>
       </c>
       <c r="F3" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G3" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I3" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K3" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M3" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N3" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P3" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q3" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R3" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B4" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C4" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D4" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E4" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F4" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G4" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I4" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K4" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M4" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N4" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O4" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P4" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q4" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R4" t="n">
         <v>15000</v>
@@ -81800,40 +81891,40 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B5" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C5" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D5" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E5" t="n">
         <v>9100</v>
       </c>
       <c r="F5" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G5" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I5" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K5" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M5" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N5" t="n">
         <v>189475</v>
       </c>
       <c r="O5" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P5" t="n">
         <v>375660</v>
@@ -81842,6 +81933,53 @@
         <v>773586</v>
       </c>
       <c r="R5" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C6" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K6" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N6" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O6" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P6" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R6" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80513,9 +80513,36 @@
       <c r="A2458" s="4" t="n">
         <v>46287</v>
       </c>
+      <c r="B2458" t="n">
+        <v>3.259</v>
+      </c>
+      <c r="C2458" t="n">
+        <v>3.268</v>
+      </c>
+      <c r="D2458" t="n">
+        <v>1.449</v>
+      </c>
+      <c r="E2458" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="F2458" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="G2458" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="H2458" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="I2458" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="K2458" t="n">
+        <v>12.187</v>
+      </c>
       <c r="L2458" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80724,7 +80751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80789,22 +80816,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C2" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D2" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F2" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G2" t="n">
         <v>0.462</v>
@@ -80813,30 +80840,30 @@
         <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K2" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C3" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F3" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G3" t="n">
         <v>0.462</v>
@@ -80845,100 +80872,97 @@
         <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K3" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C4" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D4" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F4" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H4" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K4" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C5" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D5" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F5" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H5" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I5" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J5" t="n">
         <v>0.014</v>
       </c>
       <c r="K5" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B6" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C6" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D6" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F6" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G6" t="n">
         <v>0.395</v>
@@ -80953,6 +80977,41 @@
         <v>0.014</v>
       </c>
       <c r="K6" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K7" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -80967,7 +81026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81037,22 +81096,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C2" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D2" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F2" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G2" t="n">
         <v>0.462</v>
@@ -81061,33 +81120,33 @@
         <v>0.343</v>
       </c>
       <c r="I2" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K2" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L2" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C3" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F3" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G3" t="n">
         <v>0.462</v>
@@ -81096,109 +81155,106 @@
         <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K3" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L3" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C4" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D4" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F4" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H4" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K4" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L4" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C5" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D5" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F5" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H5" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I5" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J5" t="n">
         <v>0.014</v>
       </c>
       <c r="K5" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L5" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B6" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C6" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D6" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F6" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G6" t="n">
         <v>0.395</v>
@@ -81213,9 +81269,47 @@
         <v>0.014</v>
       </c>
       <c r="K6" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K7" t="n">
         <v>12.277</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81656,7 +81750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81756,34 +81850,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B2" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C2" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D2" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E2" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G2" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I2" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K2" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M2" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -81792,42 +81886,42 @@
         <v>264857</v>
       </c>
       <c r="P2" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q2" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B3" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C3" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D3" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E3" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G3" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I3" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K3" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M3" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -81836,101 +81930,98 @@
         <v>264857</v>
       </c>
       <c r="P3" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q3" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B4" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C4" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D4" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E4" t="n">
         <v>9300</v>
       </c>
       <c r="F4" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G4" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I4" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K4" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M4" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N4" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P4" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q4" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R4" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B5" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C5" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D5" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E5" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F5" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G5" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I5" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K5" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M5" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N5" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O5" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P5" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q5" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R5" t="n">
         <v>15000</v>
@@ -81938,40 +82029,40 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B6" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C6" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D6" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E6" t="n">
         <v>9100</v>
       </c>
       <c r="F6" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G6" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I6" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K6" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M6" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N6" t="n">
         <v>189475</v>
       </c>
       <c r="O6" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P6" t="n">
         <v>375660</v>
@@ -81980,6 +82071,53 @@
         <v>773586</v>
       </c>
       <c r="R6" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C7" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K7" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N7" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O7" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P7" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R7" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80503,9 +80503,36 @@
       <c r="A2457" s="4" t="n">
         <v>46286</v>
       </c>
+      <c r="B2457" t="n">
+        <v>3.263</v>
+      </c>
+      <c r="C2457" t="n">
+        <v>3.261</v>
+      </c>
+      <c r="D2457" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="E2457" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="F2457" t="n">
+        <v>2.197</v>
+      </c>
+      <c r="G2457" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="H2457" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="I2457" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K2457" t="n">
+        <v>12.224</v>
+      </c>
       <c r="L2457" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80751,7 +80778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80816,54 +80843,54 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C2" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D2" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F2" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G2" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C3" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F3" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G3" t="n">
         <v>0.462</v>
@@ -80872,30 +80899,30 @@
         <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K3" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C4" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F4" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G4" t="n">
         <v>0.462</v>
@@ -80904,100 +80931,97 @@
         <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K4" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B5" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C5" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D5" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F5" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G5" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K5" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B6" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C6" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D6" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F6" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H6" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J6" t="n">
         <v>0.014</v>
       </c>
       <c r="K6" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B7" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C7" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D7" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F7" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G7" t="n">
         <v>0.395</v>
@@ -81012,6 +81036,41 @@
         <v>0.014</v>
       </c>
       <c r="K7" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K8" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81026,7 +81085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81096,57 +81155,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C2" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D2" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F2" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G2" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H2" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L2" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C3" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E3" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F3" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G3" t="n">
         <v>0.462</v>
@@ -81155,33 +81214,33 @@
         <v>0.343</v>
       </c>
       <c r="I3" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K3" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L3" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C4" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F4" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G4" t="n">
         <v>0.462</v>
@@ -81190,109 +81249,106 @@
         <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K4" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L4" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B5" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C5" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D5" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F5" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G5" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K5" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L5" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B6" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C6" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D6" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F6" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G6" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H6" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I6" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J6" t="n">
         <v>0.014</v>
       </c>
       <c r="K6" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L6" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B7" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C7" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D7" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F7" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G7" t="n">
         <v>0.395</v>
@@ -81307,9 +81363,47 @@
         <v>0.014</v>
       </c>
       <c r="K7" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K8" t="n">
         <v>12.277</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81750,7 +81844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81850,78 +81944,78 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B2" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C2" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D2" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E2" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G2" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I2" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K2" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M2" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P2" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q2" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B3" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C3" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D3" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E3" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G3" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I3" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K3" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M3" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -81930,42 +82024,42 @@
         <v>264857</v>
       </c>
       <c r="P3" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q3" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B4" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C4" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D4" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E4" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G4" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I4" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K4" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M4" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -81974,101 +82068,98 @@
         <v>264857</v>
       </c>
       <c r="P4" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q4" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B5" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C5" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D5" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E5" t="n">
         <v>9300</v>
       </c>
       <c r="F5" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G5" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I5" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K5" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M5" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N5" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P5" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q5" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R5" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B6" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C6" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D6" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E6" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F6" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G6" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I6" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K6" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M6" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N6" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O6" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P6" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q6" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R6" t="n">
         <v>15000</v>
@@ -82076,40 +82167,40 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B7" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C7" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D7" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E7" t="n">
         <v>9100</v>
       </c>
       <c r="F7" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G7" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I7" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K7" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M7" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N7" t="n">
         <v>189475</v>
       </c>
       <c r="O7" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P7" t="n">
         <v>375660</v>
@@ -82118,6 +82209,53 @@
         <v>773586</v>
       </c>
       <c r="R7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C8" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E8" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K8" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N8" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O8" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P8" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R8" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80493,9 +80493,36 @@
       <c r="A2456" s="4" t="n">
         <v>46285</v>
       </c>
+      <c r="B2456" t="n">
+        <v>3.232</v>
+      </c>
+      <c r="C2456" t="n">
+        <v>3.162</v>
+      </c>
+      <c r="D2456" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="E2456" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F2456" t="n">
+        <v>2.324</v>
+      </c>
+      <c r="G2456" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="H2456" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="I2456" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K2456" t="n">
+        <v>12.276</v>
+      </c>
       <c r="L2456" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80778,7 +80805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80843,22 +80870,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C2" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D2" t="n">
         <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F2" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G2" t="n">
         <v>0.446</v>
@@ -80870,59 +80897,59 @@
         <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C3" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D3" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F3" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G3" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C4" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D4" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E4" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F4" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G4" t="n">
         <v>0.462</v>
@@ -80931,30 +80958,30 @@
         <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K4" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C5" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E5" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F5" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G5" t="n">
         <v>0.462</v>
@@ -80963,100 +80990,97 @@
         <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K5" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C6" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D6" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F6" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K6" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B7" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C7" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D7" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E7" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F7" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I7" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J7" t="n">
         <v>0.014</v>
       </c>
       <c r="K7" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B8" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C8" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D8" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F8" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G8" t="n">
         <v>0.395</v>
@@ -81071,6 +81095,41 @@
         <v>0.014</v>
       </c>
       <c r="K8" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K9" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81085,7 +81144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81155,22 +81214,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C2" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D2" t="n">
         <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F2" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G2" t="n">
         <v>0.446</v>
@@ -81182,65 +81241,65 @@
         <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L2" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C3" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D3" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F3" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G3" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H3" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L3" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C4" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D4" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E4" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F4" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G4" t="n">
         <v>0.462</v>
@@ -81249,33 +81308,33 @@
         <v>0.343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K4" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L4" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C5" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E5" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F5" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G5" t="n">
         <v>0.462</v>
@@ -81284,109 +81343,106 @@
         <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K5" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L5" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C6" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D6" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F6" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H6" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K6" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L6" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B7" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C7" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D7" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E7" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F7" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I7" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J7" t="n">
         <v>0.014</v>
       </c>
       <c r="K7" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L7" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B8" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C8" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D8" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F8" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G8" t="n">
         <v>0.395</v>
@@ -81401,9 +81457,47 @@
         <v>0.014</v>
       </c>
       <c r="K8" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B9" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K9" t="n">
         <v>12.277</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81844,7 +81938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81944,34 +82038,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B2" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C2" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D2" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E2" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G2" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I2" t="n">
         <v>1488515</v>
       </c>
       <c r="K2" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M2" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -81980,7 +82074,7 @@
         <v>247857</v>
       </c>
       <c r="P2" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q2" t="n">
         <v>738429</v>
@@ -81988,78 +82082,78 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B3" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C3" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D3" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E3" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G3" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I3" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K3" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M3" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P3" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q3" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B4" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C4" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D4" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E4" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G4" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I4" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K4" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M4" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -82068,42 +82162,42 @@
         <v>264857</v>
       </c>
       <c r="P4" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q4" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B5" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C5" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D5" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E5" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G5" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I5" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K5" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M5" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -82112,101 +82206,98 @@
         <v>264857</v>
       </c>
       <c r="P5" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q5" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B6" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C6" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D6" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E6" t="n">
         <v>9300</v>
       </c>
       <c r="F6" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G6" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I6" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K6" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M6" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N6" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P6" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q6" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R6" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B7" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C7" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D7" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E7" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F7" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G7" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I7" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K7" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M7" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N7" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O7" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P7" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q7" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R7" t="n">
         <v>15000</v>
@@ -82214,40 +82305,40 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B8" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C8" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D8" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E8" t="n">
         <v>9100</v>
       </c>
       <c r="F8" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G8" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I8" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K8" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M8" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N8" t="n">
         <v>189475</v>
       </c>
       <c r="O8" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P8" t="n">
         <v>375660</v>
@@ -82256,6 +82347,53 @@
         <v>773586</v>
       </c>
       <c r="R8" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C9" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E9" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K9" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N9" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O9" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P9" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R9" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80483,9 +80483,36 @@
       <c r="A2455" s="4" t="n">
         <v>46284</v>
       </c>
+      <c r="B2455" t="n">
+        <v>3.176</v>
+      </c>
+      <c r="C2455" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="D2455" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="E2455" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="F2455" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="G2455" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="H2455" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="I2455" t="n">
+        <v>0.712</v>
+      </c>
+      <c r="K2455" t="n">
+        <v>12.569</v>
+      </c>
       <c r="L2455" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80805,7 +80832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80870,22 +80897,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C2" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D2" t="n">
         <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F2" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G2" t="n">
         <v>0.446</v>
@@ -80897,27 +80924,27 @@
         <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C3" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D3" t="n">
         <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F3" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G3" t="n">
         <v>0.446</v>
@@ -80929,59 +80956,59 @@
         <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C4" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F4" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G4" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C5" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D5" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F5" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G5" t="n">
         <v>0.462</v>
@@ -80990,30 +81017,30 @@
         <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K5" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C6" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D6" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E6" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F6" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G6" t="n">
         <v>0.462</v>
@@ -81022,100 +81049,97 @@
         <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K6" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B7" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C7" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D7" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F7" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G7" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K7" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B8" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C8" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D8" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E8" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F8" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H8" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I8" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J8" t="n">
         <v>0.014</v>
       </c>
       <c r="K8" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B9" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C9" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D9" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F9" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G9" t="n">
         <v>0.395</v>
@@ -81130,6 +81154,41 @@
         <v>0.014</v>
       </c>
       <c r="K9" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K10" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81144,7 +81203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81214,22 +81273,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C2" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D2" t="n">
         <v>1.435</v>
       </c>
       <c r="E2" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F2" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G2" t="n">
         <v>0.446</v>
@@ -81241,30 +81300,30 @@
         <v>0.712</v>
       </c>
       <c r="K2" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L2" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C3" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D3" t="n">
         <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F3" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G3" t="n">
         <v>0.446</v>
@@ -81276,65 +81335,65 @@
         <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L3" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C4" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F4" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G4" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H4" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L4" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C5" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D5" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E5" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F5" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G5" t="n">
         <v>0.462</v>
@@ -81343,33 +81402,33 @@
         <v>0.343</v>
       </c>
       <c r="I5" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K5" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L5" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C6" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D6" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E6" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F6" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G6" t="n">
         <v>0.462</v>
@@ -81378,109 +81437,106 @@
         <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K6" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L6" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B7" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C7" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D7" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F7" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G7" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H7" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K7" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L7" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B8" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C8" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D8" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E8" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F8" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H8" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I8" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J8" t="n">
         <v>0.014</v>
       </c>
       <c r="K8" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L8" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B9" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C9" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D9" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F9" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G9" t="n">
         <v>0.395</v>
@@ -81495,9 +81551,47 @@
         <v>0.014</v>
       </c>
       <c r="K9" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K10" t="n">
         <v>12.277</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -81938,7 +82032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82038,34 +82132,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B2" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C2" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D2" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G2" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I2" t="n">
         <v>1488515</v>
       </c>
       <c r="K2" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M2" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -82074,7 +82168,7 @@
         <v>247857</v>
       </c>
       <c r="P2" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q2" t="n">
         <v>738429</v>
@@ -82082,34 +82176,34 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B3" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C3" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D3" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E3" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G3" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I3" t="n">
         <v>1488515</v>
       </c>
       <c r="K3" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M3" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -82118,7 +82212,7 @@
         <v>247857</v>
       </c>
       <c r="P3" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q3" t="n">
         <v>738429</v>
@@ -82126,78 +82220,78 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B4" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C4" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D4" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E4" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G4" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I4" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K4" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M4" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P4" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q4" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B5" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C5" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D5" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E5" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G5" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I5" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K5" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M5" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -82206,42 +82300,42 @@
         <v>264857</v>
       </c>
       <c r="P5" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q5" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B6" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C6" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D6" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E6" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G6" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I6" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K6" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M6" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -82250,101 +82344,98 @@
         <v>264857</v>
       </c>
       <c r="P6" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q6" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B7" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C7" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D7" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E7" t="n">
         <v>9300</v>
       </c>
       <c r="F7" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G7" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I7" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K7" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M7" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N7" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P7" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q7" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R7" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B8" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C8" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D8" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E8" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F8" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G8" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I8" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K8" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M8" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N8" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O8" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P8" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q8" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R8" t="n">
         <v>15000</v>
@@ -82352,40 +82443,40 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B9" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C9" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D9" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E9" t="n">
         <v>9100</v>
       </c>
       <c r="F9" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G9" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I9" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K9" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M9" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N9" t="n">
         <v>189475</v>
       </c>
       <c r="O9" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P9" t="n">
         <v>375660</v>
@@ -82394,6 +82485,53 @@
         <v>773586</v>
       </c>
       <c r="R9" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C10" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K10" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N10" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O10" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P10" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R10" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80473,9 +80473,36 @@
       <c r="A2454" s="4" t="n">
         <v>46283</v>
       </c>
+      <c r="B2454" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C2454" t="n">
+        <v>3.232</v>
+      </c>
+      <c r="D2454" t="n">
+        <v>1.484</v>
+      </c>
+      <c r="E2454" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="F2454" t="n">
+        <v>2.598</v>
+      </c>
+      <c r="G2454" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="H2454" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I2454" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="K2454" t="n">
+        <v>12.634</v>
+      </c>
       <c r="L2454" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80832,7 +80859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80897,54 +80924,54 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C2" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D2" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H2" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K2" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C3" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D3" t="n">
         <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F3" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G3" t="n">
         <v>0.446</v>
@@ -80956,27 +80983,27 @@
         <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B4" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C4" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D4" t="n">
         <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F4" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G4" t="n">
         <v>0.446</v>
@@ -80988,59 +81015,59 @@
         <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C5" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D5" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F5" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C6" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D6" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E6" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F6" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G6" t="n">
         <v>0.462</v>
@@ -81049,30 +81076,30 @@
         <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K6" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B7" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C7" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D7" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E7" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F7" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G7" t="n">
         <v>0.462</v>
@@ -81081,100 +81108,97 @@
         <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K7" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B8" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C8" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D8" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F8" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K8" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C9" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D9" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F9" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H9" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J9" t="n">
         <v>0.014</v>
       </c>
       <c r="K9" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B10" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C10" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D10" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F10" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G10" t="n">
         <v>0.395</v>
@@ -81189,6 +81213,41 @@
         <v>0.014</v>
       </c>
       <c r="K10" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K11" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81203,7 +81262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81273,57 +81332,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C2" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D2" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E2" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H2" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K2" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L2" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C3" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D3" t="n">
         <v>1.435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F3" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G3" t="n">
         <v>0.446</v>
@@ -81335,30 +81394,30 @@
         <v>0.712</v>
       </c>
       <c r="K3" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L3" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B4" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C4" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D4" t="n">
         <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F4" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G4" t="n">
         <v>0.446</v>
@@ -81370,65 +81429,65 @@
         <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L4" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C5" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D5" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F5" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H5" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L5" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C6" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D6" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E6" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F6" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G6" t="n">
         <v>0.462</v>
@@ -81437,33 +81496,33 @@
         <v>0.343</v>
       </c>
       <c r="I6" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K6" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L6" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B7" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C7" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D7" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E7" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F7" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G7" t="n">
         <v>0.462</v>
@@ -81472,109 +81531,106 @@
         <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K7" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L7" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B8" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C8" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D8" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F8" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G8" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H8" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K8" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L8" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C9" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D9" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F9" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G9" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H9" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I9" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J9" t="n">
         <v>0.014</v>
       </c>
       <c r="K9" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L9" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B10" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C10" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D10" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F10" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G10" t="n">
         <v>0.395</v>
@@ -81589,9 +81645,47 @@
         <v>0.014</v>
       </c>
       <c r="K10" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B11" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K11" t="n">
         <v>12.277</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82032,7 +82126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82132,78 +82226,78 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B2" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C2" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D2" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G2" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I2" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K2" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M2" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O2" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P2" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q2" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B3" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C3" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D3" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G3" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I3" t="n">
         <v>1488515</v>
       </c>
       <c r="K3" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M3" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -82212,7 +82306,7 @@
         <v>247857</v>
       </c>
       <c r="P3" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q3" t="n">
         <v>738429</v>
@@ -82220,34 +82314,34 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B4" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C4" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D4" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E4" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G4" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I4" t="n">
         <v>1488515</v>
       </c>
       <c r="K4" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M4" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -82256,7 +82350,7 @@
         <v>247857</v>
       </c>
       <c r="P4" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q4" t="n">
         <v>738429</v>
@@ -82264,78 +82358,78 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B5" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C5" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D5" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E5" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G5" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I5" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K5" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M5" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P5" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q5" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B6" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C6" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D6" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E6" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G6" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I6" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K6" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M6" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -82344,42 +82438,42 @@
         <v>264857</v>
       </c>
       <c r="P6" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q6" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B7" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C7" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D7" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E7" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G7" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I7" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K7" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M7" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -82388,101 +82482,98 @@
         <v>264857</v>
       </c>
       <c r="P7" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q7" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B8" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C8" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D8" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E8" t="n">
         <v>9300</v>
       </c>
       <c r="F8" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G8" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I8" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K8" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M8" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N8" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P8" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q8" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R8" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B9" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C9" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D9" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E9" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F9" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G9" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I9" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K9" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M9" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N9" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O9" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P9" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q9" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R9" t="n">
         <v>15000</v>
@@ -82490,40 +82581,40 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B10" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C10" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D10" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E10" t="n">
         <v>9100</v>
       </c>
       <c r="F10" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G10" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I10" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K10" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M10" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N10" t="n">
         <v>189475</v>
       </c>
       <c r="O10" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P10" t="n">
         <v>375660</v>
@@ -82532,6 +82623,53 @@
         <v>773586</v>
       </c>
       <c r="R10" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C11" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K11" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N11" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O11" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P11" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R11" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80463,9 +80463,36 @@
       <c r="A2453" s="4" t="n">
         <v>46282</v>
       </c>
+      <c r="B2453" t="n">
+        <v>3.196</v>
+      </c>
+      <c r="C2453" t="n">
+        <v>3.232</v>
+      </c>
+      <c r="D2453" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="E2453" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="F2453" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="G2453" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="H2453" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="I2453" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K2453" t="n">
+        <v>12.272</v>
+      </c>
       <c r="L2453" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80859,7 +80886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80924,86 +80951,86 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C2" t="n">
         <v>3.232</v>
       </c>
       <c r="D2" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F2" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K2" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C3" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D3" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K3" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C4" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D4" t="n">
         <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F4" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G4" t="n">
         <v>0.446</v>
@@ -81015,27 +81042,27 @@
         <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C5" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D5" t="n">
         <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F5" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G5" t="n">
         <v>0.446</v>
@@ -81047,59 +81074,59 @@
         <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C6" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D6" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F6" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I6" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C7" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D7" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E7" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F7" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G7" t="n">
         <v>0.462</v>
@@ -81108,30 +81135,30 @@
         <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K7" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B8" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C8" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D8" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E8" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F8" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G8" t="n">
         <v>0.462</v>
@@ -81140,100 +81167,97 @@
         <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K8" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B9" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C9" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D9" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F9" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K9" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B10" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C10" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D10" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E10" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F10" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G10" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H10" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J10" t="n">
         <v>0.014</v>
       </c>
       <c r="K10" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B11" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C11" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D11" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F11" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G11" t="n">
         <v>0.395</v>
@@ -81248,6 +81272,41 @@
         <v>0.014</v>
       </c>
       <c r="K11" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K12" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81262,7 +81321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81332,92 +81391,92 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C2" t="n">
         <v>3.232</v>
       </c>
       <c r="D2" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F2" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H2" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K2" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L2" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C3" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D3" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H3" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I3" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K3" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L3" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C4" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D4" t="n">
         <v>1.435</v>
       </c>
       <c r="E4" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F4" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G4" t="n">
         <v>0.446</v>
@@ -81429,30 +81488,30 @@
         <v>0.712</v>
       </c>
       <c r="K4" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L4" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C5" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D5" t="n">
         <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F5" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G5" t="n">
         <v>0.446</v>
@@ -81464,65 +81523,65 @@
         <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L5" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C6" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D6" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F6" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H6" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I6" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L6" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C7" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D7" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E7" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F7" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G7" t="n">
         <v>0.462</v>
@@ -81531,33 +81590,33 @@
         <v>0.343</v>
       </c>
       <c r="I7" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K7" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L7" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B8" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C8" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D8" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E8" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F8" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G8" t="n">
         <v>0.462</v>
@@ -81566,109 +81625,106 @@
         <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K8" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L8" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B9" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C9" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D9" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F9" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G9" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K9" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L9" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B10" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C10" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D10" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E10" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F10" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G10" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H10" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J10" t="n">
         <v>0.014</v>
       </c>
       <c r="K10" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L10" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B11" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C11" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D11" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F11" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G11" t="n">
         <v>0.395</v>
@@ -81683,9 +81739,47 @@
         <v>0.014</v>
       </c>
       <c r="K11" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B12" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K12" t="n">
         <v>12.277</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82126,7 +82220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82226,13 +82320,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B2" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C2" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D2" t="n">
         <v>1438502</v>
@@ -82241,107 +82335,107 @@
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G2" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I2" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K2" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M2" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N2" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O2" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P2" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q2" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B3" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C3" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D3" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G3" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I3" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K3" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M3" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O3" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P3" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q3" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B4" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C4" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D4" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G4" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I4" t="n">
         <v>1488515</v>
       </c>
       <c r="K4" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M4" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -82350,7 +82444,7 @@
         <v>247857</v>
       </c>
       <c r="P4" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q4" t="n">
         <v>738429</v>
@@ -82358,34 +82452,34 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B5" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C5" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D5" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E5" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G5" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I5" t="n">
         <v>1488515</v>
       </c>
       <c r="K5" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M5" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -82394,7 +82488,7 @@
         <v>247857</v>
       </c>
       <c r="P5" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q5" t="n">
         <v>738429</v>
@@ -82402,78 +82496,78 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B6" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C6" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D6" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E6" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G6" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I6" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K6" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M6" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P6" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q6" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B7" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C7" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D7" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E7" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G7" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I7" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K7" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M7" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -82482,42 +82576,42 @@
         <v>264857</v>
       </c>
       <c r="P7" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q7" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B8" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C8" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D8" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E8" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G8" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I8" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K8" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M8" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -82526,101 +82620,98 @@
         <v>264857</v>
       </c>
       <c r="P8" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q8" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B9" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C9" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D9" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E9" t="n">
         <v>9300</v>
       </c>
       <c r="F9" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G9" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I9" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K9" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M9" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N9" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P9" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q9" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R9" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B10" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C10" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D10" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E10" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F10" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G10" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I10" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K10" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M10" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N10" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O10" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P10" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q10" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R10" t="n">
         <v>15000</v>
@@ -82628,40 +82719,40 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B11" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C11" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D11" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E11" t="n">
         <v>9100</v>
       </c>
       <c r="F11" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G11" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I11" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K11" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M11" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N11" t="n">
         <v>189475</v>
       </c>
       <c r="O11" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P11" t="n">
         <v>375660</v>
@@ -82670,6 +82761,53 @@
         <v>773586</v>
       </c>
       <c r="R11" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C12" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K12" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N12" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O12" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P12" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R12" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80453,9 +80453,36 @@
       <c r="A2452" s="4" t="n">
         <v>46281</v>
       </c>
+      <c r="B2452" t="n">
+        <v>3.195</v>
+      </c>
+      <c r="C2452" t="n">
+        <v>3.193</v>
+      </c>
+      <c r="D2452" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="E2452" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="F2452" t="n">
+        <v>2.577</v>
+      </c>
+      <c r="G2452" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="H2452" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="I2452" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="K2452" t="n">
+        <v>12.108</v>
+      </c>
       <c r="L2452" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80886,7 +80913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80951,118 +80978,118 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C2" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D2" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G2" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K2" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C3" t="n">
         <v>3.232</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F3" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K3" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C4" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D4" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E4" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H4" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K4" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C5" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D5" t="n">
         <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F5" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G5" t="n">
         <v>0.446</v>
@@ -81074,27 +81101,27 @@
         <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B6" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C6" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D6" t="n">
         <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F6" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G6" t="n">
         <v>0.446</v>
@@ -81106,59 +81133,59 @@
         <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B7" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C7" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F7" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I7" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C8" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D8" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F8" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G8" t="n">
         <v>0.462</v>
@@ -81167,30 +81194,30 @@
         <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K8" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B9" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C9" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F9" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G9" t="n">
         <v>0.462</v>
@@ -81199,100 +81226,97 @@
         <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K9" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B10" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C10" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D10" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F10" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G10" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H10" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K10" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C11" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D11" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E11" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F11" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G11" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J11" t="n">
         <v>0.014</v>
       </c>
       <c r="K11" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B12" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C12" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D12" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F12" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G12" t="n">
         <v>0.395</v>
@@ -81307,6 +81331,41 @@
         <v>0.014</v>
       </c>
       <c r="K12" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K13" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81321,7 +81380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81391,127 +81450,127 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C2" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D2" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E2" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G2" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K2" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L2" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C3" t="n">
         <v>3.232</v>
       </c>
       <c r="D3" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F3" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H3" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K3" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L3" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C4" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D4" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E4" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G4" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H4" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K4" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L4" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C5" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D5" t="n">
         <v>1.435</v>
       </c>
       <c r="E5" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F5" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G5" t="n">
         <v>0.446</v>
@@ -81523,30 +81582,30 @@
         <v>0.712</v>
       </c>
       <c r="K5" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L5" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B6" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C6" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D6" t="n">
         <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F6" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G6" t="n">
         <v>0.446</v>
@@ -81558,65 +81617,65 @@
         <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L6" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B7" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C7" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F7" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I7" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L7" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C8" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D8" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F8" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G8" t="n">
         <v>0.462</v>
@@ -81625,33 +81684,33 @@
         <v>0.343</v>
       </c>
       <c r="I8" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K8" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L8" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B9" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C9" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E9" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F9" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G9" t="n">
         <v>0.462</v>
@@ -81660,109 +81719,106 @@
         <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K9" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L9" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B10" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C10" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D10" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F10" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G10" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H10" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K10" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L10" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C11" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D11" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E11" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F11" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G11" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I11" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J11" t="n">
         <v>0.014</v>
       </c>
       <c r="K11" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L11" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B12" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C12" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D12" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F12" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G12" t="n">
         <v>0.395</v>
@@ -81777,9 +81833,47 @@
         <v>0.014</v>
       </c>
       <c r="K12" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K13" t="n">
         <v>12.277</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82220,7 +82314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82320,57 +82414,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B2" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C2" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D2" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G2" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I2" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K2" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M2" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N2" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P2" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q2" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B3" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C3" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D3" t="n">
         <v>1438502</v>
@@ -82379,107 +82473,107 @@
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G3" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I3" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K3" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M3" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N3" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O3" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P3" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q3" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B4" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C4" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D4" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G4" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I4" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K4" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M4" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O4" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P4" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q4" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B5" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C5" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D5" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G5" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I5" t="n">
         <v>1488515</v>
       </c>
       <c r="K5" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M5" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -82488,7 +82582,7 @@
         <v>247857</v>
       </c>
       <c r="P5" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q5" t="n">
         <v>738429</v>
@@ -82496,34 +82590,34 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B6" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C6" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D6" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E6" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G6" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I6" t="n">
         <v>1488515</v>
       </c>
       <c r="K6" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M6" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -82532,7 +82626,7 @@
         <v>247857</v>
       </c>
       <c r="P6" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q6" t="n">
         <v>738429</v>
@@ -82540,78 +82634,78 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B7" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C7" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D7" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E7" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G7" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I7" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K7" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M7" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P7" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q7" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B8" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C8" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D8" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E8" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G8" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I8" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K8" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M8" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -82620,42 +82714,42 @@
         <v>264857</v>
       </c>
       <c r="P8" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q8" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B9" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C9" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D9" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E9" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G9" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I9" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K9" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M9" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -82664,101 +82758,98 @@
         <v>264857</v>
       </c>
       <c r="P9" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q9" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B10" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C10" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D10" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E10" t="n">
         <v>9300</v>
       </c>
       <c r="F10" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G10" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I10" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K10" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M10" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N10" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P10" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q10" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R10" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B11" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C11" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D11" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E11" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F11" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G11" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I11" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K11" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M11" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N11" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O11" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P11" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q11" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R11" t="n">
         <v>15000</v>
@@ -82766,40 +82857,40 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B12" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C12" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D12" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E12" t="n">
         <v>9100</v>
       </c>
       <c r="F12" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G12" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I12" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K12" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M12" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N12" t="n">
         <v>189475</v>
       </c>
       <c r="O12" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P12" t="n">
         <v>375660</v>
@@ -82808,6 +82899,53 @@
         <v>773586</v>
       </c>
       <c r="R12" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C13" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K13" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N13" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O13" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P13" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R13" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80443,9 +80443,36 @@
       <c r="A2451" s="4" t="n">
         <v>46280</v>
       </c>
+      <c r="B2451" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="C2451" t="n">
+        <v>3.299</v>
+      </c>
+      <c r="D2451" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="E2451" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="F2451" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="G2451" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="H2451" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="I2451" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K2451" t="n">
+        <v>12.02</v>
+      </c>
       <c r="L2451" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80913,7 +80940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -80978,150 +81005,150 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C2" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F2" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G2" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K2" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B3" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C3" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D3" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E3" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K3" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C4" t="n">
         <v>3.232</v>
       </c>
       <c r="D4" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F4" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K4" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C5" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D5" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H5" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K5" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B6" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C6" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D6" t="n">
         <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F6" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G6" t="n">
         <v>0.446</v>
@@ -81133,27 +81160,27 @@
         <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B7" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C7" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D7" t="n">
         <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F7" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G7" t="n">
         <v>0.446</v>
@@ -81165,59 +81192,59 @@
         <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C8" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D8" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F8" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G8" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H8" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I8" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C9" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D9" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E9" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F9" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G9" t="n">
         <v>0.462</v>
@@ -81226,30 +81253,30 @@
         <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K9" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C10" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F10" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G10" t="n">
         <v>0.462</v>
@@ -81258,100 +81285,97 @@
         <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K10" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B11" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C11" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D11" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F11" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G11" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K11" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C12" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D12" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F12" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G12" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H12" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J12" t="n">
         <v>0.014</v>
       </c>
       <c r="K12" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B13" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C13" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D13" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F13" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G13" t="n">
         <v>0.395</v>
@@ -81366,6 +81390,41 @@
         <v>0.014</v>
       </c>
       <c r="K13" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K14" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81380,7 +81439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81450,162 +81509,162 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C2" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D2" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F2" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G2" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K2" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L2" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B3" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C3" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D3" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E3" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K3" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L3" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C4" t="n">
         <v>3.232</v>
       </c>
       <c r="D4" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F4" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H4" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K4" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L4" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C5" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D5" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E5" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H5" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I5" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K5" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L5" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B6" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C6" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D6" t="n">
         <v>1.435</v>
       </c>
       <c r="E6" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F6" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G6" t="n">
         <v>0.446</v>
@@ -81617,30 +81676,30 @@
         <v>0.712</v>
       </c>
       <c r="K6" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L6" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B7" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C7" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D7" t="n">
         <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F7" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G7" t="n">
         <v>0.446</v>
@@ -81652,65 +81711,65 @@
         <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L7" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C8" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D8" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F8" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G8" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H8" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I8" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L8" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C9" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D9" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E9" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F9" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G9" t="n">
         <v>0.462</v>
@@ -81719,33 +81778,33 @@
         <v>0.343</v>
       </c>
       <c r="I9" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K9" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L9" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C10" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F10" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G10" t="n">
         <v>0.462</v>
@@ -81754,109 +81813,106 @@
         <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K10" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L10" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B11" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C11" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D11" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F11" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G11" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H11" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K11" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L11" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C12" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D12" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F12" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G12" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H12" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J12" t="n">
         <v>0.014</v>
       </c>
       <c r="K12" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L12" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B13" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C13" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D13" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F13" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G13" t="n">
         <v>0.395</v>
@@ -81871,9 +81927,47 @@
         <v>0.014</v>
       </c>
       <c r="K13" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K14" t="n">
         <v>12.277</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82314,7 +82408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82414,101 +82508,101 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B2" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C2" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D2" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E2" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G2" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I2" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K2" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M2" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O2" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P2" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q2" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B3" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C3" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D3" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G3" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I3" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K3" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M3" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N3" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P3" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q3" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B4" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C4" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D4" t="n">
         <v>1438502</v>
@@ -82517,107 +82611,107 @@
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G4" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I4" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K4" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M4" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N4" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O4" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P4" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q4" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B5" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C5" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D5" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G5" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I5" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K5" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M5" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O5" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P5" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q5" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B6" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C6" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D6" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G6" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I6" t="n">
         <v>1488515</v>
       </c>
       <c r="K6" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M6" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -82626,7 +82720,7 @@
         <v>247857</v>
       </c>
       <c r="P6" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q6" t="n">
         <v>738429</v>
@@ -82634,34 +82728,34 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B7" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C7" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D7" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E7" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G7" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I7" t="n">
         <v>1488515</v>
       </c>
       <c r="K7" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M7" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -82670,7 +82764,7 @@
         <v>247857</v>
       </c>
       <c r="P7" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q7" t="n">
         <v>738429</v>
@@ -82678,78 +82772,78 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B8" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C8" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D8" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G8" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I8" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K8" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M8" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P8" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q8" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B9" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C9" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D9" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E9" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G9" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I9" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K9" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M9" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -82758,42 +82852,42 @@
         <v>264857</v>
       </c>
       <c r="P9" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q9" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B10" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C10" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D10" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E10" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G10" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I10" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K10" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M10" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -82802,101 +82896,98 @@
         <v>264857</v>
       </c>
       <c r="P10" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q10" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B11" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C11" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D11" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E11" t="n">
         <v>9300</v>
       </c>
       <c r="F11" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G11" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I11" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K11" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M11" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N11" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P11" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q11" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R11" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B12" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C12" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D12" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E12" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F12" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G12" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I12" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K12" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M12" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N12" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O12" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P12" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q12" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R12" t="n">
         <v>15000</v>
@@ -82904,40 +82995,40 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B13" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C13" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D13" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E13" t="n">
         <v>9100</v>
       </c>
       <c r="F13" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G13" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I13" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K13" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M13" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N13" t="n">
         <v>189475</v>
       </c>
       <c r="O13" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P13" t="n">
         <v>375660</v>
@@ -82946,6 +83037,53 @@
         <v>773586</v>
       </c>
       <c r="R13" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C14" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E14" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K14" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N14" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O14" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P14" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R14" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80433,9 +80433,36 @@
       <c r="A2450" s="4" t="n">
         <v>46279</v>
       </c>
+      <c r="B2450" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="C2450" t="n">
+        <v>3.219</v>
+      </c>
+      <c r="D2450" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E2450" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F2450" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="G2450" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="H2450" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="I2450" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K2450" t="n">
+        <v>12.229</v>
+      </c>
       <c r="L2450" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80940,7 +80967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81005,182 +81032,182 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C2" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D2" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F2" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K2" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C3" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D3" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F3" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K3" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B4" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C4" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D4" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E4" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K4" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B5" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C5" t="n">
         <v>3.232</v>
       </c>
       <c r="D5" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F5" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H5" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K5" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C6" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D6" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H6" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K6" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B7" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C7" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D7" t="n">
         <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F7" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G7" t="n">
         <v>0.446</v>
@@ -81192,27 +81219,27 @@
         <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B8" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C8" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D8" t="n">
         <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F8" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G8" t="n">
         <v>0.446</v>
@@ -81224,59 +81251,59 @@
         <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B9" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C9" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D9" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F9" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G9" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I9" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C10" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D10" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E10" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F10" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G10" t="n">
         <v>0.462</v>
@@ -81285,30 +81312,30 @@
         <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K10" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B11" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C11" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E11" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F11" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G11" t="n">
         <v>0.462</v>
@@ -81317,100 +81344,97 @@
         <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K11" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B12" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C12" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D12" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F12" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G12" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H12" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K12" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B13" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C13" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D13" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E13" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F13" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G13" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H13" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I13" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J13" t="n">
         <v>0.014</v>
       </c>
       <c r="K13" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B14" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C14" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F14" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G14" t="n">
         <v>0.395</v>
@@ -81425,6 +81449,41 @@
         <v>0.014</v>
       </c>
       <c r="K14" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81439,7 +81498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81509,197 +81568,197 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C2" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D2" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F2" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H2" t="n">
         <v>0.365</v>
       </c>
       <c r="I2" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K2" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L2" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C3" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D3" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F3" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K3" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L3" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B4" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C4" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D4" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E4" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G4" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K4" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L4" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B5" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C5" t="n">
         <v>3.232</v>
       </c>
       <c r="D5" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F5" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H5" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K5" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L5" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C6" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D6" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E6" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G6" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H6" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I6" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K6" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L6" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B7" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C7" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D7" t="n">
         <v>1.435</v>
       </c>
       <c r="E7" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F7" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G7" t="n">
         <v>0.446</v>
@@ -81711,30 +81770,30 @@
         <v>0.712</v>
       </c>
       <c r="K7" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L7" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B8" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C8" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D8" t="n">
         <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F8" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G8" t="n">
         <v>0.446</v>
@@ -81746,65 +81805,65 @@
         <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L8" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B9" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C9" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D9" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F9" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G9" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I9" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L9" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C10" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D10" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E10" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F10" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G10" t="n">
         <v>0.462</v>
@@ -81813,33 +81872,33 @@
         <v>0.343</v>
       </c>
       <c r="I10" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K10" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L10" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B11" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C11" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E11" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F11" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G11" t="n">
         <v>0.462</v>
@@ -81848,109 +81907,106 @@
         <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K11" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L11" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B12" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C12" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D12" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F12" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G12" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H12" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K12" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L12" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B13" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C13" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D13" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E13" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F13" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G13" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H13" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I13" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J13" t="n">
         <v>0.014</v>
       </c>
       <c r="K13" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L13" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B14" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C14" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F14" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G14" t="n">
         <v>0.395</v>
@@ -81965,9 +82021,47 @@
         <v>0.014</v>
       </c>
       <c r="K14" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L14" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.277</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82408,7 +82502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82508,145 +82602,145 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B2" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C2" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D2" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E2" t="n">
         <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G2" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I2" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K2" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M2" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N2" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P2" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q2" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B3" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C3" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D3" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E3" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G3" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I3" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K3" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M3" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O3" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P3" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q3" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B4" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C4" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D4" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G4" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I4" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K4" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M4" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N4" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P4" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q4" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B5" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C5" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D5" t="n">
         <v>1438502</v>
@@ -82655,107 +82749,107 @@
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G5" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I5" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K5" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M5" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N5" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O5" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P5" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q5" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B6" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C6" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D6" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G6" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I6" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K6" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M6" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N6" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O6" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P6" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q6" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B7" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C7" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D7" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G7" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I7" t="n">
         <v>1488515</v>
       </c>
       <c r="K7" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M7" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -82764,7 +82858,7 @@
         <v>247857</v>
       </c>
       <c r="P7" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q7" t="n">
         <v>738429</v>
@@ -82772,34 +82866,34 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B8" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C8" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D8" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E8" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G8" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I8" t="n">
         <v>1488515</v>
       </c>
       <c r="K8" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M8" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -82808,7 +82902,7 @@
         <v>247857</v>
       </c>
       <c r="P8" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q8" t="n">
         <v>738429</v>
@@ -82816,78 +82910,78 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B9" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C9" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D9" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E9" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G9" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I9" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K9" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M9" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P9" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q9" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B10" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C10" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D10" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E10" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G10" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I10" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K10" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M10" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -82896,42 +82990,42 @@
         <v>264857</v>
       </c>
       <c r="P10" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q10" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B11" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C11" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D11" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E11" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G11" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I11" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K11" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M11" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -82940,101 +83034,98 @@
         <v>264857</v>
       </c>
       <c r="P11" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q11" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B12" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C12" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D12" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E12" t="n">
         <v>9300</v>
       </c>
       <c r="F12" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G12" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I12" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K12" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M12" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N12" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P12" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q12" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R12" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B13" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C13" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D13" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E13" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F13" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G13" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I13" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K13" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M13" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N13" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O13" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P13" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q13" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R13" t="n">
         <v>15000</v>
@@ -83042,40 +83133,40 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B14" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C14" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D14" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E14" t="n">
         <v>9100</v>
       </c>
       <c r="F14" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G14" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I14" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K14" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M14" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N14" t="n">
         <v>189475</v>
       </c>
       <c r="O14" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P14" t="n">
         <v>375660</v>
@@ -83084,6 +83175,53 @@
         <v>773586</v>
       </c>
       <c r="R14" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C15" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K15" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N15" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O15" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P15" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R15" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80423,9 +80423,36 @@
       <c r="A2449" s="4" t="n">
         <v>46278</v>
       </c>
+      <c r="B2449" t="n">
+        <v>3.218</v>
+      </c>
+      <c r="C2449" t="n">
+        <v>3.218</v>
+      </c>
+      <c r="D2449" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E2449" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="F2449" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="G2449" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="H2449" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2449" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="K2449" t="n">
+        <v>12.233</v>
+      </c>
       <c r="L2449" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80967,7 +80994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81032,214 +81059,214 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B2" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D2" t="n">
         <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G2" t="n">
         <v>0.435</v>
       </c>
       <c r="H2" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K2" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C3" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D3" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F3" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K3" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C4" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F4" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G4" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K4" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B5" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C5" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D5" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K5" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B6" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C6" t="n">
         <v>3.232</v>
       </c>
       <c r="D6" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F6" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K6" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C7" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E7" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H7" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K7" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B8" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C8" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D8" t="n">
         <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F8" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G8" t="n">
         <v>0.446</v>
@@ -81251,27 +81278,27 @@
         <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B9" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C9" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D9" t="n">
         <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F9" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G9" t="n">
         <v>0.446</v>
@@ -81283,59 +81310,59 @@
         <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B10" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C10" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D10" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F10" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G10" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H10" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I10" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C11" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D11" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E11" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F11" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G11" t="n">
         <v>0.462</v>
@@ -81344,30 +81371,30 @@
         <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K11" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B12" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C12" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E12" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F12" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G12" t="n">
         <v>0.462</v>
@@ -81376,100 +81403,97 @@
         <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K12" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C13" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F13" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G13" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H13" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K13" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B14" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C14" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D14" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F14" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G14" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H14" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I14" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J14" t="n">
         <v>0.014</v>
       </c>
       <c r="K14" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B15" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C15" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D15" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F15" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G15" t="n">
         <v>0.395</v>
@@ -81484,6 +81508,41 @@
         <v>0.014</v>
       </c>
       <c r="K15" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81498,7 +81557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81568,232 +81627,232 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B2" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C2" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D2" t="n">
         <v>1.44</v>
       </c>
       <c r="E2" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G2" t="n">
         <v>0.435</v>
       </c>
       <c r="H2" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K2" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L2" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C3" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D3" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F3" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H3" t="n">
         <v>0.365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L3" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C4" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F4" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G4" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K4" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L4" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B5" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C5" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D5" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K5" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L5" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B6" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C6" t="n">
         <v>3.232</v>
       </c>
       <c r="D6" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F6" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H6" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K6" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L6" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C7" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E7" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H7" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K7" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L7" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B8" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C8" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D8" t="n">
         <v>1.435</v>
       </c>
       <c r="E8" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F8" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G8" t="n">
         <v>0.446</v>
@@ -81805,30 +81864,30 @@
         <v>0.712</v>
       </c>
       <c r="K8" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L8" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B9" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C9" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D9" t="n">
         <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F9" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G9" t="n">
         <v>0.446</v>
@@ -81840,65 +81899,65 @@
         <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L9" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B10" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C10" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D10" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F10" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G10" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H10" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I10" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L10" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C11" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D11" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E11" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F11" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G11" t="n">
         <v>0.462</v>
@@ -81907,33 +81966,33 @@
         <v>0.343</v>
       </c>
       <c r="I11" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K11" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L11" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B12" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C12" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E12" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F12" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G12" t="n">
         <v>0.462</v>
@@ -81942,109 +82001,106 @@
         <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K12" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L12" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C13" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F13" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G13" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H13" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K13" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L13" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B14" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C14" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D14" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F14" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G14" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H14" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I14" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J14" t="n">
         <v>0.014</v>
       </c>
       <c r="K14" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L14" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B15" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C15" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D15" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F15" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G15" t="n">
         <v>0.395</v>
@@ -82059,9 +82115,47 @@
         <v>0.014</v>
       </c>
       <c r="K15" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L15" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.277</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82502,7 +82596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82602,34 +82696,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B2" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C2" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D2" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E2" t="n">
         <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G2" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I2" t="n">
         <v>1493578</v>
       </c>
       <c r="K2" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M2" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -82638,153 +82732,153 @@
         <v>236857</v>
       </c>
       <c r="P2" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q2" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B3" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C3" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D3" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E3" t="n">
         <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G3" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I3" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K3" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M3" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N3" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P3" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q3" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B4" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C4" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D4" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E4" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G4" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I4" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K4" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M4" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O4" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P4" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q4" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B5" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C5" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D5" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G5" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I5" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K5" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M5" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N5" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P5" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q5" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B6" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C6" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D6" t="n">
         <v>1438502</v>
@@ -82793,107 +82887,107 @@
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G6" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I6" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K6" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M6" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N6" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O6" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P6" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q6" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B7" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C7" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D7" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G7" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I7" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K7" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M7" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N7" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O7" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P7" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q7" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B8" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C8" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D8" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G8" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I8" t="n">
         <v>1488515</v>
       </c>
       <c r="K8" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M8" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -82902,7 +82996,7 @@
         <v>247857</v>
       </c>
       <c r="P8" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q8" t="n">
         <v>738429</v>
@@ -82910,34 +83004,34 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B9" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C9" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D9" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E9" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G9" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I9" t="n">
         <v>1488515</v>
       </c>
       <c r="K9" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M9" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -82946,7 +83040,7 @@
         <v>247857</v>
       </c>
       <c r="P9" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q9" t="n">
         <v>738429</v>
@@ -82954,78 +83048,78 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B10" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C10" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D10" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E10" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G10" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I10" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K10" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M10" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P10" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q10" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B11" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C11" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D11" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E11" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G11" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I11" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K11" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M11" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -83034,42 +83128,42 @@
         <v>264857</v>
       </c>
       <c r="P11" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q11" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B12" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C12" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D12" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E12" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G12" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I12" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K12" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M12" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -83078,101 +83172,98 @@
         <v>264857</v>
       </c>
       <c r="P12" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q12" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B13" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C13" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D13" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E13" t="n">
         <v>9300</v>
       </c>
       <c r="F13" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G13" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I13" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K13" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M13" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N13" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O13" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P13" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q13" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R13" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B14" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C14" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D14" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E14" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F14" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G14" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I14" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K14" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M14" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N14" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O14" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P14" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q14" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R14" t="n">
         <v>15000</v>
@@ -83180,40 +83271,40 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B15" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C15" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D15" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E15" t="n">
         <v>9100</v>
       </c>
       <c r="F15" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G15" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I15" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K15" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M15" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N15" t="n">
         <v>189475</v>
       </c>
       <c r="O15" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P15" t="n">
         <v>375660</v>
@@ -83222,6 +83313,53 @@
         <v>773586</v>
       </c>
       <c r="R15" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C16" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K16" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N16" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O16" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P16" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R16" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80413,9 +80413,36 @@
       <c r="A2448" s="4" t="n">
         <v>46277</v>
       </c>
+      <c r="B2448" t="n">
+        <v>3.244</v>
+      </c>
+      <c r="C2448" t="n">
+        <v>3.247</v>
+      </c>
+      <c r="D2448" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E2448" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="F2448" t="n">
+        <v>2.638</v>
+      </c>
+      <c r="G2448" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="H2448" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2448" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="K2448" t="n">
+        <v>12.294</v>
+      </c>
       <c r="L2448" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -80994,7 +81021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81059,13 +81086,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B2" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D2" t="n">
         <v>1.44</v>
@@ -81074,7 +81101,7 @@
         <v>0.261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G2" t="n">
         <v>0.435</v>
@@ -81083,222 +81110,222 @@
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K2" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C3" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D3" t="n">
         <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F3" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G3" t="n">
         <v>0.435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K3" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C4" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D4" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F4" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K4" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B5" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C5" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D5" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F5" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K5" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B6" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C6" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D6" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E6" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K6" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B7" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C7" t="n">
         <v>3.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F7" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K7" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C8" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D8" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E8" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G8" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H8" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K8" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B9" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C9" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D9" t="n">
         <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F9" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G9" t="n">
         <v>0.446</v>
@@ -81310,27 +81337,27 @@
         <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B10" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C10" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D10" t="n">
         <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F10" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G10" t="n">
         <v>0.446</v>
@@ -81342,59 +81369,59 @@
         <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B11" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C11" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D11" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F11" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G11" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H11" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C12" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D12" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E12" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F12" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G12" t="n">
         <v>0.462</v>
@@ -81403,30 +81430,30 @@
         <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K12" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B13" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C13" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E13" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F13" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G13" t="n">
         <v>0.462</v>
@@ -81435,100 +81462,97 @@
         <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K13" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B14" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C14" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F14" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G14" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H14" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K14" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B15" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C15" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D15" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F15" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G15" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H15" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I15" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J15" t="n">
         <v>0.014</v>
       </c>
       <c r="K15" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B16" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C16" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D16" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F16" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G16" t="n">
         <v>0.395</v>
@@ -81543,6 +81567,41 @@
         <v>0.014</v>
       </c>
       <c r="K16" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81557,7 +81616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81627,13 +81686,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B2" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D2" t="n">
         <v>1.44</v>
@@ -81642,7 +81701,7 @@
         <v>0.261</v>
       </c>
       <c r="F2" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G2" t="n">
         <v>0.435</v>
@@ -81651,243 +81710,243 @@
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K2" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L2" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C3" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D3" t="n">
         <v>1.44</v>
       </c>
       <c r="E3" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F3" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G3" t="n">
         <v>0.435</v>
       </c>
       <c r="H3" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K3" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L3" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C4" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D4" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F4" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H4" t="n">
         <v>0.365</v>
       </c>
       <c r="I4" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K4" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L4" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B5" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C5" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D5" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F5" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G5" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K5" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L5" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B6" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C6" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D6" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E6" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G6" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K6" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L6" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B7" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C7" t="n">
         <v>3.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F7" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H7" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K7" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L7" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C8" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D8" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E8" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G8" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H8" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I8" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K8" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L8" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B9" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C9" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D9" t="n">
         <v>1.435</v>
       </c>
       <c r="E9" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F9" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G9" t="n">
         <v>0.446</v>
@@ -81899,30 +81958,30 @@
         <v>0.712</v>
       </c>
       <c r="K9" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L9" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B10" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C10" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D10" t="n">
         <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F10" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G10" t="n">
         <v>0.446</v>
@@ -81934,65 +81993,65 @@
         <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L10" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B11" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C11" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D11" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F11" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G11" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H11" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I11" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L11" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C12" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D12" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E12" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F12" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G12" t="n">
         <v>0.462</v>
@@ -82001,33 +82060,33 @@
         <v>0.343</v>
       </c>
       <c r="I12" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K12" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L12" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B13" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C13" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E13" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F13" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G13" t="n">
         <v>0.462</v>
@@ -82036,109 +82095,106 @@
         <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K13" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L13" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B14" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C14" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F14" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G14" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H14" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K14" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L14" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B15" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C15" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D15" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F15" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G15" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H15" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I15" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J15" t="n">
         <v>0.014</v>
       </c>
       <c r="K15" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L15" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B16" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C16" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D16" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F16" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G16" t="n">
         <v>0.395</v>
@@ -82153,9 +82209,47 @@
         <v>0.014</v>
       </c>
       <c r="K16" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L16" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.277</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82596,7 +82690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82696,25 +82790,25 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B2" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C2" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D2" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E2" t="n">
         <v>9400</v>
       </c>
       <c r="F2" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G2" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I2" t="n">
         <v>1493578</v>
@@ -82723,7 +82817,7 @@
         <v>270165</v>
       </c>
       <c r="M2" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -82735,39 +82829,39 @@
         <v>380581</v>
       </c>
       <c r="Q2" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B3" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C3" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D3" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E3" t="n">
         <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G3" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I3" t="n">
         <v>1493578</v>
       </c>
       <c r="K3" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M3" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -82776,153 +82870,153 @@
         <v>236857</v>
       </c>
       <c r="P3" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q3" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B4" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C4" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D4" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E4" t="n">
         <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G4" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I4" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K4" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M4" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N4" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P4" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q4" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B5" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C5" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D5" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E5" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G5" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I5" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K5" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M5" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O5" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P5" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q5" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B6" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C6" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D6" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G6" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I6" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K6" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M6" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N6" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P6" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q6" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B7" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C7" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D7" t="n">
         <v>1438502</v>
@@ -82931,107 +83025,107 @@
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G7" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I7" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K7" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M7" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N7" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O7" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P7" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q7" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B8" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C8" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D8" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G8" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I8" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K8" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M8" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N8" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O8" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P8" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q8" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B9" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C9" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D9" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G9" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I9" t="n">
         <v>1488515</v>
       </c>
       <c r="K9" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M9" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -83040,7 +83134,7 @@
         <v>247857</v>
       </c>
       <c r="P9" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q9" t="n">
         <v>738429</v>
@@ -83048,34 +83142,34 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B10" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C10" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D10" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E10" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G10" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I10" t="n">
         <v>1488515</v>
       </c>
       <c r="K10" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M10" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -83084,7 +83178,7 @@
         <v>247857</v>
       </c>
       <c r="P10" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q10" t="n">
         <v>738429</v>
@@ -83092,78 +83186,78 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B11" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C11" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D11" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E11" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G11" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I11" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K11" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M11" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P11" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q11" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B12" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C12" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D12" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E12" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G12" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I12" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K12" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M12" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -83172,42 +83266,42 @@
         <v>264857</v>
       </c>
       <c r="P12" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q12" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B13" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C13" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D13" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E13" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G13" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I13" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K13" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M13" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -83216,101 +83310,98 @@
         <v>264857</v>
       </c>
       <c r="P13" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q13" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B14" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C14" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D14" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E14" t="n">
         <v>9300</v>
       </c>
       <c r="F14" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G14" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I14" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K14" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M14" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N14" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O14" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P14" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q14" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R14" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B15" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C15" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D15" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E15" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F15" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G15" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I15" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K15" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M15" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N15" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O15" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P15" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q15" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R15" t="n">
         <v>15000</v>
@@ -83318,40 +83409,40 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B16" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C16" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D16" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E16" t="n">
         <v>9100</v>
       </c>
       <c r="F16" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G16" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I16" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K16" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M16" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N16" t="n">
         <v>189475</v>
       </c>
       <c r="O16" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P16" t="n">
         <v>375660</v>
@@ -83360,6 +83451,53 @@
         <v>773586</v>
       </c>
       <c r="R16" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C17" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K17" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N17" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O17" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P17" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R17" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80403,9 +80403,36 @@
       <c r="A2447" s="4" t="n">
         <v>46276</v>
       </c>
+      <c r="B2447" t="n">
+        <v>3.287</v>
+      </c>
+      <c r="C2447" t="n">
+        <v>3.198</v>
+      </c>
+      <c r="D2447" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E2447" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="F2447" t="n">
+        <v>2.607</v>
+      </c>
+      <c r="G2447" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="H2447" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2447" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="K2447" t="n">
+        <v>12.171</v>
+      </c>
       <c r="L2447" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81021,7 +81048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81086,45 +81113,45 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C2" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E2" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F2" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G2" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K2" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C3" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D3" t="n">
         <v>1.44</v>
@@ -81133,7 +81160,7 @@
         <v>0.261</v>
       </c>
       <c r="F3" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G3" t="n">
         <v>0.435</v>
@@ -81142,222 +81169,222 @@
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K3" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B4" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C4" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D4" t="n">
         <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F4" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G4" t="n">
         <v>0.435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K4" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B5" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C5" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D5" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F5" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K5" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C6" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F6" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K6" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B7" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C7" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D7" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K7" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B8" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C8" t="n">
         <v>3.232</v>
       </c>
       <c r="D8" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F8" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G8" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K8" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C9" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D9" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G9" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H9" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K9" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B10" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C10" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D10" t="n">
         <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F10" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G10" t="n">
         <v>0.446</v>
@@ -81369,27 +81396,27 @@
         <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B11" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C11" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D11" t="n">
         <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F11" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G11" t="n">
         <v>0.446</v>
@@ -81401,59 +81428,59 @@
         <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B12" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C12" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D12" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F12" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G12" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H12" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I12" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C13" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D13" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E13" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F13" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G13" t="n">
         <v>0.462</v>
@@ -81462,30 +81489,30 @@
         <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K13" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B14" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C14" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E14" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F14" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G14" t="n">
         <v>0.462</v>
@@ -81494,100 +81521,97 @@
         <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K14" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B15" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C15" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F15" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G15" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H15" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K15" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C16" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D16" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F16" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G16" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H16" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I16" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J16" t="n">
         <v>0.014</v>
       </c>
       <c r="K16" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B17" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C17" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F17" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G17" t="n">
         <v>0.395</v>
@@ -81602,6 +81626,41 @@
         <v>0.014</v>
       </c>
       <c r="K17" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81616,7 +81675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81686,48 +81745,48 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C2" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E2" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F2" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G2" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K2" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L2" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C3" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D3" t="n">
         <v>1.44</v>
@@ -81736,7 +81795,7 @@
         <v>0.261</v>
       </c>
       <c r="F3" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G3" t="n">
         <v>0.435</v>
@@ -81745,243 +81804,243 @@
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K3" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L3" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B4" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C4" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D4" t="n">
         <v>1.44</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F4" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G4" t="n">
         <v>0.435</v>
       </c>
       <c r="H4" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K4" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L4" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B5" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C5" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D5" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F5" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H5" t="n">
         <v>0.365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K5" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L5" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C6" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D6" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F6" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G6" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K6" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L6" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B7" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C7" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D7" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E7" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G7" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K7" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L7" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B8" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C8" t="n">
         <v>3.232</v>
       </c>
       <c r="D8" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F8" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G8" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K8" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L8" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C9" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D9" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G9" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H9" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K9" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L9" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B10" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C10" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D10" t="n">
         <v>1.435</v>
       </c>
       <c r="E10" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F10" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G10" t="n">
         <v>0.446</v>
@@ -81993,30 +82052,30 @@
         <v>0.712</v>
       </c>
       <c r="K10" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L10" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B11" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C11" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D11" t="n">
         <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F11" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G11" t="n">
         <v>0.446</v>
@@ -82028,65 +82087,65 @@
         <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L11" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B12" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C12" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D12" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F12" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G12" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H12" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I12" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L12" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C13" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D13" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E13" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F13" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G13" t="n">
         <v>0.462</v>
@@ -82095,33 +82154,33 @@
         <v>0.343</v>
       </c>
       <c r="I13" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K13" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L13" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B14" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C14" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E14" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F14" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G14" t="n">
         <v>0.462</v>
@@ -82130,109 +82189,106 @@
         <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K14" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L14" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B15" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C15" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F15" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G15" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H15" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K15" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L15" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C16" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D16" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F16" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G16" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H16" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I16" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J16" t="n">
         <v>0.014</v>
       </c>
       <c r="K16" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L16" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B17" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C17" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D17" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F17" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G17" t="n">
         <v>0.395</v>
@@ -82247,9 +82303,47 @@
         <v>0.014</v>
       </c>
       <c r="K17" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L17" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.277</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82690,7 +82784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82790,69 +82884,69 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B2" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C2" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D2" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E2" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G2" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I2" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K2" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M2" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O2" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P2" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q2" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B3" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C3" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D3" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E3" t="n">
         <v>9400</v>
       </c>
       <c r="F3" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G3" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I3" t="n">
         <v>1493578</v>
@@ -82861,7 +82955,7 @@
         <v>270165</v>
       </c>
       <c r="M3" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -82873,39 +82967,39 @@
         <v>380581</v>
       </c>
       <c r="Q3" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B4" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C4" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D4" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E4" t="n">
         <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G4" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I4" t="n">
         <v>1493578</v>
       </c>
       <c r="K4" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M4" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -82914,153 +83008,153 @@
         <v>236857</v>
       </c>
       <c r="P4" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q4" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B5" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C5" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D5" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E5" t="n">
         <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G5" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I5" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K5" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M5" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N5" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P5" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q5" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B6" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C6" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D6" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E6" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G6" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I6" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K6" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M6" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N6" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O6" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P6" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q6" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B7" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C7" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D7" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G7" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I7" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K7" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M7" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N7" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P7" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q7" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B8" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C8" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D8" t="n">
         <v>1438502</v>
@@ -83069,107 +83163,107 @@
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G8" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I8" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K8" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M8" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N8" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O8" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P8" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q8" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B9" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C9" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D9" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G9" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I9" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K9" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M9" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N9" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O9" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P9" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q9" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B10" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C10" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D10" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G10" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I10" t="n">
         <v>1488515</v>
       </c>
       <c r="K10" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M10" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -83178,7 +83272,7 @@
         <v>247857</v>
       </c>
       <c r="P10" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q10" t="n">
         <v>738429</v>
@@ -83186,34 +83280,34 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B11" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C11" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D11" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E11" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G11" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I11" t="n">
         <v>1488515</v>
       </c>
       <c r="K11" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M11" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -83222,7 +83316,7 @@
         <v>247857</v>
       </c>
       <c r="P11" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q11" t="n">
         <v>738429</v>
@@ -83230,78 +83324,78 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B12" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C12" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D12" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E12" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G12" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I12" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K12" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M12" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P12" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q12" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B13" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C13" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D13" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E13" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G13" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I13" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K13" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M13" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -83310,42 +83404,42 @@
         <v>264857</v>
       </c>
       <c r="P13" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q13" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B14" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C14" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D14" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E14" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G14" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I14" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K14" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M14" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -83354,101 +83448,98 @@
         <v>264857</v>
       </c>
       <c r="P14" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q14" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B15" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C15" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D15" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E15" t="n">
         <v>9300</v>
       </c>
       <c r="F15" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G15" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I15" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K15" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M15" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N15" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O15" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P15" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q15" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R15" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B16" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C16" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D16" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E16" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F16" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G16" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I16" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K16" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M16" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N16" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O16" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P16" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q16" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R16" t="n">
         <v>15000</v>
@@ -83456,40 +83547,40 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B17" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C17" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D17" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E17" t="n">
         <v>9100</v>
       </c>
       <c r="F17" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G17" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I17" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K17" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M17" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N17" t="n">
         <v>189475</v>
       </c>
       <c r="O17" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P17" t="n">
         <v>375660</v>
@@ -83498,6 +83589,53 @@
         <v>773586</v>
       </c>
       <c r="R17" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C18" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K18" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N18" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O18" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P18" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R18" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80393,9 +80393,36 @@
       <c r="A2446" s="4" t="n">
         <v>46275</v>
       </c>
+      <c r="B2446" t="n">
+        <v>3.334</v>
+      </c>
+      <c r="C2446" t="n">
+        <v>3.234</v>
+      </c>
+      <c r="D2446" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="E2446" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F2446" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="G2446" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="H2446" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2446" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K2446" t="n">
+        <v>12.347</v>
+      </c>
       <c r="L2446" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81048,7 +81075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81113,77 +81140,77 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C2" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D2" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E2" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C3" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E3" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F3" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G3" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K3" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B4" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C4" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D4" t="n">
         <v>1.44</v>
@@ -81192,7 +81219,7 @@
         <v>0.261</v>
       </c>
       <c r="F4" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G4" t="n">
         <v>0.435</v>
@@ -81201,222 +81228,222 @@
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K4" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B5" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C5" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D5" t="n">
         <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F5" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G5" t="n">
         <v>0.435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K5" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B6" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C6" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D6" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F6" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K6" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B7" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C7" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D7" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F7" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K7" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B8" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C8" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D8" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G8" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K8" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B9" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C9" t="n">
         <v>3.232</v>
       </c>
       <c r="D9" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F9" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G9" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K9" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C10" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D10" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E10" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G10" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H10" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K10" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B11" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C11" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D11" t="n">
         <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F11" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G11" t="n">
         <v>0.446</v>
@@ -81428,27 +81455,27 @@
         <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B12" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C12" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D12" t="n">
         <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F12" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G12" t="n">
         <v>0.446</v>
@@ -81460,59 +81487,59 @@
         <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C13" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D13" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F13" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G13" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H13" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I13" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C14" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D14" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E14" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F14" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G14" t="n">
         <v>0.462</v>
@@ -81521,30 +81548,30 @@
         <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K14" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C15" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E15" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F15" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G15" t="n">
         <v>0.462</v>
@@ -81553,100 +81580,97 @@
         <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K15" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B16" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C16" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D16" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F16" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G16" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K16" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C17" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D17" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E17" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F17" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G17" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H17" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I17" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J17" t="n">
         <v>0.014</v>
       </c>
       <c r="K17" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B18" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C18" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D18" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F18" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G18" t="n">
         <v>0.395</v>
@@ -81661,6 +81685,41 @@
         <v>0.014</v>
       </c>
       <c r="K18" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81675,7 +81734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81745,83 +81804,83 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C2" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D2" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E2" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G2" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L2" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C3" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E3" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F3" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G3" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K3" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L3" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B4" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C4" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D4" t="n">
         <v>1.44</v>
@@ -81830,7 +81889,7 @@
         <v>0.261</v>
       </c>
       <c r="F4" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G4" t="n">
         <v>0.435</v>
@@ -81839,243 +81898,243 @@
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K4" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L4" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B5" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C5" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D5" t="n">
         <v>1.44</v>
       </c>
       <c r="E5" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F5" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G5" t="n">
         <v>0.435</v>
       </c>
       <c r="H5" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K5" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L5" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B6" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C6" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D6" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F6" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H6" t="n">
         <v>0.365</v>
       </c>
       <c r="I6" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K6" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L6" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B7" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C7" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D7" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F7" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G7" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K7" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L7" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B8" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C8" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D8" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G8" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K8" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L8" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B9" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C9" t="n">
         <v>3.232</v>
       </c>
       <c r="D9" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F9" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G9" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H9" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K9" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L9" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C10" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D10" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E10" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G10" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H10" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I10" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K10" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L10" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B11" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C11" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D11" t="n">
         <v>1.435</v>
       </c>
       <c r="E11" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F11" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G11" t="n">
         <v>0.446</v>
@@ -82087,30 +82146,30 @@
         <v>0.712</v>
       </c>
       <c r="K11" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L11" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B12" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C12" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D12" t="n">
         <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F12" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G12" t="n">
         <v>0.446</v>
@@ -82122,65 +82181,65 @@
         <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L12" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C13" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D13" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F13" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G13" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H13" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I13" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L13" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C14" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D14" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E14" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F14" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G14" t="n">
         <v>0.462</v>
@@ -82189,33 +82248,33 @@
         <v>0.343</v>
       </c>
       <c r="I14" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K14" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L14" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C15" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E15" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F15" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G15" t="n">
         <v>0.462</v>
@@ -82224,109 +82283,106 @@
         <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K15" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L15" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B16" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C16" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D16" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F16" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G16" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H16" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K16" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L16" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C17" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D17" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E17" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F17" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G17" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H17" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I17" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J17" t="n">
         <v>0.014</v>
       </c>
       <c r="K17" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L17" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B18" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C18" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D18" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F18" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G18" t="n">
         <v>0.395</v>
@@ -82341,9 +82397,47 @@
         <v>0.014</v>
       </c>
       <c r="K18" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L18" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.277</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L19" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82784,7 +82878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82884,113 +82978,113 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B2" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C2" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D2" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G2" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I2" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K2" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M2" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N2" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P2" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q2" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B3" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C3" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D3" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E3" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G3" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I3" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K3" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M3" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O3" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P3" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q3" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B4" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C4" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D4" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E4" t="n">
         <v>9400</v>
       </c>
       <c r="F4" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G4" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I4" t="n">
         <v>1493578</v>
@@ -82999,7 +83093,7 @@
         <v>270165</v>
       </c>
       <c r="M4" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -83011,39 +83105,39 @@
         <v>380581</v>
       </c>
       <c r="Q4" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B5" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C5" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D5" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E5" t="n">
         <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G5" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I5" t="n">
         <v>1493578</v>
       </c>
       <c r="K5" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M5" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -83052,153 +83146,153 @@
         <v>236857</v>
       </c>
       <c r="P5" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q5" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B6" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C6" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D6" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E6" t="n">
         <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G6" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I6" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K6" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M6" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N6" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P6" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q6" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B7" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C7" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D7" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E7" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G7" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I7" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K7" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M7" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N7" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O7" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P7" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q7" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B8" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C8" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D8" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G8" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I8" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K8" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M8" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N8" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P8" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q8" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B9" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C9" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D9" t="n">
         <v>1438502</v>
@@ -83207,107 +83301,107 @@
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G9" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I9" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K9" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M9" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N9" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O9" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P9" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q9" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B10" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C10" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D10" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G10" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I10" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K10" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M10" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N10" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O10" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P10" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q10" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B11" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C11" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D11" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G11" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I11" t="n">
         <v>1488515</v>
       </c>
       <c r="K11" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M11" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -83316,7 +83410,7 @@
         <v>247857</v>
       </c>
       <c r="P11" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q11" t="n">
         <v>738429</v>
@@ -83324,34 +83418,34 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B12" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C12" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D12" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E12" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G12" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I12" t="n">
         <v>1488515</v>
       </c>
       <c r="K12" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M12" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -83360,7 +83454,7 @@
         <v>247857</v>
       </c>
       <c r="P12" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q12" t="n">
         <v>738429</v>
@@ -83368,78 +83462,78 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B13" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C13" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D13" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E13" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G13" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I13" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K13" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M13" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
       </c>
       <c r="O13" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P13" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q13" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B14" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C14" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D14" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E14" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G14" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I14" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K14" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M14" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -83448,42 +83542,42 @@
         <v>264857</v>
       </c>
       <c r="P14" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q14" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B15" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C15" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D15" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E15" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G15" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I15" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K15" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M15" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -83492,101 +83586,98 @@
         <v>264857</v>
       </c>
       <c r="P15" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q15" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B16" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C16" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D16" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E16" t="n">
         <v>9300</v>
       </c>
       <c r="F16" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G16" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I16" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K16" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M16" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N16" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O16" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P16" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q16" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R16" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B17" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C17" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D17" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E17" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F17" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G17" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I17" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K17" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M17" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N17" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O17" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P17" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q17" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R17" t="n">
         <v>15000</v>
@@ -83594,40 +83685,40 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B18" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C18" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D18" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E18" t="n">
         <v>9100</v>
       </c>
       <c r="F18" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G18" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I18" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K18" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M18" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N18" t="n">
         <v>189475</v>
       </c>
       <c r="O18" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P18" t="n">
         <v>375660</v>
@@ -83636,6 +83727,53 @@
         <v>773586</v>
       </c>
       <c r="R18" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C19" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E19" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K19" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N19" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O19" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P19" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R19" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80383,9 +80383,36 @@
       <c r="A2445" s="4" t="n">
         <v>46274</v>
       </c>
+      <c r="B2445" t="n">
+        <v>3.215</v>
+      </c>
+      <c r="C2445" t="n">
+        <v>3.214</v>
+      </c>
+      <c r="D2445" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="E2445" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="F2445" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="G2445" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="H2445" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2445" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="K2445" t="n">
+        <v>12.126</v>
+      </c>
       <c r="L2445" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81075,7 +81102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81140,109 +81167,109 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C2" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D2" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F2" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K2" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C3" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D3" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C4" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E4" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F4" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K4" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B5" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C5" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D5" t="n">
         <v>1.44</v>
@@ -81251,7 +81278,7 @@
         <v>0.261</v>
       </c>
       <c r="F5" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G5" t="n">
         <v>0.435</v>
@@ -81260,222 +81287,222 @@
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K5" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C6" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D6" t="n">
         <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G6" t="n">
         <v>0.435</v>
       </c>
       <c r="H6" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K6" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C7" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D7" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F7" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K7" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C8" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F8" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G8" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K8" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B9" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C9" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D9" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E9" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K9" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B10" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C10" t="n">
         <v>3.232</v>
       </c>
       <c r="D10" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F10" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H10" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K10" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C11" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D11" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E11" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G11" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H11" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K11" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B12" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C12" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D12" t="n">
         <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F12" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G12" t="n">
         <v>0.446</v>
@@ -81487,27 +81514,27 @@
         <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B13" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C13" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D13" t="n">
         <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F13" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G13" t="n">
         <v>0.446</v>
@@ -81519,59 +81546,59 @@
         <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B14" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C14" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D14" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F14" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H14" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C15" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D15" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F15" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G15" t="n">
         <v>0.462</v>
@@ -81580,30 +81607,30 @@
         <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K15" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C16" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D16" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E16" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F16" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G16" t="n">
         <v>0.462</v>
@@ -81612,100 +81639,97 @@
         <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K16" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B17" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C17" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D17" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F17" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G17" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H17" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K17" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B18" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C18" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D18" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E18" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F18" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G18" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H18" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J18" t="n">
         <v>0.014</v>
       </c>
       <c r="K18" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B19" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C19" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D19" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F19" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G19" t="n">
         <v>0.395</v>
@@ -81720,6 +81744,41 @@
         <v>0.014</v>
       </c>
       <c r="K19" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81734,7 +81793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81804,118 +81863,118 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B2" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C2" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D2" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F2" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K2" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L2" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C3" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D3" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E3" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G3" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L3" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C4" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E4" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F4" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G4" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K4" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L4" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B5" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C5" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D5" t="n">
         <v>1.44</v>
@@ -81924,7 +81983,7 @@
         <v>0.261</v>
       </c>
       <c r="F5" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G5" t="n">
         <v>0.435</v>
@@ -81933,243 +81992,243 @@
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K5" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L5" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B6" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C6" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D6" t="n">
         <v>1.44</v>
       </c>
       <c r="E6" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G6" t="n">
         <v>0.435</v>
       </c>
       <c r="H6" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K6" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L6" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C7" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D7" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F7" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H7" t="n">
         <v>0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K7" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L7" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C8" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F8" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G8" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K8" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L8" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B9" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C9" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D9" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E9" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K9" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L9" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B10" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C10" t="n">
         <v>3.232</v>
       </c>
       <c r="D10" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F10" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H10" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K10" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L10" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C11" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D11" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E11" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G11" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H11" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I11" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K11" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L11" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B12" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C12" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D12" t="n">
         <v>1.435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F12" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G12" t="n">
         <v>0.446</v>
@@ -82181,30 +82240,30 @@
         <v>0.712</v>
       </c>
       <c r="K12" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L12" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B13" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C13" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D13" t="n">
         <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F13" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G13" t="n">
         <v>0.446</v>
@@ -82216,65 +82275,65 @@
         <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L13" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B14" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C14" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D14" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F14" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G14" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H14" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I14" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L14" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C15" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D15" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E15" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F15" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G15" t="n">
         <v>0.462</v>
@@ -82283,33 +82342,33 @@
         <v>0.343</v>
       </c>
       <c r="I15" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K15" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L15" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C16" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D16" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E16" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F16" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G16" t="n">
         <v>0.462</v>
@@ -82318,109 +82377,106 @@
         <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K16" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L16" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B17" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C17" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D17" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F17" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G17" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H17" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K17" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L17" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B18" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C18" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D18" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E18" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F18" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G18" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H18" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I18" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J18" t="n">
         <v>0.014</v>
       </c>
       <c r="K18" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L18" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B19" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C19" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D19" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F19" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G19" t="n">
         <v>0.395</v>
@@ -82435,9 +82491,47 @@
         <v>0.014</v>
       </c>
       <c r="K19" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.277</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82878,7 +82972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82978,157 +83072,157 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B2" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C2" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D2" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G2" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I2" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K2" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M2" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O2" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P2" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q2" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B3" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C3" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D3" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G3" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I3" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K3" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M3" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N3" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P3" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q3" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B4" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C4" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D4" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E4" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G4" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I4" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K4" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M4" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O4" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P4" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q4" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B5" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C5" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D5" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E5" t="n">
         <v>9400</v>
       </c>
       <c r="F5" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G5" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I5" t="n">
         <v>1493578</v>
@@ -83137,7 +83231,7 @@
         <v>270165</v>
       </c>
       <c r="M5" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -83149,39 +83243,39 @@
         <v>380581</v>
       </c>
       <c r="Q5" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B6" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C6" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D6" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E6" t="n">
         <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G6" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I6" t="n">
         <v>1493578</v>
       </c>
       <c r="K6" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M6" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -83190,153 +83284,153 @@
         <v>236857</v>
       </c>
       <c r="P6" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q6" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B7" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C7" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D7" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E7" t="n">
         <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G7" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I7" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K7" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M7" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N7" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P7" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q7" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B8" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C8" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D8" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E8" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G8" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I8" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K8" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M8" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N8" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O8" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P8" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q8" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B9" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C9" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D9" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G9" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I9" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K9" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M9" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N9" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P9" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q9" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B10" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C10" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D10" t="n">
         <v>1438502</v>
@@ -83345,107 +83439,107 @@
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G10" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I10" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K10" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M10" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N10" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O10" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P10" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q10" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B11" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C11" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D11" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G11" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I11" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K11" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M11" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N11" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O11" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P11" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q11" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B12" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C12" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D12" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G12" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I12" t="n">
         <v>1488515</v>
       </c>
       <c r="K12" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M12" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -83454,7 +83548,7 @@
         <v>247857</v>
       </c>
       <c r="P12" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q12" t="n">
         <v>738429</v>
@@ -83462,34 +83556,34 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B13" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C13" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D13" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E13" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G13" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I13" t="n">
         <v>1488515</v>
       </c>
       <c r="K13" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M13" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -83498,7 +83592,7 @@
         <v>247857</v>
       </c>
       <c r="P13" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q13" t="n">
         <v>738429</v>
@@ -83506,78 +83600,78 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B14" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C14" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D14" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E14" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G14" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I14" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K14" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M14" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
       </c>
       <c r="O14" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P14" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q14" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B15" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C15" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D15" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E15" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G15" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I15" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K15" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M15" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -83586,42 +83680,42 @@
         <v>264857</v>
       </c>
       <c r="P15" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q15" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B16" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C16" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D16" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E16" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G16" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I16" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K16" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M16" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -83630,101 +83724,98 @@
         <v>264857</v>
       </c>
       <c r="P16" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q16" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B17" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C17" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D17" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E17" t="n">
         <v>9300</v>
       </c>
       <c r="F17" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G17" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I17" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K17" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M17" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N17" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O17" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P17" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q17" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R17" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B18" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C18" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D18" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E18" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F18" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G18" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I18" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K18" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M18" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N18" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O18" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P18" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q18" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R18" t="n">
         <v>15000</v>
@@ -83732,40 +83823,40 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B19" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C19" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D19" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E19" t="n">
         <v>9100</v>
       </c>
       <c r="F19" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G19" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I19" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K19" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M19" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N19" t="n">
         <v>189475</v>
       </c>
       <c r="O19" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P19" t="n">
         <v>375660</v>
@@ -83774,6 +83865,53 @@
         <v>773586</v>
       </c>
       <c r="R19" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C20" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K20" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N20" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O20" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P20" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R20" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80373,9 +80373,36 @@
       <c r="A2444" s="4" t="n">
         <v>46273</v>
       </c>
+      <c r="B2444" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="C2444" t="n">
+        <v>3.213</v>
+      </c>
+      <c r="D2444" t="n">
+        <v>1.275</v>
+      </c>
+      <c r="E2444" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="F2444" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G2444" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="H2444" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="I2444" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K2444" t="n">
+        <v>11.961</v>
+      </c>
       <c r="L2444" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81102,7 +81129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81167,141 +81194,141 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B2" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C2" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D2" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I2" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B3" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C3" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D3" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F3" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K3" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C4" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D4" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E4" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C5" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E5" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F5" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G5" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K5" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C6" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D6" t="n">
         <v>1.44</v>
@@ -81310,7 +81337,7 @@
         <v>0.261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G6" t="n">
         <v>0.435</v>
@@ -81319,222 +81346,222 @@
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K6" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B7" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C7" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F7" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G7" t="n">
         <v>0.435</v>
       </c>
       <c r="H7" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K7" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B8" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C8" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D8" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K8" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C9" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D9" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F9" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G9" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K9" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B10" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C10" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D10" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G10" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K10" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B11" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C11" t="n">
         <v>3.232</v>
       </c>
       <c r="D11" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F11" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G11" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K11" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C12" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D12" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G12" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H12" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K12" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B13" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C13" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D13" t="n">
         <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F13" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G13" t="n">
         <v>0.446</v>
@@ -81546,27 +81573,27 @@
         <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B14" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C14" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D14" t="n">
         <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F14" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
@@ -81578,59 +81605,59 @@
         <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B15" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C15" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D15" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F15" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G15" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I15" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B16" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C16" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D16" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E16" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F16" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G16" t="n">
         <v>0.462</v>
@@ -81639,30 +81666,30 @@
         <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K16" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C17" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D17" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E17" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F17" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G17" t="n">
         <v>0.462</v>
@@ -81671,100 +81698,97 @@
         <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K17" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B18" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C18" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D18" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F18" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G18" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K18" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B19" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C19" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D19" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F19" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G19" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I19" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J19" t="n">
         <v>0.014</v>
       </c>
       <c r="K19" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B20" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C20" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D20" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F20" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G20" t="n">
         <v>0.395</v>
@@ -81779,6 +81803,41 @@
         <v>0.014</v>
       </c>
       <c r="K20" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81793,7 +81852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81863,153 +81922,153 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B2" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C2" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D2" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E2" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I2" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L2" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B3" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C3" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D3" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F3" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K3" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L3" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C4" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D4" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E4" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G4" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L4" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C5" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E5" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F5" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G5" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K5" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L5" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C6" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D6" t="n">
         <v>1.44</v>
@@ -82018,7 +82077,7 @@
         <v>0.261</v>
       </c>
       <c r="F6" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G6" t="n">
         <v>0.435</v>
@@ -82027,243 +82086,243 @@
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K6" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L6" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B7" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C7" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
       </c>
       <c r="E7" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F7" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G7" t="n">
         <v>0.435</v>
       </c>
       <c r="H7" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K7" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L7" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B8" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C8" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D8" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H8" t="n">
         <v>0.365</v>
       </c>
       <c r="I8" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K8" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L8" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C9" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D9" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F9" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G9" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K9" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L9" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B10" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C10" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D10" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E10" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G10" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K10" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L10" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B11" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C11" t="n">
         <v>3.232</v>
       </c>
       <c r="D11" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F11" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G11" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H11" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K11" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L11" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C12" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D12" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G12" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H12" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I12" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K12" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L12" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B13" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C13" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D13" t="n">
         <v>1.435</v>
       </c>
       <c r="E13" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F13" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G13" t="n">
         <v>0.446</v>
@@ -82275,30 +82334,30 @@
         <v>0.712</v>
       </c>
       <c r="K13" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L13" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B14" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C14" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D14" t="n">
         <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F14" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
@@ -82310,65 +82369,65 @@
         <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L14" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B15" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C15" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D15" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F15" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G15" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H15" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I15" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L15" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B16" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C16" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D16" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E16" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F16" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G16" t="n">
         <v>0.462</v>
@@ -82377,33 +82436,33 @@
         <v>0.343</v>
       </c>
       <c r="I16" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K16" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L16" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C17" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D17" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E17" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F17" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G17" t="n">
         <v>0.462</v>
@@ -82412,109 +82471,106 @@
         <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K17" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L17" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B18" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C18" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D18" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F18" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G18" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H18" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K18" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L18" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B19" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C19" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D19" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F19" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G19" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I19" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J19" t="n">
         <v>0.014</v>
       </c>
       <c r="K19" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L19" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B20" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C20" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D20" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F20" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G20" t="n">
         <v>0.395</v>
@@ -82529,9 +82585,47 @@
         <v>0.014</v>
       </c>
       <c r="K20" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L20" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.277</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -82972,7 +83066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83072,201 +83166,201 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B2" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C2" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D2" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G2" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I2" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K2" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M2" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N2" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O2" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P2" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q2" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B3" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C3" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D3" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G3" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I3" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K3" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M3" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O3" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P3" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q3" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B4" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C4" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D4" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G4" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I4" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K4" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M4" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N4" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P4" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q4" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B5" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C5" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D5" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E5" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G5" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I5" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K5" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M5" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O5" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P5" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q5" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B6" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C6" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D6" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E6" t="n">
         <v>9400</v>
       </c>
       <c r="F6" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G6" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I6" t="n">
         <v>1493578</v>
@@ -83275,7 +83369,7 @@
         <v>270165</v>
       </c>
       <c r="M6" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -83287,39 +83381,39 @@
         <v>380581</v>
       </c>
       <c r="Q6" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B7" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C7" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D7" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E7" t="n">
         <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G7" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I7" t="n">
         <v>1493578</v>
       </c>
       <c r="K7" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M7" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -83328,153 +83422,153 @@
         <v>236857</v>
       </c>
       <c r="P7" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q7" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B8" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C8" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D8" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E8" t="n">
         <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G8" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I8" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K8" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M8" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N8" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P8" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q8" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B9" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C9" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D9" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E9" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G9" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I9" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K9" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M9" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N9" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O9" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P9" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q9" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B10" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C10" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D10" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G10" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I10" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K10" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M10" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N10" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P10" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q10" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B11" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C11" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D11" t="n">
         <v>1438502</v>
@@ -83483,107 +83577,107 @@
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G11" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I11" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K11" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M11" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N11" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O11" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P11" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q11" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B12" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C12" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D12" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G12" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I12" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K12" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M12" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N12" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O12" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P12" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q12" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B13" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C13" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D13" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G13" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I13" t="n">
         <v>1488515</v>
       </c>
       <c r="K13" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M13" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -83592,7 +83686,7 @@
         <v>247857</v>
       </c>
       <c r="P13" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q13" t="n">
         <v>738429</v>
@@ -83600,34 +83694,34 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B14" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C14" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D14" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E14" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G14" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I14" t="n">
         <v>1488515</v>
       </c>
       <c r="K14" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M14" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -83636,7 +83730,7 @@
         <v>247857</v>
       </c>
       <c r="P14" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q14" t="n">
         <v>738429</v>
@@ -83644,78 +83738,78 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B15" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C15" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D15" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E15" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G15" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I15" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K15" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M15" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
       </c>
       <c r="O15" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P15" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q15" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B16" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C16" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D16" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E16" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G16" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I16" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K16" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M16" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -83724,42 +83818,42 @@
         <v>264857</v>
       </c>
       <c r="P16" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q16" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B17" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C17" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D17" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E17" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G17" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I17" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K17" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M17" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -83768,101 +83862,98 @@
         <v>264857</v>
       </c>
       <c r="P17" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q17" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B18" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C18" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D18" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E18" t="n">
         <v>9300</v>
       </c>
       <c r="F18" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G18" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I18" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K18" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M18" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N18" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O18" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P18" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q18" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R18" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B19" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C19" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D19" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E19" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F19" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G19" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I19" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K19" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M19" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N19" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O19" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P19" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q19" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R19" t="n">
         <v>15000</v>
@@ -83870,40 +83961,40 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B20" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C20" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D20" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E20" t="n">
         <v>9100</v>
       </c>
       <c r="F20" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G20" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I20" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K20" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M20" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N20" t="n">
         <v>189475</v>
       </c>
       <c r="O20" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P20" t="n">
         <v>375660</v>
@@ -83912,6 +84003,53 @@
         <v>773586</v>
       </c>
       <c r="R20" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C21" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K21" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N21" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O21" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P21" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R21" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -83979,7 +84117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E650"/>
+  <dimension ref="A1:E658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91229,8 +91367,93 @@
         <v>4.436</v>
       </c>
     </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Calcasieu Pass</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>0.408</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>1.383</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>2.494</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Elba Island</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Freeport</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>0.413</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Golden Pass</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>0.701</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Plaquemines</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>3.234</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Sabine Pass</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>3.264</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="106">
+  <mergeCells count="107">
     <mergeCell ref="A544:A551"/>
     <mergeCell ref="A584:A591"/>
     <mergeCell ref="A88:A91"/>
@@ -91283,6 +91506,7 @@
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="A82:A84"/>
     <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A651:A658"/>
     <mergeCell ref="A616:A623"/>
     <mergeCell ref="A426:A432"/>
     <mergeCell ref="A184:A189"/>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80363,9 +80363,36 @@
       <c r="A2443" s="4" t="n">
         <v>46272</v>
       </c>
+      <c r="B2443" t="n">
+        <v>3.227</v>
+      </c>
+      <c r="C2443" t="n">
+        <v>3.139</v>
+      </c>
+      <c r="D2443" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E2443" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="F2443" t="n">
+        <v>2.554</v>
+      </c>
+      <c r="G2443" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="H2443" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2443" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K2443" t="n">
+        <v>11.936</v>
+      </c>
       <c r="L2443" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81129,7 +81156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81194,173 +81221,173 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B2" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C2" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D2" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I2" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B3" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C3" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D3" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F3" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C4" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D4" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F4" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K4" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C5" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D5" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C6" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E6" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F6" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K6" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C7" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -81369,7 +81396,7 @@
         <v>0.261</v>
       </c>
       <c r="F7" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G7" t="n">
         <v>0.435</v>
@@ -81378,222 +81405,222 @@
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K7" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B8" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C8" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D8" t="n">
         <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F8" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G8" t="n">
         <v>0.435</v>
       </c>
       <c r="H8" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K8" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C9" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D9" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F9" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K9" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C10" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D10" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F10" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G10" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K10" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C11" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D11" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E11" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G11" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K11" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B12" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C12" t="n">
         <v>3.232</v>
       </c>
       <c r="D12" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F12" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G12" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H12" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K12" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C13" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D13" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E13" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G13" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H13" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K13" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B14" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C14" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D14" t="n">
         <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F14" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
@@ -81605,27 +81632,27 @@
         <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B15" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C15" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D15" t="n">
         <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F15" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G15" t="n">
         <v>0.446</v>
@@ -81637,59 +81664,59 @@
         <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B16" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C16" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D16" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F16" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G16" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H16" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B17" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C17" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D17" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E17" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F17" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G17" t="n">
         <v>0.462</v>
@@ -81698,30 +81725,30 @@
         <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K17" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C18" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D18" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E18" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F18" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G18" t="n">
         <v>0.462</v>
@@ -81730,100 +81757,97 @@
         <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K18" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B19" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C19" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D19" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F19" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G19" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H19" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K19" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C20" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D20" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E20" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F20" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G20" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H20" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I20" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J20" t="n">
         <v>0.014</v>
       </c>
       <c r="K20" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B21" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C21" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D21" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F21" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G21" t="n">
         <v>0.395</v>
@@ -81838,6 +81862,41 @@
         <v>0.014</v>
       </c>
       <c r="K21" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81852,7 +81911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81922,188 +81981,188 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B2" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C2" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D2" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E2" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
       </c>
       <c r="H2" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I2" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L2" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B3" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C3" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D3" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E3" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F3" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I3" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L3" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C4" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D4" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F4" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G4" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K4" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L4" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C5" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D5" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E5" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L5" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C6" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E6" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F6" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K6" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L6" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C7" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D7" t="n">
         <v>1.44</v>
@@ -82112,7 +82171,7 @@
         <v>0.261</v>
       </c>
       <c r="F7" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G7" t="n">
         <v>0.435</v>
@@ -82121,243 +82180,243 @@
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K7" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L7" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B8" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C8" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D8" t="n">
         <v>1.44</v>
       </c>
       <c r="E8" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F8" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G8" t="n">
         <v>0.435</v>
       </c>
       <c r="H8" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K8" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L8" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C9" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D9" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F9" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H9" t="n">
         <v>0.365</v>
       </c>
       <c r="I9" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K9" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L9" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C10" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D10" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F10" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G10" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K10" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L10" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C11" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D11" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E11" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G11" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K11" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L11" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B12" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C12" t="n">
         <v>3.232</v>
       </c>
       <c r="D12" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F12" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G12" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H12" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K12" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L12" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C13" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D13" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E13" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G13" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H13" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K13" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L13" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B14" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C14" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D14" t="n">
         <v>1.435</v>
       </c>
       <c r="E14" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F14" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
@@ -82369,30 +82428,30 @@
         <v>0.712</v>
       </c>
       <c r="K14" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L14" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B15" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C15" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D15" t="n">
         <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F15" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G15" t="n">
         <v>0.446</v>
@@ -82404,65 +82463,65 @@
         <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L15" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B16" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C16" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D16" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F16" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G16" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H16" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L16" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B17" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C17" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D17" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E17" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F17" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G17" t="n">
         <v>0.462</v>
@@ -82471,33 +82530,33 @@
         <v>0.343</v>
       </c>
       <c r="I17" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K17" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L17" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C18" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D18" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E18" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F18" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G18" t="n">
         <v>0.462</v>
@@ -82506,109 +82565,106 @@
         <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K18" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L18" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B19" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C19" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D19" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F19" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G19" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H19" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K19" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L19" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C20" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D20" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E20" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F20" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G20" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H20" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I20" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J20" t="n">
         <v>0.014</v>
       </c>
       <c r="K20" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L20" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B21" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C21" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D21" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F21" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G21" t="n">
         <v>0.395</v>
@@ -82623,9 +82679,47 @@
         <v>0.014</v>
       </c>
       <c r="K21" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.277</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83066,7 +83160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83166,43 +83260,43 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B2" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C2" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D2" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G2" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I2" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K2" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M2" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N2" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P2" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q2" t="n">
         <v>710782</v>
@@ -83210,201 +83304,201 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B3" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C3" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D3" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G3" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I3" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K3" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M3" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N3" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O3" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P3" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q3" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B4" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C4" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D4" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G4" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I4" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K4" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M4" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O4" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P4" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q4" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B5" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C5" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D5" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G5" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I5" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K5" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M5" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N5" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P5" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q5" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B6" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C6" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D6" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E6" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G6" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I6" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K6" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M6" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N6" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O6" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P6" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q6" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B7" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C7" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D7" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E7" t="n">
         <v>9400</v>
       </c>
       <c r="F7" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G7" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I7" t="n">
         <v>1493578</v>
@@ -83413,7 +83507,7 @@
         <v>270165</v>
       </c>
       <c r="M7" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -83425,39 +83519,39 @@
         <v>380581</v>
       </c>
       <c r="Q7" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B8" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C8" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D8" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E8" t="n">
         <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G8" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I8" t="n">
         <v>1493578</v>
       </c>
       <c r="K8" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M8" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -83466,153 +83560,153 @@
         <v>236857</v>
       </c>
       <c r="P8" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q8" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B9" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C9" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D9" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E9" t="n">
         <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G9" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I9" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K9" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M9" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N9" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P9" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q9" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B10" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C10" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D10" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E10" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G10" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I10" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K10" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M10" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N10" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O10" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P10" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q10" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B11" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C11" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D11" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G11" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I11" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K11" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M11" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N11" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P11" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q11" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B12" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C12" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D12" t="n">
         <v>1438502</v>
@@ -83621,107 +83715,107 @@
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G12" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I12" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K12" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M12" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N12" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O12" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P12" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q12" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B13" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C13" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D13" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G13" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I13" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K13" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M13" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N13" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O13" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P13" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q13" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B14" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C14" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D14" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E14" t="n">
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G14" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I14" t="n">
         <v>1488515</v>
       </c>
       <c r="K14" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M14" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -83730,7 +83824,7 @@
         <v>247857</v>
       </c>
       <c r="P14" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q14" t="n">
         <v>738429</v>
@@ -83738,34 +83832,34 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B15" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C15" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D15" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E15" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G15" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I15" t="n">
         <v>1488515</v>
       </c>
       <c r="K15" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M15" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -83774,7 +83868,7 @@
         <v>247857</v>
       </c>
       <c r="P15" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q15" t="n">
         <v>738429</v>
@@ -83782,78 +83876,78 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B16" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C16" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D16" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E16" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G16" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I16" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K16" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M16" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
       </c>
       <c r="O16" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P16" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q16" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B17" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C17" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D17" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E17" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G17" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I17" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K17" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M17" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -83862,42 +83956,42 @@
         <v>264857</v>
       </c>
       <c r="P17" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q17" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B18" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C18" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D18" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E18" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F18" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G18" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I18" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K18" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M18" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
@@ -83906,101 +84000,98 @@
         <v>264857</v>
       </c>
       <c r="P18" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q18" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B19" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C19" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D19" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E19" t="n">
         <v>9300</v>
       </c>
       <c r="F19" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G19" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I19" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K19" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M19" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N19" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O19" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P19" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q19" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R19" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B20" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C20" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D20" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E20" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F20" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G20" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I20" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K20" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M20" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N20" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O20" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P20" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q20" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R20" t="n">
         <v>15000</v>
@@ -84008,40 +84099,40 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B21" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C21" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D21" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E21" t="n">
         <v>9100</v>
       </c>
       <c r="F21" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G21" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I21" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K21" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M21" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N21" t="n">
         <v>189475</v>
       </c>
       <c r="O21" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P21" t="n">
         <v>375660</v>
@@ -84050,6 +84141,53 @@
         <v>773586</v>
       </c>
       <c r="R21" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C22" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K22" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N22" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O22" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P22" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R22" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -91379,7 +91517,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.408</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="652">
@@ -91389,7 +91527,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.383</v>
+        <v>1.376</v>
       </c>
     </row>
     <row r="653">
@@ -91399,7 +91537,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.494</v>
+        <v>2.497</v>
       </c>
     </row>
     <row r="654">
@@ -91419,7 +91557,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.413</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="656">
@@ -91429,7 +91567,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.701</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="657">
@@ -91439,7 +91577,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3.234</v>
+        <v>3.229</v>
       </c>
     </row>
     <row r="658">
@@ -91449,7 +91587,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.264</v>
+        <v>3.263</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80353,9 +80353,36 @@
       <c r="A2442" s="4" t="n">
         <v>46271</v>
       </c>
+      <c r="B2442" t="n">
+        <v>3.177</v>
+      </c>
+      <c r="C2442" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="D2442" t="n">
+        <v>1.485</v>
+      </c>
+      <c r="E2442" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="F2442" t="n">
+        <v>2.586</v>
+      </c>
+      <c r="G2442" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="H2442" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2442" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K2442" t="n">
+        <v>11.931</v>
+      </c>
       <c r="L2442" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81156,7 +81183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81221,22 +81248,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C2" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D2" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E2" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
@@ -81248,178 +81275,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B3" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C3" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D3" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I3" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C4" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D4" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C5" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D5" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F5" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G5" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K5" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B6" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C6" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D6" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E6" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C7" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E7" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K7" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B8" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C8" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D8" t="n">
         <v>1.44</v>
@@ -81428,7 +81455,7 @@
         <v>0.261</v>
       </c>
       <c r="F8" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G8" t="n">
         <v>0.435</v>
@@ -81437,222 +81464,222 @@
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K8" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B9" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C9" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D9" t="n">
         <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F9" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G9" t="n">
         <v>0.435</v>
       </c>
       <c r="H9" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K9" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B10" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C10" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D10" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F10" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K10" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C11" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D11" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F11" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G11" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K11" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B12" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C12" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D12" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E12" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G12" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K12" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B13" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C13" t="n">
         <v>3.232</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F13" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G13" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H13" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K13" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C14" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D14" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H14" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K14" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B15" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C15" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D15" t="n">
         <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F15" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G15" t="n">
         <v>0.446</v>
@@ -81664,27 +81691,27 @@
         <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B16" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C16" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D16" t="n">
         <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F16" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G16" t="n">
         <v>0.446</v>
@@ -81696,59 +81723,59 @@
         <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B17" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C17" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D17" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F17" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G17" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H17" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I17" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B18" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C18" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D18" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E18" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F18" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G18" t="n">
         <v>0.462</v>
@@ -81757,30 +81784,30 @@
         <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K18" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C19" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D19" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E19" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F19" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G19" t="n">
         <v>0.462</v>
@@ -81789,100 +81816,97 @@
         <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K19" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B20" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C20" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D20" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E20" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F20" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G20" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H20" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K20" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B21" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C21" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D21" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E21" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F21" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G21" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H21" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I21" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J21" t="n">
         <v>0.014</v>
       </c>
       <c r="K21" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B22" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C22" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D22" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F22" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G22" t="n">
         <v>0.395</v>
@@ -81897,6 +81921,41 @@
         <v>0.014</v>
       </c>
       <c r="K22" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K23" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81911,7 +81970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81981,22 +82040,22 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C2" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D2" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E2" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G2" t="n">
         <v>0.437</v>
@@ -82008,196 +82067,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L2" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B3" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C3" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D3" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
       </c>
       <c r="H3" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I3" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L3" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C4" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D4" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E4" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L4" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C5" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D5" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F5" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G5" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K5" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L5" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B6" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C6" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D6" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E6" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F6" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L6" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C7" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D7" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E7" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K7" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L7" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B8" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C8" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D8" t="n">
         <v>1.44</v>
@@ -82206,7 +82265,7 @@
         <v>0.261</v>
       </c>
       <c r="F8" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G8" t="n">
         <v>0.435</v>
@@ -82215,243 +82274,243 @@
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K8" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L8" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B9" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C9" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D9" t="n">
         <v>1.44</v>
       </c>
       <c r="E9" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F9" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G9" t="n">
         <v>0.435</v>
       </c>
       <c r="H9" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K9" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L9" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B10" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C10" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D10" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F10" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H10" t="n">
         <v>0.365</v>
       </c>
       <c r="I10" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K10" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L10" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C11" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D11" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F11" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G11" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K11" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L11" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B12" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C12" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D12" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E12" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G12" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K12" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L12" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B13" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C13" t="n">
         <v>3.232</v>
       </c>
       <c r="D13" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F13" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G13" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H13" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K13" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L13" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C14" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D14" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E14" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G14" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H14" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I14" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K14" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L14" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B15" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C15" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D15" t="n">
         <v>1.435</v>
       </c>
       <c r="E15" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F15" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G15" t="n">
         <v>0.446</v>
@@ -82463,30 +82522,30 @@
         <v>0.712</v>
       </c>
       <c r="K15" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L15" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B16" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C16" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D16" t="n">
         <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F16" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G16" t="n">
         <v>0.446</v>
@@ -82498,65 +82557,65 @@
         <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L16" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B17" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C17" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D17" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F17" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G17" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H17" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I17" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L17" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B18" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C18" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D18" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E18" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F18" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G18" t="n">
         <v>0.462</v>
@@ -82565,33 +82624,33 @@
         <v>0.343</v>
       </c>
       <c r="I18" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K18" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L18" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C19" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D19" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E19" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F19" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G19" t="n">
         <v>0.462</v>
@@ -82600,109 +82659,106 @@
         <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K19" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L19" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B20" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C20" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D20" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E20" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F20" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G20" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H20" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K20" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L20" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B21" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C21" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D21" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E21" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F21" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G21" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H21" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I21" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J21" t="n">
         <v>0.014</v>
       </c>
       <c r="K21" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L21" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B22" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C22" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D22" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F22" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G22" t="n">
         <v>0.395</v>
@@ -82717,9 +82773,47 @@
         <v>0.014</v>
       </c>
       <c r="K22" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L22" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K23" t="n">
         <v>12.277</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83160,7 +83254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83260,34 +83354,34 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B2" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C2" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D2" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G2" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I2" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K2" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M2" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
@@ -83296,7 +83390,7 @@
         <v>238857</v>
       </c>
       <c r="P2" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q2" t="n">
         <v>710782</v>
@@ -83304,43 +83398,43 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B3" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C3" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D3" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G3" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I3" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K3" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M3" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N3" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P3" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q3" t="n">
         <v>710782</v>
@@ -83348,201 +83442,201 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B4" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C4" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D4" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G4" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I4" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K4" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M4" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N4" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O4" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P4" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q4" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C5" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D5" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G5" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I5" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K5" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M5" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O5" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P5" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q5" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B6" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C6" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D6" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G6" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I6" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K6" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M6" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N6" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P6" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q6" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B7" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C7" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D7" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E7" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G7" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I7" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K7" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M7" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N7" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O7" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P7" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q7" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B8" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C8" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D8" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E8" t="n">
         <v>9400</v>
       </c>
       <c r="F8" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G8" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I8" t="n">
         <v>1493578</v>
@@ -83551,7 +83645,7 @@
         <v>270165</v>
       </c>
       <c r="M8" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -83563,39 +83657,39 @@
         <v>380581</v>
       </c>
       <c r="Q8" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B9" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C9" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D9" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E9" t="n">
         <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G9" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I9" t="n">
         <v>1493578</v>
       </c>
       <c r="K9" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M9" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -83604,153 +83698,153 @@
         <v>236857</v>
       </c>
       <c r="P9" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q9" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B10" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C10" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D10" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E10" t="n">
         <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G10" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I10" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K10" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M10" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N10" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P10" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q10" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B11" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C11" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D11" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E11" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G11" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I11" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K11" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M11" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N11" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O11" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P11" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q11" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B12" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C12" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D12" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G12" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I12" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K12" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M12" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N12" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P12" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q12" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B13" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C13" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D13" t="n">
         <v>1438502</v>
@@ -83759,107 +83853,107 @@
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G13" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I13" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K13" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M13" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N13" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O13" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P13" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q13" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B14" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C14" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D14" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E14" t="n">
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G14" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I14" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K14" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M14" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N14" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O14" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P14" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q14" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B15" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C15" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D15" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E15" t="n">
         <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G15" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I15" t="n">
         <v>1488515</v>
       </c>
       <c r="K15" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M15" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -83868,7 +83962,7 @@
         <v>247857</v>
       </c>
       <c r="P15" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q15" t="n">
         <v>738429</v>
@@ -83876,34 +83970,34 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B16" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C16" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D16" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E16" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G16" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I16" t="n">
         <v>1488515</v>
       </c>
       <c r="K16" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M16" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -83912,7 +84006,7 @@
         <v>247857</v>
       </c>
       <c r="P16" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q16" t="n">
         <v>738429</v>
@@ -83920,78 +84014,78 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B17" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C17" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D17" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E17" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G17" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I17" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K17" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M17" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
       </c>
       <c r="O17" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P17" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q17" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B18" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C18" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D18" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E18" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G18" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I18" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K18" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M18" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
@@ -84000,42 +84094,42 @@
         <v>264857</v>
       </c>
       <c r="P18" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q18" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B19" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C19" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D19" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E19" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F19" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G19" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I19" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K19" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M19" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N19" t="n">
         <v>214475</v>
@@ -84044,101 +84138,98 @@
         <v>264857</v>
       </c>
       <c r="P19" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q19" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B20" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C20" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D20" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E20" t="n">
         <v>9300</v>
       </c>
       <c r="F20" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G20" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I20" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K20" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M20" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N20" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O20" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P20" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q20" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R20" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B21" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C21" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D21" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E21" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F21" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G21" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I21" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K21" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M21" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N21" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O21" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P21" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q21" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R21" t="n">
         <v>15000</v>
@@ -84146,40 +84237,40 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B22" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C22" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D22" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E22" t="n">
         <v>9100</v>
       </c>
       <c r="F22" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G22" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I22" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K22" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M22" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N22" t="n">
         <v>189475</v>
       </c>
       <c r="O22" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P22" t="n">
         <v>375660</v>
@@ -84188,6 +84279,53 @@
         <v>773586</v>
       </c>
       <c r="R22" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C23" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E23" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K23" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N23" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O23" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P23" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R23" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -91517,7 +91655,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="652">
@@ -91527,7 +91665,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.376</v>
+        <v>1.381</v>
       </c>
     </row>
     <row r="653">
@@ -91537,7 +91675,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.497</v>
+        <v>2.501</v>
       </c>
     </row>
     <row r="654">
@@ -91547,7 +91685,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="655">
@@ -91557,7 +91695,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
     </row>
     <row r="656">
@@ -91567,7 +91705,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.7</v>
+        <v>0.699</v>
       </c>
     </row>
     <row r="657">
@@ -91577,7 +91715,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3.229</v>
+        <v>3.212</v>
       </c>
     </row>
     <row r="658">
@@ -91587,7 +91725,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.263</v>
+        <v>3.259</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80343,9 +80343,36 @@
       <c r="A2441" s="4" t="n">
         <v>46270</v>
       </c>
+      <c r="B2441" t="n">
+        <v>3.391</v>
+      </c>
+      <c r="C2441" t="n">
+        <v>3.261</v>
+      </c>
+      <c r="D2441" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="E2441" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F2441" t="n">
+        <v>2.592</v>
+      </c>
+      <c r="G2441" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H2441" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I2441" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="K2441" t="n">
+        <v>12.341</v>
+      </c>
       <c r="L2441" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81183,7 +81210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81248,25 +81275,25 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C2" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E2" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F2" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G2" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
@@ -81275,27 +81302,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B3" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C3" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D3" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F3" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
@@ -81307,178 +81334,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B4" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C4" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D4" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E4" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I4" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C5" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D5" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F5" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C6" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D6" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F6" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K6" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B7" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C7" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D7" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E7" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C8" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E8" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F8" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K8" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C9" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D9" t="n">
         <v>1.44</v>
@@ -81487,7 +81514,7 @@
         <v>0.261</v>
       </c>
       <c r="F9" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G9" t="n">
         <v>0.435</v>
@@ -81496,222 +81523,222 @@
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K9" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B10" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C10" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D10" t="n">
         <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G10" t="n">
         <v>0.435</v>
       </c>
       <c r="H10" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K10" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B11" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C11" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D11" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G11" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K11" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C12" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D12" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F12" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G12" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K12" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C13" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D13" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E13" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G13" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K13" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B14" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C14" t="n">
         <v>3.232</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F14" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G14" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K14" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C15" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D15" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H15" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K15" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B16" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C16" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D16" t="n">
         <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F16" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G16" t="n">
         <v>0.446</v>
@@ -81723,27 +81750,27 @@
         <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B17" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C17" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D17" t="n">
         <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F17" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G17" t="n">
         <v>0.446</v>
@@ -81755,59 +81782,59 @@
         <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B18" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C18" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D18" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F18" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G18" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I18" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B19" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C19" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D19" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E19" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F19" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G19" t="n">
         <v>0.462</v>
@@ -81816,30 +81843,30 @@
         <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K19" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C20" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D20" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E20" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F20" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G20" t="n">
         <v>0.462</v>
@@ -81848,100 +81875,97 @@
         <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K20" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B21" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C21" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D21" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F21" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G21" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H21" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K21" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B22" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C22" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D22" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F22" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G22" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H22" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I22" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J22" t="n">
         <v>0.014</v>
       </c>
       <c r="K22" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B23" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C23" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D23" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F23" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G23" t="n">
         <v>0.395</v>
@@ -81956,6 +81980,41 @@
         <v>0.014</v>
       </c>
       <c r="K23" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K24" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -81970,7 +82029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82040,25 +82099,25 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C2" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D2" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E2" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F2" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G2" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H2" t="n">
         <v>0.367</v>
@@ -82067,30 +82126,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L2" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B3" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C3" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D3" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F3" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G3" t="n">
         <v>0.437</v>
@@ -82102,196 +82161,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L3" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B4" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C4" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D4" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E4" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
       </c>
       <c r="H4" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I4" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L4" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C5" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D5" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E5" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F5" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L5" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C6" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D6" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F6" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K6" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L6" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B7" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C7" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D7" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E7" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F7" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G7" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L7" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C8" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E8" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F8" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K8" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L8" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C9" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D9" t="n">
         <v>1.44</v>
@@ -82300,7 +82359,7 @@
         <v>0.261</v>
       </c>
       <c r="F9" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G9" t="n">
         <v>0.435</v>
@@ -82309,243 +82368,243 @@
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K9" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L9" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B10" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C10" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D10" t="n">
         <v>1.44</v>
       </c>
       <c r="E10" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G10" t="n">
         <v>0.435</v>
       </c>
       <c r="H10" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K10" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L10" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B11" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C11" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D11" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F11" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G11" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H11" t="n">
         <v>0.365</v>
       </c>
       <c r="I11" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K11" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L11" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C12" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D12" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F12" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G12" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K12" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L12" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C13" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D13" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E13" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G13" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K13" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L13" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B14" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C14" t="n">
         <v>3.232</v>
       </c>
       <c r="D14" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F14" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G14" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H14" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K14" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L14" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C15" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D15" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E15" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H15" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I15" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K15" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L15" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B16" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C16" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D16" t="n">
         <v>1.435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F16" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G16" t="n">
         <v>0.446</v>
@@ -82557,30 +82616,30 @@
         <v>0.712</v>
       </c>
       <c r="K16" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L16" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B17" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C17" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D17" t="n">
         <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F17" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G17" t="n">
         <v>0.446</v>
@@ -82592,65 +82651,65 @@
         <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L17" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B18" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C18" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D18" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F18" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G18" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H18" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I18" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L18" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B19" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C19" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D19" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E19" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F19" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G19" t="n">
         <v>0.462</v>
@@ -82659,33 +82718,33 @@
         <v>0.343</v>
       </c>
       <c r="I19" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K19" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L19" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C20" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D20" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E20" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F20" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G20" t="n">
         <v>0.462</v>
@@ -82694,109 +82753,106 @@
         <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K20" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L20" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B21" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C21" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D21" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F21" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G21" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H21" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K21" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L21" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B22" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C22" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D22" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F22" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G22" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H22" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I22" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J22" t="n">
         <v>0.014</v>
       </c>
       <c r="K22" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L22" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B23" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C23" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D23" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F23" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G23" t="n">
         <v>0.395</v>
@@ -82811,9 +82867,47 @@
         <v>0.014</v>
       </c>
       <c r="K23" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K24" t="n">
         <v>12.277</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83254,7 +83348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83354,13 +83448,13 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B2" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C2" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D2" t="n">
         <v>1336369</v>
@@ -83369,28 +83463,28 @@
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G2" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I2" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K2" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M2" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O2" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P2" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q2" t="n">
         <v>710782</v>
@@ -83398,34 +83492,34 @@
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B3" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C3" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D3" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G3" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I3" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K3" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M3" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
@@ -83434,7 +83528,7 @@
         <v>238857</v>
       </c>
       <c r="P3" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q3" t="n">
         <v>710782</v>
@@ -83442,43 +83536,43 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B4" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C4" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D4" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G4" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I4" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K4" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M4" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N4" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P4" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q4" t="n">
         <v>710782</v>
@@ -83486,201 +83580,201 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B5" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C5" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D5" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G5" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I5" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K5" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M5" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N5" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O5" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P5" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q5" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B6" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C6" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D6" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G6" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I6" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K6" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M6" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N6" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O6" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P6" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q6" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B7" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C7" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D7" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G7" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I7" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K7" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M7" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N7" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P7" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q7" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B8" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C8" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D8" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E8" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G8" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I8" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K8" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M8" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N8" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O8" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P8" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q8" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B9" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C9" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D9" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E9" t="n">
         <v>9400</v>
       </c>
       <c r="F9" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G9" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I9" t="n">
         <v>1493578</v>
@@ -83689,7 +83783,7 @@
         <v>270165</v>
       </c>
       <c r="M9" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -83701,39 +83795,39 @@
         <v>380581</v>
       </c>
       <c r="Q9" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B10" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C10" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D10" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E10" t="n">
         <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G10" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I10" t="n">
         <v>1493578</v>
       </c>
       <c r="K10" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M10" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -83742,153 +83836,153 @@
         <v>236857</v>
       </c>
       <c r="P10" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q10" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B11" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C11" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D11" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E11" t="n">
         <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G11" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I11" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K11" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M11" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N11" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P11" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q11" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B12" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C12" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D12" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E12" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G12" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I12" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K12" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M12" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N12" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O12" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P12" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q12" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B13" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C13" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D13" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G13" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I13" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K13" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M13" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N13" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O13" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P13" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q13" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B14" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C14" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D14" t="n">
         <v>1438502</v>
@@ -83897,107 +83991,107 @@
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G14" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I14" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K14" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M14" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N14" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O14" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P14" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q14" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B15" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C15" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D15" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E15" t="n">
         <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G15" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I15" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K15" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M15" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N15" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O15" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P15" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q15" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B16" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C16" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D16" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E16" t="n">
         <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G16" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I16" t="n">
         <v>1488515</v>
       </c>
       <c r="K16" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M16" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -84006,7 +84100,7 @@
         <v>247857</v>
       </c>
       <c r="P16" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q16" t="n">
         <v>738429</v>
@@ -84014,34 +84108,34 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B17" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C17" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D17" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E17" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G17" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I17" t="n">
         <v>1488515</v>
       </c>
       <c r="K17" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M17" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -84050,7 +84144,7 @@
         <v>247857</v>
       </c>
       <c r="P17" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q17" t="n">
         <v>738429</v>
@@ -84058,78 +84152,78 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B18" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C18" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D18" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E18" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F18" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G18" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I18" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K18" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M18" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
       </c>
       <c r="O18" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P18" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q18" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B19" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C19" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D19" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E19" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G19" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I19" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K19" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M19" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N19" t="n">
         <v>214475</v>
@@ -84138,42 +84232,42 @@
         <v>264857</v>
       </c>
       <c r="P19" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q19" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B20" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C20" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D20" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E20" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F20" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G20" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I20" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K20" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M20" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N20" t="n">
         <v>214475</v>
@@ -84182,101 +84276,98 @@
         <v>264857</v>
       </c>
       <c r="P20" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q20" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B21" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C21" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D21" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E21" t="n">
         <v>9300</v>
       </c>
       <c r="F21" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G21" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I21" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K21" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M21" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N21" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O21" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P21" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q21" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R21" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B22" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C22" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D22" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E22" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F22" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G22" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I22" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K22" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M22" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N22" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O22" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P22" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q22" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R22" t="n">
         <v>15000</v>
@@ -84284,40 +84375,40 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B23" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C23" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D23" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E23" t="n">
         <v>9100</v>
       </c>
       <c r="F23" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G23" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I23" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K23" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M23" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N23" t="n">
         <v>189475</v>
       </c>
       <c r="O23" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P23" t="n">
         <v>375660</v>
@@ -84326,6 +84417,53 @@
         <v>773586</v>
       </c>
       <c r="R23" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C24" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K24" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N24" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O24" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P24" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R24" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -91655,7 +91793,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
     </row>
     <row r="652">
@@ -91665,7 +91803,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.381</v>
+        <v>1.385</v>
       </c>
     </row>
     <row r="653">
@@ -91675,7 +91813,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.501</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="654">
@@ -91695,7 +91833,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.415</v>
+        <v>0.409</v>
       </c>
     </row>
     <row r="656">
@@ -91715,7 +91853,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3.212</v>
+        <v>3.214</v>
       </c>
     </row>
     <row r="658">
@@ -91725,7 +91863,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.259</v>
+        <v>3.264</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80333,9 +80333,36 @@
       <c r="A2440" s="4" t="n">
         <v>46269</v>
       </c>
+      <c r="B2440" t="n">
+        <v>3.405</v>
+      </c>
+      <c r="C2440" t="n">
+        <v>3.204</v>
+      </c>
+      <c r="D2440" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="E2440" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="F2440" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="G2440" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="H2440" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="I2440" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="K2440" t="n">
+        <v>12.376</v>
+      </c>
       <c r="L2440" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81210,7 +81237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81275,57 +81302,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B2" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C2" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D2" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F2" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K2" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C3" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D3" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F3" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G3" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
@@ -81334,27 +81361,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B4" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C4" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D4" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F4" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
@@ -81366,178 +81393,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B5" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C5" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D5" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E5" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I5" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B6" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C6" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D6" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F6" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
       </c>
       <c r="H6" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I6" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C7" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D7" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F7" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G7" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K7" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B8" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C8" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D8" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C9" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E9" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F9" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K9" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B10" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C10" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D10" t="n">
         <v>1.44</v>
@@ -81546,7 +81573,7 @@
         <v>0.261</v>
       </c>
       <c r="F10" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G10" t="n">
         <v>0.435</v>
@@ -81555,222 +81582,222 @@
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K10" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B11" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C11" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D11" t="n">
         <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F11" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G11" t="n">
         <v>0.435</v>
       </c>
       <c r="H11" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K11" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B12" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C12" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D12" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F12" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K12" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C13" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D13" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F13" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G13" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K13" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B14" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C14" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D14" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E14" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G14" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K14" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B15" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C15" t="n">
         <v>3.232</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F15" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H15" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K15" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C16" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D16" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G16" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K16" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B17" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C17" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D17" t="n">
         <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F17" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G17" t="n">
         <v>0.446</v>
@@ -81782,27 +81809,27 @@
         <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B18" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C18" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D18" t="n">
         <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F18" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G18" t="n">
         <v>0.446</v>
@@ -81814,59 +81841,59 @@
         <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B19" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C19" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D19" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F19" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G19" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H19" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B20" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C20" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D20" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E20" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F20" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G20" t="n">
         <v>0.462</v>
@@ -81875,30 +81902,30 @@
         <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K20" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B21" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C21" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D21" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E21" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F21" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G21" t="n">
         <v>0.462</v>
@@ -81907,100 +81934,97 @@
         <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K21" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B22" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C22" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D22" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F22" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G22" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H22" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K22" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B23" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C23" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D23" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E23" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F23" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G23" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H23" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J23" t="n">
         <v>0.014</v>
       </c>
       <c r="K23" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B24" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C24" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D24" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F24" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G24" t="n">
         <v>0.395</v>
@@ -82015,6 +82039,41 @@
         <v>0.014</v>
       </c>
       <c r="K24" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K25" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82029,7 +82088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82099,60 +82158,60 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B2" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C2" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D2" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F2" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G2" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K2" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L2" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C3" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D3" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F3" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G3" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H3" t="n">
         <v>0.367</v>
@@ -82161,30 +82220,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L3" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B4" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C4" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D4" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E4" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F4" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G4" t="n">
         <v>0.437</v>
@@ -82196,196 +82255,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L4" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B5" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C5" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D5" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E5" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
       </c>
       <c r="H5" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I5" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L5" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B6" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C6" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D6" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E6" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F6" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
       </c>
       <c r="H6" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I6" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L6" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C7" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D7" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F7" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G7" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K7" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L7" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B8" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C8" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D8" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L8" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C9" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E9" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F9" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K9" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L9" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B10" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C10" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D10" t="n">
         <v>1.44</v>
@@ -82394,7 +82453,7 @@
         <v>0.261</v>
       </c>
       <c r="F10" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G10" t="n">
         <v>0.435</v>
@@ -82403,243 +82462,243 @@
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K10" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L10" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B11" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C11" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D11" t="n">
         <v>1.44</v>
       </c>
       <c r="E11" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F11" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G11" t="n">
         <v>0.435</v>
       </c>
       <c r="H11" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K11" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L11" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B12" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C12" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D12" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F12" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H12" t="n">
         <v>0.365</v>
       </c>
       <c r="I12" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K12" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L12" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C13" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D13" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F13" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G13" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K13" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L13" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B14" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C14" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D14" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E14" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G14" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K14" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L14" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B15" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C15" t="n">
         <v>3.232</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F15" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H15" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K15" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L15" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C16" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D16" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E16" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G16" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I16" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K16" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L16" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B17" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C17" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D17" t="n">
         <v>1.435</v>
       </c>
       <c r="E17" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F17" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G17" t="n">
         <v>0.446</v>
@@ -82651,30 +82710,30 @@
         <v>0.712</v>
       </c>
       <c r="K17" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L17" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B18" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C18" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D18" t="n">
         <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F18" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G18" t="n">
         <v>0.446</v>
@@ -82686,65 +82745,65 @@
         <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L18" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B19" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C19" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D19" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F19" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G19" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H19" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I19" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L19" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B20" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C20" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D20" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E20" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F20" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G20" t="n">
         <v>0.462</v>
@@ -82753,33 +82812,33 @@
         <v>0.343</v>
       </c>
       <c r="I20" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K20" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L20" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B21" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C21" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D21" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E21" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F21" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G21" t="n">
         <v>0.462</v>
@@ -82788,109 +82847,106 @@
         <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K21" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L21" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B22" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C22" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D22" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F22" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G22" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H22" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K22" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L22" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B23" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C23" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D23" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E23" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F23" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G23" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H23" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I23" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J23" t="n">
         <v>0.014</v>
       </c>
       <c r="K23" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L23" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B24" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C24" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D24" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F24" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G24" t="n">
         <v>0.395</v>
@@ -82905,9 +82961,47 @@
         <v>0.014</v>
       </c>
       <c r="K24" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K25" t="n">
         <v>12.277</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L25" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83348,7 +83442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83448,57 +83542,57 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B2" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C2" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D2" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G2" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I2" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K2" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M2" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N2" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P2" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q2" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B3" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C3" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D3" t="n">
         <v>1336369</v>
@@ -83507,28 +83601,28 @@
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G3" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I3" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K3" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M3" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O3" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P3" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q3" t="n">
         <v>710782</v>
@@ -83536,34 +83630,34 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B4" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C4" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D4" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G4" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I4" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K4" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M4" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
@@ -83572,7 +83666,7 @@
         <v>238857</v>
       </c>
       <c r="P4" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q4" t="n">
         <v>710782</v>
@@ -83580,43 +83674,43 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B5" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C5" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D5" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G5" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I5" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K5" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M5" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N5" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P5" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q5" t="n">
         <v>710782</v>
@@ -83624,201 +83718,201 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B6" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C6" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D6" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G6" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I6" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K6" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M6" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N6" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O6" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P6" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q6" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B7" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C7" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D7" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G7" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I7" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K7" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M7" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N7" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O7" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P7" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q7" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B8" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C8" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D8" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G8" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I8" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K8" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M8" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N8" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P8" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q8" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B9" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C9" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D9" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E9" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G9" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I9" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K9" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M9" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N9" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O9" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P9" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q9" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B10" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C10" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D10" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E10" t="n">
         <v>9400</v>
       </c>
       <c r="F10" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G10" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I10" t="n">
         <v>1493578</v>
@@ -83827,7 +83921,7 @@
         <v>270165</v>
       </c>
       <c r="M10" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -83839,39 +83933,39 @@
         <v>380581</v>
       </c>
       <c r="Q10" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B11" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C11" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D11" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E11" t="n">
         <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G11" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I11" t="n">
         <v>1493578</v>
       </c>
       <c r="K11" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M11" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -83880,153 +83974,153 @@
         <v>236857</v>
       </c>
       <c r="P11" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q11" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B12" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C12" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D12" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E12" t="n">
         <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G12" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I12" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K12" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M12" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N12" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P12" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q12" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B13" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C13" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D13" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E13" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G13" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I13" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K13" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M13" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N13" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O13" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P13" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q13" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B14" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C14" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D14" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E14" t="n">
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G14" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I14" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K14" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M14" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N14" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O14" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P14" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q14" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B15" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C15" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D15" t="n">
         <v>1438502</v>
@@ -84035,107 +84129,107 @@
         <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G15" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I15" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K15" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M15" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N15" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O15" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P15" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q15" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B16" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C16" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D16" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E16" t="n">
         <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G16" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I16" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K16" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M16" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N16" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O16" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P16" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q16" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B17" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C17" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D17" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E17" t="n">
         <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G17" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I17" t="n">
         <v>1488515</v>
       </c>
       <c r="K17" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M17" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -84144,7 +84238,7 @@
         <v>247857</v>
       </c>
       <c r="P17" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q17" t="n">
         <v>738429</v>
@@ -84152,34 +84246,34 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B18" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C18" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D18" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E18" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G18" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I18" t="n">
         <v>1488515</v>
       </c>
       <c r="K18" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M18" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
@@ -84188,7 +84282,7 @@
         <v>247857</v>
       </c>
       <c r="P18" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q18" t="n">
         <v>738429</v>
@@ -84196,78 +84290,78 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B19" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C19" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D19" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E19" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F19" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G19" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I19" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K19" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M19" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N19" t="n">
         <v>214475</v>
       </c>
       <c r="O19" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P19" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q19" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B20" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C20" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D20" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E20" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G20" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I20" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K20" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M20" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N20" t="n">
         <v>214475</v>
@@ -84276,42 +84370,42 @@
         <v>264857</v>
       </c>
       <c r="P20" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q20" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B21" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C21" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D21" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E21" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F21" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G21" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I21" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K21" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M21" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N21" t="n">
         <v>214475</v>
@@ -84320,101 +84414,98 @@
         <v>264857</v>
       </c>
       <c r="P21" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q21" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B22" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C22" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D22" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E22" t="n">
         <v>9300</v>
       </c>
       <c r="F22" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G22" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I22" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K22" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M22" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N22" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O22" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P22" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q22" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R22" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B23" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C23" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D23" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E23" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F23" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G23" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I23" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K23" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M23" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N23" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O23" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P23" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q23" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R23" t="n">
         <v>15000</v>
@@ -84422,40 +84513,40 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B24" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C24" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D24" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E24" t="n">
         <v>9100</v>
       </c>
       <c r="F24" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G24" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I24" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K24" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M24" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N24" t="n">
         <v>189475</v>
       </c>
       <c r="O24" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P24" t="n">
         <v>375660</v>
@@ -84464,6 +84555,53 @@
         <v>773586</v>
       </c>
       <c r="R24" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C25" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K25" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N25" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O25" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P25" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R25" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -91793,7 +91931,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.395</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="652">
@@ -91803,7 +91941,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.385</v>
+        <v>1.389</v>
       </c>
     </row>
     <row r="653">
@@ -91813,7 +91951,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.505</v>
+        <v>2.507</v>
       </c>
     </row>
     <row r="654">
@@ -91833,7 +91971,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="656">
@@ -91843,7 +91981,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.699</v>
+        <v>0.698</v>
       </c>
     </row>
     <row r="657">
@@ -91863,7 +92001,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.264</v>
+        <v>3.27</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80323,9 +80323,36 @@
       <c r="A2439" s="4" t="n">
         <v>46268</v>
       </c>
+      <c r="B2439" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="C2439" t="n">
+        <v>3.142</v>
+      </c>
+      <c r="D2439" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="E2439" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="F2439" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="G2439" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H2439" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="I2439" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="K2439" t="n">
+        <v>11.787</v>
+      </c>
       <c r="L2439" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81237,7 +81264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81302,89 +81329,89 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C2" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D2" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G2" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K2" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C3" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D3" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E3" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F3" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G3" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K3" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C4" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E4" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F4" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G4" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
@@ -81393,27 +81420,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B5" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C5" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D5" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F5" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
@@ -81425,178 +81452,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B6" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C6" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D6" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
       </c>
       <c r="H6" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I6" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B7" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C7" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D7" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F7" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I7" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B8" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C8" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D8" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F8" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G8" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K8" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B9" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C9" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D9" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E9" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C10" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E10" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F10" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G10" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K10" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B11" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C11" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D11" t="n">
         <v>1.44</v>
@@ -81605,7 +81632,7 @@
         <v>0.261</v>
       </c>
       <c r="F11" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G11" t="n">
         <v>0.435</v>
@@ -81614,222 +81641,222 @@
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K11" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B12" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C12" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D12" t="n">
         <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F12" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G12" t="n">
         <v>0.435</v>
       </c>
       <c r="H12" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K12" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B13" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C13" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D13" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K13" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B14" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C14" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F14" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G14" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K14" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B15" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C15" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D15" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E15" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G15" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K15" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B16" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C16" t="n">
         <v>3.232</v>
       </c>
       <c r="D16" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F16" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G16" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H16" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K16" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C17" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D17" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E17" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G17" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H17" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I17" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K17" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B18" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C18" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D18" t="n">
         <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F18" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G18" t="n">
         <v>0.446</v>
@@ -81841,27 +81868,27 @@
         <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B19" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C19" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D19" t="n">
         <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F19" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G19" t="n">
         <v>0.446</v>
@@ -81873,59 +81900,59 @@
         <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B20" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C20" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D20" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F20" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G20" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H20" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I20" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B21" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C21" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D21" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E21" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F21" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G21" t="n">
         <v>0.462</v>
@@ -81934,30 +81961,30 @@
         <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K21" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C22" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D22" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E22" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F22" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G22" t="n">
         <v>0.462</v>
@@ -81966,100 +81993,97 @@
         <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K22" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B23" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C23" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D23" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F23" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G23" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K23" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B24" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C24" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D24" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E24" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F24" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G24" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H24" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J24" t="n">
         <v>0.014</v>
       </c>
       <c r="K24" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B25" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C25" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D25" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F25" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G25" t="n">
         <v>0.395</v>
@@ -82074,6 +82098,41 @@
         <v>0.014</v>
       </c>
       <c r="K25" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K26" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82088,7 +82147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82158,95 +82217,95 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C2" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D2" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E2" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F2" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G2" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I2" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K2" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L2" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C3" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D3" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E3" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F3" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G3" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H3" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K3" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L3" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C4" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D4" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E4" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F4" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G4" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H4" t="n">
         <v>0.367</v>
@@ -82255,30 +82314,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L4" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B5" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C5" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D5" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F5" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G5" t="n">
         <v>0.437</v>
@@ -82290,196 +82349,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L5" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B6" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C6" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D6" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
       </c>
       <c r="H6" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I6" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L6" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B7" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C7" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D7" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F7" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I7" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L7" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B8" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C8" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D8" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F8" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G8" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K8" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L8" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B9" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C9" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D9" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E9" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G9" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L9" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C10" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E10" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F10" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G10" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K10" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L10" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B11" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C11" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D11" t="n">
         <v>1.44</v>
@@ -82488,7 +82547,7 @@
         <v>0.261</v>
       </c>
       <c r="F11" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G11" t="n">
         <v>0.435</v>
@@ -82497,243 +82556,243 @@
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K11" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L11" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B12" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C12" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D12" t="n">
         <v>1.44</v>
       </c>
       <c r="E12" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F12" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G12" t="n">
         <v>0.435</v>
       </c>
       <c r="H12" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K12" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L12" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B13" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C13" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D13" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H13" t="n">
         <v>0.365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K13" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L13" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B14" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C14" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F14" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G14" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K14" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L14" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B15" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C15" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D15" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E15" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G15" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K15" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L15" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B16" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C16" t="n">
         <v>3.232</v>
       </c>
       <c r="D16" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F16" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G16" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H16" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K16" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L16" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C17" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D17" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E17" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G17" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H17" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I17" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K17" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L17" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B18" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C18" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D18" t="n">
         <v>1.435</v>
       </c>
       <c r="E18" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F18" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G18" t="n">
         <v>0.446</v>
@@ -82745,30 +82804,30 @@
         <v>0.712</v>
       </c>
       <c r="K18" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L18" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B19" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C19" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D19" t="n">
         <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F19" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G19" t="n">
         <v>0.446</v>
@@ -82780,65 +82839,65 @@
         <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L19" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B20" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C20" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D20" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F20" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G20" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H20" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I20" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L20" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B21" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C21" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D21" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E21" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F21" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G21" t="n">
         <v>0.462</v>
@@ -82847,33 +82906,33 @@
         <v>0.343</v>
       </c>
       <c r="I21" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K21" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L21" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C22" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D22" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E22" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F22" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G22" t="n">
         <v>0.462</v>
@@ -82882,109 +82941,106 @@
         <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K22" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L22" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B23" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C23" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D23" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F23" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G23" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H23" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K23" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L23" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B24" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C24" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D24" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E24" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F24" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G24" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H24" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I24" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J24" t="n">
         <v>0.014</v>
       </c>
       <c r="K24" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L24" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B25" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C25" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D25" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F25" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G25" t="n">
         <v>0.395</v>
@@ -82999,9 +83055,47 @@
         <v>0.014</v>
       </c>
       <c r="K25" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L25" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K26" t="n">
         <v>12.277</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L26" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83442,7 +83536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83542,101 +83636,101 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B2" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C2" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D2" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E2" t="n">
         <v>9200</v>
       </c>
       <c r="F2" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G2" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I2" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K2" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M2" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P2" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q2" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B3" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C3" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D3" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G3" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I3" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K3" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M3" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N3" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P3" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q3" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B4" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C4" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D4" t="n">
         <v>1336369</v>
@@ -83645,28 +83739,28 @@
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G4" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I4" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K4" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M4" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O4" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P4" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q4" t="n">
         <v>710782</v>
@@ -83674,34 +83768,34 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B5" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C5" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D5" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G5" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I5" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K5" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M5" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
@@ -83710,7 +83804,7 @@
         <v>238857</v>
       </c>
       <c r="P5" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q5" t="n">
         <v>710782</v>
@@ -83718,43 +83812,43 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B6" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C6" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D6" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G6" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I6" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K6" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M6" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N6" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P6" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q6" t="n">
         <v>710782</v>
@@ -83762,201 +83856,201 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B7" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C7" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D7" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G7" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I7" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K7" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M7" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N7" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O7" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P7" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q7" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B8" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C8" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D8" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G8" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I8" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K8" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M8" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N8" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O8" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P8" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q8" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B9" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C9" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D9" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G9" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I9" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K9" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M9" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N9" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P9" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q9" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B10" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C10" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D10" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E10" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G10" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I10" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K10" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M10" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N10" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O10" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P10" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q10" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B11" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C11" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D11" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E11" t="n">
         <v>9400</v>
       </c>
       <c r="F11" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G11" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I11" t="n">
         <v>1493578</v>
@@ -83965,7 +84059,7 @@
         <v>270165</v>
       </c>
       <c r="M11" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -83977,39 +84071,39 @@
         <v>380581</v>
       </c>
       <c r="Q11" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B12" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C12" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D12" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E12" t="n">
         <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G12" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I12" t="n">
         <v>1493578</v>
       </c>
       <c r="K12" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M12" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -84018,153 +84112,153 @@
         <v>236857</v>
       </c>
       <c r="P12" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q12" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B13" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C13" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D13" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E13" t="n">
         <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G13" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I13" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K13" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M13" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N13" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O13" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P13" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q13" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B14" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C14" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D14" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E14" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G14" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I14" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K14" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M14" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N14" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O14" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P14" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q14" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B15" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C15" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D15" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E15" t="n">
         <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G15" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I15" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K15" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M15" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N15" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O15" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P15" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q15" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B16" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C16" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D16" t="n">
         <v>1438502</v>
@@ -84173,107 +84267,107 @@
         <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G16" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I16" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K16" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M16" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N16" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O16" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P16" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q16" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B17" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C17" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D17" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E17" t="n">
         <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G17" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I17" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K17" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M17" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N17" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O17" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P17" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q17" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B18" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C18" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D18" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E18" t="n">
         <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G18" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I18" t="n">
         <v>1488515</v>
       </c>
       <c r="K18" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M18" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
@@ -84282,7 +84376,7 @@
         <v>247857</v>
       </c>
       <c r="P18" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q18" t="n">
         <v>738429</v>
@@ -84290,34 +84384,34 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B19" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C19" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D19" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E19" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G19" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I19" t="n">
         <v>1488515</v>
       </c>
       <c r="K19" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M19" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N19" t="n">
         <v>214475</v>
@@ -84326,7 +84420,7 @@
         <v>247857</v>
       </c>
       <c r="P19" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q19" t="n">
         <v>738429</v>
@@ -84334,78 +84428,78 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B20" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C20" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D20" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E20" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F20" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G20" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I20" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K20" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M20" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N20" t="n">
         <v>214475</v>
       </c>
       <c r="O20" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P20" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q20" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B21" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C21" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D21" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E21" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G21" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I21" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K21" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M21" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N21" t="n">
         <v>214475</v>
@@ -84414,42 +84508,42 @@
         <v>264857</v>
       </c>
       <c r="P21" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q21" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B22" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C22" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D22" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E22" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F22" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G22" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I22" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K22" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M22" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N22" t="n">
         <v>214475</v>
@@ -84458,101 +84552,98 @@
         <v>264857</v>
       </c>
       <c r="P22" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q22" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B23" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C23" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D23" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E23" t="n">
         <v>9300</v>
       </c>
       <c r="F23" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G23" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I23" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K23" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M23" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N23" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O23" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P23" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q23" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R23" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B24" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C24" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D24" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E24" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F24" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G24" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I24" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K24" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M24" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N24" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O24" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P24" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q24" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R24" t="n">
         <v>15000</v>
@@ -84560,40 +84651,40 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B25" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C25" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D25" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E25" t="n">
         <v>9100</v>
       </c>
       <c r="F25" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G25" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I25" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K25" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M25" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N25" t="n">
         <v>189475</v>
       </c>
       <c r="O25" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P25" t="n">
         <v>375660</v>
@@ -84602,6 +84693,53 @@
         <v>773586</v>
       </c>
       <c r="R25" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C26" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E26" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K26" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N26" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O26" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P26" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R26" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -91931,7 +92069,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.389</v>
+        <v>0.382</v>
       </c>
     </row>
     <row r="652">
@@ -91951,7 +92089,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.507</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="654">
@@ -91961,7 +92099,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
     </row>
     <row r="655">
@@ -91971,7 +92109,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.41</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="656">
@@ -91981,7 +92119,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.698</v>
+        <v>0.696</v>
       </c>
     </row>
     <row r="657">
@@ -91991,7 +92129,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3.214</v>
+        <v>3.211</v>
       </c>
     </row>
     <row r="658">
@@ -92001,7 +92139,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.27</v>
+        <v>3.262</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80313,9 +80313,36 @@
       <c r="A2438" s="4" t="n">
         <v>46267</v>
       </c>
+      <c r="B2438" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="C2438" t="n">
+        <v>3.117</v>
+      </c>
+      <c r="D2438" t="n">
+        <v>1.454</v>
+      </c>
+      <c r="E2438" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="F2438" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="G2438" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H2438" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="I2438" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="K2438" t="n">
+        <v>11.345</v>
+      </c>
       <c r="L2438" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81264,7 +81291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81329,121 +81356,121 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B2" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C2" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D2" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F2" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G2" t="n">
         <v>0.444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I2" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K2" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B3" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C3" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D3" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F3" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H3" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K3" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C4" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D4" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F4" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H4" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K4" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C5" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D5" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F5" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
@@ -81452,27 +81479,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B6" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C6" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D6" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E6" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F6" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
@@ -81484,178 +81511,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B7" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C7" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D7" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I7" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B8" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C8" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D8" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F8" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
       </c>
       <c r="H8" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I8" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B9" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C9" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D9" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F9" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G9" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K9" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B10" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C10" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D10" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E10" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C11" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E11" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F11" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G11" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K11" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B12" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C12" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D12" t="n">
         <v>1.44</v>
@@ -81664,7 +81691,7 @@
         <v>0.261</v>
       </c>
       <c r="F12" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G12" t="n">
         <v>0.435</v>
@@ -81673,222 +81700,222 @@
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K12" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B13" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C13" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D13" t="n">
         <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F13" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G13" t="n">
         <v>0.435</v>
       </c>
       <c r="H13" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K13" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B14" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C14" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D14" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F14" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G14" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K14" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C15" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D15" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F15" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G15" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K15" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B16" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C16" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D16" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E16" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K16" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B17" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C17" t="n">
         <v>3.232</v>
       </c>
       <c r="D17" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F17" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K17" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C18" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D18" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E18" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G18" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H18" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I18" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K18" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B19" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C19" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D19" t="n">
         <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F19" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G19" t="n">
         <v>0.446</v>
@@ -81900,27 +81927,27 @@
         <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B20" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C20" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D20" t="n">
         <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F20" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G20" t="n">
         <v>0.446</v>
@@ -81932,59 +81959,59 @@
         <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B21" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C21" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D21" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F21" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G21" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H21" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I21" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B22" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C22" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D22" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E22" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F22" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G22" t="n">
         <v>0.462</v>
@@ -81993,30 +82020,30 @@
         <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K22" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B23" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C23" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D23" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E23" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F23" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G23" t="n">
         <v>0.462</v>
@@ -82025,100 +82052,97 @@
         <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K23" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B24" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C24" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D24" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E24" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F24" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G24" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H24" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K24" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B25" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C25" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D25" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E25" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G25" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H25" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J25" t="n">
         <v>0.014</v>
       </c>
       <c r="K25" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B26" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C26" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D26" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F26" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G26" t="n">
         <v>0.395</v>
@@ -82133,6 +82157,41 @@
         <v>0.014</v>
       </c>
       <c r="K26" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K27" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82147,7 +82206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82217,130 +82276,130 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B2" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C2" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D2" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E2" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F2" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G2" t="n">
         <v>0.444</v>
       </c>
       <c r="H2" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I2" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K2" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L2" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B3" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C3" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D3" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E3" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F3" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G3" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H3" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I3" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K3" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L3" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C4" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D4" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E4" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F4" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G4" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H4" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K4" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L4" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C5" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D5" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E5" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F5" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H5" t="n">
         <v>0.367</v>
@@ -82349,30 +82408,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L5" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B6" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C6" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D6" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E6" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F6" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G6" t="n">
         <v>0.437</v>
@@ -82384,196 +82443,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L6" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B7" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C7" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D7" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F7" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
       </c>
       <c r="H7" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I7" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L7" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B8" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C8" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D8" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F8" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
       </c>
       <c r="H8" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I8" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L8" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B9" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C9" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D9" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F9" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G9" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K9" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L9" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B10" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C10" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D10" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E10" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G10" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L10" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C11" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E11" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F11" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G11" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K11" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L11" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B12" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C12" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D12" t="n">
         <v>1.44</v>
@@ -82582,7 +82641,7 @@
         <v>0.261</v>
       </c>
       <c r="F12" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G12" t="n">
         <v>0.435</v>
@@ -82591,243 +82650,243 @@
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K12" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L12" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B13" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C13" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D13" t="n">
         <v>1.44</v>
       </c>
       <c r="E13" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F13" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G13" t="n">
         <v>0.435</v>
       </c>
       <c r="H13" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K13" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L13" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B14" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C14" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D14" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F14" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G14" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H14" t="n">
         <v>0.365</v>
       </c>
       <c r="I14" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K14" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L14" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C15" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D15" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F15" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G15" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K15" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L15" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B16" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C16" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D16" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E16" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K16" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L16" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B17" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C17" t="n">
         <v>3.232</v>
       </c>
       <c r="D17" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F17" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G17" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H17" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K17" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L17" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C18" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D18" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E18" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G18" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H18" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I18" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K18" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L18" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B19" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C19" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D19" t="n">
         <v>1.435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F19" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G19" t="n">
         <v>0.446</v>
@@ -82839,30 +82898,30 @@
         <v>0.712</v>
       </c>
       <c r="K19" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L19" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B20" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C20" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D20" t="n">
         <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F20" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G20" t="n">
         <v>0.446</v>
@@ -82874,65 +82933,65 @@
         <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L20" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B21" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C21" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D21" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F21" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G21" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H21" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I21" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L21" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B22" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C22" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D22" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E22" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F22" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G22" t="n">
         <v>0.462</v>
@@ -82941,33 +83000,33 @@
         <v>0.343</v>
       </c>
       <c r="I22" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K22" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L22" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B23" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C23" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D23" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E23" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F23" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G23" t="n">
         <v>0.462</v>
@@ -82976,109 +83035,106 @@
         <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K23" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L23" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B24" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C24" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D24" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E24" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F24" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G24" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H24" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K24" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L24" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B25" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C25" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D25" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E25" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F25" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G25" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H25" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J25" t="n">
         <v>0.014</v>
       </c>
       <c r="K25" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L25" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B26" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C26" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D26" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F26" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G26" t="n">
         <v>0.395</v>
@@ -83093,9 +83149,47 @@
         <v>0.014</v>
       </c>
       <c r="K26" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L26" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K27" t="n">
         <v>12.277</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83536,7 +83630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83636,145 +83730,145 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B2" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C2" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D2" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E2" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G2" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I2" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K2" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M2" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P2" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q2" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B3" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C3" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D3" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E3" t="n">
         <v>9200</v>
       </c>
       <c r="F3" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G3" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I3" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K3" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M3" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P3" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q3" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B4" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C4" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D4" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G4" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I4" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K4" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M4" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N4" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P4" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q4" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B5" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C5" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D5" t="n">
         <v>1336369</v>
@@ -83783,28 +83877,28 @@
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G5" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I5" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K5" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M5" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O5" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P5" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q5" t="n">
         <v>710782</v>
@@ -83812,34 +83906,34 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B6" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C6" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D6" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G6" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I6" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K6" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M6" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
@@ -83848,7 +83942,7 @@
         <v>238857</v>
       </c>
       <c r="P6" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q6" t="n">
         <v>710782</v>
@@ -83856,43 +83950,43 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B7" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C7" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D7" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G7" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I7" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K7" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M7" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N7" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P7" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q7" t="n">
         <v>710782</v>
@@ -83900,201 +83994,201 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B8" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C8" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D8" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G8" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I8" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K8" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M8" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N8" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O8" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P8" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q8" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B9" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C9" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D9" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G9" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I9" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K9" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M9" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N9" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O9" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P9" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q9" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B10" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C10" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D10" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G10" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I10" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K10" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M10" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N10" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P10" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q10" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B11" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C11" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D11" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E11" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G11" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I11" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K11" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M11" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N11" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O11" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P11" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q11" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B12" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C12" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D12" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E12" t="n">
         <v>9400</v>
       </c>
       <c r="F12" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G12" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I12" t="n">
         <v>1493578</v>
@@ -84103,7 +84197,7 @@
         <v>270165</v>
       </c>
       <c r="M12" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N12" t="n">
         <v>214475</v>
@@ -84115,39 +84209,39 @@
         <v>380581</v>
       </c>
       <c r="Q12" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B13" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C13" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D13" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E13" t="n">
         <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G13" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I13" t="n">
         <v>1493578</v>
       </c>
       <c r="K13" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M13" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -84156,153 +84250,153 @@
         <v>236857</v>
       </c>
       <c r="P13" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q13" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B14" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C14" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D14" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E14" t="n">
         <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G14" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I14" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K14" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M14" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N14" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O14" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P14" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q14" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B15" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C15" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D15" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E15" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G15" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I15" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K15" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M15" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N15" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O15" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P15" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q15" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B16" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C16" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D16" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E16" t="n">
         <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G16" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I16" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K16" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M16" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N16" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O16" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P16" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q16" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B17" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C17" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D17" t="n">
         <v>1438502</v>
@@ -84311,107 +84405,107 @@
         <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G17" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I17" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K17" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M17" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N17" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O17" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P17" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q17" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B18" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C18" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D18" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E18" t="n">
         <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G18" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I18" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K18" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M18" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N18" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O18" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P18" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q18" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B19" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C19" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D19" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E19" t="n">
         <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G19" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I19" t="n">
         <v>1488515</v>
       </c>
       <c r="K19" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M19" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N19" t="n">
         <v>214475</v>
@@ -84420,7 +84514,7 @@
         <v>247857</v>
       </c>
       <c r="P19" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q19" t="n">
         <v>738429</v>
@@ -84428,34 +84522,34 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B20" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C20" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D20" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E20" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G20" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I20" t="n">
         <v>1488515</v>
       </c>
       <c r="K20" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M20" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N20" t="n">
         <v>214475</v>
@@ -84464,7 +84558,7 @@
         <v>247857</v>
       </c>
       <c r="P20" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q20" t="n">
         <v>738429</v>
@@ -84472,78 +84566,78 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B21" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C21" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D21" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E21" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F21" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G21" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I21" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K21" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M21" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N21" t="n">
         <v>214475</v>
       </c>
       <c r="O21" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P21" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q21" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B22" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C22" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D22" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E22" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F22" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G22" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I22" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K22" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M22" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N22" t="n">
         <v>214475</v>
@@ -84552,42 +84646,42 @@
         <v>264857</v>
       </c>
       <c r="P22" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q22" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B23" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C23" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D23" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E23" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F23" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G23" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I23" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K23" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M23" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N23" t="n">
         <v>214475</v>
@@ -84596,101 +84690,98 @@
         <v>264857</v>
       </c>
       <c r="P23" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q23" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B24" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C24" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D24" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E24" t="n">
         <v>9300</v>
       </c>
       <c r="F24" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G24" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I24" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K24" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M24" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N24" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O24" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P24" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q24" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R24" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B25" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C25" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D25" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E25" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F25" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G25" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I25" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K25" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M25" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N25" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O25" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P25" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q25" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R25" t="n">
         <v>15000</v>
@@ -84698,40 +84789,40 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B26" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C26" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D26" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E26" t="n">
         <v>9100</v>
       </c>
       <c r="F26" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G26" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I26" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K26" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M26" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N26" t="n">
         <v>189475</v>
       </c>
       <c r="O26" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P26" t="n">
         <v>375660</v>
@@ -84740,6 +84831,53 @@
         <v>773586</v>
       </c>
       <c r="R26" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C27" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E27" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K27" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N27" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O27" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P27" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R27" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -92069,7 +92207,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.382</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="652">
@@ -92079,7 +92217,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.389</v>
+        <v>1.391</v>
       </c>
     </row>
     <row r="653">
@@ -92089,7 +92227,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.51</v>
+        <v>2.515</v>
       </c>
     </row>
     <row r="654">
@@ -92099,7 +92237,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
     </row>
     <row r="655">
@@ -92109,7 +92247,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
     </row>
     <row r="656">
@@ -92119,7 +92257,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.696</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="657">
@@ -92129,7 +92267,7 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3.211</v>
+        <v>3.207</v>
       </c>
     </row>
     <row r="658">
@@ -92139,7 +92277,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.262</v>
+        <v>3.239</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80303,9 +80303,36 @@
       <c r="A2437" s="4" t="n">
         <v>46266</v>
       </c>
+      <c r="B2437" t="n">
+        <v>3.163</v>
+      </c>
+      <c r="C2437" t="n">
+        <v>3.205</v>
+      </c>
+      <c r="D2437" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="E2437" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="F2437" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="G2437" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="H2437" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="I2437" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="K2437" t="n">
+        <v>12.109</v>
+      </c>
       <c r="L2437" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81291,7 +81318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81356,153 +81383,153 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B2" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C2" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D2" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F2" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G2" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H2" t="n">
         <v>0.342</v>
       </c>
       <c r="I2" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K2" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C3" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F3" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G3" t="n">
         <v>0.444</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K3" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B4" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C4" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D4" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E4" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K4" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B5" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C5" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D5" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F5" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G5" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K5" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B6" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C6" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D6" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F6" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
@@ -81511,27 +81538,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B7" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C7" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D7" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E7" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F7" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
@@ -81543,178 +81570,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B8" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C8" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D8" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
       </c>
       <c r="H8" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I8" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B9" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C9" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D9" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F9" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B10" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C10" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D10" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G10" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K10" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B11" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C11" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D11" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E11" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G11" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C12" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F12" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G12" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K12" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B13" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C13" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D13" t="n">
         <v>1.44</v>
@@ -81723,7 +81750,7 @@
         <v>0.261</v>
       </c>
       <c r="F13" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G13" t="n">
         <v>0.435</v>
@@ -81732,222 +81759,222 @@
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K13" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B14" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C14" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D14" t="n">
         <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F14" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G14" t="n">
         <v>0.435</v>
       </c>
       <c r="H14" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K14" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B15" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C15" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D15" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F15" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G15" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K15" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B16" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C16" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D16" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F16" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G16" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K16" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B17" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C17" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D17" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E17" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G17" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K17" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B18" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C18" t="n">
         <v>3.232</v>
       </c>
       <c r="D18" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F18" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G18" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H18" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K18" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C19" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D19" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G19" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H19" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K19" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B20" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C20" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D20" t="n">
         <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F20" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G20" t="n">
         <v>0.446</v>
@@ -81959,27 +81986,27 @@
         <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B21" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C21" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D21" t="n">
         <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F21" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G21" t="n">
         <v>0.446</v>
@@ -81991,59 +82018,59 @@
         <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B22" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C22" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D22" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F22" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G22" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H22" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I22" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B23" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C23" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D23" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E23" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F23" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G23" t="n">
         <v>0.462</v>
@@ -82052,30 +82079,30 @@
         <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K23" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B24" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C24" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D24" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F24" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G24" t="n">
         <v>0.462</v>
@@ -82084,100 +82111,97 @@
         <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K24" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B25" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C25" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D25" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E25" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F25" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G25" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H25" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K25" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B26" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C26" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D26" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E26" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F26" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G26" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H26" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J26" t="n">
         <v>0.014</v>
       </c>
       <c r="K26" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B27" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C27" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D27" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F27" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G27" t="n">
         <v>0.395</v>
@@ -82192,6 +82216,41 @@
         <v>0.014</v>
       </c>
       <c r="K27" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82206,7 +82265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82276,165 +82335,165 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B2" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C2" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D2" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F2" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G2" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H2" t="n">
         <v>0.342</v>
       </c>
       <c r="I2" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K2" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
       <c r="L2" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C3" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D3" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F3" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G3" t="n">
         <v>0.444</v>
       </c>
       <c r="H3" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K3" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L3" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B4" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C4" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D4" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E4" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F4" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I4" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K4" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L4" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B5" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C5" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D5" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E5" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F5" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G5" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K5" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L5" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B6" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C6" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D6" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F6" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G6" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H6" t="n">
         <v>0.367</v>
@@ -82443,30 +82502,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L6" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B7" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C7" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D7" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E7" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F7" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G7" t="n">
         <v>0.437</v>
@@ -82478,196 +82537,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L7" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B8" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C8" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D8" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E8" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F8" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
       </c>
       <c r="H8" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I8" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L8" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B9" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C9" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D9" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E9" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F9" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I9" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L9" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B10" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C10" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D10" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F10" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G10" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K10" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L10" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B11" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C11" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D11" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E11" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F11" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G11" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L11" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C12" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E12" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F12" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G12" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K12" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L12" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B13" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C13" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D13" t="n">
         <v>1.44</v>
@@ -82676,7 +82735,7 @@
         <v>0.261</v>
       </c>
       <c r="F13" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G13" t="n">
         <v>0.435</v>
@@ -82685,243 +82744,243 @@
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K13" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L13" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B14" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C14" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D14" t="n">
         <v>1.44</v>
       </c>
       <c r="E14" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F14" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G14" t="n">
         <v>0.435</v>
       </c>
       <c r="H14" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K14" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L14" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B15" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C15" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D15" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F15" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G15" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H15" t="n">
         <v>0.365</v>
       </c>
       <c r="I15" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K15" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L15" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B16" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C16" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D16" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F16" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G16" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K16" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L16" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B17" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C17" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D17" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E17" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G17" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K17" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L17" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B18" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C18" t="n">
         <v>3.232</v>
       </c>
       <c r="D18" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F18" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G18" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H18" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K18" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L18" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C19" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D19" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E19" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G19" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H19" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I19" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K19" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L19" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B20" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C20" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D20" t="n">
         <v>1.435</v>
       </c>
       <c r="E20" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F20" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G20" t="n">
         <v>0.446</v>
@@ -82933,30 +82992,30 @@
         <v>0.712</v>
       </c>
       <c r="K20" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L20" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B21" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C21" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D21" t="n">
         <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F21" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G21" t="n">
         <v>0.446</v>
@@ -82968,65 +83027,65 @@
         <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L21" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B22" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C22" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D22" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F22" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G22" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H22" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I22" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L22" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B23" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C23" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D23" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E23" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F23" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G23" t="n">
         <v>0.462</v>
@@ -83035,33 +83094,33 @@
         <v>0.343</v>
       </c>
       <c r="I23" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K23" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L23" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B24" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C24" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D24" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E24" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F24" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G24" t="n">
         <v>0.462</v>
@@ -83070,109 +83129,106 @@
         <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K24" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L24" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B25" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C25" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D25" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E25" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F25" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G25" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H25" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K25" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L25" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B26" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C26" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D26" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E26" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F26" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G26" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H26" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I26" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J26" t="n">
         <v>0.014</v>
       </c>
       <c r="K26" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L26" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B27" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C27" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D27" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F27" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G27" t="n">
         <v>0.395</v>
@@ -83187,9 +83243,47 @@
         <v>0.014</v>
       </c>
       <c r="K27" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.277</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L28" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83630,7 +83724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R27"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83730,189 +83824,189 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B2" t="n">
-        <v>977033</v>
+        <v>1104818</v>
       </c>
       <c r="C2" t="n">
-        <v>493347</v>
+        <v>667392</v>
       </c>
       <c r="D2" t="n">
-        <v>1277653</v>
+        <v>1498652</v>
       </c>
       <c r="E2" t="n">
         <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>1875666</v>
+        <v>1894575</v>
       </c>
       <c r="G2" t="n">
-        <v>1356150</v>
+        <v>1428865</v>
       </c>
       <c r="I2" t="n">
-        <v>1507739</v>
+        <v>1526911</v>
       </c>
       <c r="K2" t="n">
-        <v>213692</v>
+        <v>285753</v>
       </c>
       <c r="M2" t="n">
-        <v>2729375</v>
+        <v>2731003</v>
       </c>
       <c r="N2" t="n">
         <v>214475</v>
       </c>
       <c r="O2" t="n">
-        <v>246357</v>
+        <v>224840</v>
       </c>
       <c r="P2" t="n">
-        <v>354625</v>
+        <v>355073</v>
       </c>
       <c r="Q2" t="n">
-        <v>508923</v>
+        <v>614624</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C3" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D3" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E3" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F3" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G3" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I3" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K3" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M3" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P3" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q3" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B4" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C4" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D4" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E4" t="n">
         <v>9200</v>
       </c>
       <c r="F4" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G4" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I4" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K4" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M4" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P4" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q4" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B5" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C5" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D5" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G5" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I5" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K5" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M5" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N5" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P5" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q5" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B6" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C6" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D6" t="n">
         <v>1336369</v>
@@ -83921,28 +84015,28 @@
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G6" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I6" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K6" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M6" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N6" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O6" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P6" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q6" t="n">
         <v>710782</v>
@@ -83950,34 +84044,34 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B7" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C7" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D7" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G7" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I7" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K7" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M7" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
@@ -83986,7 +84080,7 @@
         <v>238857</v>
       </c>
       <c r="P7" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q7" t="n">
         <v>710782</v>
@@ -83994,43 +84088,43 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B8" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C8" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D8" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G8" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I8" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K8" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M8" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N8" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P8" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q8" t="n">
         <v>710782</v>
@@ -84038,201 +84132,201 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B9" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C9" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D9" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G9" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I9" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K9" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M9" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N9" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O9" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P9" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q9" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B10" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C10" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D10" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G10" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I10" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K10" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M10" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N10" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O10" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P10" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q10" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B11" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C11" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D11" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G11" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I11" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K11" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M11" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N11" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P11" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q11" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B12" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C12" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D12" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E12" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G12" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I12" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K12" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M12" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N12" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O12" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P12" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q12" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B13" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C13" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D13" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E13" t="n">
         <v>9400</v>
       </c>
       <c r="F13" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G13" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I13" t="n">
         <v>1493578</v>
@@ -84241,7 +84335,7 @@
         <v>270165</v>
       </c>
       <c r="M13" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N13" t="n">
         <v>214475</v>
@@ -84253,39 +84347,39 @@
         <v>380581</v>
       </c>
       <c r="Q13" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B14" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C14" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D14" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E14" t="n">
         <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G14" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I14" t="n">
         <v>1493578</v>
       </c>
       <c r="K14" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M14" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -84294,153 +84388,153 @@
         <v>236857</v>
       </c>
       <c r="P14" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q14" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B15" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C15" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D15" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E15" t="n">
         <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G15" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I15" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K15" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M15" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N15" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O15" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P15" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q15" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B16" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C16" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D16" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E16" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G16" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I16" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K16" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M16" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N16" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O16" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P16" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q16" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B17" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C17" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D17" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E17" t="n">
         <v>9200</v>
       </c>
       <c r="F17" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G17" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I17" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K17" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M17" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N17" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O17" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P17" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q17" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B18" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C18" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D18" t="n">
         <v>1438502</v>
@@ -84449,107 +84543,107 @@
         <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G18" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I18" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K18" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M18" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N18" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O18" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P18" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q18" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B19" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C19" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D19" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E19" t="n">
         <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G19" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I19" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K19" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M19" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N19" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O19" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P19" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q19" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B20" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C20" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D20" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E20" t="n">
         <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G20" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I20" t="n">
         <v>1488515</v>
       </c>
       <c r="K20" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M20" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N20" t="n">
         <v>214475</v>
@@ -84558,7 +84652,7 @@
         <v>247857</v>
       </c>
       <c r="P20" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q20" t="n">
         <v>738429</v>
@@ -84566,34 +84660,34 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B21" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C21" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D21" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E21" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G21" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I21" t="n">
         <v>1488515</v>
       </c>
       <c r="K21" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M21" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N21" t="n">
         <v>214475</v>
@@ -84602,7 +84696,7 @@
         <v>247857</v>
       </c>
       <c r="P21" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q21" t="n">
         <v>738429</v>
@@ -84610,78 +84704,78 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B22" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C22" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D22" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E22" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F22" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G22" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I22" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K22" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M22" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N22" t="n">
         <v>214475</v>
       </c>
       <c r="O22" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P22" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q22" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B23" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C23" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D23" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E23" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F23" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G23" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I23" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K23" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M23" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N23" t="n">
         <v>214475</v>
@@ -84690,42 +84784,42 @@
         <v>264857</v>
       </c>
       <c r="P23" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q23" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B24" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C24" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D24" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E24" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F24" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G24" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I24" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K24" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M24" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N24" t="n">
         <v>214475</v>
@@ -84734,101 +84828,98 @@
         <v>264857</v>
       </c>
       <c r="P24" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q24" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B25" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C25" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D25" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E25" t="n">
         <v>9300</v>
       </c>
       <c r="F25" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G25" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I25" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K25" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M25" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N25" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O25" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P25" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q25" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R25" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B26" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C26" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D26" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E26" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F26" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G26" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I26" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K26" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M26" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N26" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O26" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P26" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q26" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R26" t="n">
         <v>15000</v>
@@ -84836,40 +84927,40 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B27" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C27" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D27" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E27" t="n">
         <v>9100</v>
       </c>
       <c r="F27" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G27" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I27" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K27" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M27" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N27" t="n">
         <v>189475</v>
       </c>
       <c r="O27" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P27" t="n">
         <v>375660</v>
@@ -84878,6 +84969,53 @@
         <v>773586</v>
       </c>
       <c r="R27" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C28" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K28" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N28" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O28" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P28" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R28" t="n">
         <v>15000</v>
       </c>
     </row>
@@ -92207,7 +92345,7 @@
         </is>
       </c>
       <c r="D651" t="n">
-        <v>0.375</v>
+        <v>0.371</v>
       </c>
     </row>
     <row r="652">
@@ -92217,7 +92355,7 @@
         </is>
       </c>
       <c r="D652" t="n">
-        <v>1.391</v>
+        <v>1.394</v>
       </c>
     </row>
     <row r="653">
@@ -92227,7 +92365,7 @@
         </is>
       </c>
       <c r="D653" t="n">
-        <v>2.515</v>
+        <v>2.519</v>
       </c>
     </row>
     <row r="654">
@@ -92237,7 +92375,7 @@
         </is>
       </c>
       <c r="D654" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="655">
@@ -92247,7 +92385,7 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="656">
@@ -92257,7 +92395,7 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="657">
@@ -92277,7 +92415,7 @@
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3.239</v>
+        <v>3.236</v>
       </c>
     </row>
   </sheetData>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80293,9 +80293,36 @@
       <c r="A2436" s="4" t="n">
         <v>46265</v>
       </c>
+      <c r="B2436" t="n">
+        <v>3.392</v>
+      </c>
+      <c r="C2436" t="n">
+        <v>3.207</v>
+      </c>
+      <c r="D2436" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="E2436" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="F2436" t="n">
+        <v>2.512</v>
+      </c>
+      <c r="G2436" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="H2436" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="I2436" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="K2436" t="n">
+        <v>12.534</v>
+      </c>
       <c r="L2436" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81318,7 +81345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81383,185 +81410,185 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B2" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C2" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E2" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F2" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H2" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K2" t="n">
-        <v>12.108</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B3" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C3" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D3" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F3" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G3" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H3" t="n">
         <v>0.342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K3" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B4" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C4" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D4" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F4" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G4" t="n">
         <v>0.444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K4" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C5" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D5" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E5" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F5" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K5" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C6" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D6" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E6" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F6" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H6" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K6" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B7" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C7" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F7" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G7" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
@@ -81570,27 +81597,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B8" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C8" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D8" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F8" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
@@ -81602,178 +81629,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B9" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C9" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D9" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I9" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C10" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D10" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E10" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F10" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
       </c>
       <c r="H10" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I10" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B11" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C11" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D11" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F11" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G11" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K11" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B12" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C12" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D12" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C13" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E13" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F13" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G13" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K13" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B14" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C14" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D14" t="n">
         <v>1.44</v>
@@ -81782,7 +81809,7 @@
         <v>0.261</v>
       </c>
       <c r="F14" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G14" t="n">
         <v>0.435</v>
@@ -81791,222 +81818,222 @@
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K14" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B15" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C15" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D15" t="n">
         <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F15" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G15" t="n">
         <v>0.435</v>
       </c>
       <c r="H15" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K15" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B16" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C16" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D16" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F16" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G16" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K16" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B17" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C17" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F17" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G17" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K17" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B18" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C18" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D18" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E18" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G18" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K18" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B19" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C19" t="n">
         <v>3.232</v>
       </c>
       <c r="D19" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F19" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G19" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H19" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K19" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C20" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D20" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E20" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G20" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H20" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K20" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B21" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C21" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D21" t="n">
         <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F21" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G21" t="n">
         <v>0.446</v>
@@ -82018,27 +82045,27 @@
         <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B22" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C22" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D22" t="n">
         <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F22" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G22" t="n">
         <v>0.446</v>
@@ -82050,59 +82077,59 @@
         <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B23" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C23" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D23" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F23" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G23" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H23" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I23" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B24" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C24" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D24" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E24" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F24" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G24" t="n">
         <v>0.462</v>
@@ -82111,30 +82138,30 @@
         <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K24" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B25" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C25" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D25" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E25" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F25" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G25" t="n">
         <v>0.462</v>
@@ -82143,100 +82170,97 @@
         <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K25" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C26" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D26" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E26" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F26" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G26" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K26" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B27" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C27" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D27" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E27" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F27" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G27" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H27" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J27" t="n">
         <v>0.014</v>
       </c>
       <c r="K27" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B28" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C28" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D28" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F28" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G28" t="n">
         <v>0.395</v>
@@ -82251,6 +82275,41 @@
         <v>0.014</v>
       </c>
       <c r="K28" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82265,7 +82324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82335,200 +82394,200 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B2" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C2" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E2" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F2" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H2" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K2" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
       <c r="L2" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B3" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C3" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D3" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F3" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G3" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H3" t="n">
         <v>0.342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K3" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
       <c r="L3" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B4" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C4" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D4" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E4" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F4" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G4" t="n">
         <v>0.444</v>
       </c>
       <c r="H4" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K4" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L4" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C5" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D5" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E5" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F5" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I5" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K5" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L5" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C6" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D6" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E6" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F6" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G6" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H6" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K6" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L6" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B7" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C7" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F7" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G7" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H7" t="n">
         <v>0.367</v>
@@ -82537,30 +82596,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L7" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B8" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C8" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D8" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F8" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
@@ -82572,196 +82631,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L8" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B9" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C9" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D9" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F9" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
       </c>
       <c r="H9" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I9" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L9" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C10" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D10" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E10" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F10" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
       </c>
       <c r="H10" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I10" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L10" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B11" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C11" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D11" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F11" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G11" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K11" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L11" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B12" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C12" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D12" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E12" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G12" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L12" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C13" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E13" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F13" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G13" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K13" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L13" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B14" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C14" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D14" t="n">
         <v>1.44</v>
@@ -82770,7 +82829,7 @@
         <v>0.261</v>
       </c>
       <c r="F14" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G14" t="n">
         <v>0.435</v>
@@ -82779,243 +82838,243 @@
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K14" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L14" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B15" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C15" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D15" t="n">
         <v>1.44</v>
       </c>
       <c r="E15" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F15" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G15" t="n">
         <v>0.435</v>
       </c>
       <c r="H15" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K15" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L15" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B16" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C16" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D16" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F16" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G16" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H16" t="n">
         <v>0.365</v>
       </c>
       <c r="I16" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K16" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L16" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B17" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C17" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F17" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G17" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K17" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L17" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B18" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C18" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D18" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E18" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G18" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K18" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L18" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B19" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C19" t="n">
         <v>3.232</v>
       </c>
       <c r="D19" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F19" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G19" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H19" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K19" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L19" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C20" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D20" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E20" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G20" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H20" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K20" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L20" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B21" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C21" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D21" t="n">
         <v>1.435</v>
       </c>
       <c r="E21" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F21" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G21" t="n">
         <v>0.446</v>
@@ -83027,30 +83086,30 @@
         <v>0.712</v>
       </c>
       <c r="K21" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L21" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B22" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C22" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D22" t="n">
         <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F22" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G22" t="n">
         <v>0.446</v>
@@ -83062,65 +83121,65 @@
         <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L22" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B23" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C23" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D23" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F23" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G23" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H23" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I23" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L23" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B24" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C24" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D24" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E24" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F24" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G24" t="n">
         <v>0.462</v>
@@ -83129,33 +83188,33 @@
         <v>0.343</v>
       </c>
       <c r="I24" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K24" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L24" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B25" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C25" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D25" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E25" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F25" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G25" t="n">
         <v>0.462</v>
@@ -83164,109 +83223,106 @@
         <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K25" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L25" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C26" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D26" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E26" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F26" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G26" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K26" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L26" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B27" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C27" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D27" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E27" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F27" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G27" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H27" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I27" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J27" t="n">
         <v>0.014</v>
       </c>
       <c r="K27" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L27" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B28" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C28" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D28" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F28" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G28" t="n">
         <v>0.395</v>
@@ -83281,9 +83337,47 @@
         <v>0.014</v>
       </c>
       <c r="K28" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.277</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L29" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83724,7 +83818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83824,233 +83918,233 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B2" t="n">
-        <v>1104818</v>
+        <v>1453305</v>
       </c>
       <c r="C2" t="n">
-        <v>667392</v>
+        <v>660021</v>
       </c>
       <c r="D2" t="n">
-        <v>1498652</v>
+        <v>1394810</v>
       </c>
       <c r="E2" t="n">
         <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>1894575</v>
+        <v>1966997</v>
       </c>
       <c r="G2" t="n">
-        <v>1428865</v>
+        <v>1358589</v>
       </c>
       <c r="I2" t="n">
-        <v>1526911</v>
+        <v>1530881</v>
       </c>
       <c r="K2" t="n">
-        <v>285753</v>
+        <v>224505</v>
       </c>
       <c r="M2" t="n">
-        <v>2731003</v>
+        <v>2605275</v>
       </c>
       <c r="N2" t="n">
-        <v>214475</v>
+        <v>273068</v>
       </c>
       <c r="O2" t="n">
-        <v>224840</v>
+        <v>402811</v>
       </c>
       <c r="P2" t="n">
-        <v>355073</v>
+        <v>368707</v>
       </c>
       <c r="Q2" t="n">
-        <v>614624</v>
+        <v>750038</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B3" t="n">
-        <v>977033</v>
+        <v>1104818</v>
       </c>
       <c r="C3" t="n">
-        <v>493347</v>
+        <v>667392</v>
       </c>
       <c r="D3" t="n">
-        <v>1277653</v>
+        <v>1498652</v>
       </c>
       <c r="E3" t="n">
         <v>9000</v>
       </c>
       <c r="F3" t="n">
-        <v>1875666</v>
+        <v>1894575</v>
       </c>
       <c r="G3" t="n">
-        <v>1356150</v>
+        <v>1428865</v>
       </c>
       <c r="I3" t="n">
-        <v>1507739</v>
+        <v>1526911</v>
       </c>
       <c r="K3" t="n">
-        <v>213692</v>
+        <v>285753</v>
       </c>
       <c r="M3" t="n">
-        <v>2729375</v>
+        <v>2731003</v>
       </c>
       <c r="N3" t="n">
         <v>214475</v>
       </c>
       <c r="O3" t="n">
-        <v>246357</v>
+        <v>224840</v>
       </c>
       <c r="P3" t="n">
-        <v>354625</v>
+        <v>355073</v>
       </c>
       <c r="Q3" t="n">
-        <v>508923</v>
+        <v>614624</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B4" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C4" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D4" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E4" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F4" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G4" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I4" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K4" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M4" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P4" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q4" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B5" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C5" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D5" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E5" t="n">
         <v>9200</v>
       </c>
       <c r="F5" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G5" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I5" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K5" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M5" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P5" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q5" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B6" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C6" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D6" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G6" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I6" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K6" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M6" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N6" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P6" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q6" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B7" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C7" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D7" t="n">
         <v>1336369</v>
@@ -84059,28 +84153,28 @@
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G7" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I7" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K7" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M7" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N7" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O7" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P7" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q7" t="n">
         <v>710782</v>
@@ -84088,34 +84182,34 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B8" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C8" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D8" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G8" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I8" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K8" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M8" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
@@ -84124,7 +84218,7 @@
         <v>238857</v>
       </c>
       <c r="P8" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q8" t="n">
         <v>710782</v>
@@ -84132,43 +84226,43 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B9" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C9" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D9" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G9" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I9" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K9" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M9" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N9" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P9" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q9" t="n">
         <v>710782</v>
@@ -84176,201 +84270,201 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B10" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C10" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D10" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G10" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I10" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K10" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M10" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N10" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O10" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P10" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q10" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B11" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C11" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D11" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G11" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I11" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K11" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M11" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N11" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O11" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P11" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q11" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B12" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C12" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D12" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G12" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I12" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K12" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M12" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N12" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P12" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q12" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B13" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C13" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D13" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E13" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G13" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I13" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K13" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M13" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N13" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O13" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P13" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q13" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B14" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C14" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D14" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E14" t="n">
         <v>9400</v>
       </c>
       <c r="F14" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G14" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I14" t="n">
         <v>1493578</v>
@@ -84379,7 +84473,7 @@
         <v>270165</v>
       </c>
       <c r="M14" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N14" t="n">
         <v>214475</v>
@@ -84391,39 +84485,39 @@
         <v>380581</v>
       </c>
       <c r="Q14" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B15" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C15" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D15" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E15" t="n">
         <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G15" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I15" t="n">
         <v>1493578</v>
       </c>
       <c r="K15" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M15" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -84432,153 +84526,153 @@
         <v>236857</v>
       </c>
       <c r="P15" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q15" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B16" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C16" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D16" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E16" t="n">
         <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G16" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I16" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K16" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M16" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N16" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O16" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P16" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q16" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B17" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C17" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D17" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E17" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G17" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I17" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K17" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M17" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N17" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O17" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P17" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q17" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B18" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C18" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D18" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E18" t="n">
         <v>9200</v>
       </c>
       <c r="F18" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G18" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I18" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K18" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M18" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N18" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O18" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P18" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q18" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B19" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C19" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D19" t="n">
         <v>1438502</v>
@@ -84587,107 +84681,107 @@
         <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G19" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I19" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K19" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M19" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N19" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O19" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P19" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q19" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B20" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C20" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D20" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E20" t="n">
         <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G20" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I20" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K20" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M20" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N20" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O20" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P20" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q20" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B21" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C21" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D21" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E21" t="n">
         <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G21" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I21" t="n">
         <v>1488515</v>
       </c>
       <c r="K21" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M21" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N21" t="n">
         <v>214475</v>
@@ -84696,7 +84790,7 @@
         <v>247857</v>
       </c>
       <c r="P21" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q21" t="n">
         <v>738429</v>
@@ -84704,34 +84798,34 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B22" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C22" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D22" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E22" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F22" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G22" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I22" t="n">
         <v>1488515</v>
       </c>
       <c r="K22" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M22" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N22" t="n">
         <v>214475</v>
@@ -84740,7 +84834,7 @@
         <v>247857</v>
       </c>
       <c r="P22" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q22" t="n">
         <v>738429</v>
@@ -84748,78 +84842,78 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B23" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C23" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D23" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E23" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F23" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G23" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I23" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K23" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M23" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N23" t="n">
         <v>214475</v>
       </c>
       <c r="O23" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P23" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q23" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B24" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C24" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D24" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E24" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F24" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G24" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I24" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K24" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M24" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N24" t="n">
         <v>214475</v>
@@ -84828,42 +84922,42 @@
         <v>264857</v>
       </c>
       <c r="P24" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q24" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B25" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C25" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D25" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E25" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F25" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G25" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I25" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K25" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M25" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N25" t="n">
         <v>214475</v>
@@ -84872,101 +84966,98 @@
         <v>264857</v>
       </c>
       <c r="P25" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q25" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B26" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C26" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D26" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E26" t="n">
         <v>9300</v>
       </c>
       <c r="F26" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G26" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I26" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K26" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M26" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N26" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O26" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P26" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q26" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R26" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B27" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C27" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D27" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E27" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F27" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G27" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I27" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K27" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M27" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N27" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O27" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P27" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q27" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R27" t="n">
         <v>15000</v>
@@ -84974,40 +85065,40 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B28" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C28" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D28" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E28" t="n">
         <v>9100</v>
       </c>
       <c r="F28" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G28" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I28" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K28" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M28" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N28" t="n">
         <v>189475</v>
       </c>
       <c r="O28" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P28" t="n">
         <v>375660</v>
@@ -85016,6 +85107,53 @@
         <v>773586</v>
       </c>
       <c r="R28" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C29" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K29" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N29" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O29" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P29" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R29" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80283,9 +80283,36 @@
       <c r="A2435" s="4" t="n">
         <v>46264</v>
       </c>
+      <c r="B2435" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C2435" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="D2435" t="n">
+        <v>1.463</v>
+      </c>
+      <c r="E2435" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="F2435" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G2435" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="H2435" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I2435" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="K2435" t="n">
+        <v>12.429</v>
+      </c>
       <c r="L2435" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81345,7 +81372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81410,217 +81437,217 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B2" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C2" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D2" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F2" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H2" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K2" t="n">
-        <v>12.534</v>
+        <v>12.428</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B3" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C3" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F3" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K3" t="n">
-        <v>12.108</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C4" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D4" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F4" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G4" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H4" t="n">
         <v>0.342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K4" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B5" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C5" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D5" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E5" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G5" t="n">
         <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K5" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B6" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C6" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D6" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F6" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G6" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K6" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C7" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D7" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E7" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F7" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G7" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H7" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K7" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B8" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C8" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D8" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E8" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F8" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
@@ -81629,27 +81656,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B9" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C9" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D9" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
@@ -81661,178 +81688,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B10" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C10" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D10" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
       </c>
       <c r="H10" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I10" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C11" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D11" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E11" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F11" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
       </c>
       <c r="H11" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I11" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C12" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D12" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F12" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G12" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K12" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B13" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C13" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D13" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E13" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C14" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E14" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F14" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G14" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K14" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B15" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C15" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D15" t="n">
         <v>1.44</v>
@@ -81841,7 +81868,7 @@
         <v>0.261</v>
       </c>
       <c r="F15" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G15" t="n">
         <v>0.435</v>
@@ -81850,222 +81877,222 @@
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K15" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B16" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C16" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D16" t="n">
         <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F16" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G16" t="n">
         <v>0.435</v>
       </c>
       <c r="H16" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K16" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B17" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C17" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D17" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G17" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K17" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B18" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C18" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D18" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F18" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G18" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K18" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B19" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C19" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D19" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E19" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G19" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K19" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C20" t="n">
         <v>3.232</v>
       </c>
       <c r="D20" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F20" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G20" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K20" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B21" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C21" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E21" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G21" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K21" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B22" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C22" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D22" t="n">
         <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F22" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G22" t="n">
         <v>0.446</v>
@@ -82077,27 +82104,27 @@
         <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B23" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C23" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D23" t="n">
         <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F23" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G23" t="n">
         <v>0.446</v>
@@ -82109,59 +82136,59 @@
         <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B24" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C24" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D24" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F24" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G24" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H24" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I24" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B25" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C25" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D25" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E25" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F25" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G25" t="n">
         <v>0.462</v>
@@ -82170,30 +82197,30 @@
         <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K25" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B26" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C26" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D26" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E26" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F26" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G26" t="n">
         <v>0.462</v>
@@ -82202,100 +82229,97 @@
         <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K26" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C27" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D27" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E27" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F27" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G27" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H27" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K27" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B28" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C28" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D28" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E28" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F28" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G28" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H28" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J28" t="n">
         <v>0.014</v>
       </c>
       <c r="K28" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B29" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C29" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D29" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F29" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G29" t="n">
         <v>0.395</v>
@@ -82310,6 +82334,41 @@
         <v>0.014</v>
       </c>
       <c r="K29" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82324,7 +82383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82394,235 +82453,235 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B2" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C2" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D2" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E2" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F2" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G2" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H2" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K2" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
       <c r="L2" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B3" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C3" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E3" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F3" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G3" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H3" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I3" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K3" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
       <c r="L3" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C4" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D4" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F4" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G4" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H4" t="n">
         <v>0.342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K4" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
       <c r="L4" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B5" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C5" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D5" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E5" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F5" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G5" t="n">
         <v>0.444</v>
       </c>
       <c r="H5" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K5" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L5" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B6" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C6" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D6" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F6" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G6" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I6" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K6" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L6" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C7" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D7" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E7" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F7" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G7" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H7" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K7" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L7" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B8" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C8" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D8" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E8" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F8" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H8" t="n">
         <v>0.367</v>
@@ -82631,30 +82690,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L8" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B9" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C9" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D9" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E9" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F9" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G9" t="n">
         <v>0.437</v>
@@ -82666,196 +82725,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L9" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B10" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C10" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D10" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E10" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
       </c>
       <c r="H10" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I10" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L10" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C11" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D11" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E11" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F11" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
       </c>
       <c r="H11" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I11" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L11" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C12" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D12" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F12" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G12" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H12" t="n">
         <v>0.367</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K12" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L12" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B13" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C13" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D13" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E13" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L13" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C14" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E14" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F14" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G14" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K14" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L14" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B15" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C15" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D15" t="n">
         <v>1.44</v>
@@ -82864,7 +82923,7 @@
         <v>0.261</v>
       </c>
       <c r="F15" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G15" t="n">
         <v>0.435</v>
@@ -82873,243 +82932,243 @@
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K15" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L15" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B16" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C16" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D16" t="n">
         <v>1.44</v>
       </c>
       <c r="E16" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F16" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G16" t="n">
         <v>0.435</v>
       </c>
       <c r="H16" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K16" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L16" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B17" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C17" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D17" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F17" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G17" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H17" t="n">
         <v>0.365</v>
       </c>
       <c r="I17" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K17" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L17" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B18" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C18" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D18" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F18" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G18" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K18" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L18" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B19" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C19" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D19" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E19" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G19" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K19" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L19" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C20" t="n">
         <v>3.232</v>
       </c>
       <c r="D20" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F20" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G20" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K20" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L20" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B21" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C21" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E21" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G21" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H21" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K21" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L21" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B22" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C22" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D22" t="n">
         <v>1.435</v>
       </c>
       <c r="E22" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F22" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G22" t="n">
         <v>0.446</v>
@@ -83121,30 +83180,30 @@
         <v>0.712</v>
       </c>
       <c r="K22" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L22" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B23" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C23" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D23" t="n">
         <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F23" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G23" t="n">
         <v>0.446</v>
@@ -83156,65 +83215,65 @@
         <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L23" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B24" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C24" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D24" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F24" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G24" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H24" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I24" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L24" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B25" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C25" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D25" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E25" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F25" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G25" t="n">
         <v>0.462</v>
@@ -83223,33 +83282,33 @@
         <v>0.343</v>
       </c>
       <c r="I25" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K25" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L25" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B26" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C26" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D26" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E26" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F26" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G26" t="n">
         <v>0.462</v>
@@ -83258,109 +83317,106 @@
         <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K26" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L26" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C27" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D27" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E27" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F27" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G27" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H27" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K27" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L27" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B28" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C28" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D28" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E28" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F28" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G28" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H28" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J28" t="n">
         <v>0.014</v>
       </c>
       <c r="K28" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L28" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B29" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C29" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D29" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F29" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G29" t="n">
         <v>0.395</v>
@@ -83375,9 +83431,47 @@
         <v>0.014</v>
       </c>
       <c r="K29" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L29" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.277</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83818,7 +83912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -83918,277 +84012,277 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B2" t="n">
-        <v>1453305</v>
+        <v>1428345</v>
       </c>
       <c r="C2" t="n">
-        <v>660021</v>
+        <v>613887</v>
       </c>
       <c r="D2" t="n">
-        <v>1394810</v>
+        <v>1360335</v>
       </c>
       <c r="E2" t="n">
         <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>1966997</v>
+        <v>2000629</v>
       </c>
       <c r="G2" t="n">
-        <v>1358589</v>
+        <v>1229134</v>
       </c>
       <c r="I2" t="n">
-        <v>1530881</v>
+        <v>1516881</v>
       </c>
       <c r="K2" t="n">
-        <v>224505</v>
+        <v>265281</v>
       </c>
       <c r="M2" t="n">
-        <v>2605275</v>
+        <v>2655010</v>
       </c>
       <c r="N2" t="n">
-        <v>273068</v>
+        <v>275644</v>
       </c>
       <c r="O2" t="n">
-        <v>402811</v>
+        <v>405391</v>
       </c>
       <c r="P2" t="n">
-        <v>368707</v>
+        <v>393345</v>
       </c>
       <c r="Q2" t="n">
-        <v>750038</v>
+        <v>735394</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B3" t="n">
-        <v>1104818</v>
+        <v>1453305</v>
       </c>
       <c r="C3" t="n">
-        <v>667392</v>
+        <v>660021</v>
       </c>
       <c r="D3" t="n">
-        <v>1498652</v>
+        <v>1394810</v>
       </c>
       <c r="E3" t="n">
         <v>9000</v>
       </c>
       <c r="F3" t="n">
-        <v>1894575</v>
+        <v>1966997</v>
       </c>
       <c r="G3" t="n">
-        <v>1428865</v>
+        <v>1358589</v>
       </c>
       <c r="I3" t="n">
-        <v>1526911</v>
+        <v>1530881</v>
       </c>
       <c r="K3" t="n">
-        <v>285753</v>
+        <v>224505</v>
       </c>
       <c r="M3" t="n">
-        <v>2731003</v>
+        <v>2605275</v>
       </c>
       <c r="N3" t="n">
-        <v>214475</v>
+        <v>273068</v>
       </c>
       <c r="O3" t="n">
-        <v>224840</v>
+        <v>402811</v>
       </c>
       <c r="P3" t="n">
-        <v>355073</v>
+        <v>368707</v>
       </c>
       <c r="Q3" t="n">
-        <v>614624</v>
+        <v>750038</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>977033</v>
+        <v>1104818</v>
       </c>
       <c r="C4" t="n">
-        <v>493347</v>
+        <v>667392</v>
       </c>
       <c r="D4" t="n">
-        <v>1277653</v>
+        <v>1498652</v>
       </c>
       <c r="E4" t="n">
         <v>9000</v>
       </c>
       <c r="F4" t="n">
-        <v>1875666</v>
+        <v>1894575</v>
       </c>
       <c r="G4" t="n">
-        <v>1356150</v>
+        <v>1428865</v>
       </c>
       <c r="I4" t="n">
-        <v>1507739</v>
+        <v>1526911</v>
       </c>
       <c r="K4" t="n">
-        <v>213692</v>
+        <v>285753</v>
       </c>
       <c r="M4" t="n">
-        <v>2729375</v>
+        <v>2731003</v>
       </c>
       <c r="N4" t="n">
         <v>214475</v>
       </c>
       <c r="O4" t="n">
-        <v>246357</v>
+        <v>224840</v>
       </c>
       <c r="P4" t="n">
-        <v>354625</v>
+        <v>355073</v>
       </c>
       <c r="Q4" t="n">
-        <v>508923</v>
+        <v>614624</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B5" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C5" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D5" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E5" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F5" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G5" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I5" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K5" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M5" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P5" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q5" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B6" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C6" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D6" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E6" t="n">
         <v>9200</v>
       </c>
       <c r="F6" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G6" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I6" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K6" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M6" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P6" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q6" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B7" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C7" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D7" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G7" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I7" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K7" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M7" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N7" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P7" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q7" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B8" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C8" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D8" t="n">
         <v>1336369</v>
@@ -84197,28 +84291,28 @@
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G8" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I8" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K8" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M8" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N8" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O8" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P8" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q8" t="n">
         <v>710782</v>
@@ -84226,34 +84320,34 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B9" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C9" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D9" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G9" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I9" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K9" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M9" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N9" t="n">
         <v>214475</v>
@@ -84262,7 +84356,7 @@
         <v>238857</v>
       </c>
       <c r="P9" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q9" t="n">
         <v>710782</v>
@@ -84270,43 +84364,43 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B10" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C10" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D10" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G10" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I10" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K10" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M10" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N10" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O10" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P10" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q10" t="n">
         <v>710782</v>
@@ -84314,201 +84408,201 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B11" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C11" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D11" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G11" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I11" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K11" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M11" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N11" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O11" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P11" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q11" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B12" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C12" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D12" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G12" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I12" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K12" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M12" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N12" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O12" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P12" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q12" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B13" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C13" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D13" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G13" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I13" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K13" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M13" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N13" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O13" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P13" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q13" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B14" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C14" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D14" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E14" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G14" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I14" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K14" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M14" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N14" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O14" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P14" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q14" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B15" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C15" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D15" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E15" t="n">
         <v>9400</v>
       </c>
       <c r="F15" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G15" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I15" t="n">
         <v>1493578</v>
@@ -84517,7 +84611,7 @@
         <v>270165</v>
       </c>
       <c r="M15" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N15" t="n">
         <v>214475</v>
@@ -84529,39 +84623,39 @@
         <v>380581</v>
       </c>
       <c r="Q15" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B16" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C16" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D16" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E16" t="n">
         <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G16" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I16" t="n">
         <v>1493578</v>
       </c>
       <c r="K16" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M16" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -84570,153 +84664,153 @@
         <v>236857</v>
       </c>
       <c r="P16" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q16" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B17" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C17" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D17" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E17" t="n">
         <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G17" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I17" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K17" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M17" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N17" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O17" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P17" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q17" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B18" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C18" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D18" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E18" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F18" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G18" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I18" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K18" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M18" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N18" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O18" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P18" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q18" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B19" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C19" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D19" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E19" t="n">
         <v>9200</v>
       </c>
       <c r="F19" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G19" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I19" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K19" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M19" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N19" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O19" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P19" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q19" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B20" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C20" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D20" t="n">
         <v>1438502</v>
@@ -84725,107 +84819,107 @@
         <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G20" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I20" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K20" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M20" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N20" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O20" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P20" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q20" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B21" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C21" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D21" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E21" t="n">
         <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G21" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I21" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K21" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M21" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N21" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O21" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P21" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q21" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B22" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C22" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D22" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E22" t="n">
         <v>9200</v>
       </c>
       <c r="F22" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G22" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I22" t="n">
         <v>1488515</v>
       </c>
       <c r="K22" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M22" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N22" t="n">
         <v>214475</v>
@@ -84834,7 +84928,7 @@
         <v>247857</v>
       </c>
       <c r="P22" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q22" t="n">
         <v>738429</v>
@@ -84842,34 +84936,34 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B23" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C23" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D23" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E23" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F23" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G23" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I23" t="n">
         <v>1488515</v>
       </c>
       <c r="K23" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M23" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N23" t="n">
         <v>214475</v>
@@ -84878,7 +84972,7 @@
         <v>247857</v>
       </c>
       <c r="P23" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q23" t="n">
         <v>738429</v>
@@ -84886,78 +84980,78 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B24" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C24" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D24" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E24" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F24" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G24" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I24" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K24" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M24" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N24" t="n">
         <v>214475</v>
       </c>
       <c r="O24" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P24" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q24" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B25" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C25" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D25" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E25" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F25" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G25" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I25" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K25" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M25" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N25" t="n">
         <v>214475</v>
@@ -84966,42 +85060,42 @@
         <v>264857</v>
       </c>
       <c r="P25" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q25" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B26" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C26" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D26" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E26" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F26" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G26" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I26" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K26" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M26" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N26" t="n">
         <v>214475</v>
@@ -85010,101 +85104,98 @@
         <v>264857</v>
       </c>
       <c r="P26" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q26" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B27" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C27" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D27" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E27" t="n">
         <v>9300</v>
       </c>
       <c r="F27" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G27" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I27" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K27" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M27" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N27" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O27" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P27" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q27" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R27" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B28" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C28" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D28" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E28" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F28" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G28" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I28" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K28" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M28" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N28" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O28" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P28" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q28" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R28" t="n">
         <v>15000</v>
@@ -85112,40 +85203,40 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B29" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C29" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D29" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E29" t="n">
         <v>9100</v>
       </c>
       <c r="F29" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G29" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I29" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K29" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M29" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N29" t="n">
         <v>189475</v>
       </c>
       <c r="O29" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P29" t="n">
         <v>375660</v>
@@ -85154,6 +85245,53 @@
         <v>773586</v>
       </c>
       <c r="R29" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C30" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E30" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K30" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N30" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O30" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P30" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R30" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80273,9 +80273,36 @@
       <c r="A2434" s="4" t="n">
         <v>46263</v>
       </c>
+      <c r="B2434" t="n">
+        <v>3.404</v>
+      </c>
+      <c r="C2434" t="n">
+        <v>3.112</v>
+      </c>
+      <c r="D2434" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="E2434" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="F2434" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="G2434" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H2434" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I2434" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="K2434" t="n">
+        <v>12.136</v>
+      </c>
       <c r="L2434" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81372,7 +81399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81437,249 +81464,249 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B2" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C2" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H2" t="n">
         <v>0.379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K2" t="n">
-        <v>12.428</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B3" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C3" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D3" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F3" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H3" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K3" t="n">
-        <v>12.534</v>
+        <v>12.428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C4" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D4" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F4" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G4" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H4" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K4" t="n">
-        <v>12.108</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B5" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C5" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D5" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F5" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H5" t="n">
         <v>0.342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K5" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B6" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C6" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D6" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F6" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G6" t="n">
         <v>0.444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K6" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B7" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C7" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D7" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F7" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G7" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K7" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B8" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C8" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D8" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E8" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F8" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G8" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H8" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K8" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B9" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C9" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D9" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F9" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
@@ -81688,27 +81715,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B10" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C10" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D10" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E10" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F10" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
@@ -81720,178 +81747,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B11" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C11" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D11" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E11" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
       </c>
       <c r="H11" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I11" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C12" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D12" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E12" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F12" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G12" t="n">
         <v>0.437</v>
       </c>
       <c r="H12" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I12" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B13" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C13" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D13" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F13" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G13" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K13" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B14" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C14" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D14" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E14" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G14" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C15" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E15" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F15" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G15" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H15" t="n">
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K15" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B16" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C16" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D16" t="n">
         <v>1.44</v>
@@ -81900,7 +81927,7 @@
         <v>0.261</v>
       </c>
       <c r="F16" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G16" t="n">
         <v>0.435</v>
@@ -81909,222 +81936,222 @@
         <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K16" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B17" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C17" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D17" t="n">
         <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F17" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G17" t="n">
         <v>0.435</v>
       </c>
       <c r="H17" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K17" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B18" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C18" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D18" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F18" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G18" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K18" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B19" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C19" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D19" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F19" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G19" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K19" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B20" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C20" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D20" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E20" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G20" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H20" t="n">
         <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K20" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C21" t="n">
         <v>3.232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F21" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G21" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H21" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K21" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B22" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C22" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D22" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G22" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K22" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B23" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C23" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D23" t="n">
         <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F23" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G23" t="n">
         <v>0.446</v>
@@ -82136,27 +82163,27 @@
         <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B24" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C24" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D24" t="n">
         <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F24" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G24" t="n">
         <v>0.446</v>
@@ -82168,59 +82195,59 @@
         <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B25" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C25" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D25" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E25" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F25" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G25" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H25" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I25" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K25" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B26" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C26" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D26" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E26" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F26" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G26" t="n">
         <v>0.462</v>
@@ -82229,30 +82256,30 @@
         <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K26" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B27" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C27" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D27" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E27" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F27" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G27" t="n">
         <v>0.462</v>
@@ -82261,100 +82288,97 @@
         <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K27" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B28" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C28" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D28" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E28" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F28" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G28" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H28" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K28" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B29" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C29" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D29" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E29" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F29" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G29" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H29" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J29" t="n">
         <v>0.014</v>
       </c>
       <c r="K29" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B30" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C30" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D30" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F30" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G30" t="n">
         <v>0.395</v>
@@ -82369,6 +82393,41 @@
         <v>0.014</v>
       </c>
       <c r="K30" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82383,7 +82442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82453,270 +82512,270 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B2" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C2" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D2" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E2" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F2" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G2" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H2" t="n">
         <v>0.379</v>
       </c>
       <c r="I2" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K2" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
       <c r="L2" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B3" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C3" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D3" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E3" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F3" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H3" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K3" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
       <c r="L3" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C4" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D4" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E4" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F4" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G4" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H4" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I4" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K4" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
       <c r="L4" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B5" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C5" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D5" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E5" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F5" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H5" t="n">
         <v>0.342</v>
       </c>
       <c r="I5" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K5" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
       <c r="L5" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B6" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C6" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D6" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F6" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G6" t="n">
         <v>0.444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K6" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L6" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B7" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C7" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D7" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F7" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G7" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I7" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K7" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L7" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B8" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C8" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D8" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E8" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F8" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G8" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H8" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K8" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L8" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B9" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C9" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D9" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E9" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F9" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G9" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H9" t="n">
         <v>0.367</v>
@@ -82725,30 +82784,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L9" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B10" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C10" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D10" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E10" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F10" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G10" t="n">
         <v>0.437</v>
@@ -82760,196 +82819,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L10" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B11" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C11" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D11" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E11" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
       </c>
       <c r="H11" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I11" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L11" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C12" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D12" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E12" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F12" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G12" t="n">
         <v>0.437</v>
       </c>
       <c r="H12" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I12" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L12" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B13" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C13" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D13" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F13" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G13" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H13" t="n">
         <v>0.367</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K13" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L13" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B14" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C14" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D14" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E14" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F14" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G14" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L14" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C15" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E15" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F15" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G15" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H15" t="n">
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K15" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L15" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B16" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C16" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D16" t="n">
         <v>1.44</v>
@@ -82958,7 +83017,7 @@
         <v>0.261</v>
       </c>
       <c r="F16" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G16" t="n">
         <v>0.435</v>
@@ -82967,243 +83026,243 @@
         <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K16" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L16" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B17" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C17" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D17" t="n">
         <v>1.44</v>
       </c>
       <c r="E17" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F17" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G17" t="n">
         <v>0.435</v>
       </c>
       <c r="H17" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K17" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L17" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B18" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C18" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D18" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F18" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G18" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H18" t="n">
         <v>0.365</v>
       </c>
       <c r="I18" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K18" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L18" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B19" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C19" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D19" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F19" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G19" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K19" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L19" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B20" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C20" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D20" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E20" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G20" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H20" t="n">
         <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K20" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L20" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C21" t="n">
         <v>3.232</v>
       </c>
       <c r="D21" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F21" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G21" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H21" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K21" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L21" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B22" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C22" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D22" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E22" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G22" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H22" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I22" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K22" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L22" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B23" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C23" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D23" t="n">
         <v>1.435</v>
       </c>
       <c r="E23" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F23" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G23" t="n">
         <v>0.446</v>
@@ -83215,30 +83274,30 @@
         <v>0.712</v>
       </c>
       <c r="K23" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L23" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B24" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C24" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D24" t="n">
         <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F24" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G24" t="n">
         <v>0.446</v>
@@ -83250,65 +83309,65 @@
         <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L24" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B25" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C25" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D25" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E25" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F25" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G25" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H25" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I25" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K25" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L25" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B26" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C26" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D26" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E26" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F26" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G26" t="n">
         <v>0.462</v>
@@ -83317,33 +83376,33 @@
         <v>0.343</v>
       </c>
       <c r="I26" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K26" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L26" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B27" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C27" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D27" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E27" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F27" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G27" t="n">
         <v>0.462</v>
@@ -83352,109 +83411,106 @@
         <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K27" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L27" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B28" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C28" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D28" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E28" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F28" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G28" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H28" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K28" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L28" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B29" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C29" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D29" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E29" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F29" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G29" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H29" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J29" t="n">
         <v>0.014</v>
       </c>
       <c r="K29" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L29" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B30" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C30" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D30" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F30" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G30" t="n">
         <v>0.395</v>
@@ -83469,9 +83525,47 @@
         <v>0.014</v>
       </c>
       <c r="K30" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L30" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.277</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L31" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -83912,7 +84006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R30"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -84012,321 +84106,321 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B2" t="n">
-        <v>1428345</v>
+        <v>1453284</v>
       </c>
       <c r="C2" t="n">
-        <v>613887</v>
+        <v>668222</v>
       </c>
       <c r="D2" t="n">
-        <v>1360335</v>
+        <v>1399375</v>
       </c>
       <c r="E2" t="n">
         <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>2000629</v>
+        <v>1997673</v>
       </c>
       <c r="G2" t="n">
-        <v>1229134</v>
+        <v>1229304</v>
       </c>
       <c r="I2" t="n">
-        <v>1516881</v>
+        <v>1526881</v>
       </c>
       <c r="K2" t="n">
-        <v>265281</v>
+        <v>210710</v>
       </c>
       <c r="M2" t="n">
-        <v>2655010</v>
+        <v>2315158</v>
       </c>
       <c r="N2" t="n">
-        <v>275644</v>
+        <v>274632</v>
       </c>
       <c r="O2" t="n">
-        <v>405391</v>
+        <v>404378</v>
       </c>
       <c r="P2" t="n">
         <v>393345</v>
       </c>
       <c r="Q2" t="n">
-        <v>735394</v>
+        <v>702775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B3" t="n">
-        <v>1453305</v>
+        <v>1428345</v>
       </c>
       <c r="C3" t="n">
-        <v>660021</v>
+        <v>613887</v>
       </c>
       <c r="D3" t="n">
-        <v>1394810</v>
+        <v>1360335</v>
       </c>
       <c r="E3" t="n">
         <v>9000</v>
       </c>
       <c r="F3" t="n">
-        <v>1966997</v>
+        <v>2000629</v>
       </c>
       <c r="G3" t="n">
-        <v>1358589</v>
+        <v>1229134</v>
       </c>
       <c r="I3" t="n">
-        <v>1530881</v>
+        <v>1516881</v>
       </c>
       <c r="K3" t="n">
-        <v>224505</v>
+        <v>265281</v>
       </c>
       <c r="M3" t="n">
-        <v>2605275</v>
+        <v>2655010</v>
       </c>
       <c r="N3" t="n">
-        <v>273068</v>
+        <v>275644</v>
       </c>
       <c r="O3" t="n">
-        <v>402811</v>
+        <v>405391</v>
       </c>
       <c r="P3" t="n">
-        <v>368707</v>
+        <v>393345</v>
       </c>
       <c r="Q3" t="n">
-        <v>750038</v>
+        <v>735394</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B4" t="n">
-        <v>1104818</v>
+        <v>1453305</v>
       </c>
       <c r="C4" t="n">
-        <v>667392</v>
+        <v>660021</v>
       </c>
       <c r="D4" t="n">
-        <v>1498652</v>
+        <v>1394810</v>
       </c>
       <c r="E4" t="n">
         <v>9000</v>
       </c>
       <c r="F4" t="n">
-        <v>1894575</v>
+        <v>1966997</v>
       </c>
       <c r="G4" t="n">
-        <v>1428865</v>
+        <v>1358589</v>
       </c>
       <c r="I4" t="n">
-        <v>1526911</v>
+        <v>1530881</v>
       </c>
       <c r="K4" t="n">
-        <v>285753</v>
+        <v>224505</v>
       </c>
       <c r="M4" t="n">
-        <v>2731003</v>
+        <v>2605275</v>
       </c>
       <c r="N4" t="n">
-        <v>214475</v>
+        <v>273068</v>
       </c>
       <c r="O4" t="n">
-        <v>224840</v>
+        <v>402811</v>
       </c>
       <c r="P4" t="n">
-        <v>355073</v>
+        <v>368707</v>
       </c>
       <c r="Q4" t="n">
-        <v>614624</v>
+        <v>750038</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B5" t="n">
-        <v>977033</v>
+        <v>1104818</v>
       </c>
       <c r="C5" t="n">
-        <v>493347</v>
+        <v>667392</v>
       </c>
       <c r="D5" t="n">
-        <v>1277653</v>
+        <v>1498652</v>
       </c>
       <c r="E5" t="n">
         <v>9000</v>
       </c>
       <c r="F5" t="n">
-        <v>1875666</v>
+        <v>1894575</v>
       </c>
       <c r="G5" t="n">
-        <v>1356150</v>
+        <v>1428865</v>
       </c>
       <c r="I5" t="n">
-        <v>1507739</v>
+        <v>1526911</v>
       </c>
       <c r="K5" t="n">
-        <v>213692</v>
+        <v>285753</v>
       </c>
       <c r="M5" t="n">
-        <v>2729375</v>
+        <v>2731003</v>
       </c>
       <c r="N5" t="n">
         <v>214475</v>
       </c>
       <c r="O5" t="n">
-        <v>246357</v>
+        <v>224840</v>
       </c>
       <c r="P5" t="n">
-        <v>354625</v>
+        <v>355073</v>
       </c>
       <c r="Q5" t="n">
-        <v>508923</v>
+        <v>614624</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B6" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C6" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D6" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E6" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F6" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G6" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I6" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K6" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M6" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P6" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q6" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B7" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C7" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D7" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E7" t="n">
         <v>9200</v>
       </c>
       <c r="F7" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G7" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I7" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K7" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M7" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P7" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q7" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B8" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C8" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D8" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G8" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I8" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K8" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M8" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N8" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P8" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q8" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B9" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C9" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D9" t="n">
         <v>1336369</v>
@@ -84335,28 +84429,28 @@
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G9" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I9" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K9" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M9" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N9" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O9" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P9" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q9" t="n">
         <v>710782</v>
@@ -84364,34 +84458,34 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B10" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C10" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D10" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E10" t="n">
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G10" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I10" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K10" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M10" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N10" t="n">
         <v>214475</v>
@@ -84400,7 +84494,7 @@
         <v>238857</v>
       </c>
       <c r="P10" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q10" t="n">
         <v>710782</v>
@@ -84408,43 +84502,43 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B11" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C11" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D11" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G11" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I11" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K11" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M11" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N11" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O11" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P11" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q11" t="n">
         <v>710782</v>
@@ -84452,201 +84546,201 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B12" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C12" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D12" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G12" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I12" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K12" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M12" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N12" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O12" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P12" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q12" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B13" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C13" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D13" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G13" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I13" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K13" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M13" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N13" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O13" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P13" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q13" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B14" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C14" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D14" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E14" t="n">
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G14" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I14" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K14" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M14" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N14" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O14" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P14" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q14" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B15" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C15" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D15" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E15" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G15" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I15" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K15" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M15" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N15" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O15" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P15" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q15" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B16" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C16" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D16" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E16" t="n">
         <v>9400</v>
       </c>
       <c r="F16" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G16" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I16" t="n">
         <v>1493578</v>
@@ -84655,7 +84749,7 @@
         <v>270165</v>
       </c>
       <c r="M16" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N16" t="n">
         <v>214475</v>
@@ -84667,39 +84761,39 @@
         <v>380581</v>
       </c>
       <c r="Q16" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B17" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C17" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D17" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E17" t="n">
         <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G17" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I17" t="n">
         <v>1493578</v>
       </c>
       <c r="K17" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M17" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -84708,153 +84802,153 @@
         <v>236857</v>
       </c>
       <c r="P17" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q17" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B18" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C18" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D18" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E18" t="n">
         <v>9400</v>
       </c>
       <c r="F18" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G18" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I18" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K18" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M18" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N18" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O18" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P18" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q18" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B19" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C19" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D19" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E19" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F19" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G19" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I19" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K19" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M19" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N19" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O19" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P19" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q19" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B20" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C20" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D20" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E20" t="n">
         <v>9200</v>
       </c>
       <c r="F20" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G20" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I20" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K20" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M20" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N20" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O20" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P20" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q20" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B21" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C21" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D21" t="n">
         <v>1438502</v>
@@ -84863,107 +84957,107 @@
         <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G21" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I21" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K21" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M21" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N21" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O21" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P21" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q21" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B22" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C22" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D22" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E22" t="n">
         <v>9200</v>
       </c>
       <c r="F22" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G22" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I22" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K22" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M22" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N22" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O22" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P22" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q22" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B23" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C23" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D23" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E23" t="n">
         <v>9200</v>
       </c>
       <c r="F23" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G23" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I23" t="n">
         <v>1488515</v>
       </c>
       <c r="K23" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M23" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N23" t="n">
         <v>214475</v>
@@ -84972,7 +85066,7 @@
         <v>247857</v>
       </c>
       <c r="P23" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q23" t="n">
         <v>738429</v>
@@ -84980,34 +85074,34 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B24" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C24" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D24" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E24" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F24" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G24" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I24" t="n">
         <v>1488515</v>
       </c>
       <c r="K24" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M24" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N24" t="n">
         <v>214475</v>
@@ -85016,7 +85110,7 @@
         <v>247857</v>
       </c>
       <c r="P24" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q24" t="n">
         <v>738429</v>
@@ -85024,78 +85118,78 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B25" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C25" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D25" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E25" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F25" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G25" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I25" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K25" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M25" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N25" t="n">
         <v>214475</v>
       </c>
       <c r="O25" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P25" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q25" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B26" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C26" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D26" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E26" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F26" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G26" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I26" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K26" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M26" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N26" t="n">
         <v>214475</v>
@@ -85104,42 +85198,42 @@
         <v>264857</v>
       </c>
       <c r="P26" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q26" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B27" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C27" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D27" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E27" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F27" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G27" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I27" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K27" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M27" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N27" t="n">
         <v>214475</v>
@@ -85148,101 +85242,98 @@
         <v>264857</v>
       </c>
       <c r="P27" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q27" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B28" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C28" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D28" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E28" t="n">
         <v>9300</v>
       </c>
       <c r="F28" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G28" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I28" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K28" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M28" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N28" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O28" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P28" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q28" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R28" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B29" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C29" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D29" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E29" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F29" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G29" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I29" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K29" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M29" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N29" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O29" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P29" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q29" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R29" t="n">
         <v>15000</v>
@@ -85250,40 +85341,40 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B30" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C30" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D30" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E30" t="n">
         <v>9100</v>
       </c>
       <c r="F30" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G30" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I30" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K30" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M30" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N30" t="n">
         <v>189475</v>
       </c>
       <c r="O30" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P30" t="n">
         <v>375660</v>
@@ -85292,6 +85383,53 @@
         <v>773586</v>
       </c>
       <c r="R30" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C31" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E31" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K31" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N31" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O31" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P31" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R31" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80263,9 +80263,36 @@
       <c r="A2433" s="4" t="n">
         <v>46262</v>
       </c>
+      <c r="B2433" t="n">
+        <v>3.236</v>
+      </c>
+      <c r="C2433" t="n">
+        <v>3.017</v>
+      </c>
+      <c r="D2433" t="n">
+        <v>1.456</v>
+      </c>
+      <c r="E2433" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="F2433" t="n">
+        <v>2.543</v>
+      </c>
+      <c r="G2433" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H2433" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="I2433" t="n">
+        <v>0.6820000000000001</v>
+      </c>
+      <c r="K2433" t="n">
+        <v>12.267</v>
+      </c>
       <c r="L2433" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81399,7 +81426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81464,281 +81491,281 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B2" t="n">
-        <v>3.404</v>
+        <v>3.236</v>
       </c>
       <c r="C2" t="n">
-        <v>3.112</v>
+        <v>3.017</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472</v>
+        <v>1.456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="F2" t="n">
-        <v>2.233</v>
+        <v>2.543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.655</v>
+        <v>0.74</v>
       </c>
       <c r="H2" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.678</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.136</v>
+        <v>12.269</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B3" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C3" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D3" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H3" t="n">
         <v>0.379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K3" t="n">
-        <v>12.428</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B4" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C4" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D4" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F4" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H4" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I4" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K4" t="n">
-        <v>12.534</v>
+        <v>12.428</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C5" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D5" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E5" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F5" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G5" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H5" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K5" t="n">
-        <v>12.108</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B6" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C6" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D6" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E6" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F6" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G6" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H6" t="n">
         <v>0.342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K6" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B7" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C7" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D7" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F7" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G7" t="n">
         <v>0.444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I7" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K7" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B8" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C8" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D8" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E8" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F8" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H8" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K8" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B9" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C9" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D9" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F9" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G9" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H9" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K9" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B10" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C10" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D10" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F10" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G10" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
@@ -81747,27 +81774,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B11" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C11" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D11" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E11" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F11" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
@@ -81779,178 +81806,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B12" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C12" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D12" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F12" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G12" t="n">
         <v>0.437</v>
       </c>
       <c r="H12" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I12" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C13" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D13" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F13" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
         <v>0.437</v>
       </c>
       <c r="H13" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I13" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B14" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C14" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D14" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F14" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G14" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K14" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B15" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C15" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D15" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E15" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H15" t="n">
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C16" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E16" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F16" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G16" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H16" t="n">
         <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K16" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B17" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C17" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D17" t="n">
         <v>1.44</v>
@@ -81959,7 +81986,7 @@
         <v>0.261</v>
       </c>
       <c r="F17" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G17" t="n">
         <v>0.435</v>
@@ -81968,222 +81995,222 @@
         <v>0.367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K17" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C18" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D18" t="n">
         <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F18" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G18" t="n">
         <v>0.435</v>
       </c>
       <c r="H18" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I18" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K18" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B19" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C19" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D19" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F19" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G19" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K19" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B20" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C20" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D20" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F20" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H20" t="n">
         <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K20" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B21" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C21" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D21" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E21" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G21" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H21" t="n">
         <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K21" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B22" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C22" t="n">
         <v>3.232</v>
       </c>
       <c r="D22" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F22" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G22" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H22" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I22" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K22" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B23" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C23" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D23" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E23" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G23" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K23" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B24" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C24" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D24" t="n">
         <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F24" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G24" t="n">
         <v>0.446</v>
@@ -82195,27 +82222,27 @@
         <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B25" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C25" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D25" t="n">
         <v>1.435</v>
       </c>
       <c r="E25" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F25" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G25" t="n">
         <v>0.446</v>
@@ -82227,59 +82254,59 @@
         <v>0.712</v>
       </c>
       <c r="K25" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B26" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C26" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D26" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E26" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F26" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H26" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I26" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K26" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B27" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C27" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D27" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E27" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F27" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G27" t="n">
         <v>0.462</v>
@@ -82288,30 +82315,30 @@
         <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K27" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B28" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C28" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D28" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E28" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F28" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G28" t="n">
         <v>0.462</v>
@@ -82320,100 +82347,97 @@
         <v>0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K28" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B29" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C29" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D29" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E29" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F29" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G29" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I29" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K29" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B30" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C30" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D30" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E30" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F30" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G30" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H30" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I30" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J30" t="n">
         <v>0.014</v>
       </c>
       <c r="K30" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B31" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C31" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D31" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F31" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G31" t="n">
         <v>0.395</v>
@@ -82428,6 +82452,41 @@
         <v>0.014</v>
       </c>
       <c r="K31" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K32" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82442,7 +82501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82512,305 +82571,305 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B2" t="n">
-        <v>3.404</v>
+        <v>3.236</v>
       </c>
       <c r="C2" t="n">
-        <v>3.112</v>
+        <v>3.017</v>
       </c>
       <c r="D2" t="n">
-        <v>1.472</v>
+        <v>1.456</v>
       </c>
       <c r="E2" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="F2" t="n">
-        <v>2.233</v>
+        <v>2.543</v>
       </c>
       <c r="G2" t="n">
-        <v>0.655</v>
+        <v>0.74</v>
       </c>
       <c r="H2" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="I2" t="n">
-        <v>0.678</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>12.136</v>
+        <v>12.267</v>
       </c>
       <c r="L2" t="n">
-        <v>12.136</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B3" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C3" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D3" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E3" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G3" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H3" t="n">
         <v>0.379</v>
       </c>
       <c r="I3" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K3" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
       <c r="L3" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B4" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C4" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D4" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F4" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H4" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I4" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K4" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
       <c r="L4" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C5" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D5" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E5" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F5" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G5" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H5" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K5" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
       <c r="L5" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B6" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C6" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D6" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E6" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F6" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G6" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H6" t="n">
         <v>0.342</v>
       </c>
       <c r="I6" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K6" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
       <c r="L6" t="n">
-        <v>11.345</v>
+        <v>12.109</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B7" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C7" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D7" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E7" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F7" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G7" t="n">
         <v>0.444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I7" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K7" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
       <c r="L7" t="n">
-        <v>11.787</v>
+        <v>11.345</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B8" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C8" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D8" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E8" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F8" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H8" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K8" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
       <c r="L8" t="n">
-        <v>12.376</v>
+        <v>11.787</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B9" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C9" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D9" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F9" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G9" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H9" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K9" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
       <c r="L9" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B10" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C10" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D10" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E10" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F10" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G10" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H10" t="n">
         <v>0.367</v>
@@ -82819,30 +82878,30 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
       <c r="L10" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B11" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C11" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D11" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E11" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F11" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G11" t="n">
         <v>0.437</v>
@@ -82854,196 +82913,196 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
       <c r="L11" t="n">
-        <v>11.936</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B12" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C12" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D12" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E12" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F12" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G12" t="n">
         <v>0.437</v>
       </c>
       <c r="H12" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I12" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
       <c r="L12" t="n">
-        <v>11.961</v>
+        <v>11.936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C13" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D13" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E13" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F13" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
         <v>0.437</v>
       </c>
       <c r="H13" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I13" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
       <c r="L13" t="n">
-        <v>12.126</v>
+        <v>11.961</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B14" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C14" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D14" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F14" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G14" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H14" t="n">
         <v>0.367</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K14" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
       <c r="L14" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B15" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C15" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D15" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E15" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F15" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G15" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H15" t="n">
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
       <c r="L15" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C16" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D16" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E16" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F16" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G16" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H16" t="n">
         <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K16" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
       <c r="L16" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B17" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C17" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D17" t="n">
         <v>1.44</v>
@@ -83052,7 +83111,7 @@
         <v>0.261</v>
       </c>
       <c r="F17" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G17" t="n">
         <v>0.435</v>
@@ -83061,243 +83120,243 @@
         <v>0.367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K17" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
       <c r="L17" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C18" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D18" t="n">
         <v>1.44</v>
       </c>
       <c r="E18" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F18" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G18" t="n">
         <v>0.435</v>
       </c>
       <c r="H18" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I18" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K18" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
       <c r="L18" t="n">
-        <v>12.229</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B19" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C19" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D19" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F19" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G19" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H19" t="n">
         <v>0.365</v>
       </c>
       <c r="I19" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K19" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
       <c r="L19" t="n">
-        <v>12.02</v>
+        <v>12.229</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B20" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C20" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D20" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F20" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G20" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H20" t="n">
         <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K20" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
       <c r="L20" t="n">
-        <v>12.108</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B21" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C21" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D21" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E21" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G21" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H21" t="n">
         <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K21" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
       <c r="L21" t="n">
-        <v>12.272</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B22" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C22" t="n">
         <v>3.232</v>
       </c>
       <c r="D22" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F22" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G22" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H22" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I22" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K22" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
       <c r="L22" t="n">
-        <v>12.634</v>
+        <v>12.272</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B23" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C23" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D23" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E23" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G23" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H23" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K23" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
       <c r="L23" t="n">
-        <v>12.569</v>
+        <v>12.634</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B24" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C24" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D24" t="n">
         <v>1.435</v>
       </c>
       <c r="E24" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F24" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G24" t="n">
         <v>0.446</v>
@@ -83309,30 +83368,30 @@
         <v>0.712</v>
       </c>
       <c r="K24" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
       <c r="L24" t="n">
-        <v>12.276</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B25" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C25" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D25" t="n">
         <v>1.435</v>
       </c>
       <c r="E25" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F25" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G25" t="n">
         <v>0.446</v>
@@ -83344,65 +83403,65 @@
         <v>0.712</v>
       </c>
       <c r="K25" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
       <c r="L25" t="n">
-        <v>12.224</v>
+        <v>12.276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B26" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C26" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D26" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E26" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F26" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H26" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I26" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K26" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
       <c r="L26" t="n">
-        <v>12.187</v>
+        <v>12.224</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B27" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C27" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D27" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E27" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F27" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G27" t="n">
         <v>0.462</v>
@@ -83411,33 +83470,33 @@
         <v>0.343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K27" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
       <c r="L27" t="n">
-        <v>12.08</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B28" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C28" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D28" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E28" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F28" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G28" t="n">
         <v>0.462</v>
@@ -83446,109 +83505,106 @@
         <v>0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K28" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
       <c r="L28" t="n">
-        <v>12.118</v>
+        <v>12.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B29" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C29" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D29" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E29" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F29" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G29" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H29" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I29" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K29" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
       <c r="L29" t="n">
-        <v>12.373</v>
+        <v>12.118</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B30" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C30" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D30" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E30" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F30" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G30" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H30" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I30" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J30" t="n">
         <v>0.014</v>
       </c>
       <c r="K30" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
       <c r="L30" t="n">
-        <v>12.642</v>
+        <v>12.373</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B31" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C31" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D31" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F31" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G31" t="n">
         <v>0.395</v>
@@ -83563,9 +83619,47 @@
         <v>0.014</v>
       </c>
       <c r="K31" t="n">
+        <v>12.642</v>
+      </c>
+      <c r="L31" t="n">
+        <v>12.642</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B32" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K32" t="n">
         <v>12.277</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>12.277</v>
       </c>
     </row>
@@ -84006,7 +84100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -84106,365 +84200,365 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B2" t="n">
-        <v>1453284</v>
+        <v>1326845</v>
       </c>
       <c r="C2" t="n">
-        <v>668222</v>
+        <v>630343</v>
       </c>
       <c r="D2" t="n">
-        <v>1399375</v>
+        <v>1389820</v>
       </c>
       <c r="E2" t="n">
         <v>9000</v>
       </c>
       <c r="F2" t="n">
-        <v>1997673</v>
+        <v>1898634</v>
       </c>
       <c r="G2" t="n">
-        <v>1229304</v>
+        <v>1230443</v>
       </c>
       <c r="I2" t="n">
-        <v>1526881</v>
+        <v>1509954</v>
       </c>
       <c r="K2" t="n">
-        <v>210710</v>
+        <v>223405</v>
       </c>
       <c r="M2" t="n">
-        <v>2315158</v>
+        <v>2637144</v>
       </c>
       <c r="N2" t="n">
-        <v>274632</v>
+        <v>322000</v>
       </c>
       <c r="O2" t="n">
-        <v>404378</v>
+        <v>445186</v>
       </c>
       <c r="P2" t="n">
-        <v>393345</v>
+        <v>392284</v>
       </c>
       <c r="Q2" t="n">
-        <v>702775</v>
+        <v>707427</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B3" t="n">
-        <v>1428345</v>
+        <v>1453284</v>
       </c>
       <c r="C3" t="n">
-        <v>613887</v>
+        <v>668222</v>
       </c>
       <c r="D3" t="n">
-        <v>1360335</v>
+        <v>1399375</v>
       </c>
       <c r="E3" t="n">
         <v>9000</v>
       </c>
       <c r="F3" t="n">
-        <v>2000629</v>
+        <v>1997673</v>
       </c>
       <c r="G3" t="n">
-        <v>1229134</v>
+        <v>1229304</v>
       </c>
       <c r="I3" t="n">
-        <v>1516881</v>
+        <v>1526881</v>
       </c>
       <c r="K3" t="n">
-        <v>265281</v>
+        <v>210710</v>
       </c>
       <c r="M3" t="n">
-        <v>2655010</v>
+        <v>2315158</v>
       </c>
       <c r="N3" t="n">
-        <v>275644</v>
+        <v>274632</v>
       </c>
       <c r="O3" t="n">
-        <v>405391</v>
+        <v>404378</v>
       </c>
       <c r="P3" t="n">
         <v>393345</v>
       </c>
       <c r="Q3" t="n">
-        <v>735394</v>
+        <v>702775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B4" t="n">
-        <v>1453305</v>
+        <v>1428345</v>
       </c>
       <c r="C4" t="n">
-        <v>660021</v>
+        <v>613887</v>
       </c>
       <c r="D4" t="n">
-        <v>1394810</v>
+        <v>1360335</v>
       </c>
       <c r="E4" t="n">
         <v>9000</v>
       </c>
       <c r="F4" t="n">
-        <v>1966997</v>
+        <v>2000629</v>
       </c>
       <c r="G4" t="n">
-        <v>1358589</v>
+        <v>1229134</v>
       </c>
       <c r="I4" t="n">
-        <v>1530881</v>
+        <v>1516881</v>
       </c>
       <c r="K4" t="n">
-        <v>224505</v>
+        <v>265281</v>
       </c>
       <c r="M4" t="n">
-        <v>2605275</v>
+        <v>2655010</v>
       </c>
       <c r="N4" t="n">
-        <v>273068</v>
+        <v>275644</v>
       </c>
       <c r="O4" t="n">
-        <v>402811</v>
+        <v>405391</v>
       </c>
       <c r="P4" t="n">
-        <v>368707</v>
+        <v>393345</v>
       </c>
       <c r="Q4" t="n">
-        <v>750038</v>
+        <v>735394</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B5" t="n">
-        <v>1104818</v>
+        <v>1453305</v>
       </c>
       <c r="C5" t="n">
-        <v>667392</v>
+        <v>660021</v>
       </c>
       <c r="D5" t="n">
-        <v>1498652</v>
+        <v>1394810</v>
       </c>
       <c r="E5" t="n">
         <v>9000</v>
       </c>
       <c r="F5" t="n">
-        <v>1894575</v>
+        <v>1966997</v>
       </c>
       <c r="G5" t="n">
-        <v>1428865</v>
+        <v>1358589</v>
       </c>
       <c r="I5" t="n">
-        <v>1526911</v>
+        <v>1530881</v>
       </c>
       <c r="K5" t="n">
-        <v>285753</v>
+        <v>224505</v>
       </c>
       <c r="M5" t="n">
-        <v>2731003</v>
+        <v>2605275</v>
       </c>
       <c r="N5" t="n">
-        <v>214475</v>
+        <v>273068</v>
       </c>
       <c r="O5" t="n">
-        <v>224840</v>
+        <v>402811</v>
       </c>
       <c r="P5" t="n">
-        <v>355073</v>
+        <v>368707</v>
       </c>
       <c r="Q5" t="n">
-        <v>614624</v>
+        <v>750038</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B6" t="n">
-        <v>977033</v>
+        <v>1104818</v>
       </c>
       <c r="C6" t="n">
-        <v>493347</v>
+        <v>667392</v>
       </c>
       <c r="D6" t="n">
-        <v>1277653</v>
+        <v>1498652</v>
       </c>
       <c r="E6" t="n">
         <v>9000</v>
       </c>
       <c r="F6" t="n">
-        <v>1875666</v>
+        <v>1894575</v>
       </c>
       <c r="G6" t="n">
-        <v>1356150</v>
+        <v>1428865</v>
       </c>
       <c r="I6" t="n">
-        <v>1507739</v>
+        <v>1526911</v>
       </c>
       <c r="K6" t="n">
-        <v>213692</v>
+        <v>285753</v>
       </c>
       <c r="M6" t="n">
-        <v>2729375</v>
+        <v>2731003</v>
       </c>
       <c r="N6" t="n">
         <v>214475</v>
       </c>
       <c r="O6" t="n">
-        <v>246357</v>
+        <v>224840</v>
       </c>
       <c r="P6" t="n">
-        <v>354625</v>
+        <v>355073</v>
       </c>
       <c r="Q6" t="n">
-        <v>508923</v>
+        <v>614624</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B7" t="n">
-        <v>1222754</v>
+        <v>977033</v>
       </c>
       <c r="C7" t="n">
-        <v>600260</v>
+        <v>493347</v>
       </c>
       <c r="D7" t="n">
-        <v>1343521</v>
+        <v>1277653</v>
       </c>
       <c r="E7" t="n">
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="F7" t="n">
-        <v>1872474</v>
+        <v>1875666</v>
       </c>
       <c r="G7" t="n">
-        <v>1385603</v>
+        <v>1356150</v>
       </c>
       <c r="I7" t="n">
-        <v>1436775</v>
+        <v>1507739</v>
       </c>
       <c r="K7" t="n">
-        <v>212263</v>
+        <v>213692</v>
       </c>
       <c r="M7" t="n">
-        <v>2676981</v>
+        <v>2729375</v>
       </c>
       <c r="N7" t="n">
         <v>214475</v>
       </c>
       <c r="O7" t="n">
-        <v>245565</v>
+        <v>246357</v>
       </c>
       <c r="P7" t="n">
-        <v>331850</v>
+        <v>354625</v>
       </c>
       <c r="Q7" t="n">
-        <v>670444</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B8" t="n">
-        <v>1347666</v>
+        <v>1222754</v>
       </c>
       <c r="C8" t="n">
-        <v>711291</v>
+        <v>600260</v>
       </c>
       <c r="D8" t="n">
-        <v>1463104</v>
+        <v>1343521</v>
       </c>
       <c r="E8" t="n">
         <v>9200</v>
       </c>
       <c r="F8" t="n">
-        <v>1917047</v>
+        <v>1872474</v>
       </c>
       <c r="G8" t="n">
-        <v>1405212</v>
+        <v>1385603</v>
       </c>
       <c r="I8" t="n">
-        <v>1528739</v>
+        <v>1436775</v>
       </c>
       <c r="K8" t="n">
-        <v>256281</v>
+        <v>212263</v>
       </c>
       <c r="M8" t="n">
-        <v>2665641</v>
+        <v>2676981</v>
       </c>
       <c r="N8" t="n">
         <v>214475</v>
       </c>
       <c r="O8" t="n">
-        <v>239857</v>
+        <v>245565</v>
       </c>
       <c r="P8" t="n">
-        <v>379888</v>
+        <v>331850</v>
       </c>
       <c r="Q8" t="n">
-        <v>696003</v>
+        <v>670444</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B9" t="n">
-        <v>1371402</v>
+        <v>1347666</v>
       </c>
       <c r="C9" t="n">
-        <v>799313</v>
+        <v>711291</v>
       </c>
       <c r="D9" t="n">
-        <v>1336369</v>
+        <v>1463104</v>
       </c>
       <c r="E9" t="n">
         <v>9200</v>
       </c>
       <c r="F9" t="n">
-        <v>1938280</v>
+        <v>1917047</v>
       </c>
       <c r="G9" t="n">
-        <v>1443483</v>
+        <v>1405212</v>
       </c>
       <c r="I9" t="n">
-        <v>1532739</v>
+        <v>1528739</v>
       </c>
       <c r="K9" t="n">
-        <v>307648</v>
+        <v>256281</v>
       </c>
       <c r="M9" t="n">
-        <v>2687880</v>
+        <v>2665641</v>
       </c>
       <c r="N9" t="n">
-        <v>127995</v>
+        <v>214475</v>
       </c>
       <c r="O9" t="n">
-        <v>152230</v>
+        <v>239857</v>
       </c>
       <c r="P9" t="n">
-        <v>380516</v>
+        <v>379888</v>
       </c>
       <c r="Q9" t="n">
-        <v>710782</v>
+        <v>696003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B10" t="n">
-        <v>1222188</v>
+        <v>1371402</v>
       </c>
       <c r="C10" t="n">
-        <v>726662</v>
+        <v>799313</v>
       </c>
       <c r="D10" t="n">
         <v>1336369</v>
@@ -84473,28 +84567,28 @@
         <v>9200</v>
       </c>
       <c r="F10" t="n">
-        <v>1819723</v>
+        <v>1938280</v>
       </c>
       <c r="G10" t="n">
-        <v>1144716</v>
+        <v>1443483</v>
       </c>
       <c r="I10" t="n">
-        <v>1539739</v>
+        <v>1532739</v>
       </c>
       <c r="K10" t="n">
-        <v>347698</v>
+        <v>307648</v>
       </c>
       <c r="M10" t="n">
-        <v>2681880</v>
+        <v>2687880</v>
       </c>
       <c r="N10" t="n">
-        <v>214475</v>
+        <v>127995</v>
       </c>
       <c r="O10" t="n">
-        <v>238857</v>
+        <v>152230</v>
       </c>
       <c r="P10" t="n">
-        <v>380595</v>
+        <v>380516</v>
       </c>
       <c r="Q10" t="n">
         <v>710782</v>
@@ -84502,34 +84596,34 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B11" t="n">
-        <v>1245221</v>
+        <v>1222188</v>
       </c>
       <c r="C11" t="n">
-        <v>748948</v>
+        <v>726662</v>
       </c>
       <c r="D11" t="n">
-        <v>1343138</v>
+        <v>1336369</v>
       </c>
       <c r="E11" t="n">
         <v>9200</v>
       </c>
       <c r="F11" t="n">
-        <v>1828741</v>
+        <v>1819723</v>
       </c>
       <c r="G11" t="n">
-        <v>1426853</v>
+        <v>1144716</v>
       </c>
       <c r="I11" t="n">
-        <v>1286120</v>
+        <v>1539739</v>
       </c>
       <c r="K11" t="n">
-        <v>297542</v>
+        <v>347698</v>
       </c>
       <c r="M11" t="n">
-        <v>2648485</v>
+        <v>2681880</v>
       </c>
       <c r="N11" t="n">
         <v>214475</v>
@@ -84538,7 +84632,7 @@
         <v>238857</v>
       </c>
       <c r="P11" t="n">
-        <v>380596</v>
+        <v>380595</v>
       </c>
       <c r="Q11" t="n">
         <v>710782</v>
@@ -84546,43 +84640,43 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B12" t="n">
-        <v>1270655</v>
+        <v>1245221</v>
       </c>
       <c r="C12" t="n">
-        <v>720759</v>
+        <v>748948</v>
       </c>
       <c r="D12" t="n">
-        <v>1323318</v>
+        <v>1343138</v>
       </c>
       <c r="E12" t="n">
         <v>9200</v>
       </c>
       <c r="F12" t="n">
-        <v>1887685</v>
+        <v>1828741</v>
       </c>
       <c r="G12" t="n">
-        <v>1444684</v>
+        <v>1426853</v>
       </c>
       <c r="I12" t="n">
-        <v>1322407</v>
+        <v>1286120</v>
       </c>
       <c r="K12" t="n">
-        <v>212971</v>
+        <v>297542</v>
       </c>
       <c r="M12" t="n">
-        <v>2675880</v>
+        <v>2648485</v>
       </c>
       <c r="N12" t="n">
-        <v>217075</v>
+        <v>214475</v>
       </c>
       <c r="O12" t="n">
-        <v>236445</v>
+        <v>238857</v>
       </c>
       <c r="P12" t="n">
-        <v>374416</v>
+        <v>380596</v>
       </c>
       <c r="Q12" t="n">
         <v>710782</v>
@@ -84590,201 +84684,201 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B13" t="n">
-        <v>1312169</v>
+        <v>1270655</v>
       </c>
       <c r="C13" t="n">
-        <v>724772</v>
+        <v>720759</v>
       </c>
       <c r="D13" t="n">
-        <v>1287902</v>
+        <v>1323318</v>
       </c>
       <c r="E13" t="n">
         <v>9200</v>
       </c>
       <c r="F13" t="n">
-        <v>1901259</v>
+        <v>1887685</v>
       </c>
       <c r="G13" t="n">
-        <v>1431569</v>
+        <v>1444684</v>
       </c>
       <c r="I13" t="n">
-        <v>1517739</v>
+        <v>1322407</v>
       </c>
       <c r="K13" t="n">
-        <v>215710</v>
+        <v>212971</v>
       </c>
       <c r="M13" t="n">
-        <v>2690149</v>
+        <v>2675880</v>
       </c>
       <c r="N13" t="n">
-        <v>212599</v>
+        <v>217075</v>
       </c>
       <c r="O13" t="n">
-        <v>240961</v>
+        <v>236445</v>
       </c>
       <c r="P13" t="n">
-        <v>380562</v>
+        <v>374416</v>
       </c>
       <c r="Q13" t="n">
-        <v>650000</v>
+        <v>710782</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B14" t="n">
-        <v>1329569</v>
+        <v>1312169</v>
       </c>
       <c r="C14" t="n">
-        <v>762468</v>
+        <v>724772</v>
       </c>
       <c r="D14" t="n">
-        <v>1356602</v>
+        <v>1287902</v>
       </c>
       <c r="E14" t="n">
         <v>9200</v>
       </c>
       <c r="F14" t="n">
-        <v>1904492</v>
+        <v>1901259</v>
       </c>
       <c r="G14" t="n">
-        <v>1449343</v>
+        <v>1431569</v>
       </c>
       <c r="I14" t="n">
-        <v>1411819</v>
+        <v>1517739</v>
       </c>
       <c r="K14" t="n">
-        <v>310810</v>
+        <v>215710</v>
       </c>
       <c r="M14" t="n">
-        <v>2705056</v>
+        <v>2690149</v>
       </c>
       <c r="N14" t="n">
-        <v>214475</v>
+        <v>212599</v>
       </c>
       <c r="O14" t="n">
-        <v>259857</v>
+        <v>240961</v>
       </c>
       <c r="P14" t="n">
-        <v>380664</v>
+        <v>380562</v>
       </c>
       <c r="Q14" t="n">
-        <v>709873</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B15" t="n">
-        <v>1270354</v>
+        <v>1329569</v>
       </c>
       <c r="C15" t="n">
-        <v>650008</v>
+        <v>762468</v>
       </c>
       <c r="D15" t="n">
-        <v>1478806</v>
+        <v>1356602</v>
       </c>
       <c r="E15" t="n">
         <v>9200</v>
       </c>
       <c r="F15" t="n">
-        <v>1835055</v>
+        <v>1904492</v>
       </c>
       <c r="G15" t="n">
-        <v>1481786</v>
+        <v>1449343</v>
       </c>
       <c r="I15" t="n">
-        <v>1534739</v>
+        <v>1411819</v>
       </c>
       <c r="K15" t="n">
-        <v>288093</v>
+        <v>310810</v>
       </c>
       <c r="M15" t="n">
-        <v>2703043</v>
+        <v>2705056</v>
       </c>
       <c r="N15" t="n">
-        <v>131771</v>
+        <v>214475</v>
       </c>
       <c r="O15" t="n">
-        <v>167012</v>
+        <v>259857</v>
       </c>
       <c r="P15" t="n">
-        <v>380459</v>
+        <v>380664</v>
       </c>
       <c r="Q15" t="n">
-        <v>690681</v>
+        <v>709873</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B16" t="n">
-        <v>1291024</v>
+        <v>1270354</v>
       </c>
       <c r="C16" t="n">
-        <v>625316</v>
+        <v>650008</v>
       </c>
       <c r="D16" t="n">
-        <v>1438301</v>
+        <v>1478806</v>
       </c>
       <c r="E16" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F16" t="n">
-        <v>1882671</v>
+        <v>1835055</v>
       </c>
       <c r="G16" t="n">
-        <v>1484709</v>
+        <v>1481786</v>
       </c>
       <c r="I16" t="n">
-        <v>1493578</v>
+        <v>1534739</v>
       </c>
       <c r="K16" t="n">
-        <v>270165</v>
+        <v>288093</v>
       </c>
       <c r="M16" t="n">
-        <v>2735408</v>
+        <v>2703043</v>
       </c>
       <c r="N16" t="n">
-        <v>214475</v>
+        <v>131771</v>
       </c>
       <c r="O16" t="n">
-        <v>236857</v>
+        <v>167012</v>
       </c>
       <c r="P16" t="n">
-        <v>380581</v>
+        <v>380459</v>
       </c>
       <c r="Q16" t="n">
-        <v>686237</v>
+        <v>690681</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B17" t="n">
-        <v>1240901</v>
+        <v>1291024</v>
       </c>
       <c r="C17" t="n">
-        <v>663382</v>
+        <v>625316</v>
       </c>
       <c r="D17" t="n">
-        <v>1423376</v>
+        <v>1438301</v>
       </c>
       <c r="E17" t="n">
         <v>9400</v>
       </c>
       <c r="F17" t="n">
-        <v>1882670</v>
+        <v>1882671</v>
       </c>
       <c r="G17" t="n">
-        <v>1454791</v>
+        <v>1484709</v>
       </c>
       <c r="I17" t="n">
         <v>1493578</v>
@@ -84793,7 +84887,7 @@
         <v>270165</v>
       </c>
       <c r="M17" t="n">
-        <v>2732297</v>
+        <v>2735408</v>
       </c>
       <c r="N17" t="n">
         <v>214475</v>
@@ -84805,39 +84899,39 @@
         <v>380581</v>
       </c>
       <c r="Q17" t="n">
-        <v>683510</v>
+        <v>686237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B18" t="n">
-        <v>1257633</v>
+        <v>1240901</v>
       </c>
       <c r="C18" t="n">
-        <v>611578</v>
+        <v>663382</v>
       </c>
       <c r="D18" t="n">
-        <v>1449703</v>
+        <v>1423376</v>
       </c>
       <c r="E18" t="n">
         <v>9400</v>
       </c>
       <c r="F18" t="n">
-        <v>1882647</v>
+        <v>1882670</v>
       </c>
       <c r="G18" t="n">
-        <v>1455299</v>
+        <v>1454791</v>
       </c>
       <c r="I18" t="n">
         <v>1493578</v>
       </c>
       <c r="K18" t="n">
-        <v>290165</v>
+        <v>270165</v>
       </c>
       <c r="M18" t="n">
-        <v>2705287</v>
+        <v>2732297</v>
       </c>
       <c r="N18" t="n">
         <v>214475</v>
@@ -84846,153 +84940,153 @@
         <v>236857</v>
       </c>
       <c r="P18" t="n">
-        <v>378153</v>
+        <v>380581</v>
       </c>
       <c r="Q18" t="n">
-        <v>696137</v>
+        <v>683510</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B19" t="n">
-        <v>1271516</v>
+        <v>1257633</v>
       </c>
       <c r="C19" t="n">
-        <v>597877</v>
+        <v>611578</v>
       </c>
       <c r="D19" t="n">
-        <v>1463300</v>
+        <v>1449703</v>
       </c>
       <c r="E19" t="n">
         <v>9400</v>
       </c>
       <c r="F19" t="n">
-        <v>1948739</v>
+        <v>1882647</v>
       </c>
       <c r="G19" t="n">
-        <v>1472527</v>
+        <v>1455299</v>
       </c>
       <c r="I19" t="n">
-        <v>1232047</v>
+        <v>1493578</v>
       </c>
       <c r="K19" t="n">
-        <v>334269</v>
+        <v>290165</v>
       </c>
       <c r="M19" t="n">
-        <v>2643426</v>
+        <v>2705287</v>
       </c>
       <c r="N19" t="n">
-        <v>186552</v>
+        <v>214475</v>
       </c>
       <c r="O19" t="n">
-        <v>197887</v>
+        <v>236857</v>
       </c>
       <c r="P19" t="n">
-        <v>378590</v>
+        <v>378153</v>
       </c>
       <c r="Q19" t="n">
-        <v>729365</v>
+        <v>696137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B20" t="n">
-        <v>1274678</v>
+        <v>1271516</v>
       </c>
       <c r="C20" t="n">
-        <v>523874</v>
+        <v>597877</v>
       </c>
       <c r="D20" t="n">
-        <v>1505828</v>
+        <v>1463300</v>
       </c>
       <c r="E20" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F20" t="n">
-        <v>1900789</v>
+        <v>1948739</v>
       </c>
       <c r="G20" t="n">
-        <v>1409855</v>
+        <v>1472527</v>
       </c>
       <c r="I20" t="n">
-        <v>981796</v>
+        <v>1232047</v>
       </c>
       <c r="K20" t="n">
-        <v>709874</v>
+        <v>334269</v>
       </c>
       <c r="M20" t="n">
-        <v>2672575</v>
+        <v>2643426</v>
       </c>
       <c r="N20" t="n">
-        <v>214475</v>
+        <v>186552</v>
       </c>
       <c r="O20" t="n">
-        <v>238857</v>
+        <v>197887</v>
       </c>
       <c r="P20" t="n">
-        <v>378233</v>
+        <v>378590</v>
       </c>
       <c r="Q20" t="n">
-        <v>735025</v>
+        <v>729365</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B21" t="n">
-        <v>1291480</v>
+        <v>1274678</v>
       </c>
       <c r="C21" t="n">
-        <v>574586</v>
+        <v>523874</v>
       </c>
       <c r="D21" t="n">
-        <v>1438502</v>
+        <v>1505828</v>
       </c>
       <c r="E21" t="n">
         <v>9200</v>
       </c>
       <c r="F21" t="n">
-        <v>1868644</v>
+        <v>1900789</v>
       </c>
       <c r="G21" t="n">
-        <v>1482710</v>
+        <v>1409855</v>
       </c>
       <c r="I21" t="n">
-        <v>1291683</v>
+        <v>981796</v>
       </c>
       <c r="K21" t="n">
-        <v>702469</v>
+        <v>709874</v>
       </c>
       <c r="M21" t="n">
-        <v>2637080</v>
+        <v>2672575</v>
       </c>
       <c r="N21" t="n">
-        <v>135639</v>
+        <v>214475</v>
       </c>
       <c r="O21" t="n">
-        <v>155887</v>
+        <v>238857</v>
       </c>
       <c r="P21" t="n">
-        <v>378140</v>
+        <v>378233</v>
       </c>
       <c r="Q21" t="n">
-        <v>759291</v>
+        <v>735025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B22" t="n">
-        <v>1344999</v>
+        <v>1291480</v>
       </c>
       <c r="C22" t="n">
-        <v>636735</v>
+        <v>574586</v>
       </c>
       <c r="D22" t="n">
         <v>1438502</v>
@@ -85001,107 +85095,107 @@
         <v>9200</v>
       </c>
       <c r="F22" t="n">
-        <v>1892344</v>
+        <v>1868644</v>
       </c>
       <c r="G22" t="n">
-        <v>1459196</v>
+        <v>1482710</v>
       </c>
       <c r="I22" t="n">
-        <v>1538980</v>
+        <v>1291683</v>
       </c>
       <c r="K22" t="n">
-        <v>714270</v>
+        <v>702469</v>
       </c>
       <c r="M22" t="n">
-        <v>2693673</v>
+        <v>2637080</v>
       </c>
       <c r="N22" t="n">
-        <v>131452</v>
+        <v>135639</v>
       </c>
       <c r="O22" t="n">
-        <v>166693</v>
+        <v>155887</v>
       </c>
       <c r="P22" t="n">
-        <v>373275</v>
+        <v>378140</v>
       </c>
       <c r="Q22" t="n">
-        <v>700532</v>
+        <v>759291</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B23" t="n">
-        <v>1208720</v>
+        <v>1344999</v>
       </c>
       <c r="C23" t="n">
-        <v>615524</v>
+        <v>636735</v>
       </c>
       <c r="D23" t="n">
-        <v>1460388</v>
+        <v>1438502</v>
       </c>
       <c r="E23" t="n">
         <v>9200</v>
       </c>
       <c r="F23" t="n">
-        <v>1787948</v>
+        <v>1892344</v>
       </c>
       <c r="G23" t="n">
-        <v>1492147</v>
+        <v>1459196</v>
       </c>
       <c r="I23" t="n">
-        <v>1488515</v>
+        <v>1538980</v>
       </c>
       <c r="K23" t="n">
-        <v>698623</v>
+        <v>714270</v>
       </c>
       <c r="M23" t="n">
-        <v>2703143</v>
+        <v>2693673</v>
       </c>
       <c r="N23" t="n">
-        <v>214475</v>
+        <v>131452</v>
       </c>
       <c r="O23" t="n">
-        <v>247857</v>
+        <v>166693</v>
       </c>
       <c r="P23" t="n">
-        <v>369576</v>
+        <v>373275</v>
       </c>
       <c r="Q23" t="n">
-        <v>738429</v>
+        <v>700532</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B24" t="n">
-        <v>1255158</v>
+        <v>1208720</v>
       </c>
       <c r="C24" t="n">
-        <v>621535</v>
+        <v>615524</v>
       </c>
       <c r="D24" t="n">
-        <v>1465868</v>
+        <v>1460388</v>
       </c>
       <c r="E24" t="n">
         <v>9200</v>
       </c>
       <c r="F24" t="n">
-        <v>1787951</v>
+        <v>1787948</v>
       </c>
       <c r="G24" t="n">
-        <v>1491513</v>
+        <v>1492147</v>
       </c>
       <c r="I24" t="n">
         <v>1488515</v>
       </c>
       <c r="K24" t="n">
-        <v>631586</v>
+        <v>698623</v>
       </c>
       <c r="M24" t="n">
-        <v>2409537</v>
+        <v>2703143</v>
       </c>
       <c r="N24" t="n">
         <v>214475</v>
@@ -85110,7 +85204,7 @@
         <v>247857</v>
       </c>
       <c r="P24" t="n">
-        <v>369120</v>
+        <v>369576</v>
       </c>
       <c r="Q24" t="n">
         <v>738429</v>
@@ -85118,34 +85212,34 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B25" t="n">
-        <v>1268054</v>
+        <v>1255158</v>
       </c>
       <c r="C25" t="n">
-        <v>646819</v>
+        <v>621535</v>
       </c>
       <c r="D25" t="n">
-        <v>1458973</v>
+        <v>1465868</v>
       </c>
       <c r="E25" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F25" t="n">
-        <v>1892157</v>
+        <v>1787951</v>
       </c>
       <c r="G25" t="n">
-        <v>1489325</v>
+        <v>1491513</v>
       </c>
       <c r="I25" t="n">
         <v>1488515</v>
       </c>
       <c r="K25" t="n">
-        <v>574363</v>
+        <v>631586</v>
       </c>
       <c r="M25" t="n">
-        <v>2277986</v>
+        <v>2409537</v>
       </c>
       <c r="N25" t="n">
         <v>214475</v>
@@ -85154,7 +85248,7 @@
         <v>247857</v>
       </c>
       <c r="P25" t="n">
-        <v>369082</v>
+        <v>369120</v>
       </c>
       <c r="Q25" t="n">
         <v>738429</v>
@@ -85162,78 +85256,78 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B26" t="n">
-        <v>1294415</v>
+        <v>1268054</v>
       </c>
       <c r="C26" t="n">
-        <v>622563</v>
+        <v>646819</v>
       </c>
       <c r="D26" t="n">
-        <v>1452901</v>
+        <v>1458973</v>
       </c>
       <c r="E26" t="n">
-        <v>9200</v>
+        <v>9400</v>
       </c>
       <c r="F26" t="n">
-        <v>1896083</v>
+        <v>1892157</v>
       </c>
       <c r="G26" t="n">
-        <v>1492662</v>
+        <v>1489325</v>
       </c>
       <c r="I26" t="n">
-        <v>1502826</v>
+        <v>1488515</v>
       </c>
       <c r="K26" t="n">
-        <v>414091</v>
+        <v>574363</v>
       </c>
       <c r="M26" t="n">
-        <v>2360445</v>
+        <v>2277986</v>
       </c>
       <c r="N26" t="n">
         <v>214475</v>
       </c>
       <c r="O26" t="n">
-        <v>264857</v>
+        <v>247857</v>
       </c>
       <c r="P26" t="n">
-        <v>355841</v>
+        <v>369082</v>
       </c>
       <c r="Q26" t="n">
-        <v>758041</v>
+        <v>738429</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B27" t="n">
-        <v>1287738</v>
+        <v>1294415</v>
       </c>
       <c r="C27" t="n">
-        <v>627470</v>
+        <v>622563</v>
       </c>
       <c r="D27" t="n">
-        <v>1473202</v>
+        <v>1452901</v>
       </c>
       <c r="E27" t="n">
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="F27" t="n">
-        <v>1827111</v>
+        <v>1896083</v>
       </c>
       <c r="G27" t="n">
-        <v>1442936</v>
+        <v>1492662</v>
       </c>
       <c r="I27" t="n">
-        <v>1478756</v>
+        <v>1502826</v>
       </c>
       <c r="K27" t="n">
-        <v>245359</v>
+        <v>414091</v>
       </c>
       <c r="M27" t="n">
-        <v>2544314</v>
+        <v>2360445</v>
       </c>
       <c r="N27" t="n">
         <v>214475</v>
@@ -85242,42 +85336,42 @@
         <v>264857</v>
       </c>
       <c r="P27" t="n">
-        <v>355281</v>
+        <v>355841</v>
       </c>
       <c r="Q27" t="n">
-        <v>755100</v>
+        <v>758041</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B28" t="n">
-        <v>1355779</v>
+        <v>1287738</v>
       </c>
       <c r="C28" t="n">
-        <v>636253</v>
+        <v>627470</v>
       </c>
       <c r="D28" t="n">
-        <v>1488152</v>
+        <v>1473202</v>
       </c>
       <c r="E28" t="n">
-        <v>9300</v>
+        <v>9400</v>
       </c>
       <c r="F28" t="n">
-        <v>1882472</v>
+        <v>1827111</v>
       </c>
       <c r="G28" t="n">
-        <v>1433134</v>
+        <v>1442936</v>
       </c>
       <c r="I28" t="n">
-        <v>1492810</v>
+        <v>1478756</v>
       </c>
       <c r="K28" t="n">
-        <v>262398</v>
+        <v>245359</v>
       </c>
       <c r="M28" t="n">
-        <v>2441130</v>
+        <v>2544314</v>
       </c>
       <c r="N28" t="n">
         <v>214475</v>
@@ -85286,101 +85380,98 @@
         <v>264857</v>
       </c>
       <c r="P28" t="n">
-        <v>355279</v>
+        <v>355281</v>
       </c>
       <c r="Q28" t="n">
-        <v>729723</v>
+        <v>755100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B29" t="n">
-        <v>1372528</v>
+        <v>1355779</v>
       </c>
       <c r="C29" t="n">
-        <v>661067</v>
+        <v>636253</v>
       </c>
       <c r="D29" t="n">
-        <v>1495794</v>
+        <v>1488152</v>
       </c>
       <c r="E29" t="n">
         <v>9300</v>
       </c>
       <c r="F29" t="n">
-        <v>1984198</v>
+        <v>1882472</v>
       </c>
       <c r="G29" t="n">
-        <v>1386625</v>
+        <v>1433134</v>
       </c>
       <c r="I29" t="n">
-        <v>1538415</v>
+        <v>1492810</v>
       </c>
       <c r="K29" t="n">
-        <v>423452</v>
+        <v>262398</v>
       </c>
       <c r="M29" t="n">
-        <v>2358379</v>
+        <v>2441130</v>
       </c>
       <c r="N29" t="n">
-        <v>207642</v>
+        <v>214475</v>
       </c>
       <c r="O29" t="n">
-        <v>248013</v>
+        <v>264857</v>
       </c>
       <c r="P29" t="n">
-        <v>352672</v>
+        <v>355279</v>
       </c>
       <c r="Q29" t="n">
-        <v>779164</v>
-      </c>
-      <c r="R29" t="n">
-        <v>15000</v>
+        <v>729723</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B30" t="n">
-        <v>1301942</v>
+        <v>1372528</v>
       </c>
       <c r="C30" t="n">
-        <v>666110</v>
+        <v>661067</v>
       </c>
       <c r="D30" t="n">
-        <v>1508302</v>
+        <v>1495794</v>
       </c>
       <c r="E30" t="n">
-        <v>9100</v>
+        <v>9300</v>
       </c>
       <c r="F30" t="n">
-        <v>2013551</v>
+        <v>1984198</v>
       </c>
       <c r="G30" t="n">
-        <v>1483009</v>
+        <v>1386625</v>
       </c>
       <c r="I30" t="n">
-        <v>1458275</v>
+        <v>1538415</v>
       </c>
       <c r="K30" t="n">
-        <v>590414</v>
+        <v>423452</v>
       </c>
       <c r="M30" t="n">
-        <v>2506388</v>
+        <v>2358379</v>
       </c>
       <c r="N30" t="n">
-        <v>189475</v>
+        <v>207642</v>
       </c>
       <c r="O30" t="n">
-        <v>219815</v>
+        <v>248013</v>
       </c>
       <c r="P30" t="n">
-        <v>375660</v>
+        <v>352672</v>
       </c>
       <c r="Q30" t="n">
-        <v>773586</v>
+        <v>779164</v>
       </c>
       <c r="R30" t="n">
         <v>15000</v>
@@ -85388,40 +85479,40 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B31" t="n">
-        <v>1276064</v>
+        <v>1301942</v>
       </c>
       <c r="C31" t="n">
-        <v>646110</v>
+        <v>666110</v>
       </c>
       <c r="D31" t="n">
-        <v>1498302</v>
+        <v>1508302</v>
       </c>
       <c r="E31" t="n">
         <v>9100</v>
       </c>
       <c r="F31" t="n">
-        <v>1999274</v>
+        <v>2013551</v>
       </c>
       <c r="G31" t="n">
-        <v>1468619</v>
+        <v>1483009</v>
       </c>
       <c r="I31" t="n">
-        <v>1428275</v>
+        <v>1458275</v>
       </c>
       <c r="K31" t="n">
-        <v>310625</v>
+        <v>590414</v>
       </c>
       <c r="M31" t="n">
-        <v>2522392</v>
+        <v>2506388</v>
       </c>
       <c r="N31" t="n">
         <v>189475</v>
       </c>
       <c r="O31" t="n">
-        <v>219811</v>
+        <v>219815</v>
       </c>
       <c r="P31" t="n">
         <v>375660</v>
@@ -85430,6 +85521,53 @@
         <v>773586</v>
       </c>
       <c r="R31" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1276064</v>
+      </c>
+      <c r="C32" t="n">
+        <v>646110</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1498302</v>
+      </c>
+      <c r="E32" t="n">
+        <v>9100</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1999274</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1468619</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1428275</v>
+      </c>
+      <c r="K32" t="n">
+        <v>310625</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2522392</v>
+      </c>
+      <c r="N32" t="n">
+        <v>189475</v>
+      </c>
+      <c r="O32" t="n">
+        <v>219811</v>
+      </c>
+      <c r="P32" t="n">
+        <v>375660</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>773586</v>
+      </c>
+      <c r="R32" t="n">
         <v>15000</v>
       </c>
     </row>

--- a/americas/feedgas_ebb/lng_feedgas_daily.xlsx
+++ b/americas/feedgas_ebb/lng_feedgas_daily.xlsx
@@ -80253,9 +80253,36 @@
       <c r="A2432" s="4" t="n">
         <v>46261</v>
       </c>
+      <c r="B2432" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C2432" t="n">
+        <v>3.254</v>
+      </c>
+      <c r="D2432" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="E2432" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F2432" t="n">
+        <v>2.594</v>
+      </c>
+      <c r="G2432" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="H2432" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="I2432" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="K2432" t="n">
+        <v>12.526</v>
+      </c>
       <c r="L2432" t="inlineStr">
         <is>
-          <t>no data yet (EIA runs 2-3 months behind)</t>
+          <t>metered</t>
         </is>
       </c>
     </row>
@@ -81426,7 +81453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -81491,313 +81518,313 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B2" t="n">
-        <v>3.236</v>
+        <v>3.29</v>
       </c>
       <c r="C2" t="n">
-        <v>3.017</v>
+        <v>3.254</v>
       </c>
       <c r="D2" t="n">
-        <v>1.456</v>
+        <v>1.491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.215</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>2.543</v>
+        <v>2.594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.74</v>
+        <v>0.715</v>
       </c>
       <c r="H2" t="n">
-        <v>0.378</v>
+        <v>0.385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="K2" t="n">
-        <v>12.269</v>
+        <v>12.526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B3" t="n">
-        <v>3.404</v>
+        <v>3.236</v>
       </c>
       <c r="C3" t="n">
-        <v>3.112</v>
+        <v>3.017</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472</v>
+        <v>1.456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="F3" t="n">
-        <v>2.233</v>
+        <v>2.543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.655</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.678</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.136</v>
+        <v>12.269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B4" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C4" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D4" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H4" t="n">
         <v>0.379</v>
       </c>
       <c r="I4" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K4" t="n">
-        <v>12.428</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B5" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C5" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D5" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F5" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H5" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I5" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K5" t="n">
-        <v>12.534</v>
+        <v>12.428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B6" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C6" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D6" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E6" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F6" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H6" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I6" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K6" t="n">
-        <v>12.108</v>
+        <v>12.534</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="B7" t="n">
-        <v>2.659</v>
+        <v>3.163</v>
       </c>
       <c r="C7" t="n">
-        <v>3.117</v>
+        <v>3.205</v>
       </c>
       <c r="D7" t="n">
-        <v>1.454</v>
+        <v>1.472</v>
       </c>
       <c r="E7" t="n">
-        <v>0.206</v>
+        <v>0.276</v>
       </c>
       <c r="F7" t="n">
-        <v>2.632</v>
+        <v>2.634</v>
       </c>
       <c r="G7" t="n">
-        <v>0.444</v>
+        <v>0.424</v>
       </c>
       <c r="H7" t="n">
         <v>0.342</v>
       </c>
       <c r="I7" t="n">
-        <v>0.491</v>
+        <v>0.593</v>
       </c>
       <c r="K7" t="n">
-        <v>11.344</v>
+        <v>12.108</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="B8" t="n">
-        <v>3.062</v>
+        <v>2.659</v>
       </c>
       <c r="C8" t="n">
-        <v>3.142</v>
+        <v>3.117</v>
       </c>
       <c r="D8" t="n">
-        <v>1.386</v>
+        <v>1.454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F8" t="n">
-        <v>2.581</v>
+        <v>2.632</v>
       </c>
       <c r="G8" t="n">
         <v>0.444</v>
       </c>
       <c r="H8" t="n">
-        <v>0.32</v>
+        <v>0.342</v>
       </c>
       <c r="I8" t="n">
-        <v>0.647</v>
+        <v>0.491</v>
       </c>
       <c r="K8" t="n">
-        <v>11.786</v>
+        <v>11.344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B9" t="n">
-        <v>3.405</v>
+        <v>3.062</v>
       </c>
       <c r="C9" t="n">
-        <v>3.204</v>
+        <v>3.142</v>
       </c>
       <c r="D9" t="n">
-        <v>1.474</v>
+        <v>1.386</v>
       </c>
       <c r="E9" t="n">
-        <v>0.247</v>
+        <v>0.205</v>
       </c>
       <c r="F9" t="n">
-        <v>2.571</v>
+        <v>2.581</v>
       </c>
       <c r="G9" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H9" t="n">
-        <v>0.366</v>
+        <v>0.32</v>
       </c>
       <c r="I9" t="n">
-        <v>0.671</v>
+        <v>0.647</v>
       </c>
       <c r="K9" t="n">
-        <v>12.376</v>
+        <v>11.786</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46270</v>
+        <v>46269</v>
       </c>
       <c r="B10" t="n">
-        <v>3.391</v>
+        <v>3.405</v>
       </c>
       <c r="C10" t="n">
-        <v>3.261</v>
+        <v>3.204</v>
       </c>
       <c r="D10" t="n">
-        <v>1.478</v>
+        <v>1.474</v>
       </c>
       <c r="E10" t="n">
-        <v>0.297</v>
+        <v>0.247</v>
       </c>
       <c r="F10" t="n">
-        <v>2.592</v>
+        <v>2.571</v>
       </c>
       <c r="G10" t="n">
-        <v>0.27</v>
+        <v>0.438</v>
       </c>
       <c r="H10" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="K10" t="n">
-        <v>12.341</v>
+        <v>12.376</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46271</v>
+        <v>46270</v>
       </c>
       <c r="B11" t="n">
-        <v>3.177</v>
+        <v>3.391</v>
       </c>
       <c r="C11" t="n">
-        <v>2.859</v>
+        <v>3.261</v>
       </c>
       <c r="D11" t="n">
-        <v>1.485</v>
+        <v>1.478</v>
       </c>
       <c r="E11" t="n">
-        <v>0.335</v>
+        <v>0.297</v>
       </c>
       <c r="F11" t="n">
-        <v>2.586</v>
+        <v>2.592</v>
       </c>
       <c r="G11" t="n">
-        <v>0.437</v>
+        <v>0.27</v>
       </c>
       <c r="H11" t="n">
         <v>0.367</v>
@@ -81806,27 +81833,27 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>11.931</v>
+        <v>12.341</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46272</v>
+        <v>46271</v>
       </c>
       <c r="B12" t="n">
-        <v>3.227</v>
+        <v>3.177</v>
       </c>
       <c r="C12" t="n">
-        <v>3.139</v>
+        <v>2.859</v>
       </c>
       <c r="D12" t="n">
-        <v>1.24</v>
+        <v>1.485</v>
       </c>
       <c r="E12" t="n">
-        <v>0.287</v>
+        <v>0.335</v>
       </c>
       <c r="F12" t="n">
-        <v>2.554</v>
+        <v>2.586</v>
       </c>
       <c r="G12" t="n">
         <v>0.437</v>
@@ -81838,178 +81865,178 @@
         <v>0.6850000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>11.937</v>
+        <v>11.931</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B13" t="n">
-        <v>3.205</v>
+        <v>3.227</v>
       </c>
       <c r="C13" t="n">
-        <v>3.213</v>
+        <v>3.139</v>
       </c>
       <c r="D13" t="n">
-        <v>1.275</v>
+        <v>1.24</v>
       </c>
       <c r="E13" t="n">
-        <v>0.205</v>
+        <v>0.287</v>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.554</v>
       </c>
       <c r="G13" t="n">
         <v>0.437</v>
       </c>
       <c r="H13" t="n">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="I13" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>11.964</v>
+        <v>11.937</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B14" t="n">
-        <v>3.215</v>
+        <v>3.205</v>
       </c>
       <c r="C14" t="n">
-        <v>3.214</v>
+        <v>3.213</v>
       </c>
       <c r="D14" t="n">
-        <v>1.464</v>
+        <v>1.275</v>
       </c>
       <c r="E14" t="n">
-        <v>0.208</v>
+        <v>0.205</v>
       </c>
       <c r="F14" t="n">
-        <v>2.594</v>
+        <v>2.58</v>
       </c>
       <c r="G14" t="n">
         <v>0.437</v>
       </c>
       <c r="H14" t="n">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="I14" t="n">
-        <v>0.627</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>12.126</v>
+        <v>11.964</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B15" t="n">
-        <v>3.334</v>
+        <v>3.215</v>
       </c>
       <c r="C15" t="n">
-        <v>3.234</v>
+        <v>3.214</v>
       </c>
       <c r="D15" t="n">
-        <v>1.361</v>
+        <v>1.464</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3</v>
+        <v>0.208</v>
       </c>
       <c r="F15" t="n">
-        <v>2.609</v>
+        <v>2.594</v>
       </c>
       <c r="G15" t="n">
-        <v>0.457</v>
+        <v>0.437</v>
       </c>
       <c r="H15" t="n">
         <v>0.367</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="K15" t="n">
-        <v>12.347</v>
+        <v>12.126</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="B16" t="n">
-        <v>3.287</v>
+        <v>3.334</v>
       </c>
       <c r="C16" t="n">
-        <v>3.198</v>
+        <v>3.234</v>
       </c>
       <c r="D16" t="n">
-        <v>1.48</v>
+        <v>1.361</v>
       </c>
       <c r="E16" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
       <c r="F16" t="n">
-        <v>2.607</v>
+        <v>2.609</v>
       </c>
       <c r="G16" t="n">
-        <v>0.288</v>
+        <v>0.457</v>
       </c>
       <c r="H16" t="n">
         <v>0.367</v>
       </c>
       <c r="I16" t="n">
-        <v>0.666</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>12.171</v>
+        <v>12.347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46277</v>
+        <v>46276</v>
       </c>
       <c r="B17" t="n">
-        <v>3.244</v>
+        <v>3.287</v>
       </c>
       <c r="C17" t="n">
-        <v>3.247</v>
+        <v>3.198</v>
       </c>
       <c r="D17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="E17" t="n">
-        <v>0.261</v>
+        <v>0.278</v>
       </c>
       <c r="F17" t="n">
-        <v>2.638</v>
+        <v>2.607</v>
       </c>
       <c r="G17" t="n">
-        <v>0.435</v>
+        <v>0.288</v>
       </c>
       <c r="H17" t="n">
         <v>0.367</v>
       </c>
       <c r="I17" t="n">
-        <v>0.662</v>
+        <v>0.666</v>
       </c>
       <c r="K17" t="n">
-        <v>12.294</v>
+        <v>12.171</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B18" t="n">
-        <v>3.218</v>
+        <v>3.244</v>
       </c>
       <c r="C18" t="n">
-        <v>3.218</v>
+        <v>3.247</v>
       </c>
       <c r="D18" t="n">
         <v>1.44</v>
@@ -82018,7 +82045,7 @@
         <v>0.261</v>
       </c>
       <c r="F18" t="n">
-        <v>2.635</v>
+        <v>2.638</v>
       </c>
       <c r="G18" t="n">
         <v>0.435</v>
@@ -82027,222 +82054,222 @@
         <v>0.367</v>
       </c>
       <c r="I18" t="n">
-        <v>0.659</v>
+        <v>0.662</v>
       </c>
       <c r="K18" t="n">
-        <v>12.233</v>
+        <v>12.294</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46279</v>
+        <v>46278</v>
       </c>
       <c r="B19" t="n">
-        <v>3.21</v>
+        <v>3.218</v>
       </c>
       <c r="C19" t="n">
-        <v>3.219</v>
+        <v>3.218</v>
       </c>
       <c r="D19" t="n">
         <v>1.44</v>
       </c>
       <c r="E19" t="n">
-        <v>0.28</v>
+        <v>0.261</v>
       </c>
       <c r="F19" t="n">
-        <v>2.609</v>
+        <v>2.635</v>
       </c>
       <c r="G19" t="n">
         <v>0.435</v>
       </c>
       <c r="H19" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="I19" t="n">
-        <v>0.671</v>
+        <v>0.659</v>
       </c>
       <c r="K19" t="n">
-        <v>12.228</v>
+        <v>12.233</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B20" t="n">
-        <v>3.223</v>
+        <v>3.21</v>
       </c>
       <c r="C20" t="n">
-        <v>3.299</v>
+        <v>3.219</v>
       </c>
       <c r="D20" t="n">
-        <v>1.188</v>
+        <v>1.44</v>
       </c>
       <c r="E20" t="n">
-        <v>0.322</v>
+        <v>0.28</v>
       </c>
       <c r="F20" t="n">
-        <v>2.549</v>
+        <v>2.609</v>
       </c>
       <c r="G20" t="n">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="H20" t="n">
         <v>0.365</v>
       </c>
       <c r="I20" t="n">
-        <v>0.703</v>
+        <v>0.671</v>
       </c>
       <c r="K20" t="n">
-        <v>12.021</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B21" t="n">
-        <v>3.195</v>
+        <v>3.223</v>
       </c>
       <c r="C21" t="n">
-        <v>3.193</v>
+        <v>3.299</v>
       </c>
       <c r="D21" t="n">
-        <v>0.947</v>
+        <v>1.188</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.322</v>
       </c>
       <c r="F21" t="n">
-        <v>2.577</v>
+        <v>2.549</v>
       </c>
       <c r="G21" t="n">
-        <v>0.437</v>
+        <v>0.371</v>
       </c>
       <c r="H21" t="n">
         <v>0.365</v>
       </c>
       <c r="I21" t="n">
-        <v>0.709</v>
+        <v>0.703</v>
       </c>
       <c r="K21" t="n">
-        <v>12.107</v>
+        <v>12.021</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B22" t="n">
-        <v>3.196</v>
+        <v>3.195</v>
       </c>
       <c r="C22" t="n">
-        <v>3.232</v>
+        <v>3.193</v>
       </c>
       <c r="D22" t="n">
-        <v>1.246</v>
+        <v>0.947</v>
       </c>
       <c r="E22" t="n">
-        <v>0.677</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>2.543</v>
+        <v>2.577</v>
       </c>
       <c r="G22" t="n">
-        <v>0.281</v>
+        <v>0.437</v>
       </c>
       <c r="H22" t="n">
         <v>0.365</v>
       </c>
       <c r="I22" t="n">
-        <v>0.732</v>
+        <v>0.709</v>
       </c>
       <c r="K22" t="n">
-        <v>12.271</v>
+        <v>12.107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="B23" t="n">
-        <v>3.307</v>
+        <v>3.196</v>
       </c>
       <c r="C23" t="n">
         <v>3.232</v>
       </c>
       <c r="D23" t="n">
-        <v>1.484</v>
+        <v>1.246</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.677</v>
       </c>
       <c r="F23" t="n">
-        <v>2.598</v>
+        <v>2.543</v>
       </c>
       <c r="G23" t="n">
-        <v>0.288</v>
+        <v>0.281</v>
       </c>
       <c r="H23" t="n">
-        <v>0.36</v>
+        <v>0.365</v>
       </c>
       <c r="I23" t="n">
-        <v>0.676</v>
+        <v>0.732</v>
       </c>
       <c r="K23" t="n">
-        <v>12.632</v>
+        <v>12.271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46284</v>
+        <v>46283</v>
       </c>
       <c r="B24" t="n">
-        <v>3.176</v>
+        <v>3.307</v>
       </c>
       <c r="C24" t="n">
-        <v>3.163</v>
+        <v>3.232</v>
       </c>
       <c r="D24" t="n">
-        <v>1.435</v>
+        <v>1.484</v>
       </c>
       <c r="E24" t="n">
-        <v>0.674</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.607</v>
+        <v>2.598</v>
       </c>
       <c r="G24" t="n">
-        <v>0.446</v>
+        <v>0.288</v>
       </c>
       <c r="H24" t="n">
-        <v>0.356</v>
+        <v>0.36</v>
       </c>
       <c r="I24" t="n">
-        <v>0.712</v>
+        <v>0.676</v>
       </c>
       <c r="K24" t="n">
-        <v>12.569</v>
+        <v>12.632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46285</v>
+        <v>46284</v>
       </c>
       <c r="B25" t="n">
-        <v>3.232</v>
+        <v>3.176</v>
       </c>
       <c r="C25" t="n">
-        <v>3.162</v>
+        <v>3.163</v>
       </c>
       <c r="D25" t="n">
         <v>1.435</v>
       </c>
       <c r="E25" t="n">
-        <v>0.609</v>
+        <v>0.674</v>
       </c>
       <c r="F25" t="n">
-        <v>2.324</v>
+        <v>2.607</v>
       </c>
       <c r="G25" t="n">
         <v>0.446</v>
@@ -82254,27 +82281,27 @@
         <v>0.712</v>
       </c>
       <c r="K25" t="n">
-        <v>12.277</v>
+        <v>12.569</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B26" t="n">
-        <v>3.263</v>
+        <v>3.232</v>
       </c>
       <c r="C26" t="n">
-        <v>3.261</v>
+        <v>3.162</v>
       </c>
       <c r="D26" t="n">
         <v>1.435</v>
       </c>
       <c r="E26" t="n">
-        <v>0.554</v>
+        <v>0.609</v>
       </c>
       <c r="F26" t="n">
-        <v>2.197</v>
+        <v>2.324</v>
       </c>
       <c r="G26" t="n">
         <v>0.446</v>
@@ -82286,59 +82313,59 @@
         <v>0.712</v>
       </c>
       <c r="K26" t="n">
-        <v>12.223</v>
+        <v>12.277</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B27" t="n">
-        <v>3.259</v>
+        <v>3.263</v>
       </c>
       <c r="C27" t="n">
-        <v>3.268</v>
+        <v>3.261</v>
       </c>
       <c r="D27" t="n">
-        <v>1.449</v>
+        <v>1.435</v>
       </c>
       <c r="E27" t="n">
-        <v>0.399</v>
+        <v>0.554</v>
       </c>
       <c r="F27" t="n">
-        <v>2.276</v>
+        <v>2.197</v>
       </c>
       <c r="G27" t="n">
-        <v>0.462</v>
+        <v>0.446</v>
       </c>
       <c r="H27" t="n">
-        <v>0.343</v>
+        <v>0.356</v>
       </c>
       <c r="I27" t="n">
-        <v>0.731</v>
+        <v>0.712</v>
       </c>
       <c r="K27" t="n">
-        <v>12.187</v>
+        <v>12.223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46288</v>
+        <v>46287</v>
       </c>
       <c r="B28" t="n">
-        <v>3.277</v>
+        <v>3.259</v>
       </c>
       <c r="C28" t="n">
-        <v>3.153</v>
+        <v>3.268</v>
       </c>
       <c r="D28" t="n">
-        <v>1.426</v>
+        <v>1.449</v>
       </c>
       <c r="E28" t="n">
-        <v>0.237</v>
+        <v>0.399</v>
       </c>
       <c r="F28" t="n">
-        <v>2.454</v>
+        <v>2.276</v>
       </c>
       <c r="G28" t="n">
         <v>0.462</v>
@@ -82347,30 +82374,30 @@
         <v>0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>0.728</v>
+        <v>0.731</v>
       </c>
       <c r="K28" t="n">
-        <v>12.079</v>
+        <v>12.187</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B29" t="n">
-        <v>3.365</v>
+        <v>3.277</v>
       </c>
       <c r="C29" t="n">
-        <v>3.197</v>
+        <v>3.153</v>
       </c>
       <c r="D29" t="n">
-        <v>1.44</v>
+        <v>1.426</v>
       </c>
       <c r="E29" t="n">
-        <v>0.253</v>
+        <v>0.237</v>
       </c>
       <c r="F29" t="n">
-        <v>2.354</v>
+        <v>2.454</v>
       </c>
       <c r="G29" t="n">
         <v>0.462</v>
@@ -82379,100 +82406,97 @@
         <v>0.343</v>
       </c>
       <c r="I29" t="n">
-        <v>0.704</v>
+        <v>0.728</v>
       </c>
       <c r="K29" t="n">
-        <v>12.117</v>
+        <v>12.079</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46290</v>
+        <v>46289</v>
       </c>
       <c r="B30" t="n">
-        <v>3.412</v>
+        <v>3.365</v>
       </c>
       <c r="C30" t="n">
-        <v>3.251</v>
+        <v>3.197</v>
       </c>
       <c r="D30" t="n">
-        <v>1.484</v>
+        <v>1.44</v>
       </c>
       <c r="E30" t="n">
-        <v>0.408</v>
+        <v>0.253</v>
       </c>
       <c r="F30" t="n">
-        <v>2.274</v>
+        <v>2.354</v>
       </c>
       <c r="G30" t="n">
-        <v>0.439</v>
+        <v>0.462</v>
       </c>
       <c r="H30" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="I30" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.014</v>
+        <v>0.704</v>
       </c>
       <c r="K30" t="n">
-        <v>12.374</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="B31" t="n">
-        <v>3.361</v>
+        <v>3.412</v>
       </c>
       <c r="C31" t="n">
-        <v>3.372</v>
+        <v>3.251</v>
       </c>
       <c r="D31" t="n">
-        <v>1.406</v>
+        <v>1.484</v>
       </c>
       <c r="E31" t="n">
-        <v>0.569</v>
+        <v>0.408</v>
       </c>
       <c r="F31" t="n">
-        <v>2.417</v>
+        <v>2.274</v>
       </c>
       <c r="G31" t="n">
-        <v>0.395</v>
+        <v>0.439</v>
       </c>
       <c r="H31" t="n">
-        <v>0.362</v>
+        <v>0.34</v>
       </c>
       <c r="I31" t="n">
-        <v>0.746</v>
+        <v>0.751</v>
       </c>
       <c r="J31" t="n">
         <v>0.014</v>
       </c>
       <c r="K31" t="n">
-        <v>12.643</v>
+        <v>12.374</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46292</v>
+        <v>46291</v>
       </c>
       <c r="B32" t="n">
-        <v>3.307</v>
+        <v>3.361</v>
       </c>
       <c r="C32" t="n">
-        <v>3.344</v>
+        <v>3.372</v>
       </c>
       <c r="D32" t="n">
-        <v>1.377</v>
+        <v>1.406</v>
       </c>
       <c r="E32" t="n">
-        <v>0.3</v>
+        <v>0.569</v>
       </c>
       <c r="F32" t="n">
-        <v>2.432</v>
+        <v>2.417</v>
       </c>
       <c r="G32" t="n">
         <v>0.395</v>
@@ -82487,6 +82511,41 @@
         <v>0.014</v>
       </c>
       <c r="K32" t="n">
+        <v>12.643</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B33" t="n">
+        <v>3.307</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.344</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.432</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="K33" t="n">
         <v>12.278</v>
       </c>
     </row>
@@ -82501,7 +82560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -82571,340 +82630,340 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>46262</v>
+        <v>46261</v>
       </c>
       <c r="B2" t="n">
-        <v>3.236</v>
+        <v>3.29</v>
       </c>
       <c r="C2" t="n">
-        <v>3.017</v>
+        <v>3.254</v>
       </c>
       <c r="D2" t="n">
-        <v>1.456</v>
+        <v>1.491</v>
       </c>
       <c r="E2" t="n">
-        <v>0.215</v>
+        <v>0.14</v>
       </c>
       <c r="F2" t="n">
-        <v>2.543</v>
+        <v>2.594</v>
       </c>
       <c r="G2" t="n">
-        <v>0.74</v>
+        <v>0.715</v>
       </c>
       <c r="H2" t="n">
-        <v>0.378</v>
+        <v>0.385</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="K2" t="n">
-        <v>12.267</v>
+        <v>12.526</v>
       </c>
       <c r="L2" t="n">
-        <v>12.267</v>
+        <v>12.526</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B3" t="n">
-        <v>3.404</v>
+        <v>3.236</v>
       </c>
       <c r="C3" t="n">
-        <v>3.112</v>
+        <v>3.017</v>
       </c>
       <c r="D3" t="n">
-        <v>1.472</v>
+        <v>1.456</v>
       </c>
       <c r="E3" t="n">
-        <v>0.203</v>
+        <v>0.215</v>
       </c>
       <c r="F3" t="n">
-        <v>2.233</v>
+        <v>2.543</v>
       </c>
       <c r="G3" t="n">
-        <v>0.655</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="I3" t="n">
-        <v>0.678</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>12.136</v>
+        <v>12.267</v>
       </c>
       <c r="L3" t="n">
-        <v>12.136</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B4" t="n">
-        <v>3.29</v>
+        <v>3.404</v>
       </c>
       <c r="C4" t="n">
-        <v>3.115</v>
+        <v>3.112</v>
       </c>
       <c r="D4" t="n">
-        <v>1.463</v>
+        <v>1.472</v>
       </c>
       <c r="E4" t="n">
-        <v>0.256</v>
+        <v>0.203</v>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.233</v>
       </c>
       <c r="G4" t="n">
-        <v>0.657</v>
+        <v>0.655</v>
       </c>
       <c r="H4" t="n">
         <v>0.379</v>
       </c>
       <c r="I4" t="n">
-        <v>0.709</v>
+        <v>0.678</v>
       </c>
       <c r="K4" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
       <c r="L4" t="n">
-        <v>12.429</v>
+        <v>12.136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B5" t="n">
-        <v>3.392</v>
+        <v>3.29</v>
       </c>
       <c r="C5" t="n">
-        <v>3.207</v>
+        <v>3.115</v>
       </c>
       <c r="D5" t="n">
-        <v>1.476</v>
+        <v>1.463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.216</v>
+        <v>0.256</v>
       </c>
       <c r="F5" t="n">
-        <v>2.512</v>
+        <v>2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>0.652</v>
+        <v>0.657</v>
       </c>
       <c r="H5" t="n">
-        <v>0.356</v>
+        <v>0.379</v>
       </c>
       <c r="I5" t="n">
-        <v>0.723</v>
+        <v>0.709</v>
       </c>
       <c r="K5" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
       <c r="L5" t="n">
-        <v>12.534</v>
+        <v>12.429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B6" t="n">
-        <v>3.163</v>
+        <v>3.392</v>
       </c>
       <c r="C6" t="n">
-        <v>3.205</v>
+        <v>3.207</v>
       </c>
       <c r="D6" t="n">
-        <v>1.472</v>
+        <v>1.476</v>
       </c>
       <c r="E6" t="n">
-        <v>0.276</v>
+        <v>0.216</v>
       </c>
       <c r="F6" t="n">
-        <v>2.634</v>
+        <v>2.512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.424</v>
+        <v>0.652</v>
       </c>
       <c r="H6" t="n">
-        <v>0.342</v>
+        <v>0.356</v>
       </c>
       <c r="I6" t="n">
-        <v>0.593</v>
+        <v>0.723</v>
       </c>
       <c r="K6" t="n">
-        <v>12.109</v>
+        <v>12.534</v>
       </c>
       <c 